--- a/docs/WBS.xlsx
+++ b/docs/WBS.xlsx
@@ -1731,18 +1731,22 @@
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G29" s="7" t="n"/>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>진행 중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="I29" s="9" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="J29" s="8" t="inlineStr">
         <is>
-          <t>작업 브랜치 task/17</t>
+          <t>PR #17</t>
         </is>
       </c>
       <c r="K29" s="8" t="n"/>

--- a/docs/WBS.xlsx
+++ b/docs/WBS.xlsx
@@ -1777,17 +1777,29 @@
           <t>개발</t>
         </is>
       </c>
-      <c r="F30" s="7" t="n"/>
-      <c r="G30" s="7" t="n"/>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>예정</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="I30" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="8" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="J30" s="8" t="inlineStr">
+        <is>
+          <t>PR #18</t>
+        </is>
+      </c>
       <c r="K30" s="8" t="n"/>
     </row>
     <row r="31">

--- a/docs/WBS.xlsx
+++ b/docs/WBS.xlsx
@@ -11,7 +11,7 @@
     <sheet name="요약" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS'!$A$4:$K$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS'!$A$4:$K$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -98,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -129,6 +129,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -517,7 +523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -543,7 +549,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>기준일 2026-10-17 · 상태·진척률·날짜는 직접 고쳐 쓰세요. 단계 행과 '요약' 시트는 자동으로 다시 계산됩니다.</t>
+          <t>기준일 2026-10-18 · 상태·진척률·날짜는 직접 고쳐 쓰세요. 단계 행과 '요약' 시트는 자동으로 다시 계산됩니다.</t>
         </is>
       </c>
     </row>
@@ -626,19 +632,19 @@
       <c r="G5" s="4" t="n"/>
       <c r="H5" s="4" t="n"/>
       <c r="I5" s="6">
-        <f>IFERROR(AVERAGE(I6:I8),0)</f>
+        <f>IFERROR(AVERAGE(I6:I9),0)</f>
         <v/>
       </c>
       <c r="J5" s="5" t="n"/>
       <c r="K5" s="5" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>기획·설계</t>
         </is>
@@ -653,23 +659,23 @@
           <t>과제 4개(사업계획·상품기획·브랜딩·마케팅), 적응형 질문, 사실·가정 분리 원칙</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>공동</t>
         </is>
       </c>
-      <c r="F6" s="7" t="n"/>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="F6" s="16" t="n"/>
+      <c r="G6" s="16" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="H6" s="16" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I6" s="9" t="n">
+      <c r="I6" s="17" t="n">
         <v>1</v>
       </c>
       <c r="J6" s="8" t="inlineStr">
@@ -680,12 +686,12 @@
       <c r="K6" s="8" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>기획·설계</t>
         </is>
@@ -700,27 +706,27 @@
           <t>FastAPI 하네스 구조, API 계약, 테스트 전략</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="G7" s="16" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="H7" s="16" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I7" s="9" t="n">
+      <c r="I7" s="17" t="n">
         <v>1</v>
       </c>
       <c r="J7" s="8" t="inlineStr">
@@ -731,12 +737,12 @@
       <c r="K7" s="8" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>1.3</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>기획·설계</t>
         </is>
@@ -751,27 +757,27 @@
           <t>V2 화면 흐름, 묶음 0~4로 작업 나누기</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="G8" s="16" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
+      <c r="H8" s="16" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I8" s="9" t="n">
+      <c r="I8" s="17" t="n">
         <v>1</v>
       </c>
       <c r="J8" s="8" t="inlineStr">
@@ -782,1382 +788,1433 @@
       <c r="K8" s="8" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>기획·설계</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>작업 인수인계 문서(HANDOFF)</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>지금 상태·다음 할 일·작업 방식·환경 팁, PR마다 갱신</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F9" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="G9" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="H9" s="16" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I9" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="8" t="inlineStr">
+        <is>
+          <t>PR #19</t>
+        </is>
+      </c>
+      <c r="K9" s="8" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>백엔드 기반(하네스·API)</t>
         </is>
       </c>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="4" t="n"/>
-      <c r="F9" s="4" t="n"/>
-      <c r="G9" s="4" t="n"/>
-      <c r="H9" s="4" t="n"/>
-      <c r="I9" s="6">
-        <f>IFERROR(AVERAGE(I10:I17),0)</f>
-        <v/>
-      </c>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="4" t="n"/>
+      <c r="G10" s="4" t="n"/>
+      <c r="H10" s="4" t="n"/>
+      <c r="I10" s="6">
+        <f>IFERROR(AVERAGE(I11:I18),0)</f>
+        <v/>
+      </c>
+      <c r="J10" s="5" t="n"/>
+      <c r="K10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>2.1</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>세션 상태 모델</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>사실·가정·미정 구분, 정보 출처 표시</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E11" s="16" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="F11" s="16" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="G11" s="16" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr">
+      <c r="H11" s="16" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I10" s="9" t="n">
+      <c r="I11" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="J10" s="8" t="inlineStr">
+      <c r="J11" s="8" t="inlineStr">
         <is>
           <t>PR #1</t>
         </is>
       </c>
-      <c r="K10" s="8" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="K11" s="8" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>AI 모델 연결 자리·Mock</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>비용 없이 개발·테스트하는 가짜 모델</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E12" s="16" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="F12" s="16" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="G12" s="16" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
+      <c r="H12" s="16" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I11" s="9" t="n">
+      <c r="I12" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="J11" s="8" t="inlineStr">
+      <c r="J12" s="8" t="inlineStr">
         <is>
           <t>PR #2</t>
         </is>
       </c>
-      <c r="K11" s="8" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="K12" s="8" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>2.3</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>과제 정책·프롬프트 틀</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>과제별 질문 정책(policy.yaml), 단계별 프롬프트</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E13" s="16" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F13" s="16" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="G13" s="16" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="H13" s="16" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I12" s="9" t="n">
+      <c r="I13" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="J12" s="8" t="inlineStr">
+      <c r="J13" s="8" t="inlineStr">
         <is>
           <t>PR #3</t>
         </is>
       </c>
-      <c r="K12" s="8" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="K13" s="8" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>2.4</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>질문 진행 흐름</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>모드별 질문 상한, '다른 예시 보기' 단계</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E14" s="16" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F14" s="16" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="G14" s="16" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="H14" s="16" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I13" s="9" t="n">
+      <c r="I14" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="J13" s="8" t="inlineStr">
+      <c r="J14" s="8" t="inlineStr">
         <is>
           <t>PR #4</t>
         </is>
       </c>
-      <c r="K13" s="8" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="K14" s="8" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>결과 생성·검증·시나리오 실행</t>
         </is>
       </c>
-      <c r="D14" s="8" t="n"/>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="D15" s="8" t="n"/>
+      <c r="E15" s="16" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F15" s="16" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="G15" s="16" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
+      <c r="H15" s="16" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I14" s="9" t="n">
+      <c r="I15" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="J14" s="8" t="inlineStr">
+      <c r="J15" s="8" t="inlineStr">
         <is>
           <t>PR #5</t>
         </is>
       </c>
-      <c r="K14" s="8" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="K15" s="8" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>2.6</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>과제 4개 하네스</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>과제별 정책·프롬프트·검증 규칙</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E16" s="16" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F16" s="16" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr">
+      <c r="G16" s="16" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="H16" s="16" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I15" s="9" t="n">
+      <c r="I16" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="J15" s="8" t="inlineStr">
+      <c r="J16" s="8" t="inlineStr">
         <is>
           <t>PR #6</t>
         </is>
       </c>
-      <c r="K15" s="8" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="K16" s="8" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>2.7</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>코칭 API</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>한국어 오류 문구, API 문서</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E17" s="16" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F17" s="16" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
+      <c r="G17" s="16" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
+      <c r="H17" s="16" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I16" s="9" t="n">
+      <c r="I17" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="J16" s="8" t="inlineStr">
+      <c r="J17" s="8" t="inlineStr">
         <is>
           <t>PR #7</t>
         </is>
       </c>
-      <c r="K16" s="8" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="K17" s="8" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>2.8</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>첫 화면·개발 문서·리뷰 수정</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>API에 맞춘 최소 화면, 개발 안내(CLAUDE.md)</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E18" s="16" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr">
+      <c r="F18" s="16" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G17" s="7" t="inlineStr">
+      <c r="G18" s="16" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
+      <c r="H18" s="16" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I17" s="9" t="n">
+      <c r="I18" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="J17" s="8" t="inlineStr">
+      <c r="J18" s="8" t="inlineStr">
         <is>
           <t>PR #8~#10</t>
         </is>
       </c>
-      <c r="K17" s="8" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="K18" s="8" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
       </c>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="4" t="n"/>
-      <c r="F18" s="4" t="n"/>
-      <c r="G18" s="4" t="n"/>
-      <c r="H18" s="4" t="n"/>
-      <c r="I18" s="6">
-        <f>IFERROR(AVERAGE(I19:I22),0)</f>
-        <v/>
-      </c>
-      <c r="J18" s="5" t="n"/>
-      <c r="K18" s="5" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="4" t="n"/>
+      <c r="G19" s="4" t="n"/>
+      <c r="H19" s="4" t="n"/>
+      <c r="I19" s="6">
+        <f>IFERROR(AVERAGE(I20:I23),0)</f>
+        <v/>
+      </c>
+      <c r="J19" s="5" t="n"/>
+      <c r="K19" s="5" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>3.1</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>UX V2 프로토타입</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t>전체 화면 흐름 HTML 프로토타입</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E20" s="16" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
       </c>
-      <c r="F19" s="7" t="n"/>
-      <c r="G19" s="7" t="inlineStr">
+      <c r="F20" s="16" t="n"/>
+      <c r="G20" s="16" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr">
+      <c r="H20" s="16" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I19" s="9" t="n">
+      <c r="I20" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="J19" s="8" t="inlineStr">
+      <c r="J20" s="8" t="inlineStr">
         <is>
           <t>design/2026-10-16-ux-v2</t>
         </is>
       </c>
-      <c r="K19" s="8" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="K20" s="8" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>V2 피드백 반영 수정본</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t>모든 질문에 '다른 예시 보기', 모드 설명, 이미지 블록, 생성 중·실패·최신 아님 상태</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E21" s="16" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr">
+      <c r="F21" s="16" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G20" s="7" t="inlineStr">
+      <c r="G21" s="16" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H20" s="7" t="inlineStr">
+      <c r="H21" s="16" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I20" s="9" t="n">
+      <c r="I21" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="J20" s="8" t="inlineStr">
+      <c r="J21" s="8" t="inlineStr">
         <is>
           <t>design/2026-10-17-ux-v2-feedback</t>
         </is>
       </c>
-      <c r="K20" s="8" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="K21" s="8" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>모바일 390px 화면 검수</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>반응형 자동 배치 확인</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E22" s="16" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
       </c>
-      <c r="F21" s="7" t="n"/>
-      <c r="G21" s="7" t="n"/>
-      <c r="H21" s="7" t="inlineStr">
+      <c r="F22" s="16" t="n"/>
+      <c r="G22" s="16" t="n"/>
+      <c r="H22" s="16" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="I21" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="8" t="n"/>
-      <c r="K21" s="8" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>3.4</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>디자인</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>개발 화면 피그마로 가져와 다듬기</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>/preview 화면을 html.to.design으로 가져와 수정</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>디자인</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="n"/>
-      <c r="G22" s="7" t="n"/>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>예정</t>
-        </is>
-      </c>
-      <c r="I22" s="9" t="n">
+      <c r="I22" s="17" t="n">
         <v>0</v>
       </c>
       <c r="J22" s="8" t="n"/>
       <c r="K22" s="8" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
+      <c r="B23" s="16" t="inlineStr">
+        <is>
+          <t>디자인</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>개발 화면 피그마로 가져와 다듬기</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>/preview 화면을 html.to.design으로 가져와 수정</t>
+        </is>
+      </c>
+      <c r="E23" s="16" t="inlineStr">
+        <is>
+          <t>디자인</t>
+        </is>
+      </c>
+      <c r="F23" s="16" t="n"/>
+      <c r="G23" s="16" t="n"/>
+      <c r="H23" s="16" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="I23" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="8" t="n"/>
+      <c r="K23" s="8" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>디자인 V2 화면 개발</t>
         </is>
       </c>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="4" t="n"/>
-      <c r="F23" s="4" t="n"/>
-      <c r="G23" s="4" t="n"/>
-      <c r="H23" s="4" t="n"/>
-      <c r="I23" s="6">
-        <f>IFERROR(AVERAGE(I24:I30),0)</f>
-        <v/>
-      </c>
-      <c r="J23" s="5" t="n"/>
-      <c r="K23" s="5" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="4" t="n"/>
+      <c r="G24" s="4" t="n"/>
+      <c r="H24" s="4" t="n"/>
+      <c r="I24" s="6">
+        <f>IFERROR(AVERAGE(I25:I31),0)</f>
+        <v/>
+      </c>
+      <c r="J24" s="5" t="n"/>
+      <c r="K24" s="5" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B25" s="16" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>묶음 0: 디자인 토큰·앱 뼈대·미리보기 갤러리</t>
         </is>
       </c>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="D25" s="8" t="inlineStr">
         <is>
           <t>버셀 배포 설정 포함</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="E25" s="16" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F24" s="7" t="inlineStr">
+      <c r="F25" s="16" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G24" s="7" t="inlineStr">
+      <c r="G25" s="16" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H24" s="7" t="inlineStr">
+      <c r="H25" s="16" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I24" s="9" t="n">
+      <c r="I25" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="J24" s="8" t="inlineStr">
+      <c r="J25" s="8" t="inlineStr">
         <is>
           <t>PR #12</t>
         </is>
       </c>
-      <c r="K24" s="8" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="K25" s="8" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B26" s="16" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>묶음 1: 질문 흐름 화면(홈~결과)</t>
         </is>
       </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="D26" s="8" t="inlineStr">
         <is>
           <t>답변 종류, 흐름 패널, 익명 사용자</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
+      <c r="E26" s="16" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F25" s="7" t="inlineStr">
+      <c r="F26" s="16" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G25" s="7" t="inlineStr">
+      <c r="G26" s="16" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H25" s="7" t="inlineStr">
+      <c r="H26" s="16" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I25" s="9" t="n">
+      <c r="I26" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="J25" s="8" t="inlineStr">
+      <c r="J26" s="8" t="inlineStr">
         <is>
           <t>PR #13</t>
         </is>
       </c>
-      <c r="K25" s="8" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="K26" s="8" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="16" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B27" s="16" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
       </c>
-      <c r="C26" s="8" t="inlineStr">
+      <c r="C27" s="8" t="inlineStr">
         <is>
           <t>묶음 2: 저장·버전·내 작업·결과물</t>
         </is>
       </c>
-      <c r="D26" s="8" t="inlineStr">
+      <c r="D27" s="8" t="inlineStr">
         <is>
           <t>서버 저장(SQLite), 문서 내려받기</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="E27" s="16" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F26" s="7" t="inlineStr">
+      <c r="F27" s="16" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G26" s="7" t="inlineStr">
+      <c r="G27" s="16" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H26" s="7" t="inlineStr">
+      <c r="H27" s="16" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I26" s="9" t="n">
+      <c r="I27" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="J26" s="8" t="inlineStr">
+      <c r="J27" s="8" t="inlineStr">
         <is>
           <t>PR #14</t>
         </is>
       </c>
-      <c r="K26" s="8" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="K27" s="8" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>4.4</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B28" s="16" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>묶음 3a: 문구 수정·미확인 정보 보완</t>
         </is>
       </c>
-      <c r="D27" s="8" t="inlineStr">
+      <c r="D28" s="8" t="inlineStr">
         <is>
           <t>결과를 섹션·블록으로</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="E28" s="16" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr">
+      <c r="F28" s="16" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G27" s="7" t="inlineStr">
+      <c r="G28" s="16" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H27" s="7" t="inlineStr">
+      <c r="H28" s="16" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I27" s="9" t="n">
+      <c r="I28" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="J27" s="8" t="inlineStr">
+      <c r="J28" s="8" t="inlineStr">
         <is>
           <t>PR #15</t>
         </is>
       </c>
-      <c r="K27" s="8" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="K28" s="8" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B29" s="16" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
+      <c r="C29" s="8" t="inlineStr">
         <is>
           <t>묶음 3b: 근거 자료 검토·결과 이미지</t>
         </is>
       </c>
-      <c r="D28" s="8" t="inlineStr">
+      <c r="D29" s="8" t="inlineStr">
         <is>
           <t>샘플 근거 자료, 자리표시 이미지</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="E29" s="16" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr">
+      <c r="F29" s="16" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G28" s="7" t="inlineStr">
+      <c r="G29" s="16" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H28" s="7" t="inlineStr">
+      <c r="H29" s="16" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I28" s="9" t="n">
+      <c r="I29" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="J28" s="8" t="inlineStr">
+      <c r="J29" s="8" t="inlineStr">
         <is>
           <t>PR #16</t>
         </is>
       </c>
-      <c r="K28" s="8" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="K29" s="8" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="16" t="inlineStr">
         <is>
           <t>4.6</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B30" s="16" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr">
         <is>
           <t>디자인 피드백 반영</t>
         </is>
       </c>
-      <c r="D29" s="8" t="inlineStr">
+      <c r="D30" s="8" t="inlineStr">
         <is>
           <t>생성 중·생성 실패 화면, 최신 아님 배너, 이미지 상자, 모드 설명</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="E30" s="16" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F29" s="7" t="inlineStr">
+      <c r="F30" s="16" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G29" s="7" t="inlineStr">
+      <c r="G30" s="16" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H29" s="7" t="inlineStr">
+      <c r="H30" s="16" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I29" s="9" t="n">
+      <c r="I30" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="J29" s="8" t="inlineStr">
+      <c r="J30" s="8" t="inlineStr">
         <is>
           <t>PR #17</t>
         </is>
       </c>
-      <c r="K29" s="8" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="K30" s="8" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>4.7</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B31" s="16" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
       </c>
-      <c r="C30" s="8" t="inlineStr">
+      <c r="C31" s="8" t="inlineStr">
         <is>
           <t>묶음 4: 다음 과제로 이어가기</t>
         </is>
       </c>
-      <c r="D30" s="8" t="inlineStr">
+      <c r="D31" s="8" t="inlineStr">
         <is>
           <t>이전 결과를 다음 과제의 기준으로 가져오기</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr">
+      <c r="E31" s="16" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F30" s="7" t="inlineStr">
+      <c r="F31" s="16" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G30" s="7" t="inlineStr">
+      <c r="G31" s="16" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H30" s="7" t="inlineStr">
+      <c r="H31" s="16" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I30" s="9" t="n">
+      <c r="I31" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="J30" s="8" t="inlineStr">
+      <c r="J31" s="8" t="inlineStr">
         <is>
           <t>PR #18</t>
         </is>
       </c>
-      <c r="K30" s="8" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="K31" s="8" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>배포</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>배포</t>
         </is>
       </c>
-      <c r="D31" s="5" t="n"/>
-      <c r="E31" s="4" t="n"/>
-      <c r="F31" s="4" t="n"/>
-      <c r="G31" s="4" t="n"/>
-      <c r="H31" s="4" t="n"/>
-      <c r="I31" s="6">
-        <f>IFERROR(AVERAGE(I32:I33),0)</f>
-        <v/>
-      </c>
-      <c r="J31" s="5" t="n"/>
-      <c r="K31" s="5" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="D32" s="5" t="n"/>
+      <c r="E32" s="4" t="n"/>
+      <c r="F32" s="4" t="n"/>
+      <c r="G32" s="4" t="n"/>
+      <c r="H32" s="4" t="n"/>
+      <c r="I32" s="6">
+        <f>IFERROR(AVERAGE(I33:I34),0)</f>
+        <v/>
+      </c>
+      <c r="J32" s="5" t="n"/>
+      <c r="K32" s="5" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>5.1</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B33" s="16" t="inlineStr">
         <is>
           <t>배포</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
+      <c r="C33" s="8" t="inlineStr">
         <is>
           <t>프론트 버셀 연결</t>
         </is>
       </c>
-      <c r="D32" s="8" t="inlineStr">
+      <c r="D33" s="8" t="inlineStr">
         <is>
           <t>main은 정식 주소, PR마다 미리보기 주소</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr">
+      <c r="E33" s="16" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F32" s="7" t="n"/>
-      <c r="G32" s="7" t="n"/>
-      <c r="H32" s="7" t="inlineStr">
+      <c r="F33" s="16" t="n"/>
+      <c r="G33" s="16" t="n"/>
+      <c r="H33" s="16" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="I32" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="8" t="n"/>
-      <c r="K32" s="8" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>5.2</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>배포</t>
-        </is>
-      </c>
-      <c r="C33" s="8" t="inlineStr">
-        <is>
-          <t>백엔드 서버 배포(렌더)</t>
-        </is>
-      </c>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>저장 디스크 방식 정하기, 프론트와 연결</t>
-        </is>
-      </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F33" s="7" t="n"/>
-      <c r="G33" s="7" t="n"/>
-      <c r="H33" s="7" t="inlineStr">
-        <is>
-          <t>예정</t>
-        </is>
-      </c>
-      <c r="I33" s="9" t="n">
+      <c r="I33" s="17" t="n">
         <v>0</v>
       </c>
       <c r="J33" s="8" t="n"/>
       <c r="K33" s="8" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="B34" s="16" t="inlineStr">
+        <is>
+          <t>배포</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>백엔드 서버 배포(렌더)</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>저장 디스크 방식 정하기, 프론트와 연결</t>
+        </is>
+      </c>
+      <c r="E34" s="16" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F34" s="16" t="n"/>
+      <c r="G34" s="16" t="n"/>
+      <c r="H34" s="16" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="I34" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="8" t="n"/>
+      <c r="K34" s="8" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>실제 AI 연결·튜닝</t>
         </is>
       </c>
-      <c r="D34" s="5" t="n"/>
-      <c r="E34" s="4" t="n"/>
-      <c r="F34" s="4" t="n"/>
-      <c r="G34" s="4" t="n"/>
-      <c r="H34" s="4" t="n"/>
-      <c r="I34" s="6">
-        <f>IFERROR(AVERAGE(I35:I37),0)</f>
-        <v/>
-      </c>
-      <c r="J34" s="5" t="n"/>
-      <c r="K34" s="5" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="inlineStr">
+      <c r="D35" s="5" t="n"/>
+      <c r="E35" s="4" t="n"/>
+      <c r="F35" s="4" t="n"/>
+      <c r="G35" s="4" t="n"/>
+      <c r="H35" s="4" t="n"/>
+      <c r="I35" s="6">
+        <f>IFERROR(AVERAGE(I36:I38),0)</f>
+        <v/>
+      </c>
+      <c r="J35" s="5" t="n"/>
+      <c r="K35" s="5" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>6.1</t>
         </is>
       </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="B36" s="16" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
       </c>
-      <c r="C35" s="8" t="inlineStr">
+      <c r="C36" s="8" t="inlineStr">
         <is>
           <t>Claude 모델 연결</t>
         </is>
       </c>
-      <c r="D35" s="8" t="inlineStr">
+      <c r="D36" s="8" t="inlineStr">
         <is>
           <t>가짜 모델(Mock) 대신 실제 모델</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
+      <c r="E36" s="16" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F35" s="7" t="n"/>
-      <c r="G35" s="7" t="n"/>
-      <c r="H35" s="7" t="inlineStr">
+      <c r="F36" s="16" t="n"/>
+      <c r="G36" s="16" t="n"/>
+      <c r="H36" s="16" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="I35" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="8" t="n"/>
-      <c r="K35" s="8" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>6.2</t>
-        </is>
-      </c>
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>실제 AI 연결</t>
-        </is>
-      </c>
-      <c r="C36" s="8" t="inlineStr">
-        <is>
-          <t>과제별 질문·결과 품질 튜닝</t>
-        </is>
-      </c>
-      <c r="D36" s="8" t="inlineStr">
-        <is>
-          <t>준비도 기준·항목 가중치·프롬프트를 시나리오로 측정</t>
-        </is>
-      </c>
-      <c r="E36" s="7" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F36" s="7" t="n"/>
-      <c r="G36" s="7" t="n"/>
-      <c r="H36" s="7" t="inlineStr">
-        <is>
-          <t>예정</t>
-        </is>
-      </c>
-      <c r="I36" s="9" t="n">
+      <c r="I36" s="17" t="n">
         <v>0</v>
       </c>
       <c r="J36" s="8" t="n"/>
       <c r="K36" s="8" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>6.3</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="inlineStr">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="B37" s="16" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>이미지 생성·웹 검색 근거 연결</t>
+          <t>과제별 질문·결과 품질 튜닝</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>지금의 자리표시·샘플 자리에 실제 기능 연결</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr">
+          <t>준비도 기준·항목 가중치·프롬프트를 시나리오로 측정</t>
+        </is>
+      </c>
+      <c r="E37" s="16" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F37" s="7" t="n"/>
-      <c r="G37" s="7" t="n"/>
-      <c r="H37" s="7" t="inlineStr">
+      <c r="F37" s="16" t="n"/>
+      <c r="G37" s="16" t="n"/>
+      <c r="H37" s="16" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="I37" s="9" t="n">
+      <c r="I37" s="17" t="n">
         <v>0</v>
       </c>
       <c r="J37" s="8" t="n"/>
       <c r="K37" s="8" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="A38" s="16" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="B38" s="16" t="inlineStr">
+        <is>
+          <t>실제 AI 연결</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>이미지 생성·웹 검색 근거 연결</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>지금의 자리표시·샘플 자리에 실제 기능 연결</t>
+        </is>
+      </c>
+      <c r="E38" s="16" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F38" s="16" t="n"/>
+      <c r="G38" s="16" t="n"/>
+      <c r="H38" s="16" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="I38" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="8" t="n"/>
+      <c r="K38" s="8" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>마무리</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>평가·발표</t>
         </is>
       </c>
-      <c r="D38" s="5" t="n"/>
-      <c r="E38" s="4" t="n"/>
-      <c r="F38" s="4" t="n"/>
-      <c r="G38" s="4" t="n"/>
-      <c r="H38" s="4" t="n"/>
-      <c r="I38" s="6">
-        <f>IFERROR(AVERAGE(I39:I40),0)</f>
-        <v/>
-      </c>
-      <c r="J38" s="5" t="n"/>
-      <c r="K38" s="5" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="inlineStr">
+      <c r="D39" s="5" t="n"/>
+      <c r="E39" s="4" t="n"/>
+      <c r="F39" s="4" t="n"/>
+      <c r="G39" s="4" t="n"/>
+      <c r="H39" s="4" t="n"/>
+      <c r="I39" s="6">
+        <f>IFERROR(AVERAGE(I40:I41),0)</f>
+        <v/>
+      </c>
+      <c r="J39" s="5" t="n"/>
+      <c r="K39" s="5" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="16" t="inlineStr">
         <is>
           <t>7.1</t>
         </is>
       </c>
-      <c r="B39" s="7" t="inlineStr">
+      <c r="B40" s="16" t="inlineStr">
         <is>
           <t>마무리</t>
         </is>
       </c>
-      <c r="C39" s="8" t="inlineStr">
+      <c r="C40" s="8" t="inlineStr">
         <is>
           <t>사용성 확인·평가 지표 측정</t>
         </is>
       </c>
-      <c r="D39" s="8" t="inlineStr">
+      <c r="D40" s="8" t="inlineStr">
         <is>
           <t>필수정보 충족률, 질문 효율, 가정 표시율 등(기획서 14장)</t>
         </is>
       </c>
-      <c r="E39" s="7" t="inlineStr">
+      <c r="E40" s="16" t="inlineStr">
         <is>
           <t>공동</t>
         </is>
       </c>
-      <c r="F39" s="7" t="n"/>
-      <c r="G39" s="7" t="n"/>
-      <c r="H39" s="7" t="inlineStr">
+      <c r="F40" s="16" t="n"/>
+      <c r="G40" s="16" t="n"/>
+      <c r="H40" s="16" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="I39" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="8" t="n"/>
-      <c r="K39" s="8" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>7.2</t>
-        </is>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>마무리</t>
-        </is>
-      </c>
-      <c r="C40" s="8" t="inlineStr">
-        <is>
-          <t>최종 발표 자료</t>
-        </is>
-      </c>
-      <c r="D40" s="8" t="n"/>
-      <c r="E40" s="7" t="inlineStr">
-        <is>
-          <t>공동</t>
-        </is>
-      </c>
-      <c r="F40" s="7" t="n"/>
-      <c r="G40" s="7" t="n"/>
-      <c r="H40" s="7" t="inlineStr">
-        <is>
-          <t>예정</t>
-        </is>
-      </c>
-      <c r="I40" s="9" t="n">
+      <c r="I40" s="17" t="n">
         <v>0</v>
       </c>
       <c r="J40" s="8" t="n"/>
       <c r="K40" s="8" t="n"/>
     </row>
+    <row r="41">
+      <c r="A41" s="16" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="B41" s="16" t="inlineStr">
+        <is>
+          <t>마무리</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>최종 발표 자료</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="n"/>
+      <c r="E41" s="16" t="inlineStr">
+        <is>
+          <t>공동</t>
+        </is>
+      </c>
+      <c r="F41" s="16" t="n"/>
+      <c r="G41" s="16" t="n"/>
+      <c r="H41" s="16" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="I41" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="8" t="n"/>
+      <c r="K41" s="8" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:K40"/>
-  <conditionalFormatting sqref="H5:H40">
+  <autoFilter ref="A4:K41"/>
+  <conditionalFormatting sqref="H5:H41">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"완료"</formula>
     </cfRule>
@@ -2168,7 +2225,7 @@
       <formula>"보류"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I5:I40">
+  <conditionalFormatting sqref="I5:I41">
     <cfRule type="dataBar" priority="4">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -2178,10 +2235,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="H5:H40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"완료,진행 중,예정,보류"</formula1>
     </dataValidation>
-    <dataValidation sqref="E5:E40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"개발,디자인,공동"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2252,23 +2309,23 @@
         </is>
       </c>
       <c r="B4" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$40,A4,WBS!$H$5:$H$40,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$41,A4,WBS!$H$5:$H$41,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C4" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$40,A4,WBS!$H$5:$H$40,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$41,A4,WBS!$H$5:$H$41,"완료")</f>
         <v/>
       </c>
       <c r="D4" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$40,A4,WBS!$H$5:$H$40,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$41,A4,WBS!$H$5:$H$41,"진행 중")</f>
         <v/>
       </c>
       <c r="E4" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$40,A4,WBS!$H$5:$H$40,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$41,A4,WBS!$H$5:$H$41,"예정")</f>
         <v/>
       </c>
       <c r="F4" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$40,WBS!$B$5:$B$40,A4,WBS!$H$5:$H$40,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$41,WBS!$B$5:$B$41,A4,WBS!$H$5:$H$41,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2279,23 +2336,23 @@
         </is>
       </c>
       <c r="B5" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$40,A5,WBS!$H$5:$H$40,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$41,A5,WBS!$H$5:$H$41,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C5" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$40,A5,WBS!$H$5:$H$40,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$41,A5,WBS!$H$5:$H$41,"완료")</f>
         <v/>
       </c>
       <c r="D5" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$40,A5,WBS!$H$5:$H$40,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$41,A5,WBS!$H$5:$H$41,"진행 중")</f>
         <v/>
       </c>
       <c r="E5" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$40,A5,WBS!$H$5:$H$40,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$41,A5,WBS!$H$5:$H$41,"예정")</f>
         <v/>
       </c>
       <c r="F5" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$40,WBS!$B$5:$B$40,A5,WBS!$H$5:$H$40,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$41,WBS!$B$5:$B$41,A5,WBS!$H$5:$H$41,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2306,23 +2363,23 @@
         </is>
       </c>
       <c r="B6" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$40,A6,WBS!$H$5:$H$40,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$41,A6,WBS!$H$5:$H$41,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C6" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$40,A6,WBS!$H$5:$H$40,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$41,A6,WBS!$H$5:$H$41,"완료")</f>
         <v/>
       </c>
       <c r="D6" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$40,A6,WBS!$H$5:$H$40,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$41,A6,WBS!$H$5:$H$41,"진행 중")</f>
         <v/>
       </c>
       <c r="E6" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$40,A6,WBS!$H$5:$H$40,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$41,A6,WBS!$H$5:$H$41,"예정")</f>
         <v/>
       </c>
       <c r="F6" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$40,WBS!$B$5:$B$40,A6,WBS!$H$5:$H$40,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$41,WBS!$B$5:$B$41,A6,WBS!$H$5:$H$41,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2333,23 +2390,23 @@
         </is>
       </c>
       <c r="B7" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$40,A7,WBS!$H$5:$H$40,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$41,A7,WBS!$H$5:$H$41,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C7" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$40,A7,WBS!$H$5:$H$40,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$41,A7,WBS!$H$5:$H$41,"완료")</f>
         <v/>
       </c>
       <c r="D7" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$40,A7,WBS!$H$5:$H$40,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$41,A7,WBS!$H$5:$H$41,"진행 중")</f>
         <v/>
       </c>
       <c r="E7" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$40,A7,WBS!$H$5:$H$40,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$41,A7,WBS!$H$5:$H$41,"예정")</f>
         <v/>
       </c>
       <c r="F7" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$40,WBS!$B$5:$B$40,A7,WBS!$H$5:$H$40,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$41,WBS!$B$5:$B$41,A7,WBS!$H$5:$H$41,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2360,23 +2417,23 @@
         </is>
       </c>
       <c r="B8" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$40,A8,WBS!$H$5:$H$40,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$41,A8,WBS!$H$5:$H$41,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C8" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$40,A8,WBS!$H$5:$H$40,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$41,A8,WBS!$H$5:$H$41,"완료")</f>
         <v/>
       </c>
       <c r="D8" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$40,A8,WBS!$H$5:$H$40,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$41,A8,WBS!$H$5:$H$41,"진행 중")</f>
         <v/>
       </c>
       <c r="E8" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$40,A8,WBS!$H$5:$H$40,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$41,A8,WBS!$H$5:$H$41,"예정")</f>
         <v/>
       </c>
       <c r="F8" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$40,WBS!$B$5:$B$40,A8,WBS!$H$5:$H$40,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$41,WBS!$B$5:$B$41,A8,WBS!$H$5:$H$41,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2387,23 +2444,23 @@
         </is>
       </c>
       <c r="B9" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$40,A9,WBS!$H$5:$H$40,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$41,A9,WBS!$H$5:$H$41,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C9" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$40,A9,WBS!$H$5:$H$40,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$41,A9,WBS!$H$5:$H$41,"완료")</f>
         <v/>
       </c>
       <c r="D9" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$40,A9,WBS!$H$5:$H$40,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$41,A9,WBS!$H$5:$H$41,"진행 중")</f>
         <v/>
       </c>
       <c r="E9" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$40,A9,WBS!$H$5:$H$40,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$41,A9,WBS!$H$5:$H$41,"예정")</f>
         <v/>
       </c>
       <c r="F9" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$40,WBS!$B$5:$B$40,A9,WBS!$H$5:$H$40,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$41,WBS!$B$5:$B$41,A9,WBS!$H$5:$H$41,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2414,23 +2471,23 @@
         </is>
       </c>
       <c r="B10" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$40,A10,WBS!$H$5:$H$40,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$41,A10,WBS!$H$5:$H$41,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C10" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$40,A10,WBS!$H$5:$H$40,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$41,A10,WBS!$H$5:$H$41,"완료")</f>
         <v/>
       </c>
       <c r="D10" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$40,A10,WBS!$H$5:$H$40,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$41,A10,WBS!$H$5:$H$41,"진행 중")</f>
         <v/>
       </c>
       <c r="E10" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$40,A10,WBS!$H$5:$H$40,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$41,A10,WBS!$H$5:$H$41,"예정")</f>
         <v/>
       </c>
       <c r="F10" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$40,WBS!$B$5:$B$40,A10,WBS!$H$5:$H$40,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$41,WBS!$B$5:$B$41,A10,WBS!$H$5:$H$41,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2457,7 +2514,7 @@
         <v/>
       </c>
       <c r="F11" s="14">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$40,WBS!$H$5:$H$40,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$41,WBS!$H$5:$H$41,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>

--- a/docs/WBS.xlsx
+++ b/docs/WBS.xlsx
@@ -2019,18 +2019,34 @@
           <t>개발</t>
         </is>
       </c>
-      <c r="F36" s="16" t="n"/>
-      <c r="G36" s="16" t="n"/>
+      <c r="F36" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="G36" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
       <c r="H36" s="16" t="inlineStr">
         <is>
-          <t>예정</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="I36" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="8" t="n"/>
-      <c r="K36" s="8" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="J36" s="8" t="inlineStr">
+        <is>
+          <t>PR #20</t>
+        </is>
+      </c>
+      <c r="K36" s="8" t="inlineStr">
+        <is>
+          <t>어댑터 준비(기본 Mock). 실제 호출·모델·비용은 인수 기업</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="16" t="inlineStr">

--- a/docs/WBS.xlsx
+++ b/docs/WBS.xlsx
@@ -1913,18 +1913,30 @@
           <t>개발</t>
         </is>
       </c>
-      <c r="F33" s="16" t="n"/>
+      <c r="F33" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
       <c r="G33" s="16" t="n"/>
       <c r="H33" s="16" t="inlineStr">
         <is>
-          <t>예정</t>
+          <t>진행 중</t>
         </is>
       </c>
       <c r="I33" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="8" t="n"/>
-      <c r="K33" s="8" t="n"/>
+        <v>0.5</v>
+      </c>
+      <c r="J33" s="8" t="inlineStr">
+        <is>
+          <t>PR #21</t>
+        </is>
+      </c>
+      <c r="K33" s="8" t="inlineStr">
+        <is>
+          <t>무료(버셀 Hobby), 설정·가이드 준비 → 사용자 연결 대기</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="16" t="inlineStr">
@@ -1952,18 +1964,30 @@
           <t>개발</t>
         </is>
       </c>
-      <c r="F34" s="16" t="n"/>
+      <c r="F34" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
       <c r="G34" s="16" t="n"/>
       <c r="H34" s="16" t="inlineStr">
         <is>
-          <t>예정</t>
+          <t>진행 중</t>
         </is>
       </c>
       <c r="I34" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="8" t="n"/>
-      <c r="K34" s="8" t="n"/>
+        <v>0.5</v>
+      </c>
+      <c r="J34" s="8" t="inlineStr">
+        <is>
+          <t>PR #21</t>
+        </is>
+      </c>
+      <c r="K34" s="8" t="inlineStr">
+        <is>
+          <t>무료(렌더 Free, 데이터 휘발), render.yaml 준비 → 사용자 연결 대기</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">

--- a/docs/WBS.xlsx
+++ b/docs/WBS.xlsx
@@ -1918,23 +1918,27 @@
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="G33" s="16" t="n"/>
+      <c r="G33" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
       <c r="H33" s="16" t="inlineStr">
         <is>
-          <t>진행 중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="I33" s="17" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J33" s="8" t="inlineStr">
         <is>
-          <t>PR #21</t>
+          <t>https://ax-platform-5.vercel.app</t>
         </is>
       </c>
       <c r="K33" s="8" t="inlineStr">
         <is>
-          <t>무료(버셀 Hobby), 설정·가이드 준비 → 사용자 연결 대기</t>
+          <t>버셀 Hobby(개인 계정), main 자동 배포</t>
         </is>
       </c>
     </row>
@@ -1969,23 +1973,27 @@
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="G34" s="16" t="n"/>
+      <c r="G34" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
       <c r="H34" s="16" t="inlineStr">
         <is>
-          <t>진행 중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="I34" s="17" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J34" s="8" t="inlineStr">
         <is>
-          <t>PR #21</t>
+          <t>https://ax-coaching-api.onrender.com</t>
         </is>
       </c>
       <c r="K34" s="8" t="inlineStr">
         <is>
-          <t>무료(렌더 Free, 데이터 휘발), render.yaml 준비 → 사용자 연결 대기</t>
+          <t>렌더 Free(개인 계정), Mock·데이터 휘발</t>
         </is>
       </c>
     </row>

--- a/docs/WBS.xlsx
+++ b/docs/WBS.xlsx
@@ -11,7 +11,7 @@
     <sheet name="요약" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS'!$A$4:$K$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS'!$A$4:$K$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -98,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -129,6 +129,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -523,7 +529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -632,7 +638,7 @@
       <c r="G5" s="4" t="n"/>
       <c r="H5" s="4" t="n"/>
       <c r="I5" s="6">
-        <f>IFERROR(AVERAGE(I6:I9),0)</f>
+        <f>IFERROR(AVERAGE(I6:I10),0)</f>
         <v/>
       </c>
       <c r="J5" s="5" t="n"/>
@@ -839,88 +845,88 @@
       <c r="K9" s="8" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>기획·설계</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>README 정리(팀 공유용 남은 일)</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>바로 보기 주소, 된 것, 남은 일·맡을 사람·상의할 점</t>
+        </is>
+      </c>
+      <c r="E10" s="18" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F10" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="G10" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="H10" s="18" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I10" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>PR #23</t>
+        </is>
+      </c>
+      <c r="K10" s="8" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>백엔드 기반(하네스·API)</t>
         </is>
       </c>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="4" t="n"/>
-      <c r="F10" s="4" t="n"/>
-      <c r="G10" s="4" t="n"/>
-      <c r="H10" s="4" t="n"/>
-      <c r="I10" s="6">
-        <f>IFERROR(AVERAGE(I11:I18),0)</f>
-        <v/>
-      </c>
-      <c r="J10" s="5" t="n"/>
-      <c r="K10" s="5" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="16" t="inlineStr">
-        <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>백엔드 기반</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>세션 상태 모델</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>사실·가정·미정 구분, 정보 출처 표시</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F11" s="16" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="G11" s="16" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="H11" s="16" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I11" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" s="8" t="inlineStr">
-        <is>
-          <t>PR #1</t>
-        </is>
-      </c>
-      <c r="K11" s="8" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="4" t="n"/>
+      <c r="F11" s="4" t="n"/>
+      <c r="G11" s="4" t="n"/>
+      <c r="H11" s="4" t="n"/>
+      <c r="I11" s="6">
+        <f>IFERROR(AVERAGE(I12:I19),0)</f>
+        <v/>
+      </c>
+      <c r="J11" s="5" t="n"/>
+      <c r="K11" s="5" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="16" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="B12" s="16" t="inlineStr">
@@ -930,12 +936,12 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>AI 모델 연결 자리·Mock</t>
+          <t>세션 상태 모델</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>비용 없이 개발·테스트하는 가짜 모델</t>
+          <t>사실·가정·미정 구분, 정보 출처 표시</t>
         </is>
       </c>
       <c r="E12" s="16" t="inlineStr">
@@ -963,7 +969,7 @@
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>PR #2</t>
+          <t>PR #1</t>
         </is>
       </c>
       <c r="K12" s="8" t="n"/>
@@ -971,7 +977,7 @@
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="B13" s="16" t="inlineStr">
@@ -981,12 +987,12 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>과제 정책·프롬프트 틀</t>
+          <t>AI 모델 연결 자리·Mock</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>과제별 질문 정책(policy.yaml), 단계별 프롬프트</t>
+          <t>비용 없이 개발·테스트하는 가짜 모델</t>
         </is>
       </c>
       <c r="E13" s="16" t="inlineStr">
@@ -996,7 +1002,7 @@
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G13" s="16" t="inlineStr">
@@ -1014,7 +1020,7 @@
       </c>
       <c r="J13" s="8" t="inlineStr">
         <is>
-          <t>PR #3</t>
+          <t>PR #2</t>
         </is>
       </c>
       <c r="K13" s="8" t="n"/>
@@ -1022,7 +1028,7 @@
     <row r="14">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="B14" s="16" t="inlineStr">
@@ -1032,12 +1038,12 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>질문 진행 흐름</t>
+          <t>과제 정책·프롬프트 틀</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>모드별 질문 상한, '다른 예시 보기' 단계</t>
+          <t>과제별 질문 정책(policy.yaml), 단계별 프롬프트</t>
         </is>
       </c>
       <c r="E14" s="16" t="inlineStr">
@@ -1065,7 +1071,7 @@
       </c>
       <c r="J14" s="8" t="inlineStr">
         <is>
-          <t>PR #4</t>
+          <t>PR #3</t>
         </is>
       </c>
       <c r="K14" s="8" t="n"/>
@@ -1073,7 +1079,7 @@
     <row r="15">
       <c r="A15" s="16" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="B15" s="16" t="inlineStr">
@@ -1083,10 +1089,14 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>결과 생성·검증·시나리오 실행</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="n"/>
+          <t>질문 진행 흐름</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>모드별 질문 상한, '다른 예시 보기' 단계</t>
+        </is>
+      </c>
       <c r="E15" s="16" t="inlineStr">
         <is>
           <t>개발</t>
@@ -1112,7 +1122,7 @@
       </c>
       <c r="J15" s="8" t="inlineStr">
         <is>
-          <t>PR #5</t>
+          <t>PR #4</t>
         </is>
       </c>
       <c r="K15" s="8" t="n"/>
@@ -1120,7 +1130,7 @@
     <row r="16">
       <c r="A16" s="16" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="B16" s="16" t="inlineStr">
@@ -1130,14 +1140,10 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>과제 4개 하네스</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>과제별 정책·프롬프트·검증 규칙</t>
-        </is>
-      </c>
+          <t>결과 생성·검증·시나리오 실행</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="n"/>
       <c r="E16" s="16" t="inlineStr">
         <is>
           <t>개발</t>
@@ -1163,7 +1169,7 @@
       </c>
       <c r="J16" s="8" t="inlineStr">
         <is>
-          <t>PR #6</t>
+          <t>PR #5</t>
         </is>
       </c>
       <c r="K16" s="8" t="n"/>
@@ -1171,7 +1177,7 @@
     <row r="17">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="B17" s="16" t="inlineStr">
@@ -1181,12 +1187,12 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>코칭 API</t>
+          <t>과제 4개 하네스</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>한국어 오류 문구, API 문서</t>
+          <t>과제별 정책·프롬프트·검증 규칙</t>
         </is>
       </c>
       <c r="E17" s="16" t="inlineStr">
@@ -1214,7 +1220,7 @@
       </c>
       <c r="J17" s="8" t="inlineStr">
         <is>
-          <t>PR #7</t>
+          <t>PR #6</t>
         </is>
       </c>
       <c r="K17" s="8" t="n"/>
@@ -1222,7 +1228,7 @@
     <row r="18">
       <c r="A18" s="16" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="B18" s="16" t="inlineStr">
@@ -1232,12 +1238,12 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>첫 화면·개발 문서·리뷰 수정</t>
+          <t>코칭 API</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>API에 맞춘 최소 화면, 개발 안내(CLAUDE.md)</t>
+          <t>한국어 오류 문구, API 문서</t>
         </is>
       </c>
       <c r="E18" s="16" t="inlineStr">
@@ -1265,90 +1271,94 @@
       </c>
       <c r="J18" s="8" t="inlineStr">
         <is>
+          <t>PR #7</t>
+        </is>
+      </c>
+      <c r="K18" s="8" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t>백엔드 기반</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>첫 화면·개발 문서·리뷰 수정</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>API에 맞춘 최소 화면, 개발 안내(CLAUDE.md)</t>
+        </is>
+      </c>
+      <c r="E19" s="16" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F19" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="G19" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="H19" s="16" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I19" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" s="8" t="inlineStr">
+        <is>
           <t>PR #8~#10</t>
         </is>
       </c>
-      <c r="K18" s="8" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="K19" s="8" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
       </c>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="4" t="n"/>
-      <c r="F19" s="4" t="n"/>
-      <c r="G19" s="4" t="n"/>
-      <c r="H19" s="4" t="n"/>
-      <c r="I19" s="6">
-        <f>IFERROR(AVERAGE(I20:I23),0)</f>
-        <v/>
-      </c>
-      <c r="J19" s="5" t="n"/>
-      <c r="K19" s="5" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="16" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>디자인</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>UX V2 프로토타입</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>전체 화면 흐름 HTML 프로토타입</t>
-        </is>
-      </c>
-      <c r="E20" s="16" t="inlineStr">
-        <is>
-          <t>디자인</t>
-        </is>
-      </c>
-      <c r="F20" s="16" t="n"/>
-      <c r="G20" s="16" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="H20" s="16" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I20" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" s="8" t="inlineStr">
-        <is>
-          <t>design/2026-10-16-ux-v2</t>
-        </is>
-      </c>
-      <c r="K20" s="8" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="4" t="n"/>
+      <c r="G20" s="4" t="n"/>
+      <c r="H20" s="4" t="n"/>
+      <c r="I20" s="6">
+        <f>IFERROR(AVERAGE(I21:I24),0)</f>
+        <v/>
+      </c>
+      <c r="J20" s="5" t="n"/>
+      <c r="K20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="B21" s="16" t="inlineStr">
@@ -1358,12 +1368,12 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>V2 피드백 반영 수정본</t>
+          <t>UX V2 프로토타입</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>모든 질문에 '다른 예시 보기', 모드 설명, 이미지 블록, 생성 중·실패·최신 아님 상태</t>
+          <t>전체 화면 흐름 HTML 프로토타입</t>
         </is>
       </c>
       <c r="E21" s="16" t="inlineStr">
@@ -1371,14 +1381,10 @@
           <t>디자인</t>
         </is>
       </c>
-      <c r="F21" s="16" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
+      <c r="F21" s="16" t="n"/>
       <c r="G21" s="16" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H21" s="16" t="inlineStr">
@@ -1391,7 +1397,7 @@
       </c>
       <c r="J21" s="8" t="inlineStr">
         <is>
-          <t>design/2026-10-17-ux-v2-feedback</t>
+          <t>design/2026-10-16-ux-v2</t>
         </is>
       </c>
       <c r="K21" s="8" t="n"/>
@@ -1399,7 +1405,7 @@
     <row r="22">
       <c r="A22" s="16" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="B22" s="16" t="inlineStr">
@@ -1409,12 +1415,12 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>모바일 390px 화면 검수</t>
+          <t>V2 피드백 반영 수정본</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>반응형 자동 배치 확인</t>
+          <t>모든 질문에 '다른 예시 보기', 모드 설명, 이미지 블록, 생성 중·실패·최신 아님 상태</t>
         </is>
       </c>
       <c r="E22" s="16" t="inlineStr">
@@ -1422,23 +1428,35 @@
           <t>디자인</t>
         </is>
       </c>
-      <c r="F22" s="16" t="n"/>
-      <c r="G22" s="16" t="n"/>
+      <c r="F22" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="G22" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
       <c r="H22" s="16" t="inlineStr">
         <is>
-          <t>예정</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="I22" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="8" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="J22" s="8" t="inlineStr">
+        <is>
+          <t>design/2026-10-17-ux-v2-feedback</t>
+        </is>
+      </c>
       <c r="K22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="B23" s="16" t="inlineStr">
@@ -1448,12 +1466,12 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>개발 화면 피그마로 가져와 다듬기</t>
+          <t>모바일 390px 화면 검수</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>/preview 화면을 html.to.design으로 가져와 수정</t>
+          <t>반응형 자동 배치 확인</t>
         </is>
       </c>
       <c r="E23" s="16" t="inlineStr">
@@ -1475,88 +1493,76 @@
       <c r="K23" s="8" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="16" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="inlineStr">
+        <is>
+          <t>디자인</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>개발 화면 피그마로 가져와 다듬기</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>/preview 화면을 html.to.design으로 가져와 수정</t>
+        </is>
+      </c>
+      <c r="E24" s="16" t="inlineStr">
+        <is>
+          <t>디자인</t>
+        </is>
+      </c>
+      <c r="F24" s="16" t="n"/>
+      <c r="G24" s="16" t="n"/>
+      <c r="H24" s="16" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="I24" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="8" t="n"/>
+      <c r="K24" s="8" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>디자인 V2 화면 개발</t>
         </is>
       </c>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="4" t="n"/>
-      <c r="F24" s="4" t="n"/>
-      <c r="G24" s="4" t="n"/>
-      <c r="H24" s="4" t="n"/>
-      <c r="I24" s="6">
-        <f>IFERROR(AVERAGE(I25:I31),0)</f>
-        <v/>
-      </c>
-      <c r="J24" s="5" t="n"/>
-      <c r="K24" s="5" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="16" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>화면 개발(V2)</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>묶음 0: 디자인 토큰·앱 뼈대·미리보기 갤러리</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>버셀 배포 설정 포함</t>
-        </is>
-      </c>
-      <c r="E25" s="16" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F25" s="16" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="G25" s="16" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="H25" s="16" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I25" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" s="8" t="inlineStr">
-        <is>
-          <t>PR #12</t>
-        </is>
-      </c>
-      <c r="K25" s="8" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="4" t="n"/>
+      <c r="F25" s="4" t="n"/>
+      <c r="G25" s="4" t="n"/>
+      <c r="H25" s="4" t="n"/>
+      <c r="I25" s="6">
+        <f>IFERROR(AVERAGE(I26:I32),0)</f>
+        <v/>
+      </c>
+      <c r="J25" s="5" t="n"/>
+      <c r="K25" s="5" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="16" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="B26" s="16" t="inlineStr">
@@ -1566,12 +1572,12 @@
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>묶음 1: 질문 흐름 화면(홈~결과)</t>
+          <t>묶음 0: 디자인 토큰·앱 뼈대·미리보기 갤러리</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>답변 종류, 흐름 패널, 익명 사용자</t>
+          <t>버셀 배포 설정 포함</t>
         </is>
       </c>
       <c r="E26" s="16" t="inlineStr">
@@ -1581,12 +1587,12 @@
       </c>
       <c r="F26" s="16" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G26" s="16" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H26" s="16" t="inlineStr">
@@ -1599,7 +1605,7 @@
       </c>
       <c r="J26" s="8" t="inlineStr">
         <is>
-          <t>PR #13</t>
+          <t>PR #12</t>
         </is>
       </c>
       <c r="K26" s="8" t="n"/>
@@ -1607,7 +1613,7 @@
     <row r="27">
       <c r="A27" s="16" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="B27" s="16" t="inlineStr">
@@ -1617,12 +1623,12 @@
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>묶음 2: 저장·버전·내 작업·결과물</t>
+          <t>묶음 1: 질문 흐름 화면(홈~결과)</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>서버 저장(SQLite), 문서 내려받기</t>
+          <t>답변 종류, 흐름 패널, 익명 사용자</t>
         </is>
       </c>
       <c r="E27" s="16" t="inlineStr">
@@ -1650,7 +1656,7 @@
       </c>
       <c r="J27" s="8" t="inlineStr">
         <is>
-          <t>PR #14</t>
+          <t>PR #13</t>
         </is>
       </c>
       <c r="K27" s="8" t="n"/>
@@ -1658,7 +1664,7 @@
     <row r="28">
       <c r="A28" s="16" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="B28" s="16" t="inlineStr">
@@ -1668,12 +1674,12 @@
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>묶음 3a: 문구 수정·미확인 정보 보완</t>
+          <t>묶음 2: 저장·버전·내 작업·결과물</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>결과를 섹션·블록으로</t>
+          <t>서버 저장(SQLite), 문서 내려받기</t>
         </is>
       </c>
       <c r="E28" s="16" t="inlineStr">
@@ -1701,7 +1707,7 @@
       </c>
       <c r="J28" s="8" t="inlineStr">
         <is>
-          <t>PR #15</t>
+          <t>PR #14</t>
         </is>
       </c>
       <c r="K28" s="8" t="n"/>
@@ -1709,7 +1715,7 @@
     <row r="29">
       <c r="A29" s="16" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="B29" s="16" t="inlineStr">
@@ -1719,12 +1725,12 @@
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>묶음 3b: 근거 자료 검토·결과 이미지</t>
+          <t>묶음 3a: 문구 수정·미확인 정보 보완</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>샘플 근거 자료, 자리표시 이미지</t>
+          <t>결과를 섹션·블록으로</t>
         </is>
       </c>
       <c r="E29" s="16" t="inlineStr">
@@ -1752,7 +1758,7 @@
       </c>
       <c r="J29" s="8" t="inlineStr">
         <is>
-          <t>PR #16</t>
+          <t>PR #15</t>
         </is>
       </c>
       <c r="K29" s="8" t="n"/>
@@ -1760,7 +1766,7 @@
     <row r="30">
       <c r="A30" s="16" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="B30" s="16" t="inlineStr">
@@ -1770,12 +1776,12 @@
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>디자인 피드백 반영</t>
+          <t>묶음 3b: 근거 자료 검토·결과 이미지</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>생성 중·생성 실패 화면, 최신 아님 배너, 이미지 상자, 모드 설명</t>
+          <t>샘플 근거 자료, 자리표시 이미지</t>
         </is>
       </c>
       <c r="E30" s="16" t="inlineStr">
@@ -1803,7 +1809,7 @@
       </c>
       <c r="J30" s="8" t="inlineStr">
         <is>
-          <t>PR #17</t>
+          <t>PR #16</t>
         </is>
       </c>
       <c r="K30" s="8" t="n"/>
@@ -1811,7 +1817,7 @@
     <row r="31">
       <c r="A31" s="16" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="B31" s="16" t="inlineStr">
@@ -1821,12 +1827,12 @@
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>묶음 4: 다음 과제로 이어가기</t>
+          <t>디자인 피드백 반영</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>이전 결과를 다음 과제의 기준으로 가져오기</t>
+          <t>생성 중·생성 실패 화면, 최신 아님 배너, 이미지 상자, 모드 설명</t>
         </is>
       </c>
       <c r="E31" s="16" t="inlineStr">
@@ -1854,98 +1860,94 @@
       </c>
       <c r="J31" s="8" t="inlineStr">
         <is>
+          <t>PR #17</t>
+        </is>
+      </c>
+      <c r="K31" s="8" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="B32" s="16" t="inlineStr">
+        <is>
+          <t>화면 개발(V2)</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>묶음 4: 다음 과제로 이어가기</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>이전 결과를 다음 과제의 기준으로 가져오기</t>
+        </is>
+      </c>
+      <c r="E32" s="16" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F32" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="G32" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="H32" s="16" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I32" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" s="8" t="inlineStr">
+        <is>
           <t>PR #18</t>
         </is>
       </c>
-      <c r="K31" s="8" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="K32" s="8" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>배포</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>배포</t>
         </is>
       </c>
-      <c r="D32" s="5" t="n"/>
-      <c r="E32" s="4" t="n"/>
-      <c r="F32" s="4" t="n"/>
-      <c r="G32" s="4" t="n"/>
-      <c r="H32" s="4" t="n"/>
-      <c r="I32" s="6">
-        <f>IFERROR(AVERAGE(I33:I34),0)</f>
-        <v/>
-      </c>
-      <c r="J32" s="5" t="n"/>
-      <c r="K32" s="5" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="16" t="inlineStr">
-        <is>
-          <t>5.1</t>
-        </is>
-      </c>
-      <c r="B33" s="16" t="inlineStr">
-        <is>
-          <t>배포</t>
-        </is>
-      </c>
-      <c r="C33" s="8" t="inlineStr">
-        <is>
-          <t>프론트 버셀 연결</t>
-        </is>
-      </c>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>main은 정식 주소, PR마다 미리보기 주소</t>
-        </is>
-      </c>
-      <c r="E33" s="16" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F33" s="16" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="G33" s="16" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="H33" s="16" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I33" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="J33" s="8" t="inlineStr">
-        <is>
-          <t>https://ax-platform-5.vercel.app</t>
-        </is>
-      </c>
-      <c r="K33" s="8" t="inlineStr">
-        <is>
-          <t>버셀 Hobby(개인 계정), main 자동 배포</t>
-        </is>
-      </c>
+      <c r="D33" s="5" t="n"/>
+      <c r="E33" s="4" t="n"/>
+      <c r="F33" s="4" t="n"/>
+      <c r="G33" s="4" t="n"/>
+      <c r="H33" s="4" t="n"/>
+      <c r="I33" s="6">
+        <f>IFERROR(AVERAGE(I34:I35),0)</f>
+        <v/>
+      </c>
+      <c r="J33" s="5" t="n"/>
+      <c r="K33" s="5" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="16" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="B34" s="16" t="inlineStr">
@@ -1955,12 +1957,12 @@
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>백엔드 서버 배포(렌더)</t>
+          <t>프론트 버셀 연결</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>저장 디스크 방식 정하기, 프론트와 연결</t>
+          <t>main은 정식 주소, PR마다 미리보기 주소</t>
         </is>
       </c>
       <c r="E34" s="16" t="inlineStr">
@@ -1988,102 +1990,102 @@
       </c>
       <c r="J34" s="8" t="inlineStr">
         <is>
+          <t>https://ax-platform-5.vercel.app</t>
+        </is>
+      </c>
+      <c r="K34" s="8" t="inlineStr">
+        <is>
+          <t>버셀 Hobby(개인 계정), main 자동 배포</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="B35" s="16" t="inlineStr">
+        <is>
+          <t>배포</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>백엔드 서버 배포(렌더)</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>저장 디스크 방식 정하기, 프론트와 연결</t>
+        </is>
+      </c>
+      <c r="E35" s="16" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F35" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="G35" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="H35" s="16" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I35" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" s="8" t="inlineStr">
+        <is>
           <t>https://ax-coaching-api.onrender.com</t>
         </is>
       </c>
-      <c r="K34" s="8" t="inlineStr">
+      <c r="K35" s="8" t="inlineStr">
         <is>
           <t>렌더 Free(개인 계정), Mock·데이터 휘발</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>실제 AI 연결·튜닝</t>
         </is>
       </c>
-      <c r="D35" s="5" t="n"/>
-      <c r="E35" s="4" t="n"/>
-      <c r="F35" s="4" t="n"/>
-      <c r="G35" s="4" t="n"/>
-      <c r="H35" s="4" t="n"/>
-      <c r="I35" s="6">
-        <f>IFERROR(AVERAGE(I36:I38),0)</f>
-        <v/>
-      </c>
-      <c r="J35" s="5" t="n"/>
-      <c r="K35" s="5" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="16" t="inlineStr">
-        <is>
-          <t>6.1</t>
-        </is>
-      </c>
-      <c r="B36" s="16" t="inlineStr">
-        <is>
-          <t>실제 AI 연결</t>
-        </is>
-      </c>
-      <c r="C36" s="8" t="inlineStr">
-        <is>
-          <t>Claude 모델 연결</t>
-        </is>
-      </c>
-      <c r="D36" s="8" t="inlineStr">
-        <is>
-          <t>가짜 모델(Mock) 대신 실제 모델</t>
-        </is>
-      </c>
-      <c r="E36" s="16" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F36" s="16" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="G36" s="16" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="H36" s="16" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I36" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="J36" s="8" t="inlineStr">
-        <is>
-          <t>PR #20</t>
-        </is>
-      </c>
-      <c r="K36" s="8" t="inlineStr">
-        <is>
-          <t>어댑터 준비(기본 Mock). 실제 호출·모델·비용은 인수 기업</t>
-        </is>
-      </c>
+      <c r="D36" s="5" t="n"/>
+      <c r="E36" s="4" t="n"/>
+      <c r="F36" s="4" t="n"/>
+      <c r="G36" s="4" t="n"/>
+      <c r="H36" s="4" t="n"/>
+      <c r="I36" s="6">
+        <f>IFERROR(AVERAGE(I37:I39),0)</f>
+        <v/>
+      </c>
+      <c r="J36" s="5" t="n"/>
+      <c r="K36" s="5" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="16" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="B37" s="16" t="inlineStr">
@@ -2093,12 +2095,12 @@
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>과제별 질문·결과 품질 튜닝</t>
+          <t>Claude 모델 연결</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>준비도 기준·항목 가중치·프롬프트를 시나리오로 측정</t>
+          <t>가짜 모델(Mock) 대신 실제 모델</t>
         </is>
       </c>
       <c r="E37" s="16" t="inlineStr">
@@ -2106,23 +2108,39 @@
           <t>개발</t>
         </is>
       </c>
-      <c r="F37" s="16" t="n"/>
-      <c r="G37" s="16" t="n"/>
+      <c r="F37" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="G37" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
       <c r="H37" s="16" t="inlineStr">
         <is>
-          <t>예정</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="I37" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="8" t="n"/>
-      <c r="K37" s="8" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="J37" s="8" t="inlineStr">
+        <is>
+          <t>PR #20</t>
+        </is>
+      </c>
+      <c r="K37" s="8" t="inlineStr">
+        <is>
+          <t>어댑터 준비(기본 Mock). 실제 호출·모델·비용은 인수 기업</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="16" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="B38" s="16" t="inlineStr">
@@ -2132,12 +2150,12 @@
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>이미지 생성·웹 검색 근거 연결</t>
+          <t>과제별 질문·결과 품질 튜닝</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>지금의 자리표시·샘플 자리에 실제 기능 연결</t>
+          <t>준비도 기준·항목 가중치·프롬프트를 시나리오로 측정</t>
         </is>
       </c>
       <c r="E38" s="16" t="inlineStr">
@@ -2159,76 +2177,76 @@
       <c r="K38" s="8" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="A39" s="16" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="B39" s="16" t="inlineStr">
+        <is>
+          <t>실제 AI 연결</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>이미지 생성·웹 검색 근거 연결</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>지금의 자리표시·샘플 자리에 실제 기능 연결</t>
+        </is>
+      </c>
+      <c r="E39" s="16" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F39" s="16" t="n"/>
+      <c r="G39" s="16" t="n"/>
+      <c r="H39" s="16" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="I39" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="8" t="n"/>
+      <c r="K39" s="8" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>마무리</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>평가·발표</t>
         </is>
       </c>
-      <c r="D39" s="5" t="n"/>
-      <c r="E39" s="4" t="n"/>
-      <c r="F39" s="4" t="n"/>
-      <c r="G39" s="4" t="n"/>
-      <c r="H39" s="4" t="n"/>
-      <c r="I39" s="6">
-        <f>IFERROR(AVERAGE(I40:I41),0)</f>
-        <v/>
-      </c>
-      <c r="J39" s="5" t="n"/>
-      <c r="K39" s="5" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="16" t="inlineStr">
-        <is>
-          <t>7.1</t>
-        </is>
-      </c>
-      <c r="B40" s="16" t="inlineStr">
-        <is>
-          <t>마무리</t>
-        </is>
-      </c>
-      <c r="C40" s="8" t="inlineStr">
-        <is>
-          <t>사용성 확인·평가 지표 측정</t>
-        </is>
-      </c>
-      <c r="D40" s="8" t="inlineStr">
-        <is>
-          <t>필수정보 충족률, 질문 효율, 가정 표시율 등(기획서 14장)</t>
-        </is>
-      </c>
-      <c r="E40" s="16" t="inlineStr">
-        <is>
-          <t>공동</t>
-        </is>
-      </c>
-      <c r="F40" s="16" t="n"/>
-      <c r="G40" s="16" t="n"/>
-      <c r="H40" s="16" t="inlineStr">
-        <is>
-          <t>예정</t>
-        </is>
-      </c>
-      <c r="I40" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="8" t="n"/>
-      <c r="K40" s="8" t="n"/>
+      <c r="D40" s="5" t="n"/>
+      <c r="E40" s="4" t="n"/>
+      <c r="F40" s="4" t="n"/>
+      <c r="G40" s="4" t="n"/>
+      <c r="H40" s="4" t="n"/>
+      <c r="I40" s="6">
+        <f>IFERROR(AVERAGE(I41:I42),0)</f>
+        <v/>
+      </c>
+      <c r="J40" s="5" t="n"/>
+      <c r="K40" s="5" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="16" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="B41" s="16" t="inlineStr">
@@ -2238,10 +2256,14 @@
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>최종 발표 자료</t>
-        </is>
-      </c>
-      <c r="D41" s="8" t="n"/>
+          <t>사용성 확인·평가 지표 측정</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>필수정보 충족률, 질문 효율, 가정 표시율 등(기획서 14장)</t>
+        </is>
+      </c>
       <c r="E41" s="16" t="inlineStr">
         <is>
           <t>공동</t>
@@ -2260,9 +2282,44 @@
       <c r="J41" s="8" t="n"/>
       <c r="K41" s="8" t="n"/>
     </row>
+    <row r="42">
+      <c r="A42" s="16" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="B42" s="16" t="inlineStr">
+        <is>
+          <t>마무리</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>최종 발표 자료</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="n"/>
+      <c r="E42" s="16" t="inlineStr">
+        <is>
+          <t>공동</t>
+        </is>
+      </c>
+      <c r="F42" s="16" t="n"/>
+      <c r="G42" s="16" t="n"/>
+      <c r="H42" s="16" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="I42" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="8" t="n"/>
+      <c r="K42" s="8" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:K41"/>
-  <conditionalFormatting sqref="H5:H41">
+  <autoFilter ref="A4:K42"/>
+  <conditionalFormatting sqref="H5:H42">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"완료"</formula>
     </cfRule>
@@ -2273,7 +2330,7 @@
       <formula>"보류"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I5:I41">
+  <conditionalFormatting sqref="I5:I42">
     <cfRule type="dataBar" priority="4">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -2283,10 +2340,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="H5:H41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"완료,진행 중,예정,보류"</formula1>
     </dataValidation>
-    <dataValidation sqref="E5:E41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"개발,디자인,공동"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2318,6 +2375,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -2357,23 +2415,23 @@
         </is>
       </c>
       <c r="B4" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$41,A4,WBS!$H$5:$H$41,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$42,A4,WBS!$H$5:$H$42,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C4" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$41,A4,WBS!$H$5:$H$41,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$42,A4,WBS!$H$5:$H$42,"완료")</f>
         <v/>
       </c>
       <c r="D4" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$41,A4,WBS!$H$5:$H$41,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$42,A4,WBS!$H$5:$H$42,"진행 중")</f>
         <v/>
       </c>
       <c r="E4" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$41,A4,WBS!$H$5:$H$41,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$42,A4,WBS!$H$5:$H$42,"예정")</f>
         <v/>
       </c>
       <c r="F4" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$41,WBS!$B$5:$B$41,A4,WBS!$H$5:$H$41,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$42,WBS!$B$5:$B$42,A4,WBS!$H$5:$H$42,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2384,23 +2442,23 @@
         </is>
       </c>
       <c r="B5" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$41,A5,WBS!$H$5:$H$41,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$42,A5,WBS!$H$5:$H$42,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C5" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$41,A5,WBS!$H$5:$H$41,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$42,A5,WBS!$H$5:$H$42,"완료")</f>
         <v/>
       </c>
       <c r="D5" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$41,A5,WBS!$H$5:$H$41,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$42,A5,WBS!$H$5:$H$42,"진행 중")</f>
         <v/>
       </c>
       <c r="E5" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$41,A5,WBS!$H$5:$H$41,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$42,A5,WBS!$H$5:$H$42,"예정")</f>
         <v/>
       </c>
       <c r="F5" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$41,WBS!$B$5:$B$41,A5,WBS!$H$5:$H$41,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$42,WBS!$B$5:$B$42,A5,WBS!$H$5:$H$42,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2411,23 +2469,23 @@
         </is>
       </c>
       <c r="B6" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$41,A6,WBS!$H$5:$H$41,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$42,A6,WBS!$H$5:$H$42,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C6" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$41,A6,WBS!$H$5:$H$41,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$42,A6,WBS!$H$5:$H$42,"완료")</f>
         <v/>
       </c>
       <c r="D6" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$41,A6,WBS!$H$5:$H$41,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$42,A6,WBS!$H$5:$H$42,"진행 중")</f>
         <v/>
       </c>
       <c r="E6" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$41,A6,WBS!$H$5:$H$41,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$42,A6,WBS!$H$5:$H$42,"예정")</f>
         <v/>
       </c>
       <c r="F6" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$41,WBS!$B$5:$B$41,A6,WBS!$H$5:$H$41,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$42,WBS!$B$5:$B$42,A6,WBS!$H$5:$H$42,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2438,23 +2496,23 @@
         </is>
       </c>
       <c r="B7" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$41,A7,WBS!$H$5:$H$41,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$42,A7,WBS!$H$5:$H$42,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C7" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$41,A7,WBS!$H$5:$H$41,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$42,A7,WBS!$H$5:$H$42,"완료")</f>
         <v/>
       </c>
       <c r="D7" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$41,A7,WBS!$H$5:$H$41,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$42,A7,WBS!$H$5:$H$42,"진행 중")</f>
         <v/>
       </c>
       <c r="E7" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$41,A7,WBS!$H$5:$H$41,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$42,A7,WBS!$H$5:$H$42,"예정")</f>
         <v/>
       </c>
       <c r="F7" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$41,WBS!$B$5:$B$41,A7,WBS!$H$5:$H$41,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$42,WBS!$B$5:$B$42,A7,WBS!$H$5:$H$42,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2465,23 +2523,23 @@
         </is>
       </c>
       <c r="B8" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$41,A8,WBS!$H$5:$H$41,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$42,A8,WBS!$H$5:$H$42,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C8" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$41,A8,WBS!$H$5:$H$41,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$42,A8,WBS!$H$5:$H$42,"완료")</f>
         <v/>
       </c>
       <c r="D8" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$41,A8,WBS!$H$5:$H$41,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$42,A8,WBS!$H$5:$H$42,"진행 중")</f>
         <v/>
       </c>
       <c r="E8" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$41,A8,WBS!$H$5:$H$41,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$42,A8,WBS!$H$5:$H$42,"예정")</f>
         <v/>
       </c>
       <c r="F8" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$41,WBS!$B$5:$B$41,A8,WBS!$H$5:$H$41,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$42,WBS!$B$5:$B$42,A8,WBS!$H$5:$H$42,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2492,23 +2550,23 @@
         </is>
       </c>
       <c r="B9" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$41,A9,WBS!$H$5:$H$41,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$42,A9,WBS!$H$5:$H$42,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C9" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$41,A9,WBS!$H$5:$H$41,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$42,A9,WBS!$H$5:$H$42,"완료")</f>
         <v/>
       </c>
       <c r="D9" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$41,A9,WBS!$H$5:$H$41,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$42,A9,WBS!$H$5:$H$42,"진행 중")</f>
         <v/>
       </c>
       <c r="E9" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$41,A9,WBS!$H$5:$H$41,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$42,A9,WBS!$H$5:$H$42,"예정")</f>
         <v/>
       </c>
       <c r="F9" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$41,WBS!$B$5:$B$41,A9,WBS!$H$5:$H$41,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$42,WBS!$B$5:$B$42,A9,WBS!$H$5:$H$42,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2519,23 +2577,23 @@
         </is>
       </c>
       <c r="B10" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$41,A10,WBS!$H$5:$H$41,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$42,A10,WBS!$H$5:$H$42,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C10" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$41,A10,WBS!$H$5:$H$41,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$42,A10,WBS!$H$5:$H$42,"완료")</f>
         <v/>
       </c>
       <c r="D10" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$41,A10,WBS!$H$5:$H$41,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$42,A10,WBS!$H$5:$H$42,"진행 중")</f>
         <v/>
       </c>
       <c r="E10" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$41,A10,WBS!$H$5:$H$41,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$42,A10,WBS!$H$5:$H$42,"예정")</f>
         <v/>
       </c>
       <c r="F10" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$41,WBS!$B$5:$B$41,A10,WBS!$H$5:$H$41,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$42,WBS!$B$5:$B$42,A10,WBS!$H$5:$H$42,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2562,10 +2620,11 @@
         <v/>
       </c>
       <c r="F11" s="14">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$41,WBS!$H$5:$H$41,"&lt;&gt;"),0)</f>
-        <v/>
-      </c>
-    </row>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$42,WBS!$H$5:$H$42,"&lt;&gt;"),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>

--- a/docs/WBS.xlsx
+++ b/docs/WBS.xlsx
@@ -11,7 +11,7 @@
     <sheet name="요약" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS'!$A$4:$K$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS'!$A$4:$K$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -98,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -129,6 +129,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -529,7 +535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -645,12 +651,12 @@
       <c r="K5" s="5" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>기획·설계</t>
         </is>
@@ -665,23 +671,23 @@
           <t>과제 4개(사업계획·상품기획·브랜딩·마케팅), 적응형 질문, 사실·가정 분리 원칙</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>공동</t>
         </is>
       </c>
-      <c r="F6" s="16" t="n"/>
-      <c r="G6" s="16" t="inlineStr">
+      <c r="F6" s="20" t="n"/>
+      <c r="G6" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="H6" s="16" t="inlineStr">
+      <c r="H6" s="20" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I6" s="17" t="n">
+      <c r="I6" s="21" t="n">
         <v>1</v>
       </c>
       <c r="J6" s="8" t="inlineStr">
@@ -692,12 +698,12 @@
       <c r="K6" s="8" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>기획·설계</t>
         </is>
@@ -712,27 +718,27 @@
           <t>FastAPI 하네스 구조, API 계약, 테스트 전략</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="H7" s="16" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I7" s="17" t="n">
+      <c r="I7" s="21" t="n">
         <v>1</v>
       </c>
       <c r="J7" s="8" t="inlineStr">
@@ -743,12 +749,12 @@
       <c r="K7" s="8" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>1.3</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>기획·설계</t>
         </is>
@@ -763,27 +769,27 @@
           <t>V2 화면 흐름, 묶음 0~4로 작업 나누기</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H8" s="16" t="inlineStr">
+      <c r="H8" s="20" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I8" s="17" t="n">
+      <c r="I8" s="21" t="n">
         <v>1</v>
       </c>
       <c r="J8" s="8" t="inlineStr">
@@ -794,12 +800,12 @@
       <c r="K8" s="8" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>기획·설계</t>
         </is>
@@ -814,27 +820,27 @@
           <t>지금 상태·다음 할 일·작업 방식·환경 팁, PR마다 갱신</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="G9" s="16" t="inlineStr">
+      <c r="G9" s="20" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="H9" s="16" t="inlineStr">
+      <c r="H9" s="20" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I9" s="17" t="n">
+      <c r="I9" s="21" t="n">
         <v>1</v>
       </c>
       <c r="J9" s="8" t="inlineStr">
@@ -845,12 +851,12 @@
       <c r="K9" s="8" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>기획·설계</t>
         </is>
@@ -865,27 +871,27 @@
           <t>바로 보기 주소, 된 것, 남은 일·맡을 사람·상의할 점</t>
         </is>
       </c>
-      <c r="E10" s="18" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="F10" s="20" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="G10" s="18" t="inlineStr">
+      <c r="G10" s="20" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="H10" s="18" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I10" s="19" t="n">
+      <c r="I10" s="21" t="n">
         <v>1</v>
       </c>
       <c r="J10" s="8" t="inlineStr">
@@ -924,12 +930,12 @@
       <c r="K11" s="5" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="A12" s="20" t="inlineStr">
         <is>
           <t>2.1</t>
         </is>
       </c>
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -944,27 +950,27 @@
           <t>사실·가정·미정 구분, 정보 출처 표시</t>
         </is>
       </c>
-      <c r="E12" s="16" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F12" s="16" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="G12" s="16" t="inlineStr">
+      <c r="G12" s="20" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H12" s="16" t="inlineStr">
+      <c r="H12" s="20" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I12" s="17" t="n">
+      <c r="I12" s="21" t="n">
         <v>1</v>
       </c>
       <c r="J12" s="8" t="inlineStr">
@@ -975,12 +981,12 @@
       <c r="K12" s="8" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="inlineStr">
+      <c r="A13" s="20" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -995,27 +1001,27 @@
           <t>비용 없이 개발·테스트하는 가짜 모델</t>
         </is>
       </c>
-      <c r="E13" s="16" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F13" s="16" t="inlineStr">
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="G13" s="16" t="inlineStr">
+      <c r="G13" s="20" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H13" s="16" t="inlineStr">
+      <c r="H13" s="20" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I13" s="17" t="n">
+      <c r="I13" s="21" t="n">
         <v>1</v>
       </c>
       <c r="J13" s="8" t="inlineStr">
@@ -1026,12 +1032,12 @@
       <c r="K13" s="8" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="inlineStr">
+      <c r="A14" s="20" t="inlineStr">
         <is>
           <t>2.3</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1046,27 +1052,27 @@
           <t>과제별 질문 정책(policy.yaml), 단계별 프롬프트</t>
         </is>
       </c>
-      <c r="E14" s="16" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F14" s="16" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G14" s="16" t="inlineStr">
+      <c r="G14" s="20" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H14" s="16" t="inlineStr">
+      <c r="H14" s="20" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I14" s="17" t="n">
+      <c r="I14" s="21" t="n">
         <v>1</v>
       </c>
       <c r="J14" s="8" t="inlineStr">
@@ -1077,12 +1083,12 @@
       <c r="K14" s="8" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="inlineStr">
+      <c r="A15" s="20" t="inlineStr">
         <is>
           <t>2.4</t>
         </is>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1097,27 +1103,27 @@
           <t>모드별 질문 상한, '다른 예시 보기' 단계</t>
         </is>
       </c>
-      <c r="E15" s="16" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F15" s="16" t="inlineStr">
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G15" s="16" t="inlineStr">
+      <c r="G15" s="20" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H15" s="16" t="inlineStr">
+      <c r="H15" s="20" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I15" s="17" t="n">
+      <c r="I15" s="21" t="n">
         <v>1</v>
       </c>
       <c r="J15" s="8" t="inlineStr">
@@ -1128,12 +1134,12 @@
       <c r="K15" s="8" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="16" t="inlineStr">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
       </c>
-      <c r="B16" s="16" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1144,27 +1150,27 @@
         </is>
       </c>
       <c r="D16" s="8" t="n"/>
-      <c r="E16" s="16" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F16" s="16" t="inlineStr">
+      <c r="F16" s="20" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G16" s="16" t="inlineStr">
+      <c r="G16" s="20" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H16" s="16" t="inlineStr">
+      <c r="H16" s="20" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I16" s="17" t="n">
+      <c r="I16" s="21" t="n">
         <v>1</v>
       </c>
       <c r="J16" s="8" t="inlineStr">
@@ -1175,12 +1181,12 @@
       <c r="K16" s="8" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="16" t="inlineStr">
+      <c r="A17" s="20" t="inlineStr">
         <is>
           <t>2.6</t>
         </is>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1195,27 +1201,27 @@
           <t>과제별 정책·프롬프트·검증 규칙</t>
         </is>
       </c>
-      <c r="E17" s="16" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F17" s="16" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G17" s="16" t="inlineStr">
+      <c r="G17" s="20" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H17" s="16" t="inlineStr">
+      <c r="H17" s="20" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I17" s="17" t="n">
+      <c r="I17" s="21" t="n">
         <v>1</v>
       </c>
       <c r="J17" s="8" t="inlineStr">
@@ -1226,12 +1232,12 @@
       <c r="K17" s="8" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="16" t="inlineStr">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>2.7</t>
         </is>
       </c>
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1246,27 +1252,27 @@
           <t>한국어 오류 문구, API 문서</t>
         </is>
       </c>
-      <c r="E18" s="16" t="inlineStr">
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F18" s="16" t="inlineStr">
+      <c r="F18" s="20" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G18" s="16" t="inlineStr">
+      <c r="G18" s="20" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H18" s="16" t="inlineStr">
+      <c r="H18" s="20" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I18" s="17" t="n">
+      <c r="I18" s="21" t="n">
         <v>1</v>
       </c>
       <c r="J18" s="8" t="inlineStr">
@@ -1277,12 +1283,12 @@
       <c r="K18" s="8" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>2.8</t>
         </is>
       </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1297,27 +1303,27 @@
           <t>API에 맞춘 최소 화면, 개발 안내(CLAUDE.md)</t>
         </is>
       </c>
-      <c r="E19" s="16" t="inlineStr">
+      <c r="E19" s="20" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F19" s="16" t="inlineStr">
+      <c r="F19" s="20" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G19" s="16" t="inlineStr">
+      <c r="G19" s="20" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H19" s="16" t="inlineStr">
+      <c r="H19" s="20" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I19" s="17" t="n">
+      <c r="I19" s="21" t="n">
         <v>1</v>
       </c>
       <c r="J19" s="8" t="inlineStr">
@@ -1356,12 +1362,12 @@
       <c r="K20" s="5" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="16" t="inlineStr">
+      <c r="A21" s="20" t="inlineStr">
         <is>
           <t>3.1</t>
         </is>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
@@ -1376,23 +1382,23 @@
           <t>전체 화면 흐름 HTML 프로토타입</t>
         </is>
       </c>
-      <c r="E21" s="16" t="inlineStr">
+      <c r="E21" s="20" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
       </c>
-      <c r="F21" s="16" t="n"/>
-      <c r="G21" s="16" t="inlineStr">
+      <c r="F21" s="20" t="n"/>
+      <c r="G21" s="20" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H21" s="16" t="inlineStr">
+      <c r="H21" s="20" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I21" s="17" t="n">
+      <c r="I21" s="21" t="n">
         <v>1</v>
       </c>
       <c r="J21" s="8" t="inlineStr">
@@ -1403,12 +1409,12 @@
       <c r="K21" s="8" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="16" t="inlineStr">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
       </c>
-      <c r="B22" s="16" t="inlineStr">
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
@@ -1423,27 +1429,27 @@
           <t>모든 질문에 '다른 예시 보기', 모드 설명, 이미지 블록, 생성 중·실패·최신 아님 상태</t>
         </is>
       </c>
-      <c r="E22" s="16" t="inlineStr">
+      <c r="E22" s="20" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
       </c>
-      <c r="F22" s="16" t="inlineStr">
+      <c r="F22" s="20" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G22" s="16" t="inlineStr">
+      <c r="G22" s="20" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H22" s="16" t="inlineStr">
+      <c r="H22" s="20" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I22" s="17" t="n">
+      <c r="I22" s="21" t="n">
         <v>1</v>
       </c>
       <c r="J22" s="8" t="inlineStr">
@@ -1454,12 +1460,12 @@
       <c r="K22" s="8" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="16" t="inlineStr">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
       </c>
-      <c r="B23" s="16" t="inlineStr">
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
@@ -1474,31 +1480,31 @@
           <t>반응형 자동 배치 확인</t>
         </is>
       </c>
-      <c r="E23" s="16" t="inlineStr">
+      <c r="E23" s="20" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
       </c>
-      <c r="F23" s="16" t="n"/>
-      <c r="G23" s="16" t="n"/>
-      <c r="H23" s="16" t="inlineStr">
+      <c r="F23" s="20" t="n"/>
+      <c r="G23" s="20" t="n"/>
+      <c r="H23" s="20" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="I23" s="17" t="n">
+      <c r="I23" s="21" t="n">
         <v>0</v>
       </c>
       <c r="J23" s="8" t="n"/>
       <c r="K23" s="8" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="16" t="inlineStr">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>3.4</t>
         </is>
       </c>
-      <c r="B24" s="16" t="inlineStr">
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
@@ -1513,19 +1519,19 @@
           <t>/preview 화면을 html.to.design으로 가져와 수정</t>
         </is>
       </c>
-      <c r="E24" s="16" t="inlineStr">
+      <c r="E24" s="20" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
       </c>
-      <c r="F24" s="16" t="n"/>
-      <c r="G24" s="16" t="n"/>
-      <c r="H24" s="16" t="inlineStr">
+      <c r="F24" s="20" t="n"/>
+      <c r="G24" s="20" t="n"/>
+      <c r="H24" s="20" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="I24" s="17" t="n">
+      <c r="I24" s="21" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="8" t="n"/>
@@ -1560,12 +1566,12 @@
       <c r="K25" s="5" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="16" t="inlineStr">
+      <c r="A26" s="20" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
       </c>
-      <c r="B26" s="16" t="inlineStr">
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1580,27 +1586,27 @@
           <t>버셀 배포 설정 포함</t>
         </is>
       </c>
-      <c r="E26" s="16" t="inlineStr">
+      <c r="E26" s="20" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F26" s="16" t="inlineStr">
+      <c r="F26" s="20" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G26" s="16" t="inlineStr">
+      <c r="G26" s="20" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H26" s="16" t="inlineStr">
+      <c r="H26" s="20" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I26" s="17" t="n">
+      <c r="I26" s="21" t="n">
         <v>1</v>
       </c>
       <c r="J26" s="8" t="inlineStr">
@@ -1611,12 +1617,12 @@
       <c r="K26" s="8" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="16" t="inlineStr">
+      <c r="A27" s="20" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
       </c>
-      <c r="B27" s="16" t="inlineStr">
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1631,27 +1637,27 @@
           <t>답변 종류, 흐름 패널, 익명 사용자</t>
         </is>
       </c>
-      <c r="E27" s="16" t="inlineStr">
+      <c r="E27" s="20" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F27" s="16" t="inlineStr">
+      <c r="F27" s="20" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G27" s="16" t="inlineStr">
+      <c r="G27" s="20" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H27" s="16" t="inlineStr">
+      <c r="H27" s="20" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I27" s="17" t="n">
+      <c r="I27" s="21" t="n">
         <v>1</v>
       </c>
       <c r="J27" s="8" t="inlineStr">
@@ -1662,12 +1668,12 @@
       <c r="K27" s="8" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="16" t="inlineStr">
+      <c r="A28" s="20" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
       </c>
-      <c r="B28" s="16" t="inlineStr">
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1682,27 +1688,27 @@
           <t>서버 저장(SQLite), 문서 내려받기</t>
         </is>
       </c>
-      <c r="E28" s="16" t="inlineStr">
+      <c r="E28" s="20" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F28" s="16" t="inlineStr">
+      <c r="F28" s="20" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G28" s="16" t="inlineStr">
+      <c r="G28" s="20" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H28" s="16" t="inlineStr">
+      <c r="H28" s="20" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I28" s="17" t="n">
+      <c r="I28" s="21" t="n">
         <v>1</v>
       </c>
       <c r="J28" s="8" t="inlineStr">
@@ -1713,12 +1719,12 @@
       <c r="K28" s="8" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="16" t="inlineStr">
+      <c r="A29" s="20" t="inlineStr">
         <is>
           <t>4.4</t>
         </is>
       </c>
-      <c r="B29" s="16" t="inlineStr">
+      <c r="B29" s="20" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1733,27 +1739,27 @@
           <t>결과를 섹션·블록으로</t>
         </is>
       </c>
-      <c r="E29" s="16" t="inlineStr">
+      <c r="E29" s="20" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F29" s="16" t="inlineStr">
+      <c r="F29" s="20" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G29" s="16" t="inlineStr">
+      <c r="G29" s="20" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H29" s="16" t="inlineStr">
+      <c r="H29" s="20" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I29" s="17" t="n">
+      <c r="I29" s="21" t="n">
         <v>1</v>
       </c>
       <c r="J29" s="8" t="inlineStr">
@@ -1764,12 +1770,12 @@
       <c r="K29" s="8" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="16" t="inlineStr">
+      <c r="A30" s="20" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
       </c>
-      <c r="B30" s="16" t="inlineStr">
+      <c r="B30" s="20" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1784,27 +1790,27 @@
           <t>샘플 근거 자료, 자리표시 이미지</t>
         </is>
       </c>
-      <c r="E30" s="16" t="inlineStr">
+      <c r="E30" s="20" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F30" s="16" t="inlineStr">
+      <c r="F30" s="20" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G30" s="16" t="inlineStr">
+      <c r="G30" s="20" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H30" s="16" t="inlineStr">
+      <c r="H30" s="20" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I30" s="17" t="n">
+      <c r="I30" s="21" t="n">
         <v>1</v>
       </c>
       <c r="J30" s="8" t="inlineStr">
@@ -1815,12 +1821,12 @@
       <c r="K30" s="8" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="16" t="inlineStr">
+      <c r="A31" s="20" t="inlineStr">
         <is>
           <t>4.6</t>
         </is>
       </c>
-      <c r="B31" s="16" t="inlineStr">
+      <c r="B31" s="20" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1835,27 +1841,27 @@
           <t>생성 중·생성 실패 화면, 최신 아님 배너, 이미지 상자, 모드 설명</t>
         </is>
       </c>
-      <c r="E31" s="16" t="inlineStr">
+      <c r="E31" s="20" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F31" s="16" t="inlineStr">
+      <c r="F31" s="20" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G31" s="16" t="inlineStr">
+      <c r="G31" s="20" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H31" s="16" t="inlineStr">
+      <c r="H31" s="20" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I31" s="17" t="n">
+      <c r="I31" s="21" t="n">
         <v>1</v>
       </c>
       <c r="J31" s="8" t="inlineStr">
@@ -1866,12 +1872,12 @@
       <c r="K31" s="8" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="16" t="inlineStr">
+      <c r="A32" s="20" t="inlineStr">
         <is>
           <t>4.7</t>
         </is>
       </c>
-      <c r="B32" s="16" t="inlineStr">
+      <c r="B32" s="20" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1886,27 +1892,27 @@
           <t>이전 결과를 다음 과제의 기준으로 가져오기</t>
         </is>
       </c>
-      <c r="E32" s="16" t="inlineStr">
+      <c r="E32" s="20" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F32" s="16" t="inlineStr">
+      <c r="F32" s="20" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G32" s="16" t="inlineStr">
+      <c r="G32" s="20" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H32" s="16" t="inlineStr">
+      <c r="H32" s="20" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I32" s="17" t="n">
+      <c r="I32" s="21" t="n">
         <v>1</v>
       </c>
       <c r="J32" s="8" t="inlineStr">
@@ -1945,12 +1951,12 @@
       <c r="K33" s="5" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="16" t="inlineStr">
+      <c r="A34" s="20" t="inlineStr">
         <is>
           <t>5.1</t>
         </is>
       </c>
-      <c r="B34" s="16" t="inlineStr">
+      <c r="B34" s="20" t="inlineStr">
         <is>
           <t>배포</t>
         </is>
@@ -1965,27 +1971,27 @@
           <t>main은 정식 주소, PR마다 미리보기 주소</t>
         </is>
       </c>
-      <c r="E34" s="16" t="inlineStr">
+      <c r="E34" s="20" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F34" s="16" t="inlineStr">
+      <c r="F34" s="20" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="G34" s="16" t="inlineStr">
+      <c r="G34" s="20" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="H34" s="16" t="inlineStr">
+      <c r="H34" s="20" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I34" s="17" t="n">
+      <c r="I34" s="21" t="n">
         <v>1</v>
       </c>
       <c r="J34" s="8" t="inlineStr">
@@ -2000,12 +2006,12 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="16" t="inlineStr">
+      <c r="A35" s="20" t="inlineStr">
         <is>
           <t>5.2</t>
         </is>
       </c>
-      <c r="B35" s="16" t="inlineStr">
+      <c r="B35" s="20" t="inlineStr">
         <is>
           <t>배포</t>
         </is>
@@ -2020,27 +2026,27 @@
           <t>저장 디스크 방식 정하기, 프론트와 연결</t>
         </is>
       </c>
-      <c r="E35" s="16" t="inlineStr">
+      <c r="E35" s="20" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F35" s="16" t="inlineStr">
+      <c r="F35" s="20" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="G35" s="16" t="inlineStr">
+      <c r="G35" s="20" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="H35" s="16" t="inlineStr">
+      <c r="H35" s="20" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I35" s="17" t="n">
+      <c r="I35" s="21" t="n">
         <v>1</v>
       </c>
       <c r="J35" s="8" t="inlineStr">
@@ -2076,19 +2082,19 @@
       <c r="G36" s="4" t="n"/>
       <c r="H36" s="4" t="n"/>
       <c r="I36" s="6">
-        <f>IFERROR(AVERAGE(I37:I39),0)</f>
+        <f>IFERROR(AVERAGE(I37:I40),0)</f>
         <v/>
       </c>
       <c r="J36" s="5" t="n"/>
       <c r="K36" s="5" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="16" t="inlineStr">
+      <c r="A37" s="20" t="inlineStr">
         <is>
           <t>6.1</t>
         </is>
       </c>
-      <c r="B37" s="16" t="inlineStr">
+      <c r="B37" s="20" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
@@ -2103,27 +2109,27 @@
           <t>가짜 모델(Mock) 대신 실제 모델</t>
         </is>
       </c>
-      <c r="E37" s="16" t="inlineStr">
+      <c r="E37" s="20" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F37" s="16" t="inlineStr">
+      <c r="F37" s="20" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="G37" s="16" t="inlineStr">
+      <c r="G37" s="20" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="H37" s="16" t="inlineStr">
+      <c r="H37" s="20" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I37" s="17" t="n">
+      <c r="I37" s="21" t="n">
         <v>1</v>
       </c>
       <c r="J37" s="8" t="inlineStr">
@@ -2138,12 +2144,12 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="16" t="inlineStr">
+      <c r="A38" s="20" t="inlineStr">
         <is>
           <t>6.2</t>
         </is>
       </c>
-      <c r="B38" s="16" t="inlineStr">
+      <c r="B38" s="20" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
@@ -2158,31 +2164,31 @@
           <t>준비도 기준·항목 가중치·프롬프트를 시나리오로 측정</t>
         </is>
       </c>
-      <c r="E38" s="16" t="inlineStr">
+      <c r="E38" s="20" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F38" s="16" t="n"/>
-      <c r="G38" s="16" t="n"/>
-      <c r="H38" s="16" t="inlineStr">
+      <c r="F38" s="20" t="n"/>
+      <c r="G38" s="20" t="n"/>
+      <c r="H38" s="20" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="I38" s="17" t="n">
+      <c r="I38" s="21" t="n">
         <v>0</v>
       </c>
       <c r="J38" s="8" t="n"/>
       <c r="K38" s="8" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="16" t="inlineStr">
+      <c r="A39" s="20" t="inlineStr">
         <is>
           <t>6.3</t>
         </is>
       </c>
-      <c r="B39" s="16" t="inlineStr">
+      <c r="B39" s="20" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
@@ -2197,129 +2203,176 @@
           <t>지금의 자리표시·샘플 자리에 실제 기능 연결</t>
         </is>
       </c>
-      <c r="E39" s="16" t="inlineStr">
+      <c r="E39" s="20" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F39" s="16" t="n"/>
-      <c r="G39" s="16" t="n"/>
-      <c r="H39" s="16" t="inlineStr">
+      <c r="F39" s="20" t="n"/>
+      <c r="G39" s="20" t="n"/>
+      <c r="H39" s="20" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="I39" s="17" t="n">
+      <c r="I39" s="21" t="n">
         <v>0</v>
       </c>
       <c r="J39" s="8" t="n"/>
       <c r="K39" s="8" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="A40" s="20" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>실제 AI 연결</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>외부 전송 보호(개인정보 가림·비공개·동의)</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="n"/>
+      <c r="E40" s="20" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F40" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="G40" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="H40" s="20" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I40" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" s="8" t="inlineStr">
+        <is>
+          <t>PR #24</t>
+        </is>
+      </c>
+      <c r="K40" s="8" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>마무리</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>평가·발표</t>
         </is>
       </c>
-      <c r="D40" s="5" t="n"/>
-      <c r="E40" s="4" t="n"/>
-      <c r="F40" s="4" t="n"/>
-      <c r="G40" s="4" t="n"/>
-      <c r="H40" s="4" t="n"/>
-      <c r="I40" s="6">
-        <f>IFERROR(AVERAGE(I41:I42),0)</f>
-        <v/>
-      </c>
-      <c r="J40" s="5" t="n"/>
-      <c r="K40" s="5" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="16" t="inlineStr">
+      <c r="D41" s="5" t="n"/>
+      <c r="E41" s="4" t="n"/>
+      <c r="F41" s="4" t="n"/>
+      <c r="G41" s="4" t="n"/>
+      <c r="H41" s="4" t="n"/>
+      <c r="I41" s="6">
+        <f>IFERROR(AVERAGE(I42:I43),0)</f>
+        <v/>
+      </c>
+      <c r="J41" s="5" t="n"/>
+      <c r="K41" s="5" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="20" t="inlineStr">
         <is>
           <t>7.1</t>
         </is>
       </c>
-      <c r="B41" s="16" t="inlineStr">
+      <c r="B42" s="20" t="inlineStr">
         <is>
           <t>마무리</t>
         </is>
       </c>
-      <c r="C41" s="8" t="inlineStr">
+      <c r="C42" s="8" t="inlineStr">
         <is>
           <t>사용성 확인·평가 지표 측정</t>
         </is>
       </c>
-      <c r="D41" s="8" t="inlineStr">
+      <c r="D42" s="8" t="inlineStr">
         <is>
           <t>필수정보 충족률, 질문 효율, 가정 표시율 등(기획서 14장)</t>
         </is>
       </c>
-      <c r="E41" s="16" t="inlineStr">
+      <c r="E42" s="20" t="inlineStr">
         <is>
           <t>공동</t>
         </is>
       </c>
-      <c r="F41" s="16" t="n"/>
-      <c r="G41" s="16" t="n"/>
-      <c r="H41" s="16" t="inlineStr">
+      <c r="F42" s="20" t="n"/>
+      <c r="G42" s="20" t="n"/>
+      <c r="H42" s="20" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="I41" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="8" t="n"/>
-      <c r="K41" s="8" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="16" t="inlineStr">
-        <is>
-          <t>7.2</t>
-        </is>
-      </c>
-      <c r="B42" s="16" t="inlineStr">
-        <is>
-          <t>마무리</t>
-        </is>
-      </c>
-      <c r="C42" s="8" t="inlineStr">
-        <is>
-          <t>최종 발표 자료</t>
-        </is>
-      </c>
-      <c r="D42" s="8" t="n"/>
-      <c r="E42" s="16" t="inlineStr">
-        <is>
-          <t>공동</t>
-        </is>
-      </c>
-      <c r="F42" s="16" t="n"/>
-      <c r="G42" s="16" t="n"/>
-      <c r="H42" s="16" t="inlineStr">
-        <is>
-          <t>예정</t>
-        </is>
-      </c>
-      <c r="I42" s="17" t="n">
+      <c r="I42" s="21" t="n">
         <v>0</v>
       </c>
       <c r="J42" s="8" t="n"/>
       <c r="K42" s="8" t="n"/>
     </row>
+    <row r="43">
+      <c r="A43" s="20" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="B43" s="20" t="inlineStr">
+        <is>
+          <t>마무리</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>최종 발표 자료</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="n"/>
+      <c r="E43" s="20" t="inlineStr">
+        <is>
+          <t>공동</t>
+        </is>
+      </c>
+      <c r="F43" s="20" t="n"/>
+      <c r="G43" s="20" t="n"/>
+      <c r="H43" s="20" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="I43" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="8" t="n"/>
+      <c r="K43" s="8" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:K42"/>
-  <conditionalFormatting sqref="H5:H42">
+  <autoFilter ref="A4:K43"/>
+  <conditionalFormatting sqref="H5:H43">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"완료"</formula>
     </cfRule>
@@ -2330,7 +2383,7 @@
       <formula>"보류"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I5:I42">
+  <conditionalFormatting sqref="I5:I43">
     <cfRule type="dataBar" priority="4">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -2340,10 +2393,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="H5:H42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"완료,진행 중,예정,보류"</formula1>
     </dataValidation>
-    <dataValidation sqref="E5:E42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"개발,디자인,공동"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2375,7 +2428,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -2415,23 +2467,23 @@
         </is>
       </c>
       <c r="B4" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$42,A4,WBS!$H$5:$H$42,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$43,A4,WBS!$H$5:$H$43,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C4" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$42,A4,WBS!$H$5:$H$42,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$43,A4,WBS!$H$5:$H$43,"완료")</f>
         <v/>
       </c>
       <c r="D4" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$42,A4,WBS!$H$5:$H$42,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$43,A4,WBS!$H$5:$H$43,"진행 중")</f>
         <v/>
       </c>
       <c r="E4" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$42,A4,WBS!$H$5:$H$42,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$43,A4,WBS!$H$5:$H$43,"예정")</f>
         <v/>
       </c>
       <c r="F4" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$42,WBS!$B$5:$B$42,A4,WBS!$H$5:$H$42,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$43,WBS!$B$5:$B$43,A4,WBS!$H$5:$H$43,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2442,23 +2494,23 @@
         </is>
       </c>
       <c r="B5" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$42,A5,WBS!$H$5:$H$42,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$43,A5,WBS!$H$5:$H$43,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C5" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$42,A5,WBS!$H$5:$H$42,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$43,A5,WBS!$H$5:$H$43,"완료")</f>
         <v/>
       </c>
       <c r="D5" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$42,A5,WBS!$H$5:$H$42,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$43,A5,WBS!$H$5:$H$43,"진행 중")</f>
         <v/>
       </c>
       <c r="E5" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$42,A5,WBS!$H$5:$H$42,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$43,A5,WBS!$H$5:$H$43,"예정")</f>
         <v/>
       </c>
       <c r="F5" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$42,WBS!$B$5:$B$42,A5,WBS!$H$5:$H$42,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$43,WBS!$B$5:$B$43,A5,WBS!$H$5:$H$43,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2469,23 +2521,23 @@
         </is>
       </c>
       <c r="B6" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$42,A6,WBS!$H$5:$H$42,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$43,A6,WBS!$H$5:$H$43,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C6" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$42,A6,WBS!$H$5:$H$42,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$43,A6,WBS!$H$5:$H$43,"완료")</f>
         <v/>
       </c>
       <c r="D6" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$42,A6,WBS!$H$5:$H$42,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$43,A6,WBS!$H$5:$H$43,"진행 중")</f>
         <v/>
       </c>
       <c r="E6" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$42,A6,WBS!$H$5:$H$42,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$43,A6,WBS!$H$5:$H$43,"예정")</f>
         <v/>
       </c>
       <c r="F6" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$42,WBS!$B$5:$B$42,A6,WBS!$H$5:$H$42,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$43,WBS!$B$5:$B$43,A6,WBS!$H$5:$H$43,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2496,23 +2548,23 @@
         </is>
       </c>
       <c r="B7" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$42,A7,WBS!$H$5:$H$42,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$43,A7,WBS!$H$5:$H$43,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C7" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$42,A7,WBS!$H$5:$H$42,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$43,A7,WBS!$H$5:$H$43,"완료")</f>
         <v/>
       </c>
       <c r="D7" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$42,A7,WBS!$H$5:$H$42,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$43,A7,WBS!$H$5:$H$43,"진행 중")</f>
         <v/>
       </c>
       <c r="E7" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$42,A7,WBS!$H$5:$H$42,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$43,A7,WBS!$H$5:$H$43,"예정")</f>
         <v/>
       </c>
       <c r="F7" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$42,WBS!$B$5:$B$42,A7,WBS!$H$5:$H$42,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$43,WBS!$B$5:$B$43,A7,WBS!$H$5:$H$43,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2523,23 +2575,23 @@
         </is>
       </c>
       <c r="B8" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$42,A8,WBS!$H$5:$H$42,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$43,A8,WBS!$H$5:$H$43,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C8" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$42,A8,WBS!$H$5:$H$42,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$43,A8,WBS!$H$5:$H$43,"완료")</f>
         <v/>
       </c>
       <c r="D8" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$42,A8,WBS!$H$5:$H$42,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$43,A8,WBS!$H$5:$H$43,"진행 중")</f>
         <v/>
       </c>
       <c r="E8" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$42,A8,WBS!$H$5:$H$42,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$43,A8,WBS!$H$5:$H$43,"예정")</f>
         <v/>
       </c>
       <c r="F8" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$42,WBS!$B$5:$B$42,A8,WBS!$H$5:$H$42,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$43,WBS!$B$5:$B$43,A8,WBS!$H$5:$H$43,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2550,23 +2602,23 @@
         </is>
       </c>
       <c r="B9" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$42,A9,WBS!$H$5:$H$42,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$43,A9,WBS!$H$5:$H$43,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C9" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$42,A9,WBS!$H$5:$H$42,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$43,A9,WBS!$H$5:$H$43,"완료")</f>
         <v/>
       </c>
       <c r="D9" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$42,A9,WBS!$H$5:$H$42,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$43,A9,WBS!$H$5:$H$43,"진행 중")</f>
         <v/>
       </c>
       <c r="E9" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$42,A9,WBS!$H$5:$H$42,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$43,A9,WBS!$H$5:$H$43,"예정")</f>
         <v/>
       </c>
       <c r="F9" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$42,WBS!$B$5:$B$42,A9,WBS!$H$5:$H$42,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$43,WBS!$B$5:$B$43,A9,WBS!$H$5:$H$43,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2577,23 +2629,23 @@
         </is>
       </c>
       <c r="B10" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$42,A10,WBS!$H$5:$H$42,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$43,A10,WBS!$H$5:$H$43,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C10" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$42,A10,WBS!$H$5:$H$42,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$43,A10,WBS!$H$5:$H$43,"완료")</f>
         <v/>
       </c>
       <c r="D10" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$42,A10,WBS!$H$5:$H$42,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$43,A10,WBS!$H$5:$H$43,"진행 중")</f>
         <v/>
       </c>
       <c r="E10" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$42,A10,WBS!$H$5:$H$42,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$43,A10,WBS!$H$5:$H$43,"예정")</f>
         <v/>
       </c>
       <c r="F10" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$42,WBS!$B$5:$B$42,A10,WBS!$H$5:$H$42,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$43,WBS!$B$5:$B$43,A10,WBS!$H$5:$H$43,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2620,11 +2672,10 @@
         <v/>
       </c>
       <c r="F11" s="14">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$42,WBS!$H$5:$H$42,"&lt;&gt;"),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12"/>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$43,WBS!$H$5:$H$43,"&lt;&gt;"),0)</f>
+        <v/>
+      </c>
+    </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>

--- a/docs/WBS.xlsx
+++ b/docs/WBS.xlsx
@@ -11,7 +11,7 @@
     <sheet name="요약" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS'!$A$4:$K$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS'!$A$4:$K$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -98,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -129,6 +129,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -535,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K43"/>
+  <dimension ref="A1:K44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -561,7 +567,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>기준일 2026-10-18 · 상태·진척률·날짜는 직접 고쳐 쓰세요. 단계 행과 '요약' 시트는 자동으로 다시 계산됩니다.</t>
+          <t>기준일 2026-10-19 · 상태·진척률·날짜는 직접 고쳐 쓰세요. 단계 행과 '요약' 시트는 자동으로 다시 계산됩니다.</t>
         </is>
       </c>
     </row>
@@ -651,12 +657,12 @@
       <c r="K5" s="5" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="inlineStr">
+      <c r="A6" s="22" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>기획·설계</t>
         </is>
@@ -671,23 +677,23 @@
           <t>과제 4개(사업계획·상품기획·브랜딩·마케팅), 적응형 질문, 사실·가정 분리 원칙</t>
         </is>
       </c>
-      <c r="E6" s="20" t="inlineStr">
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t>공동</t>
         </is>
       </c>
-      <c r="F6" s="20" t="n"/>
-      <c r="G6" s="20" t="inlineStr">
+      <c r="F6" s="22" t="n"/>
+      <c r="G6" s="22" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="H6" s="20" t="inlineStr">
+      <c r="H6" s="22" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I6" s="21" t="n">
+      <c r="I6" s="23" t="n">
         <v>1</v>
       </c>
       <c r="J6" s="8" t="inlineStr">
@@ -698,12 +704,12 @@
       <c r="K6" s="8" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="A7" s="22" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>기획·설계</t>
         </is>
@@ -718,27 +724,27 @@
           <t>FastAPI 하네스 구조, API 계약, 테스트 전략</t>
         </is>
       </c>
-      <c r="E7" s="20" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F7" s="20" t="inlineStr">
+      <c r="F7" s="22" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="G7" s="20" t="inlineStr">
+      <c r="G7" s="22" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="H7" s="20" t="inlineStr">
+      <c r="H7" s="22" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I7" s="21" t="n">
+      <c r="I7" s="23" t="n">
         <v>1</v>
       </c>
       <c r="J7" s="8" t="inlineStr">
@@ -749,12 +755,12 @@
       <c r="K7" s="8" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="22" t="inlineStr">
         <is>
           <t>1.3</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>기획·설계</t>
         </is>
@@ -769,27 +775,27 @@
           <t>V2 화면 흐름, 묶음 0~4로 작업 나누기</t>
         </is>
       </c>
-      <c r="E8" s="20" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F8" s="20" t="inlineStr">
+      <c r="F8" s="22" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G8" s="20" t="inlineStr">
+      <c r="G8" s="22" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H8" s="20" t="inlineStr">
+      <c r="H8" s="22" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I8" s="21" t="n">
+      <c r="I8" s="23" t="n">
         <v>1</v>
       </c>
       <c r="J8" s="8" t="inlineStr">
@@ -800,12 +806,12 @@
       <c r="K8" s="8" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="20" t="inlineStr">
+      <c r="A9" s="22" t="inlineStr">
         <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>기획·설계</t>
         </is>
@@ -820,27 +826,27 @@
           <t>지금 상태·다음 할 일·작업 방식·환경 팁, PR마다 갱신</t>
         </is>
       </c>
-      <c r="E9" s="20" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F9" s="20" t="inlineStr">
+      <c r="F9" s="22" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="G9" s="20" t="inlineStr">
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="H9" s="20" t="inlineStr">
+      <c r="H9" s="22" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I9" s="21" t="n">
+      <c r="I9" s="23" t="n">
         <v>1</v>
       </c>
       <c r="J9" s="8" t="inlineStr">
@@ -851,12 +857,12 @@
       <c r="K9" s="8" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="inlineStr">
+      <c r="A10" s="22" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>기획·설계</t>
         </is>
@@ -871,27 +877,27 @@
           <t>바로 보기 주소, 된 것, 남은 일·맡을 사람·상의할 점</t>
         </is>
       </c>
-      <c r="E10" s="20" t="inlineStr">
+      <c r="E10" s="22" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F10" s="20" t="inlineStr">
+      <c r="F10" s="22" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="G10" s="20" t="inlineStr">
+      <c r="G10" s="22" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="H10" s="20" t="inlineStr">
+      <c r="H10" s="22" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I10" s="21" t="n">
+      <c r="I10" s="23" t="n">
         <v>1</v>
       </c>
       <c r="J10" s="8" t="inlineStr">
@@ -930,12 +936,12 @@
       <c r="K11" s="5" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="inlineStr">
+      <c r="A12" s="22" t="inlineStr">
         <is>
           <t>2.1</t>
         </is>
       </c>
-      <c r="B12" s="20" t="inlineStr">
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -950,27 +956,27 @@
           <t>사실·가정·미정 구분, 정보 출처 표시</t>
         </is>
       </c>
-      <c r="E12" s="20" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F12" s="20" t="inlineStr">
+      <c r="F12" s="22" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="G12" s="20" t="inlineStr">
+      <c r="G12" s="22" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H12" s="20" t="inlineStr">
+      <c r="H12" s="22" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I12" s="21" t="n">
+      <c r="I12" s="23" t="n">
         <v>1</v>
       </c>
       <c r="J12" s="8" t="inlineStr">
@@ -981,12 +987,12 @@
       <c r="K12" s="8" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="20" t="inlineStr">
+      <c r="A13" s="22" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
       </c>
-      <c r="B13" s="20" t="inlineStr">
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1001,27 +1007,27 @@
           <t>비용 없이 개발·테스트하는 가짜 모델</t>
         </is>
       </c>
-      <c r="E13" s="20" t="inlineStr">
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F13" s="20" t="inlineStr">
+      <c r="F13" s="22" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="G13" s="20" t="inlineStr">
+      <c r="G13" s="22" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H13" s="20" t="inlineStr">
+      <c r="H13" s="22" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I13" s="21" t="n">
+      <c r="I13" s="23" t="n">
         <v>1</v>
       </c>
       <c r="J13" s="8" t="inlineStr">
@@ -1032,12 +1038,12 @@
       <c r="K13" s="8" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="inlineStr">
+      <c r="A14" s="22" t="inlineStr">
         <is>
           <t>2.3</t>
         </is>
       </c>
-      <c r="B14" s="20" t="inlineStr">
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1052,27 +1058,27 @@
           <t>과제별 질문 정책(policy.yaml), 단계별 프롬프트</t>
         </is>
       </c>
-      <c r="E14" s="20" t="inlineStr">
+      <c r="E14" s="22" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F14" s="20" t="inlineStr">
+      <c r="F14" s="22" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G14" s="20" t="inlineStr">
+      <c r="G14" s="22" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H14" s="20" t="inlineStr">
+      <c r="H14" s="22" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I14" s="21" t="n">
+      <c r="I14" s="23" t="n">
         <v>1</v>
       </c>
       <c r="J14" s="8" t="inlineStr">
@@ -1083,12 +1089,12 @@
       <c r="K14" s="8" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="20" t="inlineStr">
+      <c r="A15" s="22" t="inlineStr">
         <is>
           <t>2.4</t>
         </is>
       </c>
-      <c r="B15" s="20" t="inlineStr">
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1103,27 +1109,27 @@
           <t>모드별 질문 상한, '다른 예시 보기' 단계</t>
         </is>
       </c>
-      <c r="E15" s="20" t="inlineStr">
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F15" s="20" t="inlineStr">
+      <c r="F15" s="22" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G15" s="20" t="inlineStr">
+      <c r="G15" s="22" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H15" s="20" t="inlineStr">
+      <c r="H15" s="22" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I15" s="21" t="n">
+      <c r="I15" s="23" t="n">
         <v>1</v>
       </c>
       <c r="J15" s="8" t="inlineStr">
@@ -1134,12 +1140,12 @@
       <c r="K15" s="8" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="20" t="inlineStr">
+      <c r="A16" s="22" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
       </c>
-      <c r="B16" s="20" t="inlineStr">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1150,27 +1156,27 @@
         </is>
       </c>
       <c r="D16" s="8" t="n"/>
-      <c r="E16" s="20" t="inlineStr">
+      <c r="E16" s="22" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F16" s="20" t="inlineStr">
+      <c r="F16" s="22" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G16" s="20" t="inlineStr">
+      <c r="G16" s="22" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H16" s="20" t="inlineStr">
+      <c r="H16" s="22" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I16" s="21" t="n">
+      <c r="I16" s="23" t="n">
         <v>1</v>
       </c>
       <c r="J16" s="8" t="inlineStr">
@@ -1181,12 +1187,12 @@
       <c r="K16" s="8" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="20" t="inlineStr">
+      <c r="A17" s="22" t="inlineStr">
         <is>
           <t>2.6</t>
         </is>
       </c>
-      <c r="B17" s="20" t="inlineStr">
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1201,27 +1207,27 @@
           <t>과제별 정책·프롬프트·검증 규칙</t>
         </is>
       </c>
-      <c r="E17" s="20" t="inlineStr">
+      <c r="E17" s="22" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F17" s="20" t="inlineStr">
+      <c r="F17" s="22" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G17" s="20" t="inlineStr">
+      <c r="G17" s="22" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H17" s="20" t="inlineStr">
+      <c r="H17" s="22" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I17" s="21" t="n">
+      <c r="I17" s="23" t="n">
         <v>1</v>
       </c>
       <c r="J17" s="8" t="inlineStr">
@@ -1232,12 +1238,12 @@
       <c r="K17" s="8" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="20" t="inlineStr">
+      <c r="A18" s="22" t="inlineStr">
         <is>
           <t>2.7</t>
         </is>
       </c>
-      <c r="B18" s="20" t="inlineStr">
+      <c r="B18" s="22" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1252,27 +1258,27 @@
           <t>한국어 오류 문구, API 문서</t>
         </is>
       </c>
-      <c r="E18" s="20" t="inlineStr">
+      <c r="E18" s="22" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F18" s="20" t="inlineStr">
+      <c r="F18" s="22" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G18" s="20" t="inlineStr">
+      <c r="G18" s="22" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H18" s="20" t="inlineStr">
+      <c r="H18" s="22" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I18" s="21" t="n">
+      <c r="I18" s="23" t="n">
         <v>1</v>
       </c>
       <c r="J18" s="8" t="inlineStr">
@@ -1283,12 +1289,12 @@
       <c r="K18" s="8" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="20" t="inlineStr">
+      <c r="A19" s="22" t="inlineStr">
         <is>
           <t>2.8</t>
         </is>
       </c>
-      <c r="B19" s="20" t="inlineStr">
+      <c r="B19" s="22" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1303,27 +1309,27 @@
           <t>API에 맞춘 최소 화면, 개발 안내(CLAUDE.md)</t>
         </is>
       </c>
-      <c r="E19" s="20" t="inlineStr">
+      <c r="E19" s="22" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F19" s="20" t="inlineStr">
+      <c r="F19" s="22" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G19" s="20" t="inlineStr">
+      <c r="G19" s="22" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H19" s="20" t="inlineStr">
+      <c r="H19" s="22" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I19" s="21" t="n">
+      <c r="I19" s="23" t="n">
         <v>1</v>
       </c>
       <c r="J19" s="8" t="inlineStr">
@@ -1362,12 +1368,12 @@
       <c r="K20" s="5" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="20" t="inlineStr">
+      <c r="A21" s="22" t="inlineStr">
         <is>
           <t>3.1</t>
         </is>
       </c>
-      <c r="B21" s="20" t="inlineStr">
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
@@ -1382,23 +1388,23 @@
           <t>전체 화면 흐름 HTML 프로토타입</t>
         </is>
       </c>
-      <c r="E21" s="20" t="inlineStr">
+      <c r="E21" s="22" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
       </c>
-      <c r="F21" s="20" t="n"/>
-      <c r="G21" s="20" t="inlineStr">
+      <c r="F21" s="22" t="n"/>
+      <c r="G21" s="22" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H21" s="20" t="inlineStr">
+      <c r="H21" s="22" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I21" s="21" t="n">
+      <c r="I21" s="23" t="n">
         <v>1</v>
       </c>
       <c r="J21" s="8" t="inlineStr">
@@ -1409,12 +1415,12 @@
       <c r="K21" s="8" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="20" t="inlineStr">
+      <c r="A22" s="22" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
       </c>
-      <c r="B22" s="20" t="inlineStr">
+      <c r="B22" s="22" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
@@ -1429,27 +1435,27 @@
           <t>모든 질문에 '다른 예시 보기', 모드 설명, 이미지 블록, 생성 중·실패·최신 아님 상태</t>
         </is>
       </c>
-      <c r="E22" s="20" t="inlineStr">
+      <c r="E22" s="22" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
       </c>
-      <c r="F22" s="20" t="inlineStr">
+      <c r="F22" s="22" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G22" s="20" t="inlineStr">
+      <c r="G22" s="22" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H22" s="20" t="inlineStr">
+      <c r="H22" s="22" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I22" s="21" t="n">
+      <c r="I22" s="23" t="n">
         <v>1</v>
       </c>
       <c r="J22" s="8" t="inlineStr">
@@ -1460,12 +1466,12 @@
       <c r="K22" s="8" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="20" t="inlineStr">
+      <c r="A23" s="22" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
       </c>
-      <c r="B23" s="20" t="inlineStr">
+      <c r="B23" s="22" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
@@ -1480,31 +1486,31 @@
           <t>반응형 자동 배치 확인</t>
         </is>
       </c>
-      <c r="E23" s="20" t="inlineStr">
+      <c r="E23" s="22" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
       </c>
-      <c r="F23" s="20" t="n"/>
-      <c r="G23" s="20" t="n"/>
-      <c r="H23" s="20" t="inlineStr">
+      <c r="F23" s="22" t="n"/>
+      <c r="G23" s="22" t="n"/>
+      <c r="H23" s="22" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="I23" s="21" t="n">
+      <c r="I23" s="23" t="n">
         <v>0</v>
       </c>
       <c r="J23" s="8" t="n"/>
       <c r="K23" s="8" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="20" t="inlineStr">
+      <c r="A24" s="22" t="inlineStr">
         <is>
           <t>3.4</t>
         </is>
       </c>
-      <c r="B24" s="20" t="inlineStr">
+      <c r="B24" s="22" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
@@ -1519,19 +1525,19 @@
           <t>/preview 화면을 html.to.design으로 가져와 수정</t>
         </is>
       </c>
-      <c r="E24" s="20" t="inlineStr">
+      <c r="E24" s="22" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
       </c>
-      <c r="F24" s="20" t="n"/>
-      <c r="G24" s="20" t="n"/>
-      <c r="H24" s="20" t="inlineStr">
+      <c r="F24" s="22" t="n"/>
+      <c r="G24" s="22" t="n"/>
+      <c r="H24" s="22" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="I24" s="21" t="n">
+      <c r="I24" s="23" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="8" t="n"/>
@@ -1566,12 +1572,12 @@
       <c r="K25" s="5" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="20" t="inlineStr">
+      <c r="A26" s="22" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
       </c>
-      <c r="B26" s="20" t="inlineStr">
+      <c r="B26" s="22" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1586,27 +1592,27 @@
           <t>버셀 배포 설정 포함</t>
         </is>
       </c>
-      <c r="E26" s="20" t="inlineStr">
+      <c r="E26" s="22" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F26" s="20" t="inlineStr">
+      <c r="F26" s="22" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G26" s="20" t="inlineStr">
+      <c r="G26" s="22" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H26" s="20" t="inlineStr">
+      <c r="H26" s="22" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I26" s="21" t="n">
+      <c r="I26" s="23" t="n">
         <v>1</v>
       </c>
       <c r="J26" s="8" t="inlineStr">
@@ -1617,12 +1623,12 @@
       <c r="K26" s="8" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="20" t="inlineStr">
+      <c r="A27" s="22" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
       </c>
-      <c r="B27" s="20" t="inlineStr">
+      <c r="B27" s="22" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1637,27 +1643,27 @@
           <t>답변 종류, 흐름 패널, 익명 사용자</t>
         </is>
       </c>
-      <c r="E27" s="20" t="inlineStr">
+      <c r="E27" s="22" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F27" s="20" t="inlineStr">
+      <c r="F27" s="22" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G27" s="20" t="inlineStr">
+      <c r="G27" s="22" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H27" s="20" t="inlineStr">
+      <c r="H27" s="22" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I27" s="21" t="n">
+      <c r="I27" s="23" t="n">
         <v>1</v>
       </c>
       <c r="J27" s="8" t="inlineStr">
@@ -1668,12 +1674,12 @@
       <c r="K27" s="8" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="20" t="inlineStr">
+      <c r="A28" s="22" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
       </c>
-      <c r="B28" s="20" t="inlineStr">
+      <c r="B28" s="22" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1688,27 +1694,27 @@
           <t>서버 저장(SQLite), 문서 내려받기</t>
         </is>
       </c>
-      <c r="E28" s="20" t="inlineStr">
+      <c r="E28" s="22" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F28" s="20" t="inlineStr">
+      <c r="F28" s="22" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G28" s="20" t="inlineStr">
+      <c r="G28" s="22" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H28" s="20" t="inlineStr">
+      <c r="H28" s="22" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I28" s="21" t="n">
+      <c r="I28" s="23" t="n">
         <v>1</v>
       </c>
       <c r="J28" s="8" t="inlineStr">
@@ -1719,12 +1725,12 @@
       <c r="K28" s="8" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="20" t="inlineStr">
+      <c r="A29" s="22" t="inlineStr">
         <is>
           <t>4.4</t>
         </is>
       </c>
-      <c r="B29" s="20" t="inlineStr">
+      <c r="B29" s="22" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1739,27 +1745,27 @@
           <t>결과를 섹션·블록으로</t>
         </is>
       </c>
-      <c r="E29" s="20" t="inlineStr">
+      <c r="E29" s="22" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F29" s="20" t="inlineStr">
+      <c r="F29" s="22" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G29" s="20" t="inlineStr">
+      <c r="G29" s="22" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H29" s="20" t="inlineStr">
+      <c r="H29" s="22" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I29" s="21" t="n">
+      <c r="I29" s="23" t="n">
         <v>1</v>
       </c>
       <c r="J29" s="8" t="inlineStr">
@@ -1770,12 +1776,12 @@
       <c r="K29" s="8" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="20" t="inlineStr">
+      <c r="A30" s="22" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
       </c>
-      <c r="B30" s="20" t="inlineStr">
+      <c r="B30" s="22" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1790,27 +1796,27 @@
           <t>샘플 근거 자료, 자리표시 이미지</t>
         </is>
       </c>
-      <c r="E30" s="20" t="inlineStr">
+      <c r="E30" s="22" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F30" s="20" t="inlineStr">
+      <c r="F30" s="22" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G30" s="20" t="inlineStr">
+      <c r="G30" s="22" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H30" s="20" t="inlineStr">
+      <c r="H30" s="22" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I30" s="21" t="n">
+      <c r="I30" s="23" t="n">
         <v>1</v>
       </c>
       <c r="J30" s="8" t="inlineStr">
@@ -1821,12 +1827,12 @@
       <c r="K30" s="8" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="20" t="inlineStr">
+      <c r="A31" s="22" t="inlineStr">
         <is>
           <t>4.6</t>
         </is>
       </c>
-      <c r="B31" s="20" t="inlineStr">
+      <c r="B31" s="22" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1841,27 +1847,27 @@
           <t>생성 중·생성 실패 화면, 최신 아님 배너, 이미지 상자, 모드 설명</t>
         </is>
       </c>
-      <c r="E31" s="20" t="inlineStr">
+      <c r="E31" s="22" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F31" s="20" t="inlineStr">
+      <c r="F31" s="22" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G31" s="20" t="inlineStr">
+      <c r="G31" s="22" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H31" s="20" t="inlineStr">
+      <c r="H31" s="22" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I31" s="21" t="n">
+      <c r="I31" s="23" t="n">
         <v>1</v>
       </c>
       <c r="J31" s="8" t="inlineStr">
@@ -1872,12 +1878,12 @@
       <c r="K31" s="8" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="20" t="inlineStr">
+      <c r="A32" s="22" t="inlineStr">
         <is>
           <t>4.7</t>
         </is>
       </c>
-      <c r="B32" s="20" t="inlineStr">
+      <c r="B32" s="22" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1892,27 +1898,27 @@
           <t>이전 결과를 다음 과제의 기준으로 가져오기</t>
         </is>
       </c>
-      <c r="E32" s="20" t="inlineStr">
+      <c r="E32" s="22" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F32" s="20" t="inlineStr">
+      <c r="F32" s="22" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G32" s="20" t="inlineStr">
+      <c r="G32" s="22" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H32" s="20" t="inlineStr">
+      <c r="H32" s="22" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I32" s="21" t="n">
+      <c r="I32" s="23" t="n">
         <v>1</v>
       </c>
       <c r="J32" s="8" t="inlineStr">
@@ -1951,12 +1957,12 @@
       <c r="K33" s="5" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="20" t="inlineStr">
+      <c r="A34" s="22" t="inlineStr">
         <is>
           <t>5.1</t>
         </is>
       </c>
-      <c r="B34" s="20" t="inlineStr">
+      <c r="B34" s="22" t="inlineStr">
         <is>
           <t>배포</t>
         </is>
@@ -1971,27 +1977,27 @@
           <t>main은 정식 주소, PR마다 미리보기 주소</t>
         </is>
       </c>
-      <c r="E34" s="20" t="inlineStr">
+      <c r="E34" s="22" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F34" s="20" t="inlineStr">
+      <c r="F34" s="22" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="G34" s="20" t="inlineStr">
+      <c r="G34" s="22" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="H34" s="20" t="inlineStr">
+      <c r="H34" s="22" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I34" s="21" t="n">
+      <c r="I34" s="23" t="n">
         <v>1</v>
       </c>
       <c r="J34" s="8" t="inlineStr">
@@ -2006,12 +2012,12 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="20" t="inlineStr">
+      <c r="A35" s="22" t="inlineStr">
         <is>
           <t>5.2</t>
         </is>
       </c>
-      <c r="B35" s="20" t="inlineStr">
+      <c r="B35" s="22" t="inlineStr">
         <is>
           <t>배포</t>
         </is>
@@ -2026,27 +2032,27 @@
           <t>저장 디스크 방식 정하기, 프론트와 연결</t>
         </is>
       </c>
-      <c r="E35" s="20" t="inlineStr">
+      <c r="E35" s="22" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F35" s="20" t="inlineStr">
+      <c r="F35" s="22" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="G35" s="20" t="inlineStr">
+      <c r="G35" s="22" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="H35" s="20" t="inlineStr">
+      <c r="H35" s="22" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I35" s="21" t="n">
+      <c r="I35" s="23" t="n">
         <v>1</v>
       </c>
       <c r="J35" s="8" t="inlineStr">
@@ -2082,19 +2088,19 @@
       <c r="G36" s="4" t="n"/>
       <c r="H36" s="4" t="n"/>
       <c r="I36" s="6">
-        <f>IFERROR(AVERAGE(I37:I40),0)</f>
+        <f>IFERROR(AVERAGE(I37:I41),0)</f>
         <v/>
       </c>
       <c r="J36" s="5" t="n"/>
       <c r="K36" s="5" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="20" t="inlineStr">
+      <c r="A37" s="22" t="inlineStr">
         <is>
           <t>6.1</t>
         </is>
       </c>
-      <c r="B37" s="20" t="inlineStr">
+      <c r="B37" s="22" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
@@ -2109,27 +2115,27 @@
           <t>가짜 모델(Mock) 대신 실제 모델</t>
         </is>
       </c>
-      <c r="E37" s="20" t="inlineStr">
+      <c r="E37" s="22" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F37" s="20" t="inlineStr">
+      <c r="F37" s="22" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="G37" s="20" t="inlineStr">
+      <c r="G37" s="22" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="H37" s="20" t="inlineStr">
+      <c r="H37" s="22" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I37" s="21" t="n">
+      <c r="I37" s="23" t="n">
         <v>1</v>
       </c>
       <c r="J37" s="8" t="inlineStr">
@@ -2144,12 +2150,12 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="20" t="inlineStr">
+      <c r="A38" s="22" t="inlineStr">
         <is>
           <t>6.2</t>
         </is>
       </c>
-      <c r="B38" s="20" t="inlineStr">
+      <c r="B38" s="22" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
@@ -2164,31 +2170,31 @@
           <t>준비도 기준·항목 가중치·프롬프트를 시나리오로 측정</t>
         </is>
       </c>
-      <c r="E38" s="20" t="inlineStr">
+      <c r="E38" s="22" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F38" s="20" t="n"/>
-      <c r="G38" s="20" t="n"/>
-      <c r="H38" s="20" t="inlineStr">
+      <c r="F38" s="22" t="n"/>
+      <c r="G38" s="22" t="n"/>
+      <c r="H38" s="22" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="I38" s="21" t="n">
+      <c r="I38" s="23" t="n">
         <v>0</v>
       </c>
       <c r="J38" s="8" t="n"/>
       <c r="K38" s="8" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="20" t="inlineStr">
+      <c r="A39" s="22" t="inlineStr">
         <is>
           <t>6.3</t>
         </is>
       </c>
-      <c r="B39" s="20" t="inlineStr">
+      <c r="B39" s="22" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
@@ -2203,31 +2209,31 @@
           <t>지금의 자리표시·샘플 자리에 실제 기능 연결</t>
         </is>
       </c>
-      <c r="E39" s="20" t="inlineStr">
+      <c r="E39" s="22" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F39" s="20" t="n"/>
-      <c r="G39" s="20" t="n"/>
-      <c r="H39" s="20" t="inlineStr">
+      <c r="F39" s="22" t="n"/>
+      <c r="G39" s="22" t="n"/>
+      <c r="H39" s="22" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="I39" s="21" t="n">
+      <c r="I39" s="23" t="n">
         <v>0</v>
       </c>
       <c r="J39" s="8" t="n"/>
       <c r="K39" s="8" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="20" t="inlineStr">
+      <c r="A40" s="22" t="inlineStr">
         <is>
           <t>6.4</t>
         </is>
       </c>
-      <c r="B40" s="20" t="inlineStr">
+      <c r="B40" s="22" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
@@ -2238,27 +2244,27 @@
         </is>
       </c>
       <c r="D40" s="8" t="n"/>
-      <c r="E40" s="20" t="inlineStr">
+      <c r="E40" s="22" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F40" s="20" t="inlineStr">
+      <c r="F40" s="22" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="G40" s="20" t="inlineStr">
+      <c r="G40" s="22" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="H40" s="20" t="inlineStr">
+      <c r="H40" s="22" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I40" s="21" t="n">
+      <c r="I40" s="23" t="n">
         <v>1</v>
       </c>
       <c r="J40" s="8" t="inlineStr">
@@ -2269,110 +2275,161 @@
       <c r="K40" s="8" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="A41" s="22" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="B41" s="22" t="inlineStr">
+        <is>
+          <t>실제 AI 연결</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>프롬프트 주입 기본 방어(입력 감싸기·유출 차단)</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="n"/>
+      <c r="E41" s="22" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F41" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="G41" s="22" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="H41" s="22" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I41" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" s="8" t="inlineStr">
+        <is>
+          <t>PR #25</t>
+        </is>
+      </c>
+      <c r="K41" s="8" t="inlineStr">
+        <is>
+          <t>PR #25</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>마무리</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>평가·발표</t>
         </is>
       </c>
-      <c r="D41" s="5" t="n"/>
-      <c r="E41" s="4" t="n"/>
-      <c r="F41" s="4" t="n"/>
-      <c r="G41" s="4" t="n"/>
-      <c r="H41" s="4" t="n"/>
-      <c r="I41" s="6">
-        <f>IFERROR(AVERAGE(I42:I43),0)</f>
-        <v/>
-      </c>
-      <c r="J41" s="5" t="n"/>
-      <c r="K41" s="5" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="20" t="inlineStr">
+      <c r="D42" s="5" t="n"/>
+      <c r="E42" s="4" t="n"/>
+      <c r="F42" s="4" t="n"/>
+      <c r="G42" s="4" t="n"/>
+      <c r="H42" s="4" t="n"/>
+      <c r="I42" s="6">
+        <f>IFERROR(AVERAGE(I43:I44),0)</f>
+        <v/>
+      </c>
+      <c r="J42" s="5" t="n"/>
+      <c r="K42" s="5" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="22" t="inlineStr">
         <is>
           <t>7.1</t>
         </is>
       </c>
-      <c r="B42" s="20" t="inlineStr">
+      <c r="B43" s="22" t="inlineStr">
         <is>
           <t>마무리</t>
         </is>
       </c>
-      <c r="C42" s="8" t="inlineStr">
+      <c r="C43" s="8" t="inlineStr">
         <is>
           <t>사용성 확인·평가 지표 측정</t>
         </is>
       </c>
-      <c r="D42" s="8" t="inlineStr">
+      <c r="D43" s="8" t="inlineStr">
         <is>
           <t>필수정보 충족률, 질문 효율, 가정 표시율 등(기획서 14장)</t>
         </is>
       </c>
-      <c r="E42" s="20" t="inlineStr">
+      <c r="E43" s="22" t="inlineStr">
         <is>
           <t>공동</t>
         </is>
       </c>
-      <c r="F42" s="20" t="n"/>
-      <c r="G42" s="20" t="n"/>
-      <c r="H42" s="20" t="inlineStr">
+      <c r="F43" s="22" t="n"/>
+      <c r="G43" s="22" t="n"/>
+      <c r="H43" s="22" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="I42" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="8" t="n"/>
-      <c r="K42" s="8" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="20" t="inlineStr">
-        <is>
-          <t>7.2</t>
-        </is>
-      </c>
-      <c r="B43" s="20" t="inlineStr">
-        <is>
-          <t>마무리</t>
-        </is>
-      </c>
-      <c r="C43" s="8" t="inlineStr">
-        <is>
-          <t>최종 발표 자료</t>
-        </is>
-      </c>
-      <c r="D43" s="8" t="n"/>
-      <c r="E43" s="20" t="inlineStr">
-        <is>
-          <t>공동</t>
-        </is>
-      </c>
-      <c r="F43" s="20" t="n"/>
-      <c r="G43" s="20" t="n"/>
-      <c r="H43" s="20" t="inlineStr">
-        <is>
-          <t>예정</t>
-        </is>
-      </c>
-      <c r="I43" s="21" t="n">
+      <c r="I43" s="23" t="n">
         <v>0</v>
       </c>
       <c r="J43" s="8" t="n"/>
       <c r="K43" s="8" t="n"/>
     </row>
+    <row r="44">
+      <c r="A44" s="22" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="B44" s="22" t="inlineStr">
+        <is>
+          <t>마무리</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>최종 발표 자료</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="n"/>
+      <c r="E44" s="22" t="inlineStr">
+        <is>
+          <t>공동</t>
+        </is>
+      </c>
+      <c r="F44" s="22" t="n"/>
+      <c r="G44" s="22" t="n"/>
+      <c r="H44" s="22" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="I44" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="8" t="n"/>
+      <c r="K44" s="8" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:K43"/>
-  <conditionalFormatting sqref="H5:H43">
+  <autoFilter ref="A4:K44"/>
+  <conditionalFormatting sqref="H5:H44">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"완료"</formula>
     </cfRule>
@@ -2383,7 +2440,7 @@
       <formula>"보류"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I5:I43">
+  <conditionalFormatting sqref="I5:I44">
     <cfRule type="dataBar" priority="4">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -2393,10 +2450,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="H5:H43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"완료,진행 중,예정,보류"</formula1>
     </dataValidation>
-    <dataValidation sqref="E5:E43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"개발,디자인,공동"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2467,23 +2524,23 @@
         </is>
       </c>
       <c r="B4" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$43,A4,WBS!$H$5:$H$43,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$44,A4,WBS!$H$5:$H$44,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C4" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$43,A4,WBS!$H$5:$H$43,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$44,A4,WBS!$H$5:$H$44,"완료")</f>
         <v/>
       </c>
       <c r="D4" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$43,A4,WBS!$H$5:$H$43,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$44,A4,WBS!$H$5:$H$44,"진행 중")</f>
         <v/>
       </c>
       <c r="E4" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$43,A4,WBS!$H$5:$H$43,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$44,A4,WBS!$H$5:$H$44,"예정")</f>
         <v/>
       </c>
       <c r="F4" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$43,WBS!$B$5:$B$43,A4,WBS!$H$5:$H$43,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$44,WBS!$B$5:$B$44,A4,WBS!$H$5:$H$44,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2494,23 +2551,23 @@
         </is>
       </c>
       <c r="B5" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$43,A5,WBS!$H$5:$H$43,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$44,A5,WBS!$H$5:$H$44,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C5" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$43,A5,WBS!$H$5:$H$43,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$44,A5,WBS!$H$5:$H$44,"완료")</f>
         <v/>
       </c>
       <c r="D5" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$43,A5,WBS!$H$5:$H$43,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$44,A5,WBS!$H$5:$H$44,"진행 중")</f>
         <v/>
       </c>
       <c r="E5" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$43,A5,WBS!$H$5:$H$43,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$44,A5,WBS!$H$5:$H$44,"예정")</f>
         <v/>
       </c>
       <c r="F5" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$43,WBS!$B$5:$B$43,A5,WBS!$H$5:$H$43,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$44,WBS!$B$5:$B$44,A5,WBS!$H$5:$H$44,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2521,23 +2578,23 @@
         </is>
       </c>
       <c r="B6" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$43,A6,WBS!$H$5:$H$43,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$44,A6,WBS!$H$5:$H$44,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C6" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$43,A6,WBS!$H$5:$H$43,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$44,A6,WBS!$H$5:$H$44,"완료")</f>
         <v/>
       </c>
       <c r="D6" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$43,A6,WBS!$H$5:$H$43,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$44,A6,WBS!$H$5:$H$44,"진행 중")</f>
         <v/>
       </c>
       <c r="E6" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$43,A6,WBS!$H$5:$H$43,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$44,A6,WBS!$H$5:$H$44,"예정")</f>
         <v/>
       </c>
       <c r="F6" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$43,WBS!$B$5:$B$43,A6,WBS!$H$5:$H$43,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$44,WBS!$B$5:$B$44,A6,WBS!$H$5:$H$44,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2548,23 +2605,23 @@
         </is>
       </c>
       <c r="B7" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$43,A7,WBS!$H$5:$H$43,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$44,A7,WBS!$H$5:$H$44,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C7" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$43,A7,WBS!$H$5:$H$43,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$44,A7,WBS!$H$5:$H$44,"완료")</f>
         <v/>
       </c>
       <c r="D7" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$43,A7,WBS!$H$5:$H$43,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$44,A7,WBS!$H$5:$H$44,"진행 중")</f>
         <v/>
       </c>
       <c r="E7" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$43,A7,WBS!$H$5:$H$43,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$44,A7,WBS!$H$5:$H$44,"예정")</f>
         <v/>
       </c>
       <c r="F7" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$43,WBS!$B$5:$B$43,A7,WBS!$H$5:$H$43,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$44,WBS!$B$5:$B$44,A7,WBS!$H$5:$H$44,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2575,23 +2632,23 @@
         </is>
       </c>
       <c r="B8" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$43,A8,WBS!$H$5:$H$43,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$44,A8,WBS!$H$5:$H$44,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C8" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$43,A8,WBS!$H$5:$H$43,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$44,A8,WBS!$H$5:$H$44,"완료")</f>
         <v/>
       </c>
       <c r="D8" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$43,A8,WBS!$H$5:$H$43,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$44,A8,WBS!$H$5:$H$44,"진행 중")</f>
         <v/>
       </c>
       <c r="E8" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$43,A8,WBS!$H$5:$H$43,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$44,A8,WBS!$H$5:$H$44,"예정")</f>
         <v/>
       </c>
       <c r="F8" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$43,WBS!$B$5:$B$43,A8,WBS!$H$5:$H$43,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$44,WBS!$B$5:$B$44,A8,WBS!$H$5:$H$44,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2602,23 +2659,23 @@
         </is>
       </c>
       <c r="B9" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$43,A9,WBS!$H$5:$H$43,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$44,A9,WBS!$H$5:$H$44,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C9" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$43,A9,WBS!$H$5:$H$43,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$44,A9,WBS!$H$5:$H$44,"완료")</f>
         <v/>
       </c>
       <c r="D9" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$43,A9,WBS!$H$5:$H$43,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$44,A9,WBS!$H$5:$H$44,"진행 중")</f>
         <v/>
       </c>
       <c r="E9" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$43,A9,WBS!$H$5:$H$43,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$44,A9,WBS!$H$5:$H$44,"예정")</f>
         <v/>
       </c>
       <c r="F9" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$43,WBS!$B$5:$B$43,A9,WBS!$H$5:$H$43,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$44,WBS!$B$5:$B$44,A9,WBS!$H$5:$H$44,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2629,23 +2686,23 @@
         </is>
       </c>
       <c r="B10" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$43,A10,WBS!$H$5:$H$43,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$44,A10,WBS!$H$5:$H$44,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C10" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$43,A10,WBS!$H$5:$H$43,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$44,A10,WBS!$H$5:$H$44,"완료")</f>
         <v/>
       </c>
       <c r="D10" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$43,A10,WBS!$H$5:$H$43,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$44,A10,WBS!$H$5:$H$44,"진행 중")</f>
         <v/>
       </c>
       <c r="E10" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$43,A10,WBS!$H$5:$H$43,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$44,A10,WBS!$H$5:$H$44,"예정")</f>
         <v/>
       </c>
       <c r="F10" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$43,WBS!$B$5:$B$43,A10,WBS!$H$5:$H$43,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$44,WBS!$B$5:$B$44,A10,WBS!$H$5:$H$44,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2672,7 +2729,7 @@
         <v/>
       </c>
       <c r="F11" s="14">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$43,WBS!$H$5:$H$43,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$44,WBS!$H$5:$H$44,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>

--- a/docs/WBS.xlsx
+++ b/docs/WBS.xlsx
@@ -11,7 +11,7 @@
     <sheet name="요약" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS'!$A$4:$K$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS'!$A$4:$K$45</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -98,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -129,6 +129,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -541,7 +547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K44"/>
+  <dimension ref="A1:K45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -657,12 +663,12 @@
       <c r="K5" s="5" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="22" t="inlineStr">
+      <c r="A6" s="24" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>기획·설계</t>
         </is>
@@ -677,23 +683,23 @@
           <t>과제 4개(사업계획·상품기획·브랜딩·마케팅), 적응형 질문, 사실·가정 분리 원칙</t>
         </is>
       </c>
-      <c r="E6" s="22" t="inlineStr">
+      <c r="E6" s="24" t="inlineStr">
         <is>
           <t>공동</t>
         </is>
       </c>
-      <c r="F6" s="22" t="n"/>
-      <c r="G6" s="22" t="inlineStr">
+      <c r="F6" s="24" t="n"/>
+      <c r="G6" s="24" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="H6" s="22" t="inlineStr">
+      <c r="H6" s="24" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I6" s="23" t="n">
+      <c r="I6" s="25" t="n">
         <v>1</v>
       </c>
       <c r="J6" s="8" t="inlineStr">
@@ -704,12 +710,12 @@
       <c r="K6" s="8" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="22" t="inlineStr">
+      <c r="A7" s="24" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>기획·설계</t>
         </is>
@@ -724,27 +730,27 @@
           <t>FastAPI 하네스 구조, API 계약, 테스트 전략</t>
         </is>
       </c>
-      <c r="E7" s="22" t="inlineStr">
+      <c r="E7" s="24" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F7" s="22" t="inlineStr">
+      <c r="F7" s="24" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="G7" s="22" t="inlineStr">
+      <c r="G7" s="24" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="H7" s="22" t="inlineStr">
+      <c r="H7" s="24" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I7" s="23" t="n">
+      <c r="I7" s="25" t="n">
         <v>1</v>
       </c>
       <c r="J7" s="8" t="inlineStr">
@@ -755,12 +761,12 @@
       <c r="K7" s="8" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="22" t="inlineStr">
+      <c r="A8" s="24" t="inlineStr">
         <is>
           <t>1.3</t>
         </is>
       </c>
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>기획·설계</t>
         </is>
@@ -775,27 +781,27 @@
           <t>V2 화면 흐름, 묶음 0~4로 작업 나누기</t>
         </is>
       </c>
-      <c r="E8" s="22" t="inlineStr">
+      <c r="E8" s="24" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F8" s="22" t="inlineStr">
+      <c r="F8" s="24" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G8" s="22" t="inlineStr">
+      <c r="G8" s="24" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H8" s="22" t="inlineStr">
+      <c r="H8" s="24" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I8" s="23" t="n">
+      <c r="I8" s="25" t="n">
         <v>1</v>
       </c>
       <c r="J8" s="8" t="inlineStr">
@@ -806,12 +812,12 @@
       <c r="K8" s="8" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="22" t="inlineStr">
+      <c r="A9" s="24" t="inlineStr">
         <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B9" s="24" t="inlineStr">
         <is>
           <t>기획·설계</t>
         </is>
@@ -826,27 +832,27 @@
           <t>지금 상태·다음 할 일·작업 방식·환경 팁, PR마다 갱신</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="E9" s="24" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F9" s="22" t="inlineStr">
+      <c r="F9" s="24" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="G9" s="22" t="inlineStr">
+      <c r="G9" s="24" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="H9" s="22" t="inlineStr">
+      <c r="H9" s="24" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I9" s="23" t="n">
+      <c r="I9" s="25" t="n">
         <v>1</v>
       </c>
       <c r="J9" s="8" t="inlineStr">
@@ -857,12 +863,12 @@
       <c r="K9" s="8" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="22" t="inlineStr">
+      <c r="A10" s="24" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B10" s="24" t="inlineStr">
         <is>
           <t>기획·설계</t>
         </is>
@@ -877,27 +883,27 @@
           <t>바로 보기 주소, 된 것, 남은 일·맡을 사람·상의할 점</t>
         </is>
       </c>
-      <c r="E10" s="22" t="inlineStr">
+      <c r="E10" s="24" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F10" s="22" t="inlineStr">
+      <c r="F10" s="24" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="G10" s="22" t="inlineStr">
+      <c r="G10" s="24" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="H10" s="22" t="inlineStr">
+      <c r="H10" s="24" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I10" s="23" t="n">
+      <c r="I10" s="25" t="n">
         <v>1</v>
       </c>
       <c r="J10" s="8" t="inlineStr">
@@ -936,12 +942,12 @@
       <c r="K11" s="5" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="22" t="inlineStr">
+      <c r="A12" s="24" t="inlineStr">
         <is>
           <t>2.1</t>
         </is>
       </c>
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B12" s="24" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -956,27 +962,27 @@
           <t>사실·가정·미정 구분, 정보 출처 표시</t>
         </is>
       </c>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="E12" s="24" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F12" s="22" t="inlineStr">
+      <c r="F12" s="24" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="G12" s="22" t="inlineStr">
+      <c r="G12" s="24" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H12" s="22" t="inlineStr">
+      <c r="H12" s="24" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I12" s="23" t="n">
+      <c r="I12" s="25" t="n">
         <v>1</v>
       </c>
       <c r="J12" s="8" t="inlineStr">
@@ -987,12 +993,12 @@
       <c r="K12" s="8" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="22" t="inlineStr">
+      <c r="A13" s="24" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
       </c>
-      <c r="B13" s="22" t="inlineStr">
+      <c r="B13" s="24" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1007,27 +1013,27 @@
           <t>비용 없이 개발·테스트하는 가짜 모델</t>
         </is>
       </c>
-      <c r="E13" s="22" t="inlineStr">
+      <c r="E13" s="24" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F13" s="22" t="inlineStr">
+      <c r="F13" s="24" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="G13" s="22" t="inlineStr">
+      <c r="G13" s="24" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H13" s="22" t="inlineStr">
+      <c r="H13" s="24" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I13" s="23" t="n">
+      <c r="I13" s="25" t="n">
         <v>1</v>
       </c>
       <c r="J13" s="8" t="inlineStr">
@@ -1038,12 +1044,12 @@
       <c r="K13" s="8" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="22" t="inlineStr">
+      <c r="A14" s="24" t="inlineStr">
         <is>
           <t>2.3</t>
         </is>
       </c>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="B14" s="24" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1058,27 +1064,27 @@
           <t>과제별 질문 정책(policy.yaml), 단계별 프롬프트</t>
         </is>
       </c>
-      <c r="E14" s="22" t="inlineStr">
+      <c r="E14" s="24" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F14" s="22" t="inlineStr">
+      <c r="F14" s="24" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G14" s="22" t="inlineStr">
+      <c r="G14" s="24" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H14" s="22" t="inlineStr">
+      <c r="H14" s="24" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I14" s="23" t="n">
+      <c r="I14" s="25" t="n">
         <v>1</v>
       </c>
       <c r="J14" s="8" t="inlineStr">
@@ -1089,12 +1095,12 @@
       <c r="K14" s="8" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="22" t="inlineStr">
+      <c r="A15" s="24" t="inlineStr">
         <is>
           <t>2.4</t>
         </is>
       </c>
-      <c r="B15" s="22" t="inlineStr">
+      <c r="B15" s="24" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1109,27 +1115,27 @@
           <t>모드별 질문 상한, '다른 예시 보기' 단계</t>
         </is>
       </c>
-      <c r="E15" s="22" t="inlineStr">
+      <c r="E15" s="24" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F15" s="22" t="inlineStr">
+      <c r="F15" s="24" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G15" s="22" t="inlineStr">
+      <c r="G15" s="24" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H15" s="22" t="inlineStr">
+      <c r="H15" s="24" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I15" s="23" t="n">
+      <c r="I15" s="25" t="n">
         <v>1</v>
       </c>
       <c r="J15" s="8" t="inlineStr">
@@ -1140,12 +1146,12 @@
       <c r="K15" s="8" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="22" t="inlineStr">
+      <c r="A16" s="24" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
       </c>
-      <c r="B16" s="22" t="inlineStr">
+      <c r="B16" s="24" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1156,27 +1162,27 @@
         </is>
       </c>
       <c r="D16" s="8" t="n"/>
-      <c r="E16" s="22" t="inlineStr">
+      <c r="E16" s="24" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F16" s="22" t="inlineStr">
+      <c r="F16" s="24" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G16" s="22" t="inlineStr">
+      <c r="G16" s="24" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H16" s="22" t="inlineStr">
+      <c r="H16" s="24" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I16" s="23" t="n">
+      <c r="I16" s="25" t="n">
         <v>1</v>
       </c>
       <c r="J16" s="8" t="inlineStr">
@@ -1187,12 +1193,12 @@
       <c r="K16" s="8" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="22" t="inlineStr">
+      <c r="A17" s="24" t="inlineStr">
         <is>
           <t>2.6</t>
         </is>
       </c>
-      <c r="B17" s="22" t="inlineStr">
+      <c r="B17" s="24" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1207,27 +1213,27 @@
           <t>과제별 정책·프롬프트·검증 규칙</t>
         </is>
       </c>
-      <c r="E17" s="22" t="inlineStr">
+      <c r="E17" s="24" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F17" s="22" t="inlineStr">
+      <c r="F17" s="24" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G17" s="22" t="inlineStr">
+      <c r="G17" s="24" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H17" s="22" t="inlineStr">
+      <c r="H17" s="24" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I17" s="23" t="n">
+      <c r="I17" s="25" t="n">
         <v>1</v>
       </c>
       <c r="J17" s="8" t="inlineStr">
@@ -1238,12 +1244,12 @@
       <c r="K17" s="8" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="22" t="inlineStr">
+      <c r="A18" s="24" t="inlineStr">
         <is>
           <t>2.7</t>
         </is>
       </c>
-      <c r="B18" s="22" t="inlineStr">
+      <c r="B18" s="24" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1258,27 +1264,27 @@
           <t>한국어 오류 문구, API 문서</t>
         </is>
       </c>
-      <c r="E18" s="22" t="inlineStr">
+      <c r="E18" s="24" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F18" s="22" t="inlineStr">
+      <c r="F18" s="24" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G18" s="22" t="inlineStr">
+      <c r="G18" s="24" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H18" s="22" t="inlineStr">
+      <c r="H18" s="24" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I18" s="23" t="n">
+      <c r="I18" s="25" t="n">
         <v>1</v>
       </c>
       <c r="J18" s="8" t="inlineStr">
@@ -1289,12 +1295,12 @@
       <c r="K18" s="8" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="22" t="inlineStr">
+      <c r="A19" s="24" t="inlineStr">
         <is>
           <t>2.8</t>
         </is>
       </c>
-      <c r="B19" s="22" t="inlineStr">
+      <c r="B19" s="24" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1309,27 +1315,27 @@
           <t>API에 맞춘 최소 화면, 개발 안내(CLAUDE.md)</t>
         </is>
       </c>
-      <c r="E19" s="22" t="inlineStr">
+      <c r="E19" s="24" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F19" s="22" t="inlineStr">
+      <c r="F19" s="24" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G19" s="22" t="inlineStr">
+      <c r="G19" s="24" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H19" s="22" t="inlineStr">
+      <c r="H19" s="24" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I19" s="23" t="n">
+      <c r="I19" s="25" t="n">
         <v>1</v>
       </c>
       <c r="J19" s="8" t="inlineStr">
@@ -1368,12 +1374,12 @@
       <c r="K20" s="5" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="22" t="inlineStr">
+      <c r="A21" s="24" t="inlineStr">
         <is>
           <t>3.1</t>
         </is>
       </c>
-      <c r="B21" s="22" t="inlineStr">
+      <c r="B21" s="24" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
@@ -1388,23 +1394,23 @@
           <t>전체 화면 흐름 HTML 프로토타입</t>
         </is>
       </c>
-      <c r="E21" s="22" t="inlineStr">
+      <c r="E21" s="24" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
       </c>
-      <c r="F21" s="22" t="n"/>
-      <c r="G21" s="22" t="inlineStr">
+      <c r="F21" s="24" t="n"/>
+      <c r="G21" s="24" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H21" s="22" t="inlineStr">
+      <c r="H21" s="24" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I21" s="23" t="n">
+      <c r="I21" s="25" t="n">
         <v>1</v>
       </c>
       <c r="J21" s="8" t="inlineStr">
@@ -1415,12 +1421,12 @@
       <c r="K21" s="8" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="22" t="inlineStr">
+      <c r="A22" s="24" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
       </c>
-      <c r="B22" s="22" t="inlineStr">
+      <c r="B22" s="24" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
@@ -1435,27 +1441,27 @@
           <t>모든 질문에 '다른 예시 보기', 모드 설명, 이미지 블록, 생성 중·실패·최신 아님 상태</t>
         </is>
       </c>
-      <c r="E22" s="22" t="inlineStr">
+      <c r="E22" s="24" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
       </c>
-      <c r="F22" s="22" t="inlineStr">
+      <c r="F22" s="24" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G22" s="22" t="inlineStr">
+      <c r="G22" s="24" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H22" s="22" t="inlineStr">
+      <c r="H22" s="24" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I22" s="23" t="n">
+      <c r="I22" s="25" t="n">
         <v>1</v>
       </c>
       <c r="J22" s="8" t="inlineStr">
@@ -1466,12 +1472,12 @@
       <c r="K22" s="8" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="22" t="inlineStr">
+      <c r="A23" s="24" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
       </c>
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B23" s="24" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
@@ -1486,31 +1492,31 @@
           <t>반응형 자동 배치 확인</t>
         </is>
       </c>
-      <c r="E23" s="22" t="inlineStr">
+      <c r="E23" s="24" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
       </c>
-      <c r="F23" s="22" t="n"/>
-      <c r="G23" s="22" t="n"/>
-      <c r="H23" s="22" t="inlineStr">
+      <c r="F23" s="24" t="n"/>
+      <c r="G23" s="24" t="n"/>
+      <c r="H23" s="24" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="I23" s="23" t="n">
+      <c r="I23" s="25" t="n">
         <v>0</v>
       </c>
       <c r="J23" s="8" t="n"/>
       <c r="K23" s="8" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="22" t="inlineStr">
+      <c r="A24" s="24" t="inlineStr">
         <is>
           <t>3.4</t>
         </is>
       </c>
-      <c r="B24" s="22" t="inlineStr">
+      <c r="B24" s="24" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
@@ -1525,19 +1531,19 @@
           <t>/preview 화면을 html.to.design으로 가져와 수정</t>
         </is>
       </c>
-      <c r="E24" s="22" t="inlineStr">
+      <c r="E24" s="24" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
       </c>
-      <c r="F24" s="22" t="n"/>
-      <c r="G24" s="22" t="n"/>
-      <c r="H24" s="22" t="inlineStr">
+      <c r="F24" s="24" t="n"/>
+      <c r="G24" s="24" t="n"/>
+      <c r="H24" s="24" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="I24" s="23" t="n">
+      <c r="I24" s="25" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="8" t="n"/>
@@ -1572,12 +1578,12 @@
       <c r="K25" s="5" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="22" t="inlineStr">
+      <c r="A26" s="24" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
       </c>
-      <c r="B26" s="22" t="inlineStr">
+      <c r="B26" s="24" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1592,27 +1598,27 @@
           <t>버셀 배포 설정 포함</t>
         </is>
       </c>
-      <c r="E26" s="22" t="inlineStr">
+      <c r="E26" s="24" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F26" s="22" t="inlineStr">
+      <c r="F26" s="24" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G26" s="22" t="inlineStr">
+      <c r="G26" s="24" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H26" s="22" t="inlineStr">
+      <c r="H26" s="24" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I26" s="23" t="n">
+      <c r="I26" s="25" t="n">
         <v>1</v>
       </c>
       <c r="J26" s="8" t="inlineStr">
@@ -1623,12 +1629,12 @@
       <c r="K26" s="8" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="22" t="inlineStr">
+      <c r="A27" s="24" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
       </c>
-      <c r="B27" s="22" t="inlineStr">
+      <c r="B27" s="24" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1643,27 +1649,27 @@
           <t>답변 종류, 흐름 패널, 익명 사용자</t>
         </is>
       </c>
-      <c r="E27" s="22" t="inlineStr">
+      <c r="E27" s="24" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F27" s="22" t="inlineStr">
+      <c r="F27" s="24" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G27" s="22" t="inlineStr">
+      <c r="G27" s="24" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H27" s="22" t="inlineStr">
+      <c r="H27" s="24" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I27" s="23" t="n">
+      <c r="I27" s="25" t="n">
         <v>1</v>
       </c>
       <c r="J27" s="8" t="inlineStr">
@@ -1674,12 +1680,12 @@
       <c r="K27" s="8" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="22" t="inlineStr">
+      <c r="A28" s="24" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
       </c>
-      <c r="B28" s="22" t="inlineStr">
+      <c r="B28" s="24" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1694,27 +1700,27 @@
           <t>서버 저장(SQLite), 문서 내려받기</t>
         </is>
       </c>
-      <c r="E28" s="22" t="inlineStr">
+      <c r="E28" s="24" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F28" s="22" t="inlineStr">
+      <c r="F28" s="24" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G28" s="22" t="inlineStr">
+      <c r="G28" s="24" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H28" s="22" t="inlineStr">
+      <c r="H28" s="24" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I28" s="23" t="n">
+      <c r="I28" s="25" t="n">
         <v>1</v>
       </c>
       <c r="J28" s="8" t="inlineStr">
@@ -1725,12 +1731,12 @@
       <c r="K28" s="8" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="22" t="inlineStr">
+      <c r="A29" s="24" t="inlineStr">
         <is>
           <t>4.4</t>
         </is>
       </c>
-      <c r="B29" s="22" t="inlineStr">
+      <c r="B29" s="24" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1745,27 +1751,27 @@
           <t>결과를 섹션·블록으로</t>
         </is>
       </c>
-      <c r="E29" s="22" t="inlineStr">
+      <c r="E29" s="24" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F29" s="22" t="inlineStr">
+      <c r="F29" s="24" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G29" s="22" t="inlineStr">
+      <c r="G29" s="24" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H29" s="22" t="inlineStr">
+      <c r="H29" s="24" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I29" s="23" t="n">
+      <c r="I29" s="25" t="n">
         <v>1</v>
       </c>
       <c r="J29" s="8" t="inlineStr">
@@ -1776,12 +1782,12 @@
       <c r="K29" s="8" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="22" t="inlineStr">
+      <c r="A30" s="24" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
       </c>
-      <c r="B30" s="22" t="inlineStr">
+      <c r="B30" s="24" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1796,27 +1802,27 @@
           <t>샘플 근거 자료, 자리표시 이미지</t>
         </is>
       </c>
-      <c r="E30" s="22" t="inlineStr">
+      <c r="E30" s="24" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F30" s="22" t="inlineStr">
+      <c r="F30" s="24" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G30" s="22" t="inlineStr">
+      <c r="G30" s="24" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H30" s="22" t="inlineStr">
+      <c r="H30" s="24" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I30" s="23" t="n">
+      <c r="I30" s="25" t="n">
         <v>1</v>
       </c>
       <c r="J30" s="8" t="inlineStr">
@@ -1827,12 +1833,12 @@
       <c r="K30" s="8" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="22" t="inlineStr">
+      <c r="A31" s="24" t="inlineStr">
         <is>
           <t>4.6</t>
         </is>
       </c>
-      <c r="B31" s="22" t="inlineStr">
+      <c r="B31" s="24" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1847,27 +1853,27 @@
           <t>생성 중·생성 실패 화면, 최신 아님 배너, 이미지 상자, 모드 설명</t>
         </is>
       </c>
-      <c r="E31" s="22" t="inlineStr">
+      <c r="E31" s="24" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F31" s="22" t="inlineStr">
+      <c r="F31" s="24" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G31" s="22" t="inlineStr">
+      <c r="G31" s="24" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H31" s="22" t="inlineStr">
+      <c r="H31" s="24" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I31" s="23" t="n">
+      <c r="I31" s="25" t="n">
         <v>1</v>
       </c>
       <c r="J31" s="8" t="inlineStr">
@@ -1878,12 +1884,12 @@
       <c r="K31" s="8" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="22" t="inlineStr">
+      <c r="A32" s="24" t="inlineStr">
         <is>
           <t>4.7</t>
         </is>
       </c>
-      <c r="B32" s="22" t="inlineStr">
+      <c r="B32" s="24" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1898,27 +1904,27 @@
           <t>이전 결과를 다음 과제의 기준으로 가져오기</t>
         </is>
       </c>
-      <c r="E32" s="22" t="inlineStr">
+      <c r="E32" s="24" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F32" s="22" t="inlineStr">
+      <c r="F32" s="24" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G32" s="22" t="inlineStr">
+      <c r="G32" s="24" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H32" s="22" t="inlineStr">
+      <c r="H32" s="24" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I32" s="23" t="n">
+      <c r="I32" s="25" t="n">
         <v>1</v>
       </c>
       <c r="J32" s="8" t="inlineStr">
@@ -1957,12 +1963,12 @@
       <c r="K33" s="5" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="22" t="inlineStr">
+      <c r="A34" s="24" t="inlineStr">
         <is>
           <t>5.1</t>
         </is>
       </c>
-      <c r="B34" s="22" t="inlineStr">
+      <c r="B34" s="24" t="inlineStr">
         <is>
           <t>배포</t>
         </is>
@@ -1977,27 +1983,27 @@
           <t>main은 정식 주소, PR마다 미리보기 주소</t>
         </is>
       </c>
-      <c r="E34" s="22" t="inlineStr">
+      <c r="E34" s="24" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F34" s="22" t="inlineStr">
+      <c r="F34" s="24" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="G34" s="22" t="inlineStr">
+      <c r="G34" s="24" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="H34" s="22" t="inlineStr">
+      <c r="H34" s="24" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I34" s="23" t="n">
+      <c r="I34" s="25" t="n">
         <v>1</v>
       </c>
       <c r="J34" s="8" t="inlineStr">
@@ -2012,12 +2018,12 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="22" t="inlineStr">
+      <c r="A35" s="24" t="inlineStr">
         <is>
           <t>5.2</t>
         </is>
       </c>
-      <c r="B35" s="22" t="inlineStr">
+      <c r="B35" s="24" t="inlineStr">
         <is>
           <t>배포</t>
         </is>
@@ -2032,27 +2038,27 @@
           <t>저장 디스크 방식 정하기, 프론트와 연결</t>
         </is>
       </c>
-      <c r="E35" s="22" t="inlineStr">
+      <c r="E35" s="24" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F35" s="22" t="inlineStr">
+      <c r="F35" s="24" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="G35" s="22" t="inlineStr">
+      <c r="G35" s="24" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="H35" s="22" t="inlineStr">
+      <c r="H35" s="24" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I35" s="23" t="n">
+      <c r="I35" s="25" t="n">
         <v>1</v>
       </c>
       <c r="J35" s="8" t="inlineStr">
@@ -2088,19 +2094,19 @@
       <c r="G36" s="4" t="n"/>
       <c r="H36" s="4" t="n"/>
       <c r="I36" s="6">
-        <f>IFERROR(AVERAGE(I37:I41),0)</f>
+        <f>IFERROR(AVERAGE(I37:I42),0)</f>
         <v/>
       </c>
       <c r="J36" s="5" t="n"/>
       <c r="K36" s="5" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="22" t="inlineStr">
+      <c r="A37" s="24" t="inlineStr">
         <is>
           <t>6.1</t>
         </is>
       </c>
-      <c r="B37" s="22" t="inlineStr">
+      <c r="B37" s="24" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
@@ -2115,27 +2121,27 @@
           <t>가짜 모델(Mock) 대신 실제 모델</t>
         </is>
       </c>
-      <c r="E37" s="22" t="inlineStr">
+      <c r="E37" s="24" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F37" s="22" t="inlineStr">
+      <c r="F37" s="24" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="G37" s="22" t="inlineStr">
+      <c r="G37" s="24" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="H37" s="22" t="inlineStr">
+      <c r="H37" s="24" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I37" s="23" t="n">
+      <c r="I37" s="25" t="n">
         <v>1</v>
       </c>
       <c r="J37" s="8" t="inlineStr">
@@ -2150,12 +2156,12 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="22" t="inlineStr">
+      <c r="A38" s="24" t="inlineStr">
         <is>
           <t>6.2</t>
         </is>
       </c>
-      <c r="B38" s="22" t="inlineStr">
+      <c r="B38" s="24" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
@@ -2170,31 +2176,31 @@
           <t>준비도 기준·항목 가중치·프롬프트를 시나리오로 측정</t>
         </is>
       </c>
-      <c r="E38" s="22" t="inlineStr">
+      <c r="E38" s="24" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F38" s="22" t="n"/>
-      <c r="G38" s="22" t="n"/>
-      <c r="H38" s="22" t="inlineStr">
+      <c r="F38" s="24" t="n"/>
+      <c r="G38" s="24" t="n"/>
+      <c r="H38" s="24" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="I38" s="23" t="n">
+      <c r="I38" s="25" t="n">
         <v>0</v>
       </c>
       <c r="J38" s="8" t="n"/>
       <c r="K38" s="8" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="22" t="inlineStr">
+      <c r="A39" s="24" t="inlineStr">
         <is>
           <t>6.3</t>
         </is>
       </c>
-      <c r="B39" s="22" t="inlineStr">
+      <c r="B39" s="24" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
@@ -2209,31 +2215,31 @@
           <t>지금의 자리표시·샘플 자리에 실제 기능 연결</t>
         </is>
       </c>
-      <c r="E39" s="22" t="inlineStr">
+      <c r="E39" s="24" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F39" s="22" t="n"/>
-      <c r="G39" s="22" t="n"/>
-      <c r="H39" s="22" t="inlineStr">
+      <c r="F39" s="24" t="n"/>
+      <c r="G39" s="24" t="n"/>
+      <c r="H39" s="24" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="I39" s="23" t="n">
+      <c r="I39" s="25" t="n">
         <v>0</v>
       </c>
       <c r="J39" s="8" t="n"/>
       <c r="K39" s="8" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="22" t="inlineStr">
+      <c r="A40" s="24" t="inlineStr">
         <is>
           <t>6.4</t>
         </is>
       </c>
-      <c r="B40" s="22" t="inlineStr">
+      <c r="B40" s="24" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
@@ -2244,27 +2250,27 @@
         </is>
       </c>
       <c r="D40" s="8" t="n"/>
-      <c r="E40" s="22" t="inlineStr">
+      <c r="E40" s="24" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F40" s="22" t="inlineStr">
+      <c r="F40" s="24" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="G40" s="22" t="inlineStr">
+      <c r="G40" s="24" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="H40" s="22" t="inlineStr">
+      <c r="H40" s="24" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I40" s="23" t="n">
+      <c r="I40" s="25" t="n">
         <v>1</v>
       </c>
       <c r="J40" s="8" t="inlineStr">
@@ -2275,12 +2281,12 @@
       <c r="K40" s="8" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="22" t="inlineStr">
+      <c r="A41" s="24" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="B41" s="22" t="inlineStr">
+      <c r="B41" s="24" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
@@ -2291,27 +2297,27 @@
         </is>
       </c>
       <c r="D41" s="8" t="n"/>
-      <c r="E41" s="22" t="inlineStr">
+      <c r="E41" s="24" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F41" s="22" t="inlineStr">
+      <c r="F41" s="24" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="G41" s="22" t="inlineStr">
+      <c r="G41" s="24" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="H41" s="22" t="inlineStr">
+      <c r="H41" s="24" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I41" s="23" t="n">
+      <c r="I41" s="25" t="n">
         <v>1</v>
       </c>
       <c r="J41" s="8" t="inlineStr">
@@ -2326,110 +2332,157 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="A42" s="24" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
+      <c r="B42" s="24" t="inlineStr">
+        <is>
+          <t>실제 AI 연결</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>단계별 모델 라우팅·하네스 로드맵·인수 안내</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="n"/>
+      <c r="E42" s="24" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F42" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="G42" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="H42" s="24" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I42" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" s="8" t="inlineStr">
+        <is>
+          <t>PR #26</t>
+        </is>
+      </c>
+      <c r="K42" s="8" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>마무리</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
+      <c r="C43" s="5" t="inlineStr">
         <is>
           <t>평가·발표</t>
         </is>
       </c>
-      <c r="D42" s="5" t="n"/>
-      <c r="E42" s="4" t="n"/>
-      <c r="F42" s="4" t="n"/>
-      <c r="G42" s="4" t="n"/>
-      <c r="H42" s="4" t="n"/>
-      <c r="I42" s="6">
-        <f>IFERROR(AVERAGE(I43:I44),0)</f>
-        <v/>
-      </c>
-      <c r="J42" s="5" t="n"/>
-      <c r="K42" s="5" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="22" t="inlineStr">
+      <c r="D43" s="5" t="n"/>
+      <c r="E43" s="4" t="n"/>
+      <c r="F43" s="4" t="n"/>
+      <c r="G43" s="4" t="n"/>
+      <c r="H43" s="4" t="n"/>
+      <c r="I43" s="6">
+        <f>IFERROR(AVERAGE(I44:I45),0)</f>
+        <v/>
+      </c>
+      <c r="J43" s="5" t="n"/>
+      <c r="K43" s="5" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="24" t="inlineStr">
         <is>
           <t>7.1</t>
         </is>
       </c>
-      <c r="B43" s="22" t="inlineStr">
+      <c r="B44" s="24" t="inlineStr">
         <is>
           <t>마무리</t>
         </is>
       </c>
-      <c r="C43" s="8" t="inlineStr">
+      <c r="C44" s="8" t="inlineStr">
         <is>
           <t>사용성 확인·평가 지표 측정</t>
         </is>
       </c>
-      <c r="D43" s="8" t="inlineStr">
+      <c r="D44" s="8" t="inlineStr">
         <is>
           <t>필수정보 충족률, 질문 효율, 가정 표시율 등(기획서 14장)</t>
         </is>
       </c>
-      <c r="E43" s="22" t="inlineStr">
+      <c r="E44" s="24" t="inlineStr">
         <is>
           <t>공동</t>
         </is>
       </c>
-      <c r="F43" s="22" t="n"/>
-      <c r="G43" s="22" t="n"/>
-      <c r="H43" s="22" t="inlineStr">
+      <c r="F44" s="24" t="n"/>
+      <c r="G44" s="24" t="n"/>
+      <c r="H44" s="24" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="I43" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="8" t="n"/>
-      <c r="K43" s="8" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="22" t="inlineStr">
-        <is>
-          <t>7.2</t>
-        </is>
-      </c>
-      <c r="B44" s="22" t="inlineStr">
-        <is>
-          <t>마무리</t>
-        </is>
-      </c>
-      <c r="C44" s="8" t="inlineStr">
-        <is>
-          <t>최종 발표 자료</t>
-        </is>
-      </c>
-      <c r="D44" s="8" t="n"/>
-      <c r="E44" s="22" t="inlineStr">
-        <is>
-          <t>공동</t>
-        </is>
-      </c>
-      <c r="F44" s="22" t="n"/>
-      <c r="G44" s="22" t="n"/>
-      <c r="H44" s="22" t="inlineStr">
-        <is>
-          <t>예정</t>
-        </is>
-      </c>
-      <c r="I44" s="23" t="n">
+      <c r="I44" s="25" t="n">
         <v>0</v>
       </c>
       <c r="J44" s="8" t="n"/>
       <c r="K44" s="8" t="n"/>
     </row>
+    <row r="45">
+      <c r="A45" s="24" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="B45" s="24" t="inlineStr">
+        <is>
+          <t>마무리</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>최종 발표 자료</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="n"/>
+      <c r="E45" s="24" t="inlineStr">
+        <is>
+          <t>공동</t>
+        </is>
+      </c>
+      <c r="F45" s="24" t="n"/>
+      <c r="G45" s="24" t="n"/>
+      <c r="H45" s="24" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="I45" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="8" t="n"/>
+      <c r="K45" s="8" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:K44"/>
-  <conditionalFormatting sqref="H5:H44">
+  <autoFilter ref="A4:K45"/>
+  <conditionalFormatting sqref="H5:H45">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"완료"</formula>
     </cfRule>
@@ -2440,7 +2493,7 @@
       <formula>"보류"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I5:I44">
+  <conditionalFormatting sqref="I5:I45">
     <cfRule type="dataBar" priority="4">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -2450,10 +2503,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="H5:H44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"완료,진행 중,예정,보류"</formula1>
     </dataValidation>
-    <dataValidation sqref="E5:E44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"개발,디자인,공동"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2524,23 +2577,23 @@
         </is>
       </c>
       <c r="B4" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$44,A4,WBS!$H$5:$H$44,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$45,A4,WBS!$H$5:$H$45,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C4" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$44,A4,WBS!$H$5:$H$44,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$45,A4,WBS!$H$5:$H$45,"완료")</f>
         <v/>
       </c>
       <c r="D4" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$44,A4,WBS!$H$5:$H$44,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$45,A4,WBS!$H$5:$H$45,"진행 중")</f>
         <v/>
       </c>
       <c r="E4" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$44,A4,WBS!$H$5:$H$44,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$45,A4,WBS!$H$5:$H$45,"예정")</f>
         <v/>
       </c>
       <c r="F4" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$44,WBS!$B$5:$B$44,A4,WBS!$H$5:$H$44,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$45,WBS!$B$5:$B$45,A4,WBS!$H$5:$H$45,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2551,23 +2604,23 @@
         </is>
       </c>
       <c r="B5" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$44,A5,WBS!$H$5:$H$44,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$45,A5,WBS!$H$5:$H$45,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C5" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$44,A5,WBS!$H$5:$H$44,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$45,A5,WBS!$H$5:$H$45,"완료")</f>
         <v/>
       </c>
       <c r="D5" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$44,A5,WBS!$H$5:$H$44,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$45,A5,WBS!$H$5:$H$45,"진행 중")</f>
         <v/>
       </c>
       <c r="E5" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$44,A5,WBS!$H$5:$H$44,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$45,A5,WBS!$H$5:$H$45,"예정")</f>
         <v/>
       </c>
       <c r="F5" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$44,WBS!$B$5:$B$44,A5,WBS!$H$5:$H$44,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$45,WBS!$B$5:$B$45,A5,WBS!$H$5:$H$45,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2578,23 +2631,23 @@
         </is>
       </c>
       <c r="B6" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$44,A6,WBS!$H$5:$H$44,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$45,A6,WBS!$H$5:$H$45,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C6" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$44,A6,WBS!$H$5:$H$44,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$45,A6,WBS!$H$5:$H$45,"완료")</f>
         <v/>
       </c>
       <c r="D6" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$44,A6,WBS!$H$5:$H$44,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$45,A6,WBS!$H$5:$H$45,"진행 중")</f>
         <v/>
       </c>
       <c r="E6" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$44,A6,WBS!$H$5:$H$44,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$45,A6,WBS!$H$5:$H$45,"예정")</f>
         <v/>
       </c>
       <c r="F6" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$44,WBS!$B$5:$B$44,A6,WBS!$H$5:$H$44,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$45,WBS!$B$5:$B$45,A6,WBS!$H$5:$H$45,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2605,23 +2658,23 @@
         </is>
       </c>
       <c r="B7" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$44,A7,WBS!$H$5:$H$44,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$45,A7,WBS!$H$5:$H$45,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C7" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$44,A7,WBS!$H$5:$H$44,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$45,A7,WBS!$H$5:$H$45,"완료")</f>
         <v/>
       </c>
       <c r="D7" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$44,A7,WBS!$H$5:$H$44,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$45,A7,WBS!$H$5:$H$45,"진행 중")</f>
         <v/>
       </c>
       <c r="E7" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$44,A7,WBS!$H$5:$H$44,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$45,A7,WBS!$H$5:$H$45,"예정")</f>
         <v/>
       </c>
       <c r="F7" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$44,WBS!$B$5:$B$44,A7,WBS!$H$5:$H$44,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$45,WBS!$B$5:$B$45,A7,WBS!$H$5:$H$45,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2632,23 +2685,23 @@
         </is>
       </c>
       <c r="B8" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$44,A8,WBS!$H$5:$H$44,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$45,A8,WBS!$H$5:$H$45,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C8" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$44,A8,WBS!$H$5:$H$44,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$45,A8,WBS!$H$5:$H$45,"완료")</f>
         <v/>
       </c>
       <c r="D8" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$44,A8,WBS!$H$5:$H$44,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$45,A8,WBS!$H$5:$H$45,"진행 중")</f>
         <v/>
       </c>
       <c r="E8" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$44,A8,WBS!$H$5:$H$44,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$45,A8,WBS!$H$5:$H$45,"예정")</f>
         <v/>
       </c>
       <c r="F8" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$44,WBS!$B$5:$B$44,A8,WBS!$H$5:$H$44,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$45,WBS!$B$5:$B$45,A8,WBS!$H$5:$H$45,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2659,23 +2712,23 @@
         </is>
       </c>
       <c r="B9" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$44,A9,WBS!$H$5:$H$44,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$45,A9,WBS!$H$5:$H$45,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C9" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$44,A9,WBS!$H$5:$H$44,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$45,A9,WBS!$H$5:$H$45,"완료")</f>
         <v/>
       </c>
       <c r="D9" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$44,A9,WBS!$H$5:$H$44,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$45,A9,WBS!$H$5:$H$45,"진행 중")</f>
         <v/>
       </c>
       <c r="E9" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$44,A9,WBS!$H$5:$H$44,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$45,A9,WBS!$H$5:$H$45,"예정")</f>
         <v/>
       </c>
       <c r="F9" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$44,WBS!$B$5:$B$44,A9,WBS!$H$5:$H$44,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$45,WBS!$B$5:$B$45,A9,WBS!$H$5:$H$45,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2686,23 +2739,23 @@
         </is>
       </c>
       <c r="B10" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$44,A10,WBS!$H$5:$H$44,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$45,A10,WBS!$H$5:$H$45,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C10" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$44,A10,WBS!$H$5:$H$44,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$45,A10,WBS!$H$5:$H$45,"완료")</f>
         <v/>
       </c>
       <c r="D10" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$44,A10,WBS!$H$5:$H$44,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$45,A10,WBS!$H$5:$H$45,"진행 중")</f>
         <v/>
       </c>
       <c r="E10" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$44,A10,WBS!$H$5:$H$44,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$45,A10,WBS!$H$5:$H$45,"예정")</f>
         <v/>
       </c>
       <c r="F10" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$44,WBS!$B$5:$B$44,A10,WBS!$H$5:$H$44,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$45,WBS!$B$5:$B$45,A10,WBS!$H$5:$H$45,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2729,7 +2782,7 @@
         <v/>
       </c>
       <c r="F11" s="14">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$44,WBS!$H$5:$H$44,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$45,WBS!$H$5:$H$45,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>

--- a/docs/WBS.xlsx
+++ b/docs/WBS.xlsx
@@ -11,7 +11,7 @@
     <sheet name="요약" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS'!$A$4:$K$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS'!$A$4:$K$46</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -98,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -129,6 +129,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -547,7 +553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K45"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -663,12 +669,12 @@
       <c r="K5" s="5" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="26" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="26" t="inlineStr">
         <is>
           <t>기획·설계</t>
         </is>
@@ -683,23 +689,23 @@
           <t>과제 4개(사업계획·상품기획·브랜딩·마케팅), 적응형 질문, 사실·가정 분리 원칙</t>
         </is>
       </c>
-      <c r="E6" s="24" t="inlineStr">
+      <c r="E6" s="26" t="inlineStr">
         <is>
           <t>공동</t>
         </is>
       </c>
-      <c r="F6" s="24" t="n"/>
-      <c r="G6" s="24" t="inlineStr">
+      <c r="F6" s="26" t="n"/>
+      <c r="G6" s="26" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="H6" s="24" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I6" s="25" t="n">
+      <c r="H6" s="26" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I6" s="27" t="n">
         <v>1</v>
       </c>
       <c r="J6" s="8" t="inlineStr">
@@ -710,12 +716,12 @@
       <c r="K6" s="8" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="26" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B7" s="26" t="inlineStr">
         <is>
           <t>기획·설계</t>
         </is>
@@ -730,27 +736,27 @@
           <t>FastAPI 하네스 구조, API 계약, 테스트 전략</t>
         </is>
       </c>
-      <c r="E7" s="24" t="inlineStr">
+      <c r="E7" s="26" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F7" s="24" t="inlineStr">
+      <c r="F7" s="26" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="G7" s="24" t="inlineStr">
+      <c r="G7" s="26" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="H7" s="24" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I7" s="25" t="n">
+      <c r="H7" s="26" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I7" s="27" t="n">
         <v>1</v>
       </c>
       <c r="J7" s="8" t="inlineStr">
@@ -761,12 +767,12 @@
       <c r="K7" s="8" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="26" t="inlineStr">
         <is>
           <t>1.3</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="26" t="inlineStr">
         <is>
           <t>기획·설계</t>
         </is>
@@ -781,27 +787,27 @@
           <t>V2 화면 흐름, 묶음 0~4로 작업 나누기</t>
         </is>
       </c>
-      <c r="E8" s="24" t="inlineStr">
+      <c r="E8" s="26" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F8" s="24" t="inlineStr">
+      <c r="F8" s="26" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G8" s="24" t="inlineStr">
+      <c r="G8" s="26" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H8" s="24" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I8" s="25" t="n">
+      <c r="H8" s="26" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I8" s="27" t="n">
         <v>1</v>
       </c>
       <c r="J8" s="8" t="inlineStr">
@@ -812,12 +818,12 @@
       <c r="K8" s="8" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" s="26" t="inlineStr">
         <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B9" s="26" t="inlineStr">
         <is>
           <t>기획·설계</t>
         </is>
@@ -832,27 +838,27 @@
           <t>지금 상태·다음 할 일·작업 방식·환경 팁, PR마다 갱신</t>
         </is>
       </c>
-      <c r="E9" s="24" t="inlineStr">
+      <c r="E9" s="26" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F9" s="24" t="inlineStr">
+      <c r="F9" s="26" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="G9" s="24" t="inlineStr">
+      <c r="G9" s="26" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="H9" s="24" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I9" s="25" t="n">
+      <c r="H9" s="26" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I9" s="27" t="n">
         <v>1</v>
       </c>
       <c r="J9" s="8" t="inlineStr">
@@ -863,12 +869,12 @@
       <c r="K9" s="8" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" s="26" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="26" t="inlineStr">
         <is>
           <t>기획·설계</t>
         </is>
@@ -883,27 +889,27 @@
           <t>바로 보기 주소, 된 것, 남은 일·맡을 사람·상의할 점</t>
         </is>
       </c>
-      <c r="E10" s="24" t="inlineStr">
+      <c r="E10" s="26" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F10" s="24" t="inlineStr">
+      <c r="F10" s="26" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="G10" s="24" t="inlineStr">
+      <c r="G10" s="26" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="H10" s="24" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I10" s="25" t="n">
+      <c r="H10" s="26" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I10" s="27" t="n">
         <v>1</v>
       </c>
       <c r="J10" s="8" t="inlineStr">
@@ -942,12 +948,12 @@
       <c r="K11" s="5" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="24" t="inlineStr">
+      <c r="A12" s="26" t="inlineStr">
         <is>
           <t>2.1</t>
         </is>
       </c>
-      <c r="B12" s="24" t="inlineStr">
+      <c r="B12" s="26" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -962,27 +968,27 @@
           <t>사실·가정·미정 구분, 정보 출처 표시</t>
         </is>
       </c>
-      <c r="E12" s="24" t="inlineStr">
+      <c r="E12" s="26" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F12" s="24" t="inlineStr">
+      <c r="F12" s="26" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="G12" s="24" t="inlineStr">
+      <c r="G12" s="26" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H12" s="24" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I12" s="25" t="n">
+      <c r="H12" s="26" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I12" s="27" t="n">
         <v>1</v>
       </c>
       <c r="J12" s="8" t="inlineStr">
@@ -993,12 +999,12 @@
       <c r="K12" s="8" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="24" t="inlineStr">
+      <c r="A13" s="26" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
       </c>
-      <c r="B13" s="24" t="inlineStr">
+      <c r="B13" s="26" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1013,27 +1019,27 @@
           <t>비용 없이 개발·테스트하는 가짜 모델</t>
         </is>
       </c>
-      <c r="E13" s="24" t="inlineStr">
+      <c r="E13" s="26" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F13" s="24" t="inlineStr">
+      <c r="F13" s="26" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="G13" s="24" t="inlineStr">
+      <c r="G13" s="26" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H13" s="24" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I13" s="25" t="n">
+      <c r="H13" s="26" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I13" s="27" t="n">
         <v>1</v>
       </c>
       <c r="J13" s="8" t="inlineStr">
@@ -1044,12 +1050,12 @@
       <c r="K13" s="8" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="24" t="inlineStr">
+      <c r="A14" s="26" t="inlineStr">
         <is>
           <t>2.3</t>
         </is>
       </c>
-      <c r="B14" s="24" t="inlineStr">
+      <c r="B14" s="26" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1064,27 +1070,27 @@
           <t>과제별 질문 정책(policy.yaml), 단계별 프롬프트</t>
         </is>
       </c>
-      <c r="E14" s="24" t="inlineStr">
+      <c r="E14" s="26" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F14" s="24" t="inlineStr">
+      <c r="F14" s="26" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G14" s="24" t="inlineStr">
+      <c r="G14" s="26" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H14" s="24" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I14" s="25" t="n">
+      <c r="H14" s="26" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I14" s="27" t="n">
         <v>1</v>
       </c>
       <c r="J14" s="8" t="inlineStr">
@@ -1095,12 +1101,12 @@
       <c r="K14" s="8" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="24" t="inlineStr">
+      <c r="A15" s="26" t="inlineStr">
         <is>
           <t>2.4</t>
         </is>
       </c>
-      <c r="B15" s="24" t="inlineStr">
+      <c r="B15" s="26" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1115,27 +1121,27 @@
           <t>모드별 질문 상한, '다른 예시 보기' 단계</t>
         </is>
       </c>
-      <c r="E15" s="24" t="inlineStr">
+      <c r="E15" s="26" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F15" s="24" t="inlineStr">
+      <c r="F15" s="26" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G15" s="24" t="inlineStr">
+      <c r="G15" s="26" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H15" s="24" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I15" s="25" t="n">
+      <c r="H15" s="26" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I15" s="27" t="n">
         <v>1</v>
       </c>
       <c r="J15" s="8" t="inlineStr">
@@ -1146,12 +1152,12 @@
       <c r="K15" s="8" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="24" t="inlineStr">
+      <c r="A16" s="26" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
       </c>
-      <c r="B16" s="24" t="inlineStr">
+      <c r="B16" s="26" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1162,27 +1168,27 @@
         </is>
       </c>
       <c r="D16" s="8" t="n"/>
-      <c r="E16" s="24" t="inlineStr">
+      <c r="E16" s="26" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F16" s="24" t="inlineStr">
+      <c r="F16" s="26" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G16" s="24" t="inlineStr">
+      <c r="G16" s="26" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H16" s="24" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I16" s="25" t="n">
+      <c r="H16" s="26" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I16" s="27" t="n">
         <v>1</v>
       </c>
       <c r="J16" s="8" t="inlineStr">
@@ -1193,12 +1199,12 @@
       <c r="K16" s="8" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="24" t="inlineStr">
+      <c r="A17" s="26" t="inlineStr">
         <is>
           <t>2.6</t>
         </is>
       </c>
-      <c r="B17" s="24" t="inlineStr">
+      <c r="B17" s="26" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1213,27 +1219,27 @@
           <t>과제별 정책·프롬프트·검증 규칙</t>
         </is>
       </c>
-      <c r="E17" s="24" t="inlineStr">
+      <c r="E17" s="26" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F17" s="24" t="inlineStr">
+      <c r="F17" s="26" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G17" s="24" t="inlineStr">
+      <c r="G17" s="26" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H17" s="24" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I17" s="25" t="n">
+      <c r="H17" s="26" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I17" s="27" t="n">
         <v>1</v>
       </c>
       <c r="J17" s="8" t="inlineStr">
@@ -1244,12 +1250,12 @@
       <c r="K17" s="8" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="24" t="inlineStr">
+      <c r="A18" s="26" t="inlineStr">
         <is>
           <t>2.7</t>
         </is>
       </c>
-      <c r="B18" s="24" t="inlineStr">
+      <c r="B18" s="26" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1264,27 +1270,27 @@
           <t>한국어 오류 문구, API 문서</t>
         </is>
       </c>
-      <c r="E18" s="24" t="inlineStr">
+      <c r="E18" s="26" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F18" s="24" t="inlineStr">
+      <c r="F18" s="26" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G18" s="24" t="inlineStr">
+      <c r="G18" s="26" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H18" s="24" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I18" s="25" t="n">
+      <c r="H18" s="26" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I18" s="27" t="n">
         <v>1</v>
       </c>
       <c r="J18" s="8" t="inlineStr">
@@ -1295,12 +1301,12 @@
       <c r="K18" s="8" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="24" t="inlineStr">
+      <c r="A19" s="26" t="inlineStr">
         <is>
           <t>2.8</t>
         </is>
       </c>
-      <c r="B19" s="24" t="inlineStr">
+      <c r="B19" s="26" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1315,27 +1321,27 @@
           <t>API에 맞춘 최소 화면, 개발 안내(CLAUDE.md)</t>
         </is>
       </c>
-      <c r="E19" s="24" t="inlineStr">
+      <c r="E19" s="26" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F19" s="24" t="inlineStr">
+      <c r="F19" s="26" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G19" s="24" t="inlineStr">
+      <c r="G19" s="26" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H19" s="24" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I19" s="25" t="n">
+      <c r="H19" s="26" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I19" s="27" t="n">
         <v>1</v>
       </c>
       <c r="J19" s="8" t="inlineStr">
@@ -1374,12 +1380,12 @@
       <c r="K20" s="5" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="24" t="inlineStr">
+      <c r="A21" s="26" t="inlineStr">
         <is>
           <t>3.1</t>
         </is>
       </c>
-      <c r="B21" s="24" t="inlineStr">
+      <c r="B21" s="26" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
@@ -1394,23 +1400,23 @@
           <t>전체 화면 흐름 HTML 프로토타입</t>
         </is>
       </c>
-      <c r="E21" s="24" t="inlineStr">
+      <c r="E21" s="26" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
       </c>
-      <c r="F21" s="24" t="n"/>
-      <c r="G21" s="24" t="inlineStr">
+      <c r="F21" s="26" t="n"/>
+      <c r="G21" s="26" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H21" s="24" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I21" s="25" t="n">
+      <c r="H21" s="26" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I21" s="27" t="n">
         <v>1</v>
       </c>
       <c r="J21" s="8" t="inlineStr">
@@ -1421,12 +1427,12 @@
       <c r="K21" s="8" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="24" t="inlineStr">
+      <c r="A22" s="26" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
       </c>
-      <c r="B22" s="24" t="inlineStr">
+      <c r="B22" s="26" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
@@ -1441,27 +1447,27 @@
           <t>모든 질문에 '다른 예시 보기', 모드 설명, 이미지 블록, 생성 중·실패·최신 아님 상태</t>
         </is>
       </c>
-      <c r="E22" s="24" t="inlineStr">
+      <c r="E22" s="26" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
       </c>
-      <c r="F22" s="24" t="inlineStr">
+      <c r="F22" s="26" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G22" s="24" t="inlineStr">
+      <c r="G22" s="26" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H22" s="24" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I22" s="25" t="n">
+      <c r="H22" s="26" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I22" s="27" t="n">
         <v>1</v>
       </c>
       <c r="J22" s="8" t="inlineStr">
@@ -1472,12 +1478,12 @@
       <c r="K22" s="8" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="24" t="inlineStr">
+      <c r="A23" s="26" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
       </c>
-      <c r="B23" s="24" t="inlineStr">
+      <c r="B23" s="26" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
@@ -1492,31 +1498,31 @@
           <t>반응형 자동 배치 확인</t>
         </is>
       </c>
-      <c r="E23" s="24" t="inlineStr">
+      <c r="E23" s="26" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
       </c>
-      <c r="F23" s="24" t="n"/>
-      <c r="G23" s="24" t="n"/>
-      <c r="H23" s="24" t="inlineStr">
+      <c r="F23" s="26" t="n"/>
+      <c r="G23" s="26" t="n"/>
+      <c r="H23" s="26" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="I23" s="25" t="n">
+      <c r="I23" s="27" t="n">
         <v>0</v>
       </c>
       <c r="J23" s="8" t="n"/>
       <c r="K23" s="8" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="24" t="inlineStr">
+      <c r="A24" s="26" t="inlineStr">
         <is>
           <t>3.4</t>
         </is>
       </c>
-      <c r="B24" s="24" t="inlineStr">
+      <c r="B24" s="26" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
@@ -1531,19 +1537,19 @@
           <t>/preview 화면을 html.to.design으로 가져와 수정</t>
         </is>
       </c>
-      <c r="E24" s="24" t="inlineStr">
+      <c r="E24" s="26" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
       </c>
-      <c r="F24" s="24" t="n"/>
-      <c r="G24" s="24" t="n"/>
-      <c r="H24" s="24" t="inlineStr">
+      <c r="F24" s="26" t="n"/>
+      <c r="G24" s="26" t="n"/>
+      <c r="H24" s="26" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="I24" s="25" t="n">
+      <c r="I24" s="27" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="8" t="n"/>
@@ -1578,12 +1584,12 @@
       <c r="K25" s="5" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="24" t="inlineStr">
+      <c r="A26" s="26" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
       </c>
-      <c r="B26" s="24" t="inlineStr">
+      <c r="B26" s="26" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1598,27 +1604,27 @@
           <t>버셀 배포 설정 포함</t>
         </is>
       </c>
-      <c r="E26" s="24" t="inlineStr">
+      <c r="E26" s="26" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F26" s="24" t="inlineStr">
+      <c r="F26" s="26" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G26" s="24" t="inlineStr">
+      <c r="G26" s="26" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H26" s="24" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I26" s="25" t="n">
+      <c r="H26" s="26" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I26" s="27" t="n">
         <v>1</v>
       </c>
       <c r="J26" s="8" t="inlineStr">
@@ -1629,12 +1635,12 @@
       <c r="K26" s="8" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="24" t="inlineStr">
+      <c r="A27" s="26" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
       </c>
-      <c r="B27" s="24" t="inlineStr">
+      <c r="B27" s="26" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1649,27 +1655,27 @@
           <t>답변 종류, 흐름 패널, 익명 사용자</t>
         </is>
       </c>
-      <c r="E27" s="24" t="inlineStr">
+      <c r="E27" s="26" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F27" s="24" t="inlineStr">
+      <c r="F27" s="26" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G27" s="24" t="inlineStr">
+      <c r="G27" s="26" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H27" s="24" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I27" s="25" t="n">
+      <c r="H27" s="26" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I27" s="27" t="n">
         <v>1</v>
       </c>
       <c r="J27" s="8" t="inlineStr">
@@ -1680,12 +1686,12 @@
       <c r="K27" s="8" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="24" t="inlineStr">
+      <c r="A28" s="26" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
       </c>
-      <c r="B28" s="24" t="inlineStr">
+      <c r="B28" s="26" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1700,27 +1706,27 @@
           <t>서버 저장(SQLite), 문서 내려받기</t>
         </is>
       </c>
-      <c r="E28" s="24" t="inlineStr">
+      <c r="E28" s="26" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F28" s="24" t="inlineStr">
+      <c r="F28" s="26" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G28" s="24" t="inlineStr">
+      <c r="G28" s="26" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H28" s="24" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I28" s="25" t="n">
+      <c r="H28" s="26" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I28" s="27" t="n">
         <v>1</v>
       </c>
       <c r="J28" s="8" t="inlineStr">
@@ -1731,12 +1737,12 @@
       <c r="K28" s="8" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="24" t="inlineStr">
+      <c r="A29" s="26" t="inlineStr">
         <is>
           <t>4.4</t>
         </is>
       </c>
-      <c r="B29" s="24" t="inlineStr">
+      <c r="B29" s="26" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1751,27 +1757,27 @@
           <t>결과를 섹션·블록으로</t>
         </is>
       </c>
-      <c r="E29" s="24" t="inlineStr">
+      <c r="E29" s="26" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F29" s="24" t="inlineStr">
+      <c r="F29" s="26" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G29" s="24" t="inlineStr">
+      <c r="G29" s="26" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H29" s="24" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I29" s="25" t="n">
+      <c r="H29" s="26" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I29" s="27" t="n">
         <v>1</v>
       </c>
       <c r="J29" s="8" t="inlineStr">
@@ -1782,12 +1788,12 @@
       <c r="K29" s="8" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="24" t="inlineStr">
+      <c r="A30" s="26" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
       </c>
-      <c r="B30" s="24" t="inlineStr">
+      <c r="B30" s="26" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1802,27 +1808,27 @@
           <t>샘플 근거 자료, 자리표시 이미지</t>
         </is>
       </c>
-      <c r="E30" s="24" t="inlineStr">
+      <c r="E30" s="26" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F30" s="24" t="inlineStr">
+      <c r="F30" s="26" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G30" s="24" t="inlineStr">
+      <c r="G30" s="26" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H30" s="24" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I30" s="25" t="n">
+      <c r="H30" s="26" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I30" s="27" t="n">
         <v>1</v>
       </c>
       <c r="J30" s="8" t="inlineStr">
@@ -1833,12 +1839,12 @@
       <c r="K30" s="8" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="24" t="inlineStr">
+      <c r="A31" s="26" t="inlineStr">
         <is>
           <t>4.6</t>
         </is>
       </c>
-      <c r="B31" s="24" t="inlineStr">
+      <c r="B31" s="26" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1853,27 +1859,27 @@
           <t>생성 중·생성 실패 화면, 최신 아님 배너, 이미지 상자, 모드 설명</t>
         </is>
       </c>
-      <c r="E31" s="24" t="inlineStr">
+      <c r="E31" s="26" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F31" s="24" t="inlineStr">
+      <c r="F31" s="26" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G31" s="24" t="inlineStr">
+      <c r="G31" s="26" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H31" s="24" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I31" s="25" t="n">
+      <c r="H31" s="26" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I31" s="27" t="n">
         <v>1</v>
       </c>
       <c r="J31" s="8" t="inlineStr">
@@ -1884,12 +1890,12 @@
       <c r="K31" s="8" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="24" t="inlineStr">
+      <c r="A32" s="26" t="inlineStr">
         <is>
           <t>4.7</t>
         </is>
       </c>
-      <c r="B32" s="24" t="inlineStr">
+      <c r="B32" s="26" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1904,27 +1910,27 @@
           <t>이전 결과를 다음 과제의 기준으로 가져오기</t>
         </is>
       </c>
-      <c r="E32" s="24" t="inlineStr">
+      <c r="E32" s="26" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F32" s="24" t="inlineStr">
+      <c r="F32" s="26" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G32" s="24" t="inlineStr">
+      <c r="G32" s="26" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H32" s="24" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I32" s="25" t="n">
+      <c r="H32" s="26" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I32" s="27" t="n">
         <v>1</v>
       </c>
       <c r="J32" s="8" t="inlineStr">
@@ -1963,12 +1969,12 @@
       <c r="K33" s="5" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="24" t="inlineStr">
+      <c r="A34" s="26" t="inlineStr">
         <is>
           <t>5.1</t>
         </is>
       </c>
-      <c r="B34" s="24" t="inlineStr">
+      <c r="B34" s="26" t="inlineStr">
         <is>
           <t>배포</t>
         </is>
@@ -1983,27 +1989,27 @@
           <t>main은 정식 주소, PR마다 미리보기 주소</t>
         </is>
       </c>
-      <c r="E34" s="24" t="inlineStr">
+      <c r="E34" s="26" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F34" s="24" t="inlineStr">
+      <c r="F34" s="26" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="G34" s="24" t="inlineStr">
+      <c r="G34" s="26" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="H34" s="24" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I34" s="25" t="n">
+      <c r="H34" s="26" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I34" s="27" t="n">
         <v>1</v>
       </c>
       <c r="J34" s="8" t="inlineStr">
@@ -2018,12 +2024,12 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="24" t="inlineStr">
+      <c r="A35" s="26" t="inlineStr">
         <is>
           <t>5.2</t>
         </is>
       </c>
-      <c r="B35" s="24" t="inlineStr">
+      <c r="B35" s="26" t="inlineStr">
         <is>
           <t>배포</t>
         </is>
@@ -2038,27 +2044,27 @@
           <t>저장 디스크 방식 정하기, 프론트와 연결</t>
         </is>
       </c>
-      <c r="E35" s="24" t="inlineStr">
+      <c r="E35" s="26" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F35" s="24" t="inlineStr">
+      <c r="F35" s="26" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="G35" s="24" t="inlineStr">
+      <c r="G35" s="26" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="H35" s="24" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I35" s="25" t="n">
+      <c r="H35" s="26" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I35" s="27" t="n">
         <v>1</v>
       </c>
       <c r="J35" s="8" t="inlineStr">
@@ -2094,19 +2100,19 @@
       <c r="G36" s="4" t="n"/>
       <c r="H36" s="4" t="n"/>
       <c r="I36" s="6">
-        <f>IFERROR(AVERAGE(I37:I42),0)</f>
+        <f>IFERROR(AVERAGE(I37:I43),0)</f>
         <v/>
       </c>
       <c r="J36" s="5" t="n"/>
       <c r="K36" s="5" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="24" t="inlineStr">
+      <c r="A37" s="26" t="inlineStr">
         <is>
           <t>6.1</t>
         </is>
       </c>
-      <c r="B37" s="24" t="inlineStr">
+      <c r="B37" s="26" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
@@ -2121,27 +2127,27 @@
           <t>가짜 모델(Mock) 대신 실제 모델</t>
         </is>
       </c>
-      <c r="E37" s="24" t="inlineStr">
+      <c r="E37" s="26" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F37" s="24" t="inlineStr">
+      <c r="F37" s="26" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="G37" s="24" t="inlineStr">
+      <c r="G37" s="26" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="H37" s="24" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I37" s="25" t="n">
+      <c r="H37" s="26" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I37" s="27" t="n">
         <v>1</v>
       </c>
       <c r="J37" s="8" t="inlineStr">
@@ -2156,12 +2162,12 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="24" t="inlineStr">
+      <c r="A38" s="26" t="inlineStr">
         <is>
           <t>6.2</t>
         </is>
       </c>
-      <c r="B38" s="24" t="inlineStr">
+      <c r="B38" s="26" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
@@ -2176,31 +2182,31 @@
           <t>준비도 기준·항목 가중치·프롬프트를 시나리오로 측정</t>
         </is>
       </c>
-      <c r="E38" s="24" t="inlineStr">
+      <c r="E38" s="26" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F38" s="24" t="n"/>
-      <c r="G38" s="24" t="n"/>
-      <c r="H38" s="24" t="inlineStr">
+      <c r="F38" s="26" t="n"/>
+      <c r="G38" s="26" t="n"/>
+      <c r="H38" s="26" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="I38" s="25" t="n">
+      <c r="I38" s="27" t="n">
         <v>0</v>
       </c>
       <c r="J38" s="8" t="n"/>
       <c r="K38" s="8" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="24" t="inlineStr">
+      <c r="A39" s="26" t="inlineStr">
         <is>
           <t>6.3</t>
         </is>
       </c>
-      <c r="B39" s="24" t="inlineStr">
+      <c r="B39" s="26" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
@@ -2215,31 +2221,31 @@
           <t>지금의 자리표시·샘플 자리에 실제 기능 연결</t>
         </is>
       </c>
-      <c r="E39" s="24" t="inlineStr">
+      <c r="E39" s="26" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F39" s="24" t="n"/>
-      <c r="G39" s="24" t="n"/>
-      <c r="H39" s="24" t="inlineStr">
+      <c r="F39" s="26" t="n"/>
+      <c r="G39" s="26" t="n"/>
+      <c r="H39" s="26" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="I39" s="25" t="n">
+      <c r="I39" s="27" t="n">
         <v>0</v>
       </c>
       <c r="J39" s="8" t="n"/>
       <c r="K39" s="8" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="24" t="inlineStr">
+      <c r="A40" s="26" t="inlineStr">
         <is>
           <t>6.4</t>
         </is>
       </c>
-      <c r="B40" s="24" t="inlineStr">
+      <c r="B40" s="26" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
@@ -2250,27 +2256,27 @@
         </is>
       </c>
       <c r="D40" s="8" t="n"/>
-      <c r="E40" s="24" t="inlineStr">
+      <c r="E40" s="26" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F40" s="24" t="inlineStr">
+      <c r="F40" s="26" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="G40" s="24" t="inlineStr">
+      <c r="G40" s="26" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="H40" s="24" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I40" s="25" t="n">
+      <c r="H40" s="26" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I40" s="27" t="n">
         <v>1</v>
       </c>
       <c r="J40" s="8" t="inlineStr">
@@ -2281,12 +2287,12 @@
       <c r="K40" s="8" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="24" t="inlineStr">
+      <c r="A41" s="26" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="B41" s="24" t="inlineStr">
+      <c r="B41" s="26" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
@@ -2297,27 +2303,27 @@
         </is>
       </c>
       <c r="D41" s="8" t="n"/>
-      <c r="E41" s="24" t="inlineStr">
+      <c r="E41" s="26" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F41" s="24" t="inlineStr">
+      <c r="F41" s="26" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="G41" s="24" t="inlineStr">
+      <c r="G41" s="26" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="H41" s="24" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I41" s="25" t="n">
+      <c r="H41" s="26" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I41" s="27" t="n">
         <v>1</v>
       </c>
       <c r="J41" s="8" t="inlineStr">
@@ -2332,12 +2338,12 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="24" t="inlineStr">
+      <c r="A42" s="26" t="inlineStr">
         <is>
           <t>6.6</t>
         </is>
       </c>
-      <c r="B42" s="24" t="inlineStr">
+      <c r="B42" s="26" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
@@ -2348,27 +2354,27 @@
         </is>
       </c>
       <c r="D42" s="8" t="n"/>
-      <c r="E42" s="24" t="inlineStr">
+      <c r="E42" s="26" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F42" s="24" t="inlineStr">
+      <c r="F42" s="26" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="G42" s="24" t="inlineStr">
+      <c r="G42" s="26" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="H42" s="24" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I42" s="25" t="n">
+      <c r="H42" s="26" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I42" s="27" t="n">
         <v>1</v>
       </c>
       <c r="J42" s="8" t="inlineStr">
@@ -2379,110 +2385,161 @@
       <c r="K42" s="8" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+      <c r="A43" s="26" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="B43" s="26" t="inlineStr">
+        <is>
+          <t>실제 AI 연결</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>AI 동시 호출 상한(붐비면 503)</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>LLM·이미지 호출 자리 수 제한, 대기 뒤 거절, 세션 되돌림</t>
+        </is>
+      </c>
+      <c r="E43" s="26" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F43" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="G43" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="H43" s="26" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I43" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J43" s="8" t="inlineStr">
+        <is>
+          <t>PR #27</t>
+        </is>
+      </c>
+      <c r="K43" s="8" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>마무리</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
         <is>
           <t>평가·발표</t>
         </is>
       </c>
-      <c r="D43" s="5" t="n"/>
-      <c r="E43" s="4" t="n"/>
-      <c r="F43" s="4" t="n"/>
-      <c r="G43" s="4" t="n"/>
-      <c r="H43" s="4" t="n"/>
-      <c r="I43" s="6">
-        <f>IFERROR(AVERAGE(I44:I45),0)</f>
-        <v/>
-      </c>
-      <c r="J43" s="5" t="n"/>
-      <c r="K43" s="5" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="24" t="inlineStr">
+      <c r="D44" s="5" t="n"/>
+      <c r="E44" s="4" t="n"/>
+      <c r="F44" s="4" t="n"/>
+      <c r="G44" s="4" t="n"/>
+      <c r="H44" s="4" t="n"/>
+      <c r="I44" s="6">
+        <f>IFERROR(AVERAGE(I45:I46),0)</f>
+        <v/>
+      </c>
+      <c r="J44" s="5" t="n"/>
+      <c r="K44" s="5" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="26" t="inlineStr">
         <is>
           <t>7.1</t>
         </is>
       </c>
-      <c r="B44" s="24" t="inlineStr">
+      <c r="B45" s="26" t="inlineStr">
         <is>
           <t>마무리</t>
         </is>
       </c>
-      <c r="C44" s="8" t="inlineStr">
+      <c r="C45" s="8" t="inlineStr">
         <is>
           <t>사용성 확인·평가 지표 측정</t>
         </is>
       </c>
-      <c r="D44" s="8" t="inlineStr">
+      <c r="D45" s="8" t="inlineStr">
         <is>
           <t>필수정보 충족률, 질문 효율, 가정 표시율 등(기획서 14장)</t>
         </is>
       </c>
-      <c r="E44" s="24" t="inlineStr">
+      <c r="E45" s="26" t="inlineStr">
         <is>
           <t>공동</t>
         </is>
       </c>
-      <c r="F44" s="24" t="n"/>
-      <c r="G44" s="24" t="n"/>
-      <c r="H44" s="24" t="inlineStr">
+      <c r="F45" s="26" t="n"/>
+      <c r="G45" s="26" t="n"/>
+      <c r="H45" s="26" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="I44" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="8" t="n"/>
-      <c r="K44" s="8" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="24" t="inlineStr">
-        <is>
-          <t>7.2</t>
-        </is>
-      </c>
-      <c r="B45" s="24" t="inlineStr">
-        <is>
-          <t>마무리</t>
-        </is>
-      </c>
-      <c r="C45" s="8" t="inlineStr">
-        <is>
-          <t>최종 발표 자료</t>
-        </is>
-      </c>
-      <c r="D45" s="8" t="n"/>
-      <c r="E45" s="24" t="inlineStr">
-        <is>
-          <t>공동</t>
-        </is>
-      </c>
-      <c r="F45" s="24" t="n"/>
-      <c r="G45" s="24" t="n"/>
-      <c r="H45" s="24" t="inlineStr">
-        <is>
-          <t>예정</t>
-        </is>
-      </c>
-      <c r="I45" s="25" t="n">
+      <c r="I45" s="27" t="n">
         <v>0</v>
       </c>
       <c r="J45" s="8" t="n"/>
       <c r="K45" s="8" t="n"/>
     </row>
+    <row r="46">
+      <c r="A46" s="26" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="B46" s="26" t="inlineStr">
+        <is>
+          <t>마무리</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>최종 발표 자료</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="n"/>
+      <c r="E46" s="26" t="inlineStr">
+        <is>
+          <t>공동</t>
+        </is>
+      </c>
+      <c r="F46" s="26" t="n"/>
+      <c r="G46" s="26" t="n"/>
+      <c r="H46" s="26" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="I46" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="8" t="n"/>
+      <c r="K46" s="8" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:K45"/>
-  <conditionalFormatting sqref="H5:H45">
+  <autoFilter ref="A4:K46"/>
+  <conditionalFormatting sqref="H5:H46">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"완료"</formula>
     </cfRule>
@@ -2493,7 +2550,7 @@
       <formula>"보류"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I5:I45">
+  <conditionalFormatting sqref="I5:I46">
     <cfRule type="dataBar" priority="4">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -2503,10 +2560,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="H5:H45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"완료,진행 중,예정,보류"</formula1>
     </dataValidation>
-    <dataValidation sqref="E5:E45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"개발,디자인,공동"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2577,23 +2634,23 @@
         </is>
       </c>
       <c r="B4" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$45,A4,WBS!$H$5:$H$45,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$46,A4,WBS!$H$5:$H$46,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C4" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$45,A4,WBS!$H$5:$H$45,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$46,A4,WBS!$H$5:$H$46,"완료")</f>
         <v/>
       </c>
       <c r="D4" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$45,A4,WBS!$H$5:$H$45,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$46,A4,WBS!$H$5:$H$46,"진행 중")</f>
         <v/>
       </c>
       <c r="E4" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$45,A4,WBS!$H$5:$H$45,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$46,A4,WBS!$H$5:$H$46,"예정")</f>
         <v/>
       </c>
       <c r="F4" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$45,WBS!$B$5:$B$45,A4,WBS!$H$5:$H$45,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$46,WBS!$B$5:$B$46,A4,WBS!$H$5:$H$46,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2604,23 +2661,23 @@
         </is>
       </c>
       <c r="B5" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$45,A5,WBS!$H$5:$H$45,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$46,A5,WBS!$H$5:$H$46,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C5" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$45,A5,WBS!$H$5:$H$45,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$46,A5,WBS!$H$5:$H$46,"완료")</f>
         <v/>
       </c>
       <c r="D5" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$45,A5,WBS!$H$5:$H$45,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$46,A5,WBS!$H$5:$H$46,"진행 중")</f>
         <v/>
       </c>
       <c r="E5" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$45,A5,WBS!$H$5:$H$45,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$46,A5,WBS!$H$5:$H$46,"예정")</f>
         <v/>
       </c>
       <c r="F5" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$45,WBS!$B$5:$B$45,A5,WBS!$H$5:$H$45,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$46,WBS!$B$5:$B$46,A5,WBS!$H$5:$H$46,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2631,23 +2688,23 @@
         </is>
       </c>
       <c r="B6" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$45,A6,WBS!$H$5:$H$45,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$46,A6,WBS!$H$5:$H$46,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C6" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$45,A6,WBS!$H$5:$H$45,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$46,A6,WBS!$H$5:$H$46,"완료")</f>
         <v/>
       </c>
       <c r="D6" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$45,A6,WBS!$H$5:$H$45,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$46,A6,WBS!$H$5:$H$46,"진행 중")</f>
         <v/>
       </c>
       <c r="E6" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$45,A6,WBS!$H$5:$H$45,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$46,A6,WBS!$H$5:$H$46,"예정")</f>
         <v/>
       </c>
       <c r="F6" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$45,WBS!$B$5:$B$45,A6,WBS!$H$5:$H$45,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$46,WBS!$B$5:$B$46,A6,WBS!$H$5:$H$46,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2658,23 +2715,23 @@
         </is>
       </c>
       <c r="B7" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$45,A7,WBS!$H$5:$H$45,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$46,A7,WBS!$H$5:$H$46,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C7" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$45,A7,WBS!$H$5:$H$45,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$46,A7,WBS!$H$5:$H$46,"완료")</f>
         <v/>
       </c>
       <c r="D7" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$45,A7,WBS!$H$5:$H$45,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$46,A7,WBS!$H$5:$H$46,"진행 중")</f>
         <v/>
       </c>
       <c r="E7" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$45,A7,WBS!$H$5:$H$45,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$46,A7,WBS!$H$5:$H$46,"예정")</f>
         <v/>
       </c>
       <c r="F7" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$45,WBS!$B$5:$B$45,A7,WBS!$H$5:$H$45,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$46,WBS!$B$5:$B$46,A7,WBS!$H$5:$H$46,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2685,23 +2742,23 @@
         </is>
       </c>
       <c r="B8" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$45,A8,WBS!$H$5:$H$45,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$46,A8,WBS!$H$5:$H$46,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C8" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$45,A8,WBS!$H$5:$H$45,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$46,A8,WBS!$H$5:$H$46,"완료")</f>
         <v/>
       </c>
       <c r="D8" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$45,A8,WBS!$H$5:$H$45,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$46,A8,WBS!$H$5:$H$46,"진행 중")</f>
         <v/>
       </c>
       <c r="E8" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$45,A8,WBS!$H$5:$H$45,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$46,A8,WBS!$H$5:$H$46,"예정")</f>
         <v/>
       </c>
       <c r="F8" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$45,WBS!$B$5:$B$45,A8,WBS!$H$5:$H$45,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$46,WBS!$B$5:$B$46,A8,WBS!$H$5:$H$46,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2712,23 +2769,23 @@
         </is>
       </c>
       <c r="B9" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$45,A9,WBS!$H$5:$H$45,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$46,A9,WBS!$H$5:$H$46,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C9" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$45,A9,WBS!$H$5:$H$45,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$46,A9,WBS!$H$5:$H$46,"완료")</f>
         <v/>
       </c>
       <c r="D9" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$45,A9,WBS!$H$5:$H$45,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$46,A9,WBS!$H$5:$H$46,"진행 중")</f>
         <v/>
       </c>
       <c r="E9" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$45,A9,WBS!$H$5:$H$45,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$46,A9,WBS!$H$5:$H$46,"예정")</f>
         <v/>
       </c>
       <c r="F9" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$45,WBS!$B$5:$B$45,A9,WBS!$H$5:$H$45,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$46,WBS!$B$5:$B$46,A9,WBS!$H$5:$H$46,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2739,23 +2796,23 @@
         </is>
       </c>
       <c r="B10" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$45,A10,WBS!$H$5:$H$45,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$46,A10,WBS!$H$5:$H$46,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C10" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$45,A10,WBS!$H$5:$H$45,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$46,A10,WBS!$H$5:$H$46,"완료")</f>
         <v/>
       </c>
       <c r="D10" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$45,A10,WBS!$H$5:$H$45,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$46,A10,WBS!$H$5:$H$46,"진행 중")</f>
         <v/>
       </c>
       <c r="E10" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$45,A10,WBS!$H$5:$H$45,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$46,A10,WBS!$H$5:$H$46,"예정")</f>
         <v/>
       </c>
       <c r="F10" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$45,WBS!$B$5:$B$45,A10,WBS!$H$5:$H$45,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$46,WBS!$B$5:$B$46,A10,WBS!$H$5:$H$46,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2782,7 +2839,7 @@
         <v/>
       </c>
       <c r="F11" s="14">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$45,WBS!$H$5:$H$45,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$46,WBS!$H$5:$H$46,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>

--- a/docs/WBS.xlsx
+++ b/docs/WBS.xlsx
@@ -11,7 +11,7 @@
     <sheet name="요약" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS'!$A$4:$K$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS'!$A$4:$K$47</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -98,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -129,6 +129,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -553,7 +559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:K47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2100,7 +2106,7 @@
       <c r="G36" s="4" t="n"/>
       <c r="H36" s="4" t="n"/>
       <c r="I36" s="6">
-        <f>IFERROR(AVERAGE(I37:I43),0)</f>
+        <f>IFERROR(AVERAGE(I37:I44),0)</f>
         <v/>
       </c>
       <c r="J36" s="5" t="n"/>
@@ -2436,76 +2442,88 @@
       <c r="K43" s="8" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="A44" s="28" t="inlineStr">
+        <is>
+          <t>6.8</t>
+        </is>
+      </c>
+      <c r="B44" s="28" t="inlineStr">
+        <is>
+          <t>실제 AI 연결</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>병렬 생성(기본 꺼짐)·설계 고민 기록</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>결과 항목 조각 동시 생성·코드 합치기·부분 결과 캐시, README 설계 고민, 로드맵 측정표</t>
+        </is>
+      </c>
+      <c r="E44" s="28" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F44" s="28" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="G44" s="28" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="H44" s="28" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I44" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" s="8" t="inlineStr">
+        <is>
+          <t>PR #28</t>
+        </is>
+      </c>
+      <c r="K44" s="8" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>마무리</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
+      <c r="C45" s="5" t="inlineStr">
         <is>
           <t>평가·발표</t>
         </is>
       </c>
-      <c r="D44" s="5" t="n"/>
-      <c r="E44" s="4" t="n"/>
-      <c r="F44" s="4" t="n"/>
-      <c r="G44" s="4" t="n"/>
-      <c r="H44" s="4" t="n"/>
-      <c r="I44" s="6">
-        <f>IFERROR(AVERAGE(I45:I46),0)</f>
-        <v/>
-      </c>
-      <c r="J44" s="5" t="n"/>
-      <c r="K44" s="5" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="26" t="inlineStr">
-        <is>
-          <t>7.1</t>
-        </is>
-      </c>
-      <c r="B45" s="26" t="inlineStr">
-        <is>
-          <t>마무리</t>
-        </is>
-      </c>
-      <c r="C45" s="8" t="inlineStr">
-        <is>
-          <t>사용성 확인·평가 지표 측정</t>
-        </is>
-      </c>
-      <c r="D45" s="8" t="inlineStr">
-        <is>
-          <t>필수정보 충족률, 질문 효율, 가정 표시율 등(기획서 14장)</t>
-        </is>
-      </c>
-      <c r="E45" s="26" t="inlineStr">
-        <is>
-          <t>공동</t>
-        </is>
-      </c>
-      <c r="F45" s="26" t="n"/>
-      <c r="G45" s="26" t="n"/>
-      <c r="H45" s="26" t="inlineStr">
-        <is>
-          <t>예정</t>
-        </is>
-      </c>
-      <c r="I45" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="8" t="n"/>
-      <c r="K45" s="8" t="n"/>
+      <c r="D45" s="5" t="n"/>
+      <c r="E45" s="4" t="n"/>
+      <c r="F45" s="4" t="n"/>
+      <c r="G45" s="4" t="n"/>
+      <c r="H45" s="4" t="n"/>
+      <c r="I45" s="6">
+        <f>IFERROR(AVERAGE(I46:I47),0)</f>
+        <v/>
+      </c>
+      <c r="J45" s="5" t="n"/>
+      <c r="K45" s="5" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="26" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="B46" s="26" t="inlineStr">
@@ -2515,10 +2533,14 @@
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>최종 발표 자료</t>
-        </is>
-      </c>
-      <c r="D46" s="8" t="n"/>
+          <t>사용성 확인·평가 지표 측정</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>필수정보 충족률, 질문 효율, 가정 표시율 등(기획서 14장)</t>
+        </is>
+      </c>
       <c r="E46" s="26" t="inlineStr">
         <is>
           <t>공동</t>
@@ -2537,9 +2559,44 @@
       <c r="J46" s="8" t="n"/>
       <c r="K46" s="8" t="n"/>
     </row>
+    <row r="47">
+      <c r="A47" s="26" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="B47" s="26" t="inlineStr">
+        <is>
+          <t>마무리</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="inlineStr">
+        <is>
+          <t>최종 발표 자료</t>
+        </is>
+      </c>
+      <c r="D47" s="8" t="n"/>
+      <c r="E47" s="26" t="inlineStr">
+        <is>
+          <t>공동</t>
+        </is>
+      </c>
+      <c r="F47" s="26" t="n"/>
+      <c r="G47" s="26" t="n"/>
+      <c r="H47" s="26" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="I47" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="8" t="n"/>
+      <c r="K47" s="8" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:K46"/>
-  <conditionalFormatting sqref="H5:H46">
+  <autoFilter ref="A4:K47"/>
+  <conditionalFormatting sqref="H5:H47">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"완료"</formula>
     </cfRule>
@@ -2550,7 +2607,7 @@
       <formula>"보류"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I5:I46">
+  <conditionalFormatting sqref="I5:I47">
     <cfRule type="dataBar" priority="4">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -2560,10 +2617,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="H5:H46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"완료,진행 중,예정,보류"</formula1>
     </dataValidation>
-    <dataValidation sqref="E5:E46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"개발,디자인,공동"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2595,6 +2652,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -2634,23 +2692,23 @@
         </is>
       </c>
       <c r="B4" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$46,A4,WBS!$H$5:$H$46,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$47,A4,WBS!$H$5:$H$47,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C4" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$46,A4,WBS!$H$5:$H$46,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$47,A4,WBS!$H$5:$H$47,"완료")</f>
         <v/>
       </c>
       <c r="D4" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$46,A4,WBS!$H$5:$H$46,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$47,A4,WBS!$H$5:$H$47,"진행 중")</f>
         <v/>
       </c>
       <c r="E4" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$46,A4,WBS!$H$5:$H$46,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$47,A4,WBS!$H$5:$H$47,"예정")</f>
         <v/>
       </c>
       <c r="F4" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$46,WBS!$B$5:$B$46,A4,WBS!$H$5:$H$46,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$47,WBS!$B$5:$B$47,A4,WBS!$H$5:$H$47,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2661,23 +2719,23 @@
         </is>
       </c>
       <c r="B5" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$46,A5,WBS!$H$5:$H$46,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$47,A5,WBS!$H$5:$H$47,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C5" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$46,A5,WBS!$H$5:$H$46,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$47,A5,WBS!$H$5:$H$47,"완료")</f>
         <v/>
       </c>
       <c r="D5" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$46,A5,WBS!$H$5:$H$46,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$47,A5,WBS!$H$5:$H$47,"진행 중")</f>
         <v/>
       </c>
       <c r="E5" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$46,A5,WBS!$H$5:$H$46,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$47,A5,WBS!$H$5:$H$47,"예정")</f>
         <v/>
       </c>
       <c r="F5" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$46,WBS!$B$5:$B$46,A5,WBS!$H$5:$H$46,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$47,WBS!$B$5:$B$47,A5,WBS!$H$5:$H$47,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2688,23 +2746,23 @@
         </is>
       </c>
       <c r="B6" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$46,A6,WBS!$H$5:$H$46,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$47,A6,WBS!$H$5:$H$47,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C6" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$46,A6,WBS!$H$5:$H$46,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$47,A6,WBS!$H$5:$H$47,"완료")</f>
         <v/>
       </c>
       <c r="D6" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$46,A6,WBS!$H$5:$H$46,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$47,A6,WBS!$H$5:$H$47,"진행 중")</f>
         <v/>
       </c>
       <c r="E6" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$46,A6,WBS!$H$5:$H$46,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$47,A6,WBS!$H$5:$H$47,"예정")</f>
         <v/>
       </c>
       <c r="F6" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$46,WBS!$B$5:$B$46,A6,WBS!$H$5:$H$46,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$47,WBS!$B$5:$B$47,A6,WBS!$H$5:$H$47,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2715,23 +2773,23 @@
         </is>
       </c>
       <c r="B7" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$46,A7,WBS!$H$5:$H$46,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$47,A7,WBS!$H$5:$H$47,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C7" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$46,A7,WBS!$H$5:$H$46,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$47,A7,WBS!$H$5:$H$47,"완료")</f>
         <v/>
       </c>
       <c r="D7" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$46,A7,WBS!$H$5:$H$46,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$47,A7,WBS!$H$5:$H$47,"진행 중")</f>
         <v/>
       </c>
       <c r="E7" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$46,A7,WBS!$H$5:$H$46,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$47,A7,WBS!$H$5:$H$47,"예정")</f>
         <v/>
       </c>
       <c r="F7" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$46,WBS!$B$5:$B$46,A7,WBS!$H$5:$H$46,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$47,WBS!$B$5:$B$47,A7,WBS!$H$5:$H$47,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2742,23 +2800,23 @@
         </is>
       </c>
       <c r="B8" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$46,A8,WBS!$H$5:$H$46,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$47,A8,WBS!$H$5:$H$47,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C8" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$46,A8,WBS!$H$5:$H$46,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$47,A8,WBS!$H$5:$H$47,"완료")</f>
         <v/>
       </c>
       <c r="D8" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$46,A8,WBS!$H$5:$H$46,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$47,A8,WBS!$H$5:$H$47,"진행 중")</f>
         <v/>
       </c>
       <c r="E8" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$46,A8,WBS!$H$5:$H$46,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$47,A8,WBS!$H$5:$H$47,"예정")</f>
         <v/>
       </c>
       <c r="F8" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$46,WBS!$B$5:$B$46,A8,WBS!$H$5:$H$46,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$47,WBS!$B$5:$B$47,A8,WBS!$H$5:$H$47,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2769,23 +2827,23 @@
         </is>
       </c>
       <c r="B9" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$46,A9,WBS!$H$5:$H$46,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$47,A9,WBS!$H$5:$H$47,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C9" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$46,A9,WBS!$H$5:$H$46,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$47,A9,WBS!$H$5:$H$47,"완료")</f>
         <v/>
       </c>
       <c r="D9" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$46,A9,WBS!$H$5:$H$46,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$47,A9,WBS!$H$5:$H$47,"진행 중")</f>
         <v/>
       </c>
       <c r="E9" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$46,A9,WBS!$H$5:$H$46,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$47,A9,WBS!$H$5:$H$47,"예정")</f>
         <v/>
       </c>
       <c r="F9" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$46,WBS!$B$5:$B$46,A9,WBS!$H$5:$H$46,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$47,WBS!$B$5:$B$47,A9,WBS!$H$5:$H$47,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2796,23 +2854,23 @@
         </is>
       </c>
       <c r="B10" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$46,A10,WBS!$H$5:$H$46,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$47,A10,WBS!$H$5:$H$47,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C10" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$46,A10,WBS!$H$5:$H$46,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$47,A10,WBS!$H$5:$H$47,"완료")</f>
         <v/>
       </c>
       <c r="D10" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$46,A10,WBS!$H$5:$H$46,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$47,A10,WBS!$H$5:$H$47,"진행 중")</f>
         <v/>
       </c>
       <c r="E10" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$46,A10,WBS!$H$5:$H$46,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$47,A10,WBS!$H$5:$H$47,"예정")</f>
         <v/>
       </c>
       <c r="F10" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$46,WBS!$B$5:$B$46,A10,WBS!$H$5:$H$46,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$47,WBS!$B$5:$B$47,A10,WBS!$H$5:$H$47,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2839,10 +2897,11 @@
         <v/>
       </c>
       <c r="F11" s="14">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$46,WBS!$H$5:$H$46,"&lt;&gt;"),0)</f>
-        <v/>
-      </c>
-    </row>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$47,WBS!$H$5:$H$47,"&lt;&gt;"),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>

--- a/docs/WBS.xlsx
+++ b/docs/WBS.xlsx
@@ -11,7 +11,7 @@
     <sheet name="요약" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS'!$A$4:$K$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS'!$A$4:$K$48</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -98,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -129,6 +129,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -559,7 +565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K47"/>
+  <dimension ref="A1:K48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -675,12 +681,12 @@
       <c r="K5" s="5" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="26" t="inlineStr">
+      <c r="A6" s="28" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>기획·설계</t>
         </is>
@@ -695,23 +701,23 @@
           <t>과제 4개(사업계획·상품기획·브랜딩·마케팅), 적응형 질문, 사실·가정 분리 원칙</t>
         </is>
       </c>
-      <c r="E6" s="26" t="inlineStr">
+      <c r="E6" s="28" t="inlineStr">
         <is>
           <t>공동</t>
         </is>
       </c>
-      <c r="F6" s="26" t="n"/>
-      <c r="G6" s="26" t="inlineStr">
+      <c r="F6" s="28" t="n"/>
+      <c r="G6" s="28" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="H6" s="26" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I6" s="27" t="n">
+      <c r="H6" s="28" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I6" s="29" t="n">
         <v>1</v>
       </c>
       <c r="J6" s="8" t="inlineStr">
@@ -722,12 +728,12 @@
       <c r="K6" s="8" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="26" t="inlineStr">
+      <c r="A7" s="28" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="B7" s="26" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>기획·설계</t>
         </is>
@@ -742,27 +748,27 @@
           <t>FastAPI 하네스 구조, API 계약, 테스트 전략</t>
         </is>
       </c>
-      <c r="E7" s="26" t="inlineStr">
+      <c r="E7" s="28" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F7" s="26" t="inlineStr">
+      <c r="F7" s="28" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="G7" s="26" t="inlineStr">
+      <c r="G7" s="28" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="H7" s="26" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I7" s="27" t="n">
+      <c r="H7" s="28" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I7" s="29" t="n">
         <v>1</v>
       </c>
       <c r="J7" s="8" t="inlineStr">
@@ -773,12 +779,12 @@
       <c r="K7" s="8" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="26" t="inlineStr">
+      <c r="A8" s="28" t="inlineStr">
         <is>
           <t>1.3</t>
         </is>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>기획·설계</t>
         </is>
@@ -793,27 +799,27 @@
           <t>V2 화면 흐름, 묶음 0~4로 작업 나누기</t>
         </is>
       </c>
-      <c r="E8" s="26" t="inlineStr">
+      <c r="E8" s="28" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F8" s="26" t="inlineStr">
+      <c r="F8" s="28" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G8" s="26" t="inlineStr">
+      <c r="G8" s="28" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H8" s="26" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I8" s="27" t="n">
+      <c r="H8" s="28" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I8" s="29" t="n">
         <v>1</v>
       </c>
       <c r="J8" s="8" t="inlineStr">
@@ -824,12 +830,12 @@
       <c r="K8" s="8" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="26" t="inlineStr">
+      <c r="A9" s="28" t="inlineStr">
         <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="B9" s="26" t="inlineStr">
+      <c r="B9" s="28" t="inlineStr">
         <is>
           <t>기획·설계</t>
         </is>
@@ -844,27 +850,27 @@
           <t>지금 상태·다음 할 일·작업 방식·환경 팁, PR마다 갱신</t>
         </is>
       </c>
-      <c r="E9" s="26" t="inlineStr">
+      <c r="E9" s="28" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F9" s="26" t="inlineStr">
+      <c r="F9" s="28" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="G9" s="26" t="inlineStr">
+      <c r="G9" s="28" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="H9" s="26" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I9" s="27" t="n">
+      <c r="H9" s="28" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I9" s="29" t="n">
         <v>1</v>
       </c>
       <c r="J9" s="8" t="inlineStr">
@@ -875,12 +881,12 @@
       <c r="K9" s="8" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="26" t="inlineStr">
+      <c r="A10" s="28" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="B10" s="26" t="inlineStr">
+      <c r="B10" s="28" t="inlineStr">
         <is>
           <t>기획·설계</t>
         </is>
@@ -895,27 +901,27 @@
           <t>바로 보기 주소, 된 것, 남은 일·맡을 사람·상의할 점</t>
         </is>
       </c>
-      <c r="E10" s="26" t="inlineStr">
+      <c r="E10" s="28" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F10" s="26" t="inlineStr">
+      <c r="F10" s="28" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="G10" s="26" t="inlineStr">
+      <c r="G10" s="28" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="H10" s="26" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I10" s="27" t="n">
+      <c r="H10" s="28" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I10" s="29" t="n">
         <v>1</v>
       </c>
       <c r="J10" s="8" t="inlineStr">
@@ -954,12 +960,12 @@
       <c r="K11" s="5" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="26" t="inlineStr">
+      <c r="A12" s="28" t="inlineStr">
         <is>
           <t>2.1</t>
         </is>
       </c>
-      <c r="B12" s="26" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -974,27 +980,27 @@
           <t>사실·가정·미정 구분, 정보 출처 표시</t>
         </is>
       </c>
-      <c r="E12" s="26" t="inlineStr">
+      <c r="E12" s="28" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F12" s="26" t="inlineStr">
+      <c r="F12" s="28" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="G12" s="26" t="inlineStr">
+      <c r="G12" s="28" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H12" s="26" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I12" s="27" t="n">
+      <c r="H12" s="28" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I12" s="29" t="n">
         <v>1</v>
       </c>
       <c r="J12" s="8" t="inlineStr">
@@ -1005,12 +1011,12 @@
       <c r="K12" s="8" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="26" t="inlineStr">
+      <c r="A13" s="28" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
       </c>
-      <c r="B13" s="26" t="inlineStr">
+      <c r="B13" s="28" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1025,27 +1031,27 @@
           <t>비용 없이 개발·테스트하는 가짜 모델</t>
         </is>
       </c>
-      <c r="E13" s="26" t="inlineStr">
+      <c r="E13" s="28" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F13" s="26" t="inlineStr">
+      <c r="F13" s="28" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="G13" s="26" t="inlineStr">
+      <c r="G13" s="28" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H13" s="26" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I13" s="27" t="n">
+      <c r="H13" s="28" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I13" s="29" t="n">
         <v>1</v>
       </c>
       <c r="J13" s="8" t="inlineStr">
@@ -1056,12 +1062,12 @@
       <c r="K13" s="8" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="26" t="inlineStr">
+      <c r="A14" s="28" t="inlineStr">
         <is>
           <t>2.3</t>
         </is>
       </c>
-      <c r="B14" s="26" t="inlineStr">
+      <c r="B14" s="28" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1076,27 +1082,27 @@
           <t>과제별 질문 정책(policy.yaml), 단계별 프롬프트</t>
         </is>
       </c>
-      <c r="E14" s="26" t="inlineStr">
+      <c r="E14" s="28" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F14" s="26" t="inlineStr">
+      <c r="F14" s="28" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G14" s="26" t="inlineStr">
+      <c r="G14" s="28" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H14" s="26" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I14" s="27" t="n">
+      <c r="H14" s="28" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I14" s="29" t="n">
         <v>1</v>
       </c>
       <c r="J14" s="8" t="inlineStr">
@@ -1107,12 +1113,12 @@
       <c r="K14" s="8" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="26" t="inlineStr">
+      <c r="A15" s="28" t="inlineStr">
         <is>
           <t>2.4</t>
         </is>
       </c>
-      <c r="B15" s="26" t="inlineStr">
+      <c r="B15" s="28" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1127,27 +1133,27 @@
           <t>모드별 질문 상한, '다른 예시 보기' 단계</t>
         </is>
       </c>
-      <c r="E15" s="26" t="inlineStr">
+      <c r="E15" s="28" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F15" s="26" t="inlineStr">
+      <c r="F15" s="28" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G15" s="26" t="inlineStr">
+      <c r="G15" s="28" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H15" s="26" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I15" s="27" t="n">
+      <c r="H15" s="28" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I15" s="29" t="n">
         <v>1</v>
       </c>
       <c r="J15" s="8" t="inlineStr">
@@ -1158,12 +1164,12 @@
       <c r="K15" s="8" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="26" t="inlineStr">
+      <c r="A16" s="28" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
       </c>
-      <c r="B16" s="26" t="inlineStr">
+      <c r="B16" s="28" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1174,27 +1180,27 @@
         </is>
       </c>
       <c r="D16" s="8" t="n"/>
-      <c r="E16" s="26" t="inlineStr">
+      <c r="E16" s="28" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F16" s="26" t="inlineStr">
+      <c r="F16" s="28" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G16" s="26" t="inlineStr">
+      <c r="G16" s="28" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H16" s="26" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I16" s="27" t="n">
+      <c r="H16" s="28" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I16" s="29" t="n">
         <v>1</v>
       </c>
       <c r="J16" s="8" t="inlineStr">
@@ -1205,12 +1211,12 @@
       <c r="K16" s="8" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="26" t="inlineStr">
+      <c r="A17" s="28" t="inlineStr">
         <is>
           <t>2.6</t>
         </is>
       </c>
-      <c r="B17" s="26" t="inlineStr">
+      <c r="B17" s="28" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1225,27 +1231,27 @@
           <t>과제별 정책·프롬프트·검증 규칙</t>
         </is>
       </c>
-      <c r="E17" s="26" t="inlineStr">
+      <c r="E17" s="28" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F17" s="26" t="inlineStr">
+      <c r="F17" s="28" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G17" s="26" t="inlineStr">
+      <c r="G17" s="28" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H17" s="26" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I17" s="27" t="n">
+      <c r="H17" s="28" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I17" s="29" t="n">
         <v>1</v>
       </c>
       <c r="J17" s="8" t="inlineStr">
@@ -1256,12 +1262,12 @@
       <c r="K17" s="8" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="26" t="inlineStr">
+      <c r="A18" s="28" t="inlineStr">
         <is>
           <t>2.7</t>
         </is>
       </c>
-      <c r="B18" s="26" t="inlineStr">
+      <c r="B18" s="28" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1276,27 +1282,27 @@
           <t>한국어 오류 문구, API 문서</t>
         </is>
       </c>
-      <c r="E18" s="26" t="inlineStr">
+      <c r="E18" s="28" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F18" s="26" t="inlineStr">
+      <c r="F18" s="28" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G18" s="26" t="inlineStr">
+      <c r="G18" s="28" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H18" s="26" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I18" s="27" t="n">
+      <c r="H18" s="28" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I18" s="29" t="n">
         <v>1</v>
       </c>
       <c r="J18" s="8" t="inlineStr">
@@ -1307,12 +1313,12 @@
       <c r="K18" s="8" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="26" t="inlineStr">
+      <c r="A19" s="28" t="inlineStr">
         <is>
           <t>2.8</t>
         </is>
       </c>
-      <c r="B19" s="26" t="inlineStr">
+      <c r="B19" s="28" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1327,27 +1333,27 @@
           <t>API에 맞춘 최소 화면, 개발 안내(CLAUDE.md)</t>
         </is>
       </c>
-      <c r="E19" s="26" t="inlineStr">
+      <c r="E19" s="28" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F19" s="26" t="inlineStr">
+      <c r="F19" s="28" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G19" s="26" t="inlineStr">
+      <c r="G19" s="28" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H19" s="26" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I19" s="27" t="n">
+      <c r="H19" s="28" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I19" s="29" t="n">
         <v>1</v>
       </c>
       <c r="J19" s="8" t="inlineStr">
@@ -1386,12 +1392,12 @@
       <c r="K20" s="5" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="26" t="inlineStr">
+      <c r="A21" s="28" t="inlineStr">
         <is>
           <t>3.1</t>
         </is>
       </c>
-      <c r="B21" s="26" t="inlineStr">
+      <c r="B21" s="28" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
@@ -1406,23 +1412,23 @@
           <t>전체 화면 흐름 HTML 프로토타입</t>
         </is>
       </c>
-      <c r="E21" s="26" t="inlineStr">
+      <c r="E21" s="28" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
       </c>
-      <c r="F21" s="26" t="n"/>
-      <c r="G21" s="26" t="inlineStr">
+      <c r="F21" s="28" t="n"/>
+      <c r="G21" s="28" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H21" s="26" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I21" s="27" t="n">
+      <c r="H21" s="28" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I21" s="29" t="n">
         <v>1</v>
       </c>
       <c r="J21" s="8" t="inlineStr">
@@ -1433,12 +1439,12 @@
       <c r="K21" s="8" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="26" t="inlineStr">
+      <c r="A22" s="28" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
       </c>
-      <c r="B22" s="26" t="inlineStr">
+      <c r="B22" s="28" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
@@ -1453,27 +1459,27 @@
           <t>모든 질문에 '다른 예시 보기', 모드 설명, 이미지 블록, 생성 중·실패·최신 아님 상태</t>
         </is>
       </c>
-      <c r="E22" s="26" t="inlineStr">
+      <c r="E22" s="28" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
       </c>
-      <c r="F22" s="26" t="inlineStr">
+      <c r="F22" s="28" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G22" s="26" t="inlineStr">
+      <c r="G22" s="28" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H22" s="26" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I22" s="27" t="n">
+      <c r="H22" s="28" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I22" s="29" t="n">
         <v>1</v>
       </c>
       <c r="J22" s="8" t="inlineStr">
@@ -1484,12 +1490,12 @@
       <c r="K22" s="8" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="26" t="inlineStr">
+      <c r="A23" s="28" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
       </c>
-      <c r="B23" s="26" t="inlineStr">
+      <c r="B23" s="28" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
@@ -1504,31 +1510,31 @@
           <t>반응형 자동 배치 확인</t>
         </is>
       </c>
-      <c r="E23" s="26" t="inlineStr">
+      <c r="E23" s="28" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
       </c>
-      <c r="F23" s="26" t="n"/>
-      <c r="G23" s="26" t="n"/>
-      <c r="H23" s="26" t="inlineStr">
+      <c r="F23" s="28" t="n"/>
+      <c r="G23" s="28" t="n"/>
+      <c r="H23" s="28" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="I23" s="27" t="n">
+      <c r="I23" s="29" t="n">
         <v>0</v>
       </c>
       <c r="J23" s="8" t="n"/>
       <c r="K23" s="8" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="26" t="inlineStr">
+      <c r="A24" s="28" t="inlineStr">
         <is>
           <t>3.4</t>
         </is>
       </c>
-      <c r="B24" s="26" t="inlineStr">
+      <c r="B24" s="28" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
@@ -1543,19 +1549,19 @@
           <t>/preview 화면을 html.to.design으로 가져와 수정</t>
         </is>
       </c>
-      <c r="E24" s="26" t="inlineStr">
+      <c r="E24" s="28" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
       </c>
-      <c r="F24" s="26" t="n"/>
-      <c r="G24" s="26" t="n"/>
-      <c r="H24" s="26" t="inlineStr">
+      <c r="F24" s="28" t="n"/>
+      <c r="G24" s="28" t="n"/>
+      <c r="H24" s="28" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="I24" s="27" t="n">
+      <c r="I24" s="29" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="8" t="n"/>
@@ -1590,12 +1596,12 @@
       <c r="K25" s="5" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="26" t="inlineStr">
+      <c r="A26" s="28" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
       </c>
-      <c r="B26" s="26" t="inlineStr">
+      <c r="B26" s="28" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1610,27 +1616,27 @@
           <t>버셀 배포 설정 포함</t>
         </is>
       </c>
-      <c r="E26" s="26" t="inlineStr">
+      <c r="E26" s="28" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F26" s="26" t="inlineStr">
+      <c r="F26" s="28" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G26" s="26" t="inlineStr">
+      <c r="G26" s="28" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H26" s="26" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I26" s="27" t="n">
+      <c r="H26" s="28" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I26" s="29" t="n">
         <v>1</v>
       </c>
       <c r="J26" s="8" t="inlineStr">
@@ -1641,12 +1647,12 @@
       <c r="K26" s="8" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="26" t="inlineStr">
+      <c r="A27" s="28" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
       </c>
-      <c r="B27" s="26" t="inlineStr">
+      <c r="B27" s="28" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1661,27 +1667,27 @@
           <t>답변 종류, 흐름 패널, 익명 사용자</t>
         </is>
       </c>
-      <c r="E27" s="26" t="inlineStr">
+      <c r="E27" s="28" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F27" s="26" t="inlineStr">
+      <c r="F27" s="28" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G27" s="26" t="inlineStr">
+      <c r="G27" s="28" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H27" s="26" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I27" s="27" t="n">
+      <c r="H27" s="28" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I27" s="29" t="n">
         <v>1</v>
       </c>
       <c r="J27" s="8" t="inlineStr">
@@ -1692,12 +1698,12 @@
       <c r="K27" s="8" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="26" t="inlineStr">
+      <c r="A28" s="28" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
       </c>
-      <c r="B28" s="26" t="inlineStr">
+      <c r="B28" s="28" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1712,27 +1718,27 @@
           <t>서버 저장(SQLite), 문서 내려받기</t>
         </is>
       </c>
-      <c r="E28" s="26" t="inlineStr">
+      <c r="E28" s="28" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F28" s="26" t="inlineStr">
+      <c r="F28" s="28" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G28" s="26" t="inlineStr">
+      <c r="G28" s="28" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H28" s="26" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I28" s="27" t="n">
+      <c r="H28" s="28" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I28" s="29" t="n">
         <v>1</v>
       </c>
       <c r="J28" s="8" t="inlineStr">
@@ -1743,12 +1749,12 @@
       <c r="K28" s="8" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="26" t="inlineStr">
+      <c r="A29" s="28" t="inlineStr">
         <is>
           <t>4.4</t>
         </is>
       </c>
-      <c r="B29" s="26" t="inlineStr">
+      <c r="B29" s="28" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1763,27 +1769,27 @@
           <t>결과를 섹션·블록으로</t>
         </is>
       </c>
-      <c r="E29" s="26" t="inlineStr">
+      <c r="E29" s="28" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F29" s="26" t="inlineStr">
+      <c r="F29" s="28" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G29" s="26" t="inlineStr">
+      <c r="G29" s="28" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H29" s="26" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I29" s="27" t="n">
+      <c r="H29" s="28" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I29" s="29" t="n">
         <v>1</v>
       </c>
       <c r="J29" s="8" t="inlineStr">
@@ -1794,12 +1800,12 @@
       <c r="K29" s="8" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="26" t="inlineStr">
+      <c r="A30" s="28" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
       </c>
-      <c r="B30" s="26" t="inlineStr">
+      <c r="B30" s="28" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1814,27 +1820,27 @@
           <t>샘플 근거 자료, 자리표시 이미지</t>
         </is>
       </c>
-      <c r="E30" s="26" t="inlineStr">
+      <c r="E30" s="28" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F30" s="26" t="inlineStr">
+      <c r="F30" s="28" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G30" s="26" t="inlineStr">
+      <c r="G30" s="28" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H30" s="26" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I30" s="27" t="n">
+      <c r="H30" s="28" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I30" s="29" t="n">
         <v>1</v>
       </c>
       <c r="J30" s="8" t="inlineStr">
@@ -1845,12 +1851,12 @@
       <c r="K30" s="8" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="26" t="inlineStr">
+      <c r="A31" s="28" t="inlineStr">
         <is>
           <t>4.6</t>
         </is>
       </c>
-      <c r="B31" s="26" t="inlineStr">
+      <c r="B31" s="28" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1865,27 +1871,27 @@
           <t>생성 중·생성 실패 화면, 최신 아님 배너, 이미지 상자, 모드 설명</t>
         </is>
       </c>
-      <c r="E31" s="26" t="inlineStr">
+      <c r="E31" s="28" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F31" s="26" t="inlineStr">
+      <c r="F31" s="28" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G31" s="26" t="inlineStr">
+      <c r="G31" s="28" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H31" s="26" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I31" s="27" t="n">
+      <c r="H31" s="28" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I31" s="29" t="n">
         <v>1</v>
       </c>
       <c r="J31" s="8" t="inlineStr">
@@ -1896,12 +1902,12 @@
       <c r="K31" s="8" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="26" t="inlineStr">
+      <c r="A32" s="28" t="inlineStr">
         <is>
           <t>4.7</t>
         </is>
       </c>
-      <c r="B32" s="26" t="inlineStr">
+      <c r="B32" s="28" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1916,27 +1922,27 @@
           <t>이전 결과를 다음 과제의 기준으로 가져오기</t>
         </is>
       </c>
-      <c r="E32" s="26" t="inlineStr">
+      <c r="E32" s="28" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F32" s="26" t="inlineStr">
+      <c r="F32" s="28" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G32" s="26" t="inlineStr">
+      <c r="G32" s="28" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H32" s="26" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I32" s="27" t="n">
+      <c r="H32" s="28" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I32" s="29" t="n">
         <v>1</v>
       </c>
       <c r="J32" s="8" t="inlineStr">
@@ -1975,12 +1981,12 @@
       <c r="K33" s="5" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="26" t="inlineStr">
+      <c r="A34" s="28" t="inlineStr">
         <is>
           <t>5.1</t>
         </is>
       </c>
-      <c r="B34" s="26" t="inlineStr">
+      <c r="B34" s="28" t="inlineStr">
         <is>
           <t>배포</t>
         </is>
@@ -1995,27 +2001,27 @@
           <t>main은 정식 주소, PR마다 미리보기 주소</t>
         </is>
       </c>
-      <c r="E34" s="26" t="inlineStr">
+      <c r="E34" s="28" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F34" s="26" t="inlineStr">
+      <c r="F34" s="28" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="G34" s="26" t="inlineStr">
+      <c r="G34" s="28" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="H34" s="26" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I34" s="27" t="n">
+      <c r="H34" s="28" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I34" s="29" t="n">
         <v>1</v>
       </c>
       <c r="J34" s="8" t="inlineStr">
@@ -2030,12 +2036,12 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="26" t="inlineStr">
+      <c r="A35" s="28" t="inlineStr">
         <is>
           <t>5.2</t>
         </is>
       </c>
-      <c r="B35" s="26" t="inlineStr">
+      <c r="B35" s="28" t="inlineStr">
         <is>
           <t>배포</t>
         </is>
@@ -2050,27 +2056,27 @@
           <t>저장 디스크 방식 정하기, 프론트와 연결</t>
         </is>
       </c>
-      <c r="E35" s="26" t="inlineStr">
+      <c r="E35" s="28" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F35" s="26" t="inlineStr">
+      <c r="F35" s="28" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="G35" s="26" t="inlineStr">
+      <c r="G35" s="28" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="H35" s="26" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I35" s="27" t="n">
+      <c r="H35" s="28" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I35" s="29" t="n">
         <v>1</v>
       </c>
       <c r="J35" s="8" t="inlineStr">
@@ -2106,19 +2112,19 @@
       <c r="G36" s="4" t="n"/>
       <c r="H36" s="4" t="n"/>
       <c r="I36" s="6">
-        <f>IFERROR(AVERAGE(I37:I44),0)</f>
+        <f>IFERROR(AVERAGE(I37:I45),0)</f>
         <v/>
       </c>
       <c r="J36" s="5" t="n"/>
       <c r="K36" s="5" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="26" t="inlineStr">
+      <c r="A37" s="28" t="inlineStr">
         <is>
           <t>6.1</t>
         </is>
       </c>
-      <c r="B37" s="26" t="inlineStr">
+      <c r="B37" s="28" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
@@ -2133,27 +2139,27 @@
           <t>가짜 모델(Mock) 대신 실제 모델</t>
         </is>
       </c>
-      <c r="E37" s="26" t="inlineStr">
+      <c r="E37" s="28" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F37" s="26" t="inlineStr">
+      <c r="F37" s="28" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="G37" s="26" t="inlineStr">
+      <c r="G37" s="28" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="H37" s="26" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I37" s="27" t="n">
+      <c r="H37" s="28" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I37" s="29" t="n">
         <v>1</v>
       </c>
       <c r="J37" s="8" t="inlineStr">
@@ -2168,12 +2174,12 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="26" t="inlineStr">
+      <c r="A38" s="28" t="inlineStr">
         <is>
           <t>6.2</t>
         </is>
       </c>
-      <c r="B38" s="26" t="inlineStr">
+      <c r="B38" s="28" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
@@ -2188,31 +2194,31 @@
           <t>준비도 기준·항목 가중치·프롬프트를 시나리오로 측정</t>
         </is>
       </c>
-      <c r="E38" s="26" t="inlineStr">
+      <c r="E38" s="28" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F38" s="26" t="n"/>
-      <c r="G38" s="26" t="n"/>
-      <c r="H38" s="26" t="inlineStr">
+      <c r="F38" s="28" t="n"/>
+      <c r="G38" s="28" t="n"/>
+      <c r="H38" s="28" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="I38" s="27" t="n">
+      <c r="I38" s="29" t="n">
         <v>0</v>
       </c>
       <c r="J38" s="8" t="n"/>
       <c r="K38" s="8" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="26" t="inlineStr">
+      <c r="A39" s="28" t="inlineStr">
         <is>
           <t>6.3</t>
         </is>
       </c>
-      <c r="B39" s="26" t="inlineStr">
+      <c r="B39" s="28" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
@@ -2227,31 +2233,31 @@
           <t>지금의 자리표시·샘플 자리에 실제 기능 연결</t>
         </is>
       </c>
-      <c r="E39" s="26" t="inlineStr">
+      <c r="E39" s="28" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F39" s="26" t="n"/>
-      <c r="G39" s="26" t="n"/>
-      <c r="H39" s="26" t="inlineStr">
+      <c r="F39" s="28" t="n"/>
+      <c r="G39" s="28" t="n"/>
+      <c r="H39" s="28" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="I39" s="27" t="n">
+      <c r="I39" s="29" t="n">
         <v>0</v>
       </c>
       <c r="J39" s="8" t="n"/>
       <c r="K39" s="8" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="26" t="inlineStr">
+      <c r="A40" s="28" t="inlineStr">
         <is>
           <t>6.4</t>
         </is>
       </c>
-      <c r="B40" s="26" t="inlineStr">
+      <c r="B40" s="28" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
@@ -2262,27 +2268,27 @@
         </is>
       </c>
       <c r="D40" s="8" t="n"/>
-      <c r="E40" s="26" t="inlineStr">
+      <c r="E40" s="28" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F40" s="26" t="inlineStr">
+      <c r="F40" s="28" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="G40" s="26" t="inlineStr">
+      <c r="G40" s="28" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="H40" s="26" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I40" s="27" t="n">
+      <c r="H40" s="28" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I40" s="29" t="n">
         <v>1</v>
       </c>
       <c r="J40" s="8" t="inlineStr">
@@ -2293,12 +2299,12 @@
       <c r="K40" s="8" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="26" t="inlineStr">
+      <c r="A41" s="28" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="B41" s="26" t="inlineStr">
+      <c r="B41" s="28" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
@@ -2309,27 +2315,27 @@
         </is>
       </c>
       <c r="D41" s="8" t="n"/>
-      <c r="E41" s="26" t="inlineStr">
+      <c r="E41" s="28" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F41" s="26" t="inlineStr">
+      <c r="F41" s="28" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="G41" s="26" t="inlineStr">
+      <c r="G41" s="28" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="H41" s="26" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I41" s="27" t="n">
+      <c r="H41" s="28" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I41" s="29" t="n">
         <v>1</v>
       </c>
       <c r="J41" s="8" t="inlineStr">
@@ -2344,12 +2350,12 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="26" t="inlineStr">
+      <c r="A42" s="28" t="inlineStr">
         <is>
           <t>6.6</t>
         </is>
       </c>
-      <c r="B42" s="26" t="inlineStr">
+      <c r="B42" s="28" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
@@ -2360,27 +2366,27 @@
         </is>
       </c>
       <c r="D42" s="8" t="n"/>
-      <c r="E42" s="26" t="inlineStr">
+      <c r="E42" s="28" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F42" s="26" t="inlineStr">
+      <c r="F42" s="28" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="G42" s="26" t="inlineStr">
+      <c r="G42" s="28" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="H42" s="26" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I42" s="27" t="n">
+      <c r="H42" s="28" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I42" s="29" t="n">
         <v>1</v>
       </c>
       <c r="J42" s="8" t="inlineStr">
@@ -2391,12 +2397,12 @@
       <c r="K42" s="8" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="26" t="inlineStr">
+      <c r="A43" s="28" t="inlineStr">
         <is>
           <t>6.7</t>
         </is>
       </c>
-      <c r="B43" s="26" t="inlineStr">
+      <c r="B43" s="28" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
@@ -2411,27 +2417,27 @@
           <t>LLM·이미지 호출 자리 수 제한, 대기 뒤 거절, 세션 되돌림</t>
         </is>
       </c>
-      <c r="E43" s="26" t="inlineStr">
+      <c r="E43" s="28" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F43" s="26" t="inlineStr">
+      <c r="F43" s="28" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="G43" s="26" t="inlineStr">
+      <c r="G43" s="28" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="H43" s="26" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I43" s="27" t="n">
+      <c r="H43" s="28" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I43" s="29" t="n">
         <v>1</v>
       </c>
       <c r="J43" s="8" t="inlineStr">
@@ -2493,110 +2499,161 @@
       <c r="K44" s="8" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+      <c r="A45" s="30" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
+      <c r="B45" s="30" t="inlineStr">
+        <is>
+          <t>실제 AI 연결</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>측정 준비(응답 시간 기록·측정 도구)</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>trace duration_ms, 실제 모델용 시나리오 실행, quick-skip 시나리오, scripts/measure.py(기본 Mock, 비용 상한)</t>
+        </is>
+      </c>
+      <c r="E45" s="30" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F45" s="30" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="G45" s="30" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="H45" s="30" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I45" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" s="8" t="inlineStr">
+        <is>
+          <t>PR #29</t>
+        </is>
+      </c>
+      <c r="K45" s="8" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>마무리</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
         <is>
           <t>평가·발표</t>
         </is>
       </c>
-      <c r="D45" s="5" t="n"/>
-      <c r="E45" s="4" t="n"/>
-      <c r="F45" s="4" t="n"/>
-      <c r="G45" s="4" t="n"/>
-      <c r="H45" s="4" t="n"/>
-      <c r="I45" s="6">
-        <f>IFERROR(AVERAGE(I46:I47),0)</f>
-        <v/>
-      </c>
-      <c r="J45" s="5" t="n"/>
-      <c r="K45" s="5" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="26" t="inlineStr">
+      <c r="D46" s="5" t="n"/>
+      <c r="E46" s="4" t="n"/>
+      <c r="F46" s="4" t="n"/>
+      <c r="G46" s="4" t="n"/>
+      <c r="H46" s="4" t="n"/>
+      <c r="I46" s="6">
+        <f>IFERROR(AVERAGE(I47:I48),0)</f>
+        <v/>
+      </c>
+      <c r="J46" s="5" t="n"/>
+      <c r="K46" s="5" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="28" t="inlineStr">
         <is>
           <t>7.1</t>
         </is>
       </c>
-      <c r="B46" s="26" t="inlineStr">
+      <c r="B47" s="28" t="inlineStr">
         <is>
           <t>마무리</t>
         </is>
       </c>
-      <c r="C46" s="8" t="inlineStr">
+      <c r="C47" s="8" t="inlineStr">
         <is>
           <t>사용성 확인·평가 지표 측정</t>
         </is>
       </c>
-      <c r="D46" s="8" t="inlineStr">
+      <c r="D47" s="8" t="inlineStr">
         <is>
           <t>필수정보 충족률, 질문 효율, 가정 표시율 등(기획서 14장)</t>
         </is>
       </c>
-      <c r="E46" s="26" t="inlineStr">
+      <c r="E47" s="28" t="inlineStr">
         <is>
           <t>공동</t>
         </is>
       </c>
-      <c r="F46" s="26" t="n"/>
-      <c r="G46" s="26" t="n"/>
-      <c r="H46" s="26" t="inlineStr">
+      <c r="F47" s="28" t="n"/>
+      <c r="G47" s="28" t="n"/>
+      <c r="H47" s="28" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="I46" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" s="8" t="n"/>
-      <c r="K46" s="8" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="26" t="inlineStr">
-        <is>
-          <t>7.2</t>
-        </is>
-      </c>
-      <c r="B47" s="26" t="inlineStr">
-        <is>
-          <t>마무리</t>
-        </is>
-      </c>
-      <c r="C47" s="8" t="inlineStr">
-        <is>
-          <t>최종 발표 자료</t>
-        </is>
-      </c>
-      <c r="D47" s="8" t="n"/>
-      <c r="E47" s="26" t="inlineStr">
-        <is>
-          <t>공동</t>
-        </is>
-      </c>
-      <c r="F47" s="26" t="n"/>
-      <c r="G47" s="26" t="n"/>
-      <c r="H47" s="26" t="inlineStr">
-        <is>
-          <t>예정</t>
-        </is>
-      </c>
-      <c r="I47" s="27" t="n">
+      <c r="I47" s="29" t="n">
         <v>0</v>
       </c>
       <c r="J47" s="8" t="n"/>
       <c r="K47" s="8" t="n"/>
     </row>
+    <row r="48">
+      <c r="A48" s="28" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="B48" s="28" t="inlineStr">
+        <is>
+          <t>마무리</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>최종 발표 자료</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="n"/>
+      <c r="E48" s="28" t="inlineStr">
+        <is>
+          <t>공동</t>
+        </is>
+      </c>
+      <c r="F48" s="28" t="n"/>
+      <c r="G48" s="28" t="n"/>
+      <c r="H48" s="28" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="I48" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="8" t="n"/>
+      <c r="K48" s="8" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:K47"/>
-  <conditionalFormatting sqref="H5:H47">
+  <autoFilter ref="A4:K48"/>
+  <conditionalFormatting sqref="H5:H48">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"완료"</formula>
     </cfRule>
@@ -2607,7 +2664,7 @@
       <formula>"보류"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I5:I47">
+  <conditionalFormatting sqref="I5:I48">
     <cfRule type="dataBar" priority="4">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -2617,10 +2674,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="H5:H47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"완료,진행 중,예정,보류"</formula1>
     </dataValidation>
-    <dataValidation sqref="E5:E47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"개발,디자인,공동"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2692,23 +2749,23 @@
         </is>
       </c>
       <c r="B4" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$47,A4,WBS!$H$5:$H$47,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$48,A4,WBS!$H$5:$H$48,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C4" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$47,A4,WBS!$H$5:$H$47,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$48,A4,WBS!$H$5:$H$48,"완료")</f>
         <v/>
       </c>
       <c r="D4" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$47,A4,WBS!$H$5:$H$47,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$48,A4,WBS!$H$5:$H$48,"진행 중")</f>
         <v/>
       </c>
       <c r="E4" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$47,A4,WBS!$H$5:$H$47,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$48,A4,WBS!$H$5:$H$48,"예정")</f>
         <v/>
       </c>
       <c r="F4" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$47,WBS!$B$5:$B$47,A4,WBS!$H$5:$H$47,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$48,WBS!$B$5:$B$48,A4,WBS!$H$5:$H$48,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2719,23 +2776,23 @@
         </is>
       </c>
       <c r="B5" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$47,A5,WBS!$H$5:$H$47,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$48,A5,WBS!$H$5:$H$48,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C5" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$47,A5,WBS!$H$5:$H$47,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$48,A5,WBS!$H$5:$H$48,"완료")</f>
         <v/>
       </c>
       <c r="D5" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$47,A5,WBS!$H$5:$H$47,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$48,A5,WBS!$H$5:$H$48,"진행 중")</f>
         <v/>
       </c>
       <c r="E5" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$47,A5,WBS!$H$5:$H$47,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$48,A5,WBS!$H$5:$H$48,"예정")</f>
         <v/>
       </c>
       <c r="F5" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$47,WBS!$B$5:$B$47,A5,WBS!$H$5:$H$47,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$48,WBS!$B$5:$B$48,A5,WBS!$H$5:$H$48,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2746,23 +2803,23 @@
         </is>
       </c>
       <c r="B6" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$47,A6,WBS!$H$5:$H$47,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$48,A6,WBS!$H$5:$H$48,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C6" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$47,A6,WBS!$H$5:$H$47,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$48,A6,WBS!$H$5:$H$48,"완료")</f>
         <v/>
       </c>
       <c r="D6" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$47,A6,WBS!$H$5:$H$47,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$48,A6,WBS!$H$5:$H$48,"진행 중")</f>
         <v/>
       </c>
       <c r="E6" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$47,A6,WBS!$H$5:$H$47,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$48,A6,WBS!$H$5:$H$48,"예정")</f>
         <v/>
       </c>
       <c r="F6" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$47,WBS!$B$5:$B$47,A6,WBS!$H$5:$H$47,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$48,WBS!$B$5:$B$48,A6,WBS!$H$5:$H$48,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2773,23 +2830,23 @@
         </is>
       </c>
       <c r="B7" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$47,A7,WBS!$H$5:$H$47,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$48,A7,WBS!$H$5:$H$48,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C7" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$47,A7,WBS!$H$5:$H$47,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$48,A7,WBS!$H$5:$H$48,"완료")</f>
         <v/>
       </c>
       <c r="D7" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$47,A7,WBS!$H$5:$H$47,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$48,A7,WBS!$H$5:$H$48,"진행 중")</f>
         <v/>
       </c>
       <c r="E7" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$47,A7,WBS!$H$5:$H$47,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$48,A7,WBS!$H$5:$H$48,"예정")</f>
         <v/>
       </c>
       <c r="F7" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$47,WBS!$B$5:$B$47,A7,WBS!$H$5:$H$47,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$48,WBS!$B$5:$B$48,A7,WBS!$H$5:$H$48,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2800,23 +2857,23 @@
         </is>
       </c>
       <c r="B8" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$47,A8,WBS!$H$5:$H$47,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$48,A8,WBS!$H$5:$H$48,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C8" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$47,A8,WBS!$H$5:$H$47,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$48,A8,WBS!$H$5:$H$48,"완료")</f>
         <v/>
       </c>
       <c r="D8" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$47,A8,WBS!$H$5:$H$47,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$48,A8,WBS!$H$5:$H$48,"진행 중")</f>
         <v/>
       </c>
       <c r="E8" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$47,A8,WBS!$H$5:$H$47,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$48,A8,WBS!$H$5:$H$48,"예정")</f>
         <v/>
       </c>
       <c r="F8" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$47,WBS!$B$5:$B$47,A8,WBS!$H$5:$H$47,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$48,WBS!$B$5:$B$48,A8,WBS!$H$5:$H$48,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2827,23 +2884,23 @@
         </is>
       </c>
       <c r="B9" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$47,A9,WBS!$H$5:$H$47,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$48,A9,WBS!$H$5:$H$48,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C9" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$47,A9,WBS!$H$5:$H$47,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$48,A9,WBS!$H$5:$H$48,"완료")</f>
         <v/>
       </c>
       <c r="D9" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$47,A9,WBS!$H$5:$H$47,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$48,A9,WBS!$H$5:$H$48,"진행 중")</f>
         <v/>
       </c>
       <c r="E9" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$47,A9,WBS!$H$5:$H$47,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$48,A9,WBS!$H$5:$H$48,"예정")</f>
         <v/>
       </c>
       <c r="F9" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$47,WBS!$B$5:$B$47,A9,WBS!$H$5:$H$47,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$48,WBS!$B$5:$B$48,A9,WBS!$H$5:$H$48,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2854,23 +2911,23 @@
         </is>
       </c>
       <c r="B10" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$47,A10,WBS!$H$5:$H$47,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$48,A10,WBS!$H$5:$H$48,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C10" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$47,A10,WBS!$H$5:$H$47,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$48,A10,WBS!$H$5:$H$48,"완료")</f>
         <v/>
       </c>
       <c r="D10" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$47,A10,WBS!$H$5:$H$47,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$48,A10,WBS!$H$5:$H$48,"진행 중")</f>
         <v/>
       </c>
       <c r="E10" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$47,A10,WBS!$H$5:$H$47,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$48,A10,WBS!$H$5:$H$48,"예정")</f>
         <v/>
       </c>
       <c r="F10" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$47,WBS!$B$5:$B$47,A10,WBS!$H$5:$H$47,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$48,WBS!$B$5:$B$48,A10,WBS!$H$5:$H$48,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2897,7 +2954,7 @@
         <v/>
       </c>
       <c r="F11" s="14">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$47,WBS!$H$5:$H$47,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$48,WBS!$H$5:$H$48,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>

--- a/docs/WBS.xlsx
+++ b/docs/WBS.xlsx
@@ -681,12 +681,12 @@
       <c r="K5" s="5" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="28" t="inlineStr">
+      <c r="A6" s="30" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="B6" s="28" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>기획·설계</t>
         </is>
@@ -701,23 +701,23 @@
           <t>과제 4개(사업계획·상품기획·브랜딩·마케팅), 적응형 질문, 사실·가정 분리 원칙</t>
         </is>
       </c>
-      <c r="E6" s="28" t="inlineStr">
+      <c r="E6" s="30" t="inlineStr">
         <is>
           <t>공동</t>
         </is>
       </c>
-      <c r="F6" s="28" t="n"/>
-      <c r="G6" s="28" t="inlineStr">
+      <c r="F6" s="30" t="n"/>
+      <c r="G6" s="30" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="H6" s="28" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I6" s="29" t="n">
+      <c r="H6" s="30" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I6" s="31" t="n">
         <v>1</v>
       </c>
       <c r="J6" s="8" t="inlineStr">
@@ -728,12 +728,12 @@
       <c r="K6" s="8" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="28" t="inlineStr">
+      <c r="A7" s="30" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="B7" s="28" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>기획·설계</t>
         </is>
@@ -748,27 +748,27 @@
           <t>FastAPI 하네스 구조, API 계약, 테스트 전략</t>
         </is>
       </c>
-      <c r="E7" s="28" t="inlineStr">
+      <c r="E7" s="30" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F7" s="28" t="inlineStr">
+      <c r="F7" s="30" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="G7" s="28" t="inlineStr">
+      <c r="G7" s="30" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="H7" s="28" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I7" s="29" t="n">
+      <c r="H7" s="30" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I7" s="31" t="n">
         <v>1</v>
       </c>
       <c r="J7" s="8" t="inlineStr">
@@ -779,12 +779,12 @@
       <c r="K7" s="8" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="28" t="inlineStr">
+      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>1.3</t>
         </is>
       </c>
-      <c r="B8" s="28" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>기획·설계</t>
         </is>
@@ -799,27 +799,27 @@
           <t>V2 화면 흐름, 묶음 0~4로 작업 나누기</t>
         </is>
       </c>
-      <c r="E8" s="28" t="inlineStr">
+      <c r="E8" s="30" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F8" s="28" t="inlineStr">
+      <c r="F8" s="30" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G8" s="28" t="inlineStr">
+      <c r="G8" s="30" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H8" s="28" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I8" s="29" t="n">
+      <c r="H8" s="30" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I8" s="31" t="n">
         <v>1</v>
       </c>
       <c r="J8" s="8" t="inlineStr">
@@ -830,12 +830,12 @@
       <c r="K8" s="8" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="28" t="inlineStr">
+      <c r="A9" s="30" t="inlineStr">
         <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="B9" s="28" t="inlineStr">
+      <c r="B9" s="30" t="inlineStr">
         <is>
           <t>기획·설계</t>
         </is>
@@ -850,27 +850,27 @@
           <t>지금 상태·다음 할 일·작업 방식·환경 팁, PR마다 갱신</t>
         </is>
       </c>
-      <c r="E9" s="28" t="inlineStr">
+      <c r="E9" s="30" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F9" s="28" t="inlineStr">
+      <c r="F9" s="30" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="G9" s="28" t="inlineStr">
+      <c r="G9" s="30" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="H9" s="28" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I9" s="29" t="n">
+      <c r="H9" s="30" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I9" s="31" t="n">
         <v>1</v>
       </c>
       <c r="J9" s="8" t="inlineStr">
@@ -881,12 +881,12 @@
       <c r="K9" s="8" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="28" t="inlineStr">
+      <c r="A10" s="30" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="B10" s="28" t="inlineStr">
+      <c r="B10" s="30" t="inlineStr">
         <is>
           <t>기획·설계</t>
         </is>
@@ -901,27 +901,27 @@
           <t>바로 보기 주소, 된 것, 남은 일·맡을 사람·상의할 점</t>
         </is>
       </c>
-      <c r="E10" s="28" t="inlineStr">
+      <c r="E10" s="30" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F10" s="28" t="inlineStr">
+      <c r="F10" s="30" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="G10" s="28" t="inlineStr">
+      <c r="G10" s="30" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="H10" s="28" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I10" s="29" t="n">
+      <c r="H10" s="30" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I10" s="31" t="n">
         <v>1</v>
       </c>
       <c r="J10" s="8" t="inlineStr">
@@ -960,12 +960,12 @@
       <c r="K11" s="5" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="28" t="inlineStr">
+      <c r="A12" s="30" t="inlineStr">
         <is>
           <t>2.1</t>
         </is>
       </c>
-      <c r="B12" s="28" t="inlineStr">
+      <c r="B12" s="30" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -980,27 +980,27 @@
           <t>사실·가정·미정 구분, 정보 출처 표시</t>
         </is>
       </c>
-      <c r="E12" s="28" t="inlineStr">
+      <c r="E12" s="30" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F12" s="28" t="inlineStr">
+      <c r="F12" s="30" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="G12" s="28" t="inlineStr">
+      <c r="G12" s="30" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H12" s="28" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I12" s="29" t="n">
+      <c r="H12" s="30" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I12" s="31" t="n">
         <v>1</v>
       </c>
       <c r="J12" s="8" t="inlineStr">
@@ -1011,12 +1011,12 @@
       <c r="K12" s="8" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="28" t="inlineStr">
+      <c r="A13" s="30" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
       </c>
-      <c r="B13" s="28" t="inlineStr">
+      <c r="B13" s="30" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1031,27 +1031,27 @@
           <t>비용 없이 개발·테스트하는 가짜 모델</t>
         </is>
       </c>
-      <c r="E13" s="28" t="inlineStr">
+      <c r="E13" s="30" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F13" s="28" t="inlineStr">
+      <c r="F13" s="30" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="G13" s="28" t="inlineStr">
+      <c r="G13" s="30" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H13" s="28" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I13" s="29" t="n">
+      <c r="H13" s="30" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I13" s="31" t="n">
         <v>1</v>
       </c>
       <c r="J13" s="8" t="inlineStr">
@@ -1062,12 +1062,12 @@
       <c r="K13" s="8" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="28" t="inlineStr">
+      <c r="A14" s="30" t="inlineStr">
         <is>
           <t>2.3</t>
         </is>
       </c>
-      <c r="B14" s="28" t="inlineStr">
+      <c r="B14" s="30" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1082,27 +1082,27 @@
           <t>과제별 질문 정책(policy.yaml), 단계별 프롬프트</t>
         </is>
       </c>
-      <c r="E14" s="28" t="inlineStr">
+      <c r="E14" s="30" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F14" s="28" t="inlineStr">
+      <c r="F14" s="30" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G14" s="28" t="inlineStr">
+      <c r="G14" s="30" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H14" s="28" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I14" s="29" t="n">
+      <c r="H14" s="30" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I14" s="31" t="n">
         <v>1</v>
       </c>
       <c r="J14" s="8" t="inlineStr">
@@ -1113,12 +1113,12 @@
       <c r="K14" s="8" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="28" t="inlineStr">
+      <c r="A15" s="30" t="inlineStr">
         <is>
           <t>2.4</t>
         </is>
       </c>
-      <c r="B15" s="28" t="inlineStr">
+      <c r="B15" s="30" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1133,27 +1133,27 @@
           <t>모드별 질문 상한, '다른 예시 보기' 단계</t>
         </is>
       </c>
-      <c r="E15" s="28" t="inlineStr">
+      <c r="E15" s="30" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F15" s="28" t="inlineStr">
+      <c r="F15" s="30" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G15" s="28" t="inlineStr">
+      <c r="G15" s="30" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H15" s="28" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I15" s="29" t="n">
+      <c r="H15" s="30" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I15" s="31" t="n">
         <v>1</v>
       </c>
       <c r="J15" s="8" t="inlineStr">
@@ -1164,12 +1164,12 @@
       <c r="K15" s="8" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="28" t="inlineStr">
+      <c r="A16" s="30" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
       </c>
-      <c r="B16" s="28" t="inlineStr">
+      <c r="B16" s="30" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1180,27 +1180,27 @@
         </is>
       </c>
       <c r="D16" s="8" t="n"/>
-      <c r="E16" s="28" t="inlineStr">
+      <c r="E16" s="30" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F16" s="28" t="inlineStr">
+      <c r="F16" s="30" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G16" s="28" t="inlineStr">
+      <c r="G16" s="30" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H16" s="28" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I16" s="29" t="n">
+      <c r="H16" s="30" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I16" s="31" t="n">
         <v>1</v>
       </c>
       <c r="J16" s="8" t="inlineStr">
@@ -1211,12 +1211,12 @@
       <c r="K16" s="8" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="28" t="inlineStr">
+      <c r="A17" s="30" t="inlineStr">
         <is>
           <t>2.6</t>
         </is>
       </c>
-      <c r="B17" s="28" t="inlineStr">
+      <c r="B17" s="30" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1231,27 +1231,27 @@
           <t>과제별 정책·프롬프트·검증 규칙</t>
         </is>
       </c>
-      <c r="E17" s="28" t="inlineStr">
+      <c r="E17" s="30" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F17" s="28" t="inlineStr">
+      <c r="F17" s="30" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G17" s="28" t="inlineStr">
+      <c r="G17" s="30" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H17" s="28" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I17" s="29" t="n">
+      <c r="H17" s="30" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I17" s="31" t="n">
         <v>1</v>
       </c>
       <c r="J17" s="8" t="inlineStr">
@@ -1262,12 +1262,12 @@
       <c r="K17" s="8" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="28" t="inlineStr">
+      <c r="A18" s="30" t="inlineStr">
         <is>
           <t>2.7</t>
         </is>
       </c>
-      <c r="B18" s="28" t="inlineStr">
+      <c r="B18" s="30" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1282,27 +1282,27 @@
           <t>한국어 오류 문구, API 문서</t>
         </is>
       </c>
-      <c r="E18" s="28" t="inlineStr">
+      <c r="E18" s="30" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F18" s="28" t="inlineStr">
+      <c r="F18" s="30" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G18" s="28" t="inlineStr">
+      <c r="G18" s="30" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H18" s="28" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I18" s="29" t="n">
+      <c r="H18" s="30" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I18" s="31" t="n">
         <v>1</v>
       </c>
       <c r="J18" s="8" t="inlineStr">
@@ -1313,12 +1313,12 @@
       <c r="K18" s="8" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="28" t="inlineStr">
+      <c r="A19" s="30" t="inlineStr">
         <is>
           <t>2.8</t>
         </is>
       </c>
-      <c r="B19" s="28" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1333,27 +1333,27 @@
           <t>API에 맞춘 최소 화면, 개발 안내(CLAUDE.md)</t>
         </is>
       </c>
-      <c r="E19" s="28" t="inlineStr">
+      <c r="E19" s="30" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F19" s="28" t="inlineStr">
+      <c r="F19" s="30" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G19" s="28" t="inlineStr">
+      <c r="G19" s="30" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H19" s="28" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I19" s="29" t="n">
+      <c r="H19" s="30" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I19" s="31" t="n">
         <v>1</v>
       </c>
       <c r="J19" s="8" t="inlineStr">
@@ -1392,12 +1392,12 @@
       <c r="K20" s="5" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="28" t="inlineStr">
+      <c r="A21" s="30" t="inlineStr">
         <is>
           <t>3.1</t>
         </is>
       </c>
-      <c r="B21" s="28" t="inlineStr">
+      <c r="B21" s="30" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
@@ -1412,23 +1412,23 @@
           <t>전체 화면 흐름 HTML 프로토타입</t>
         </is>
       </c>
-      <c r="E21" s="28" t="inlineStr">
+      <c r="E21" s="30" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
       </c>
-      <c r="F21" s="28" t="n"/>
-      <c r="G21" s="28" t="inlineStr">
+      <c r="F21" s="30" t="n"/>
+      <c r="G21" s="30" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H21" s="28" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I21" s="29" t="n">
+      <c r="H21" s="30" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I21" s="31" t="n">
         <v>1</v>
       </c>
       <c r="J21" s="8" t="inlineStr">
@@ -1439,12 +1439,12 @@
       <c r="K21" s="8" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="28" t="inlineStr">
+      <c r="A22" s="30" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
       </c>
-      <c r="B22" s="28" t="inlineStr">
+      <c r="B22" s="30" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
@@ -1459,27 +1459,27 @@
           <t>모든 질문에 '다른 예시 보기', 모드 설명, 이미지 블록, 생성 중·실패·최신 아님 상태</t>
         </is>
       </c>
-      <c r="E22" s="28" t="inlineStr">
+      <c r="E22" s="30" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
       </c>
-      <c r="F22" s="28" t="inlineStr">
+      <c r="F22" s="30" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G22" s="28" t="inlineStr">
+      <c r="G22" s="30" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H22" s="28" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I22" s="29" t="n">
+      <c r="H22" s="30" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I22" s="31" t="n">
         <v>1</v>
       </c>
       <c r="J22" s="8" t="inlineStr">
@@ -1490,12 +1490,12 @@
       <c r="K22" s="8" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="28" t="inlineStr">
+      <c r="A23" s="30" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
       </c>
-      <c r="B23" s="28" t="inlineStr">
+      <c r="B23" s="30" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
@@ -1510,31 +1510,31 @@
           <t>반응형 자동 배치 확인</t>
         </is>
       </c>
-      <c r="E23" s="28" t="inlineStr">
+      <c r="E23" s="30" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
       </c>
-      <c r="F23" s="28" t="n"/>
-      <c r="G23" s="28" t="n"/>
-      <c r="H23" s="28" t="inlineStr">
+      <c r="F23" s="30" t="n"/>
+      <c r="G23" s="30" t="n"/>
+      <c r="H23" s="30" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="I23" s="29" t="n">
+      <c r="I23" s="31" t="n">
         <v>0</v>
       </c>
       <c r="J23" s="8" t="n"/>
       <c r="K23" s="8" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="28" t="inlineStr">
+      <c r="A24" s="30" t="inlineStr">
         <is>
           <t>3.4</t>
         </is>
       </c>
-      <c r="B24" s="28" t="inlineStr">
+      <c r="B24" s="30" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
@@ -1549,19 +1549,19 @@
           <t>/preview 화면을 html.to.design으로 가져와 수정</t>
         </is>
       </c>
-      <c r="E24" s="28" t="inlineStr">
+      <c r="E24" s="30" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
       </c>
-      <c r="F24" s="28" t="n"/>
-      <c r="G24" s="28" t="n"/>
-      <c r="H24" s="28" t="inlineStr">
+      <c r="F24" s="30" t="n"/>
+      <c r="G24" s="30" t="n"/>
+      <c r="H24" s="30" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="I24" s="29" t="n">
+      <c r="I24" s="31" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="8" t="n"/>
@@ -1596,12 +1596,12 @@
       <c r="K25" s="5" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="28" t="inlineStr">
+      <c r="A26" s="30" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
       </c>
-      <c r="B26" s="28" t="inlineStr">
+      <c r="B26" s="30" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1616,27 +1616,27 @@
           <t>버셀 배포 설정 포함</t>
         </is>
       </c>
-      <c r="E26" s="28" t="inlineStr">
+      <c r="E26" s="30" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F26" s="28" t="inlineStr">
+      <c r="F26" s="30" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G26" s="28" t="inlineStr">
+      <c r="G26" s="30" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H26" s="28" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I26" s="29" t="n">
+      <c r="H26" s="30" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I26" s="31" t="n">
         <v>1</v>
       </c>
       <c r="J26" s="8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       <c r="K26" s="8" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="28" t="inlineStr">
+      <c r="A27" s="30" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
       </c>
-      <c r="B27" s="28" t="inlineStr">
+      <c r="B27" s="30" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1667,27 +1667,27 @@
           <t>답변 종류, 흐름 패널, 익명 사용자</t>
         </is>
       </c>
-      <c r="E27" s="28" t="inlineStr">
+      <c r="E27" s="30" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F27" s="28" t="inlineStr">
+      <c r="F27" s="30" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G27" s="28" t="inlineStr">
+      <c r="G27" s="30" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H27" s="28" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I27" s="29" t="n">
+      <c r="H27" s="30" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I27" s="31" t="n">
         <v>1</v>
       </c>
       <c r="J27" s="8" t="inlineStr">
@@ -1698,12 +1698,12 @@
       <c r="K27" s="8" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="28" t="inlineStr">
+      <c r="A28" s="30" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
       </c>
-      <c r="B28" s="28" t="inlineStr">
+      <c r="B28" s="30" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1718,27 +1718,27 @@
           <t>서버 저장(SQLite), 문서 내려받기</t>
         </is>
       </c>
-      <c r="E28" s="28" t="inlineStr">
+      <c r="E28" s="30" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F28" s="28" t="inlineStr">
+      <c r="F28" s="30" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G28" s="28" t="inlineStr">
+      <c r="G28" s="30" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H28" s="28" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I28" s="29" t="n">
+      <c r="H28" s="30" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I28" s="31" t="n">
         <v>1</v>
       </c>
       <c r="J28" s="8" t="inlineStr">
@@ -1749,12 +1749,12 @@
       <c r="K28" s="8" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="28" t="inlineStr">
+      <c r="A29" s="30" t="inlineStr">
         <is>
           <t>4.4</t>
         </is>
       </c>
-      <c r="B29" s="28" t="inlineStr">
+      <c r="B29" s="30" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1769,27 +1769,27 @@
           <t>결과를 섹션·블록으로</t>
         </is>
       </c>
-      <c r="E29" s="28" t="inlineStr">
+      <c r="E29" s="30" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F29" s="28" t="inlineStr">
+      <c r="F29" s="30" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G29" s="28" t="inlineStr">
+      <c r="G29" s="30" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H29" s="28" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I29" s="29" t="n">
+      <c r="H29" s="30" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I29" s="31" t="n">
         <v>1</v>
       </c>
       <c r="J29" s="8" t="inlineStr">
@@ -1800,12 +1800,12 @@
       <c r="K29" s="8" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="28" t="inlineStr">
+      <c r="A30" s="30" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
       </c>
-      <c r="B30" s="28" t="inlineStr">
+      <c r="B30" s="30" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1820,27 +1820,27 @@
           <t>샘플 근거 자료, 자리표시 이미지</t>
         </is>
       </c>
-      <c r="E30" s="28" t="inlineStr">
+      <c r="E30" s="30" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F30" s="28" t="inlineStr">
+      <c r="F30" s="30" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G30" s="28" t="inlineStr">
+      <c r="G30" s="30" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H30" s="28" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I30" s="29" t="n">
+      <c r="H30" s="30" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I30" s="31" t="n">
         <v>1</v>
       </c>
       <c r="J30" s="8" t="inlineStr">
@@ -1851,12 +1851,12 @@
       <c r="K30" s="8" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="28" t="inlineStr">
+      <c r="A31" s="30" t="inlineStr">
         <is>
           <t>4.6</t>
         </is>
       </c>
-      <c r="B31" s="28" t="inlineStr">
+      <c r="B31" s="30" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1871,27 +1871,27 @@
           <t>생성 중·생성 실패 화면, 최신 아님 배너, 이미지 상자, 모드 설명</t>
         </is>
       </c>
-      <c r="E31" s="28" t="inlineStr">
+      <c r="E31" s="30" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F31" s="28" t="inlineStr">
+      <c r="F31" s="30" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G31" s="28" t="inlineStr">
+      <c r="G31" s="30" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H31" s="28" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I31" s="29" t="n">
+      <c r="H31" s="30" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I31" s="31" t="n">
         <v>1</v>
       </c>
       <c r="J31" s="8" t="inlineStr">
@@ -1902,12 +1902,12 @@
       <c r="K31" s="8" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="28" t="inlineStr">
+      <c r="A32" s="30" t="inlineStr">
         <is>
           <t>4.7</t>
         </is>
       </c>
-      <c r="B32" s="28" t="inlineStr">
+      <c r="B32" s="30" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1922,27 +1922,27 @@
           <t>이전 결과를 다음 과제의 기준으로 가져오기</t>
         </is>
       </c>
-      <c r="E32" s="28" t="inlineStr">
+      <c r="E32" s="30" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F32" s="28" t="inlineStr">
+      <c r="F32" s="30" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G32" s="28" t="inlineStr">
+      <c r="G32" s="30" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H32" s="28" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I32" s="29" t="n">
+      <c r="H32" s="30" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I32" s="31" t="n">
         <v>1</v>
       </c>
       <c r="J32" s="8" t="inlineStr">
@@ -1981,12 +1981,12 @@
       <c r="K33" s="5" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="28" t="inlineStr">
+      <c r="A34" s="30" t="inlineStr">
         <is>
           <t>5.1</t>
         </is>
       </c>
-      <c r="B34" s="28" t="inlineStr">
+      <c r="B34" s="30" t="inlineStr">
         <is>
           <t>배포</t>
         </is>
@@ -2001,27 +2001,27 @@
           <t>main은 정식 주소, PR마다 미리보기 주소</t>
         </is>
       </c>
-      <c r="E34" s="28" t="inlineStr">
+      <c r="E34" s="30" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F34" s="28" t="inlineStr">
+      <c r="F34" s="30" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="G34" s="28" t="inlineStr">
+      <c r="G34" s="30" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="H34" s="28" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I34" s="29" t="n">
+      <c r="H34" s="30" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I34" s="31" t="n">
         <v>1</v>
       </c>
       <c r="J34" s="8" t="inlineStr">
@@ -2036,12 +2036,12 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="28" t="inlineStr">
+      <c r="A35" s="30" t="inlineStr">
         <is>
           <t>5.2</t>
         </is>
       </c>
-      <c r="B35" s="28" t="inlineStr">
+      <c r="B35" s="30" t="inlineStr">
         <is>
           <t>배포</t>
         </is>
@@ -2056,27 +2056,27 @@
           <t>저장 디스크 방식 정하기, 프론트와 연결</t>
         </is>
       </c>
-      <c r="E35" s="28" t="inlineStr">
+      <c r="E35" s="30" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F35" s="28" t="inlineStr">
+      <c r="F35" s="30" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="G35" s="28" t="inlineStr">
+      <c r="G35" s="30" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="H35" s="28" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I35" s="29" t="n">
+      <c r="H35" s="30" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I35" s="31" t="n">
         <v>1</v>
       </c>
       <c r="J35" s="8" t="inlineStr">
@@ -2119,12 +2119,12 @@
       <c r="K36" s="5" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="28" t="inlineStr">
+      <c r="A37" s="30" t="inlineStr">
         <is>
           <t>6.1</t>
         </is>
       </c>
-      <c r="B37" s="28" t="inlineStr">
+      <c r="B37" s="30" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
@@ -2139,27 +2139,27 @@
           <t>가짜 모델(Mock) 대신 실제 모델</t>
         </is>
       </c>
-      <c r="E37" s="28" t="inlineStr">
+      <c r="E37" s="30" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F37" s="28" t="inlineStr">
+      <c r="F37" s="30" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="G37" s="28" t="inlineStr">
+      <c r="G37" s="30" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="H37" s="28" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I37" s="29" t="n">
+      <c r="H37" s="30" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I37" s="31" t="n">
         <v>1</v>
       </c>
       <c r="J37" s="8" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="28" t="inlineStr">
+      <c r="A38" s="30" t="inlineStr">
         <is>
           <t>6.2</t>
         </is>
       </c>
-      <c r="B38" s="28" t="inlineStr">
+      <c r="B38" s="30" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
@@ -2194,31 +2194,31 @@
           <t>준비도 기준·항목 가중치·프롬프트를 시나리오로 측정</t>
         </is>
       </c>
-      <c r="E38" s="28" t="inlineStr">
+      <c r="E38" s="30" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F38" s="28" t="n"/>
-      <c r="G38" s="28" t="n"/>
-      <c r="H38" s="28" t="inlineStr">
+      <c r="F38" s="30" t="n"/>
+      <c r="G38" s="30" t="n"/>
+      <c r="H38" s="30" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="I38" s="29" t="n">
+      <c r="I38" s="31" t="n">
         <v>0</v>
       </c>
       <c r="J38" s="8" t="n"/>
       <c r="K38" s="8" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="28" t="inlineStr">
+      <c r="A39" s="30" t="inlineStr">
         <is>
           <t>6.3</t>
         </is>
       </c>
-      <c r="B39" s="28" t="inlineStr">
+      <c r="B39" s="30" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
@@ -2233,31 +2233,31 @@
           <t>지금의 자리표시·샘플 자리에 실제 기능 연결</t>
         </is>
       </c>
-      <c r="E39" s="28" t="inlineStr">
+      <c r="E39" s="30" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F39" s="28" t="n"/>
-      <c r="G39" s="28" t="n"/>
-      <c r="H39" s="28" t="inlineStr">
+      <c r="F39" s="30" t="n"/>
+      <c r="G39" s="30" t="n"/>
+      <c r="H39" s="30" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="I39" s="29" t="n">
+      <c r="I39" s="31" t="n">
         <v>0</v>
       </c>
       <c r="J39" s="8" t="n"/>
       <c r="K39" s="8" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="28" t="inlineStr">
+      <c r="A40" s="30" t="inlineStr">
         <is>
           <t>6.4</t>
         </is>
       </c>
-      <c r="B40" s="28" t="inlineStr">
+      <c r="B40" s="30" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
@@ -2268,27 +2268,27 @@
         </is>
       </c>
       <c r="D40" s="8" t="n"/>
-      <c r="E40" s="28" t="inlineStr">
+      <c r="E40" s="30" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F40" s="28" t="inlineStr">
+      <c r="F40" s="30" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="G40" s="28" t="inlineStr">
+      <c r="G40" s="30" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="H40" s="28" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I40" s="29" t="n">
+      <c r="H40" s="30" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I40" s="31" t="n">
         <v>1</v>
       </c>
       <c r="J40" s="8" t="inlineStr">
@@ -2299,12 +2299,12 @@
       <c r="K40" s="8" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="28" t="inlineStr">
+      <c r="A41" s="30" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="B41" s="28" t="inlineStr">
+      <c r="B41" s="30" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
@@ -2315,27 +2315,27 @@
         </is>
       </c>
       <c r="D41" s="8" t="n"/>
-      <c r="E41" s="28" t="inlineStr">
+      <c r="E41" s="30" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F41" s="28" t="inlineStr">
+      <c r="F41" s="30" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="G41" s="28" t="inlineStr">
+      <c r="G41" s="30" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="H41" s="28" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I41" s="29" t="n">
+      <c r="H41" s="30" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I41" s="31" t="n">
         <v>1</v>
       </c>
       <c r="J41" s="8" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="28" t="inlineStr">
+      <c r="A42" s="30" t="inlineStr">
         <is>
           <t>6.6</t>
         </is>
       </c>
-      <c r="B42" s="28" t="inlineStr">
+      <c r="B42" s="30" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
@@ -2366,27 +2366,27 @@
         </is>
       </c>
       <c r="D42" s="8" t="n"/>
-      <c r="E42" s="28" t="inlineStr">
+      <c r="E42" s="30" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F42" s="28" t="inlineStr">
+      <c r="F42" s="30" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="G42" s="28" t="inlineStr">
+      <c r="G42" s="30" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="H42" s="28" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I42" s="29" t="n">
+      <c r="H42" s="30" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I42" s="31" t="n">
         <v>1</v>
       </c>
       <c r="J42" s="8" t="inlineStr">
@@ -2397,12 +2397,12 @@
       <c r="K42" s="8" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="28" t="inlineStr">
+      <c r="A43" s="30" t="inlineStr">
         <is>
           <t>6.7</t>
         </is>
       </c>
-      <c r="B43" s="28" t="inlineStr">
+      <c r="B43" s="30" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
@@ -2417,27 +2417,27 @@
           <t>LLM·이미지 호출 자리 수 제한, 대기 뒤 거절, 세션 되돌림</t>
         </is>
       </c>
-      <c r="E43" s="28" t="inlineStr">
+      <c r="E43" s="30" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F43" s="28" t="inlineStr">
+      <c r="F43" s="30" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="G43" s="28" t="inlineStr">
+      <c r="G43" s="30" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="H43" s="28" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I43" s="29" t="n">
+      <c r="H43" s="30" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I43" s="31" t="n">
         <v>1</v>
       </c>
       <c r="J43" s="8" t="inlineStr">
@@ -2448,12 +2448,12 @@
       <c r="K43" s="8" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="28" t="inlineStr">
+      <c r="A44" s="30" t="inlineStr">
         <is>
           <t>6.8</t>
         </is>
       </c>
-      <c r="B44" s="28" t="inlineStr">
+      <c r="B44" s="30" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
@@ -2468,27 +2468,27 @@
           <t>결과 항목 조각 동시 생성·코드 합치기·부분 결과 캐시, README 설계 고민, 로드맵 측정표</t>
         </is>
       </c>
-      <c r="E44" s="28" t="inlineStr">
+      <c r="E44" s="30" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F44" s="28" t="inlineStr">
+      <c r="F44" s="30" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="G44" s="28" t="inlineStr">
+      <c r="G44" s="30" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="H44" s="28" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I44" s="29" t="n">
+      <c r="H44" s="30" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I44" s="31" t="n">
         <v>1</v>
       </c>
       <c r="J44" s="8" t="inlineStr">
@@ -2578,12 +2578,12 @@
       <c r="K46" s="5" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="28" t="inlineStr">
+      <c r="A47" s="30" t="inlineStr">
         <is>
           <t>7.1</t>
         </is>
       </c>
-      <c r="B47" s="28" t="inlineStr">
+      <c r="B47" s="30" t="inlineStr">
         <is>
           <t>마무리</t>
         </is>
@@ -2598,31 +2598,39 @@
           <t>필수정보 충족률, 질문 효율, 가정 표시율 등(기획서 14장)</t>
         </is>
       </c>
-      <c r="E47" s="28" t="inlineStr">
+      <c r="E47" s="30" t="inlineStr">
         <is>
           <t>공동</t>
         </is>
       </c>
-      <c r="F47" s="28" t="n"/>
-      <c r="G47" s="28" t="n"/>
-      <c r="H47" s="28" t="inlineStr">
-        <is>
-          <t>예정</t>
-        </is>
-      </c>
-      <c r="I47" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" s="8" t="n"/>
+      <c r="F47" s="30" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="G47" s="30" t="n"/>
+      <c r="H47" s="30" t="inlineStr">
+        <is>
+          <t>진행 중</t>
+        </is>
+      </c>
+      <c r="I47" s="31" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J47" s="8" t="inlineStr">
+        <is>
+          <t>PR #30 평가 계획·통계 도구</t>
+        </is>
+      </c>
       <c r="K47" s="8" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="28" t="inlineStr">
+      <c r="A48" s="30" t="inlineStr">
         <is>
           <t>7.2</t>
         </is>
       </c>
-      <c r="B48" s="28" t="inlineStr">
+      <c r="B48" s="30" t="inlineStr">
         <is>
           <t>마무리</t>
         </is>
@@ -2633,22 +2641,30 @@
         </is>
       </c>
       <c r="D48" s="8" t="n"/>
-      <c r="E48" s="28" t="inlineStr">
+      <c r="E48" s="30" t="inlineStr">
         <is>
           <t>공동</t>
         </is>
       </c>
-      <c r="F48" s="28" t="n"/>
-      <c r="G48" s="28" t="n"/>
-      <c r="H48" s="28" t="inlineStr">
-        <is>
-          <t>예정</t>
-        </is>
-      </c>
-      <c r="I48" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="8" t="n"/>
+      <c r="F48" s="30" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="G48" s="30" t="n"/>
+      <c r="H48" s="30" t="inlineStr">
+        <is>
+          <t>진행 중</t>
+        </is>
+      </c>
+      <c r="I48" s="31" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J48" s="8" t="inlineStr">
+        <is>
+          <t>PR #30 시연 순서</t>
+        </is>
+      </c>
       <c r="K48" s="8" t="n"/>
     </row>
   </sheetData>
@@ -2709,7 +2725,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -2958,7 +2973,6 @@
         <v/>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>

--- a/docs/WBS.xlsx
+++ b/docs/WBS.xlsx
@@ -11,7 +11,7 @@
     <sheet name="요약" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS'!$A$4:$K$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS'!$A$4:$K$49</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -98,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -129,6 +129,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -565,7 +571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K48"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -591,7 +597,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>기준일 2026-10-19 · 상태·진척률·날짜는 직접 고쳐 쓰세요. 단계 행과 '요약' 시트는 자동으로 다시 계산됩니다.</t>
+          <t>기준일 2026-10-20 · 상태·진척률·날짜는 직접 고쳐 쓰세요. 단계 행과 '요약' 시트는 자동으로 다시 계산됩니다.</t>
         </is>
       </c>
     </row>
@@ -681,12 +687,12 @@
       <c r="K5" s="5" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="30" t="inlineStr">
+      <c r="A6" s="32" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="B6" s="30" t="inlineStr">
+      <c r="B6" s="32" t="inlineStr">
         <is>
           <t>기획·설계</t>
         </is>
@@ -701,23 +707,23 @@
           <t>과제 4개(사업계획·상품기획·브랜딩·마케팅), 적응형 질문, 사실·가정 분리 원칙</t>
         </is>
       </c>
-      <c r="E6" s="30" t="inlineStr">
+      <c r="E6" s="32" t="inlineStr">
         <is>
           <t>공동</t>
         </is>
       </c>
-      <c r="F6" s="30" t="n"/>
-      <c r="G6" s="30" t="inlineStr">
+      <c r="F6" s="32" t="n"/>
+      <c r="G6" s="32" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="H6" s="30" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I6" s="31" t="n">
+      <c r="H6" s="32" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I6" s="33" t="n">
         <v>1</v>
       </c>
       <c r="J6" s="8" t="inlineStr">
@@ -728,12 +734,12 @@
       <c r="K6" s="8" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="30" t="inlineStr">
+      <c r="A7" s="32" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="B7" s="30" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>기획·설계</t>
         </is>
@@ -748,27 +754,27 @@
           <t>FastAPI 하네스 구조, API 계약, 테스트 전략</t>
         </is>
       </c>
-      <c r="E7" s="30" t="inlineStr">
+      <c r="E7" s="32" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F7" s="30" t="inlineStr">
+      <c r="F7" s="32" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="G7" s="30" t="inlineStr">
+      <c r="G7" s="32" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="H7" s="30" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I7" s="31" t="n">
+      <c r="H7" s="32" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I7" s="33" t="n">
         <v>1</v>
       </c>
       <c r="J7" s="8" t="inlineStr">
@@ -779,12 +785,12 @@
       <c r="K7" s="8" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="30" t="inlineStr">
+      <c r="A8" s="32" t="inlineStr">
         <is>
           <t>1.3</t>
         </is>
       </c>
-      <c r="B8" s="30" t="inlineStr">
+      <c r="B8" s="32" t="inlineStr">
         <is>
           <t>기획·설계</t>
         </is>
@@ -799,27 +805,27 @@
           <t>V2 화면 흐름, 묶음 0~4로 작업 나누기</t>
         </is>
       </c>
-      <c r="E8" s="30" t="inlineStr">
+      <c r="E8" s="32" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F8" s="30" t="inlineStr">
+      <c r="F8" s="32" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G8" s="30" t="inlineStr">
+      <c r="G8" s="32" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H8" s="30" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I8" s="31" t="n">
+      <c r="H8" s="32" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I8" s="33" t="n">
         <v>1</v>
       </c>
       <c r="J8" s="8" t="inlineStr">
@@ -830,12 +836,12 @@
       <c r="K8" s="8" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="30" t="inlineStr">
+      <c r="A9" s="32" t="inlineStr">
         <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="B9" s="30" t="inlineStr">
+      <c r="B9" s="32" t="inlineStr">
         <is>
           <t>기획·설계</t>
         </is>
@@ -850,27 +856,27 @@
           <t>지금 상태·다음 할 일·작업 방식·환경 팁, PR마다 갱신</t>
         </is>
       </c>
-      <c r="E9" s="30" t="inlineStr">
+      <c r="E9" s="32" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F9" s="30" t="inlineStr">
+      <c r="F9" s="32" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="G9" s="30" t="inlineStr">
+      <c r="G9" s="32" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="H9" s="30" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I9" s="31" t="n">
+      <c r="H9" s="32" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I9" s="33" t="n">
         <v>1</v>
       </c>
       <c r="J9" s="8" t="inlineStr">
@@ -881,12 +887,12 @@
       <c r="K9" s="8" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="30" t="inlineStr">
+      <c r="A10" s="32" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="B10" s="30" t="inlineStr">
+      <c r="B10" s="32" t="inlineStr">
         <is>
           <t>기획·설계</t>
         </is>
@@ -901,27 +907,27 @@
           <t>바로 보기 주소, 된 것, 남은 일·맡을 사람·상의할 점</t>
         </is>
       </c>
-      <c r="E10" s="30" t="inlineStr">
+      <c r="E10" s="32" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F10" s="30" t="inlineStr">
+      <c r="F10" s="32" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="G10" s="30" t="inlineStr">
+      <c r="G10" s="32" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="H10" s="30" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I10" s="31" t="n">
+      <c r="H10" s="32" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I10" s="33" t="n">
         <v>1</v>
       </c>
       <c r="J10" s="8" t="inlineStr">
@@ -960,12 +966,12 @@
       <c r="K11" s="5" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="30" t="inlineStr">
+      <c r="A12" s="32" t="inlineStr">
         <is>
           <t>2.1</t>
         </is>
       </c>
-      <c r="B12" s="30" t="inlineStr">
+      <c r="B12" s="32" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -980,27 +986,27 @@
           <t>사실·가정·미정 구분, 정보 출처 표시</t>
         </is>
       </c>
-      <c r="E12" s="30" t="inlineStr">
+      <c r="E12" s="32" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F12" s="30" t="inlineStr">
+      <c r="F12" s="32" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="G12" s="30" t="inlineStr">
+      <c r="G12" s="32" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H12" s="30" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I12" s="31" t="n">
+      <c r="H12" s="32" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I12" s="33" t="n">
         <v>1</v>
       </c>
       <c r="J12" s="8" t="inlineStr">
@@ -1011,12 +1017,12 @@
       <c r="K12" s="8" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="30" t="inlineStr">
+      <c r="A13" s="32" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
       </c>
-      <c r="B13" s="30" t="inlineStr">
+      <c r="B13" s="32" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1031,27 +1037,27 @@
           <t>비용 없이 개발·테스트하는 가짜 모델</t>
         </is>
       </c>
-      <c r="E13" s="30" t="inlineStr">
+      <c r="E13" s="32" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F13" s="30" t="inlineStr">
+      <c r="F13" s="32" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="G13" s="30" t="inlineStr">
+      <c r="G13" s="32" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H13" s="30" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I13" s="31" t="n">
+      <c r="H13" s="32" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I13" s="33" t="n">
         <v>1</v>
       </c>
       <c r="J13" s="8" t="inlineStr">
@@ -1062,12 +1068,12 @@
       <c r="K13" s="8" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="30" t="inlineStr">
+      <c r="A14" s="32" t="inlineStr">
         <is>
           <t>2.3</t>
         </is>
       </c>
-      <c r="B14" s="30" t="inlineStr">
+      <c r="B14" s="32" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1082,27 +1088,27 @@
           <t>과제별 질문 정책(policy.yaml), 단계별 프롬프트</t>
         </is>
       </c>
-      <c r="E14" s="30" t="inlineStr">
+      <c r="E14" s="32" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F14" s="30" t="inlineStr">
+      <c r="F14" s="32" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G14" s="30" t="inlineStr">
+      <c r="G14" s="32" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H14" s="30" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I14" s="31" t="n">
+      <c r="H14" s="32" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I14" s="33" t="n">
         <v>1</v>
       </c>
       <c r="J14" s="8" t="inlineStr">
@@ -1113,12 +1119,12 @@
       <c r="K14" s="8" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="30" t="inlineStr">
+      <c r="A15" s="32" t="inlineStr">
         <is>
           <t>2.4</t>
         </is>
       </c>
-      <c r="B15" s="30" t="inlineStr">
+      <c r="B15" s="32" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1133,27 +1139,27 @@
           <t>모드별 질문 상한, '다른 예시 보기' 단계</t>
         </is>
       </c>
-      <c r="E15" s="30" t="inlineStr">
+      <c r="E15" s="32" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F15" s="30" t="inlineStr">
+      <c r="F15" s="32" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G15" s="30" t="inlineStr">
+      <c r="G15" s="32" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H15" s="30" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I15" s="31" t="n">
+      <c r="H15" s="32" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I15" s="33" t="n">
         <v>1</v>
       </c>
       <c r="J15" s="8" t="inlineStr">
@@ -1164,12 +1170,12 @@
       <c r="K15" s="8" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="30" t="inlineStr">
+      <c r="A16" s="32" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
       </c>
-      <c r="B16" s="30" t="inlineStr">
+      <c r="B16" s="32" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1180,27 +1186,27 @@
         </is>
       </c>
       <c r="D16" s="8" t="n"/>
-      <c r="E16" s="30" t="inlineStr">
+      <c r="E16" s="32" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F16" s="30" t="inlineStr">
+      <c r="F16" s="32" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G16" s="30" t="inlineStr">
+      <c r="G16" s="32" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H16" s="30" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I16" s="31" t="n">
+      <c r="H16" s="32" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I16" s="33" t="n">
         <v>1</v>
       </c>
       <c r="J16" s="8" t="inlineStr">
@@ -1211,12 +1217,12 @@
       <c r="K16" s="8" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="30" t="inlineStr">
+      <c r="A17" s="32" t="inlineStr">
         <is>
           <t>2.6</t>
         </is>
       </c>
-      <c r="B17" s="30" t="inlineStr">
+      <c r="B17" s="32" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1231,27 +1237,27 @@
           <t>과제별 정책·프롬프트·검증 규칙</t>
         </is>
       </c>
-      <c r="E17" s="30" t="inlineStr">
+      <c r="E17" s="32" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F17" s="30" t="inlineStr">
+      <c r="F17" s="32" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G17" s="30" t="inlineStr">
+      <c r="G17" s="32" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H17" s="30" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I17" s="31" t="n">
+      <c r="H17" s="32" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I17" s="33" t="n">
         <v>1</v>
       </c>
       <c r="J17" s="8" t="inlineStr">
@@ -1262,12 +1268,12 @@
       <c r="K17" s="8" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="30" t="inlineStr">
+      <c r="A18" s="32" t="inlineStr">
         <is>
           <t>2.7</t>
         </is>
       </c>
-      <c r="B18" s="30" t="inlineStr">
+      <c r="B18" s="32" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1282,27 +1288,27 @@
           <t>한국어 오류 문구, API 문서</t>
         </is>
       </c>
-      <c r="E18" s="30" t="inlineStr">
+      <c r="E18" s="32" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F18" s="30" t="inlineStr">
+      <c r="F18" s="32" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G18" s="30" t="inlineStr">
+      <c r="G18" s="32" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H18" s="30" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I18" s="31" t="n">
+      <c r="H18" s="32" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I18" s="33" t="n">
         <v>1</v>
       </c>
       <c r="J18" s="8" t="inlineStr">
@@ -1313,12 +1319,12 @@
       <c r="K18" s="8" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="30" t="inlineStr">
+      <c r="A19" s="32" t="inlineStr">
         <is>
           <t>2.8</t>
         </is>
       </c>
-      <c r="B19" s="30" t="inlineStr">
+      <c r="B19" s="32" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1333,27 +1339,27 @@
           <t>API에 맞춘 최소 화면, 개발 안내(CLAUDE.md)</t>
         </is>
       </c>
-      <c r="E19" s="30" t="inlineStr">
+      <c r="E19" s="32" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F19" s="30" t="inlineStr">
+      <c r="F19" s="32" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G19" s="30" t="inlineStr">
+      <c r="G19" s="32" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H19" s="30" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I19" s="31" t="n">
+      <c r="H19" s="32" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I19" s="33" t="n">
         <v>1</v>
       </c>
       <c r="J19" s="8" t="inlineStr">
@@ -1392,12 +1398,12 @@
       <c r="K20" s="5" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="30" t="inlineStr">
+      <c r="A21" s="32" t="inlineStr">
         <is>
           <t>3.1</t>
         </is>
       </c>
-      <c r="B21" s="30" t="inlineStr">
+      <c r="B21" s="32" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
@@ -1412,23 +1418,23 @@
           <t>전체 화면 흐름 HTML 프로토타입</t>
         </is>
       </c>
-      <c r="E21" s="30" t="inlineStr">
+      <c r="E21" s="32" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
       </c>
-      <c r="F21" s="30" t="n"/>
-      <c r="G21" s="30" t="inlineStr">
+      <c r="F21" s="32" t="n"/>
+      <c r="G21" s="32" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H21" s="30" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I21" s="31" t="n">
+      <c r="H21" s="32" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I21" s="33" t="n">
         <v>1</v>
       </c>
       <c r="J21" s="8" t="inlineStr">
@@ -1439,12 +1445,12 @@
       <c r="K21" s="8" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="30" t="inlineStr">
+      <c r="A22" s="32" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
       </c>
-      <c r="B22" s="30" t="inlineStr">
+      <c r="B22" s="32" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
@@ -1459,27 +1465,27 @@
           <t>모든 질문에 '다른 예시 보기', 모드 설명, 이미지 블록, 생성 중·실패·최신 아님 상태</t>
         </is>
       </c>
-      <c r="E22" s="30" t="inlineStr">
+      <c r="E22" s="32" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
       </c>
-      <c r="F22" s="30" t="inlineStr">
+      <c r="F22" s="32" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G22" s="30" t="inlineStr">
+      <c r="G22" s="32" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H22" s="30" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I22" s="31" t="n">
+      <c r="H22" s="32" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I22" s="33" t="n">
         <v>1</v>
       </c>
       <c r="J22" s="8" t="inlineStr">
@@ -1490,12 +1496,12 @@
       <c r="K22" s="8" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="30" t="inlineStr">
+      <c r="A23" s="32" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
       </c>
-      <c r="B23" s="30" t="inlineStr">
+      <c r="B23" s="32" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
@@ -1510,31 +1516,31 @@
           <t>반응형 자동 배치 확인</t>
         </is>
       </c>
-      <c r="E23" s="30" t="inlineStr">
+      <c r="E23" s="32" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
       </c>
-      <c r="F23" s="30" t="n"/>
-      <c r="G23" s="30" t="n"/>
-      <c r="H23" s="30" t="inlineStr">
+      <c r="F23" s="32" t="n"/>
+      <c r="G23" s="32" t="n"/>
+      <c r="H23" s="32" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="I23" s="31" t="n">
+      <c r="I23" s="33" t="n">
         <v>0</v>
       </c>
       <c r="J23" s="8" t="n"/>
       <c r="K23" s="8" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="30" t="inlineStr">
+      <c r="A24" s="32" t="inlineStr">
         <is>
           <t>3.4</t>
         </is>
       </c>
-      <c r="B24" s="30" t="inlineStr">
+      <c r="B24" s="32" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
@@ -1549,19 +1555,19 @@
           <t>/preview 화면을 html.to.design으로 가져와 수정</t>
         </is>
       </c>
-      <c r="E24" s="30" t="inlineStr">
+      <c r="E24" s="32" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
       </c>
-      <c r="F24" s="30" t="n"/>
-      <c r="G24" s="30" t="n"/>
-      <c r="H24" s="30" t="inlineStr">
+      <c r="F24" s="32" t="n"/>
+      <c r="G24" s="32" t="n"/>
+      <c r="H24" s="32" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="I24" s="31" t="n">
+      <c r="I24" s="33" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="8" t="n"/>
@@ -1589,19 +1595,19 @@
       <c r="G25" s="4" t="n"/>
       <c r="H25" s="4" t="n"/>
       <c r="I25" s="6">
-        <f>IFERROR(AVERAGE(I26:I32),0)</f>
+        <f>IFERROR(AVERAGE(I26:I33),0)</f>
         <v/>
       </c>
       <c r="J25" s="5" t="n"/>
       <c r="K25" s="5" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="30" t="inlineStr">
+      <c r="A26" s="32" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
       </c>
-      <c r="B26" s="30" t="inlineStr">
+      <c r="B26" s="32" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1616,27 +1622,27 @@
           <t>버셀 배포 설정 포함</t>
         </is>
       </c>
-      <c r="E26" s="30" t="inlineStr">
+      <c r="E26" s="32" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F26" s="30" t="inlineStr">
+      <c r="F26" s="32" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G26" s="30" t="inlineStr">
+      <c r="G26" s="32" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H26" s="30" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I26" s="31" t="n">
+      <c r="H26" s="32" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I26" s="33" t="n">
         <v>1</v>
       </c>
       <c r="J26" s="8" t="inlineStr">
@@ -1647,12 +1653,12 @@
       <c r="K26" s="8" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="30" t="inlineStr">
+      <c r="A27" s="32" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
       </c>
-      <c r="B27" s="30" t="inlineStr">
+      <c r="B27" s="32" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1667,27 +1673,27 @@
           <t>답변 종류, 흐름 패널, 익명 사용자</t>
         </is>
       </c>
-      <c r="E27" s="30" t="inlineStr">
+      <c r="E27" s="32" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F27" s="30" t="inlineStr">
+      <c r="F27" s="32" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G27" s="30" t="inlineStr">
+      <c r="G27" s="32" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H27" s="30" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I27" s="31" t="n">
+      <c r="H27" s="32" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I27" s="33" t="n">
         <v>1</v>
       </c>
       <c r="J27" s="8" t="inlineStr">
@@ -1698,12 +1704,12 @@
       <c r="K27" s="8" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="30" t="inlineStr">
+      <c r="A28" s="32" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
       </c>
-      <c r="B28" s="30" t="inlineStr">
+      <c r="B28" s="32" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1718,27 +1724,27 @@
           <t>서버 저장(SQLite), 문서 내려받기</t>
         </is>
       </c>
-      <c r="E28" s="30" t="inlineStr">
+      <c r="E28" s="32" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F28" s="30" t="inlineStr">
+      <c r="F28" s="32" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G28" s="30" t="inlineStr">
+      <c r="G28" s="32" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H28" s="30" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I28" s="31" t="n">
+      <c r="H28" s="32" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I28" s="33" t="n">
         <v>1</v>
       </c>
       <c r="J28" s="8" t="inlineStr">
@@ -1749,12 +1755,12 @@
       <c r="K28" s="8" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="30" t="inlineStr">
+      <c r="A29" s="32" t="inlineStr">
         <is>
           <t>4.4</t>
         </is>
       </c>
-      <c r="B29" s="30" t="inlineStr">
+      <c r="B29" s="32" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1769,27 +1775,27 @@
           <t>결과를 섹션·블록으로</t>
         </is>
       </c>
-      <c r="E29" s="30" t="inlineStr">
+      <c r="E29" s="32" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F29" s="30" t="inlineStr">
+      <c r="F29" s="32" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G29" s="30" t="inlineStr">
+      <c r="G29" s="32" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H29" s="30" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I29" s="31" t="n">
+      <c r="H29" s="32" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I29" s="33" t="n">
         <v>1</v>
       </c>
       <c r="J29" s="8" t="inlineStr">
@@ -1800,12 +1806,12 @@
       <c r="K29" s="8" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="30" t="inlineStr">
+      <c r="A30" s="32" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
       </c>
-      <c r="B30" s="30" t="inlineStr">
+      <c r="B30" s="32" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1820,27 +1826,27 @@
           <t>샘플 근거 자료, 자리표시 이미지</t>
         </is>
       </c>
-      <c r="E30" s="30" t="inlineStr">
+      <c r="E30" s="32" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F30" s="30" t="inlineStr">
+      <c r="F30" s="32" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G30" s="30" t="inlineStr">
+      <c r="G30" s="32" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H30" s="30" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I30" s="31" t="n">
+      <c r="H30" s="32" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I30" s="33" t="n">
         <v>1</v>
       </c>
       <c r="J30" s="8" t="inlineStr">
@@ -1851,12 +1857,12 @@
       <c r="K30" s="8" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="30" t="inlineStr">
+      <c r="A31" s="32" t="inlineStr">
         <is>
           <t>4.6</t>
         </is>
       </c>
-      <c r="B31" s="30" t="inlineStr">
+      <c r="B31" s="32" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1871,27 +1877,27 @@
           <t>생성 중·생성 실패 화면, 최신 아님 배너, 이미지 상자, 모드 설명</t>
         </is>
       </c>
-      <c r="E31" s="30" t="inlineStr">
+      <c r="E31" s="32" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F31" s="30" t="inlineStr">
+      <c r="F31" s="32" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G31" s="30" t="inlineStr">
+      <c r="G31" s="32" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H31" s="30" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I31" s="31" t="n">
+      <c r="H31" s="32" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I31" s="33" t="n">
         <v>1</v>
       </c>
       <c r="J31" s="8" t="inlineStr">
@@ -1902,12 +1908,12 @@
       <c r="K31" s="8" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="30" t="inlineStr">
+      <c r="A32" s="32" t="inlineStr">
         <is>
           <t>4.7</t>
         </is>
       </c>
-      <c r="B32" s="30" t="inlineStr">
+      <c r="B32" s="32" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1922,27 +1928,27 @@
           <t>이전 결과를 다음 과제의 기준으로 가져오기</t>
         </is>
       </c>
-      <c r="E32" s="30" t="inlineStr">
+      <c r="E32" s="32" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F32" s="30" t="inlineStr">
+      <c r="F32" s="32" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G32" s="30" t="inlineStr">
+      <c r="G32" s="32" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H32" s="30" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I32" s="31" t="n">
+      <c r="H32" s="32" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I32" s="33" t="n">
         <v>1</v>
       </c>
       <c r="J32" s="8" t="inlineStr">
@@ -1953,723 +1959,774 @@
       <c r="K32" s="8" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="32" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="B33" s="32" t="inlineStr">
+        <is>
+          <t>화면 개발(V2)</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>결과 문서 내보내기(PDF·Word)·예시 문구 교체</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="n"/>
+      <c r="E33" s="32" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F33" s="32" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G33" s="32" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="H33" s="32" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I33" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" s="8" t="inlineStr">
+        <is>
+          <t>PR #31</t>
+        </is>
+      </c>
+      <c r="K33" s="8" t="inlineStr">
+        <is>
+          <t>PR #31</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>배포</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>배포</t>
         </is>
       </c>
-      <c r="D33" s="5" t="n"/>
-      <c r="E33" s="4" t="n"/>
-      <c r="F33" s="4" t="n"/>
-      <c r="G33" s="4" t="n"/>
-      <c r="H33" s="4" t="n"/>
-      <c r="I33" s="6">
-        <f>IFERROR(AVERAGE(I34:I35),0)</f>
-        <v/>
-      </c>
-      <c r="J33" s="5" t="n"/>
-      <c r="K33" s="5" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="30" t="inlineStr">
+      <c r="D34" s="5" t="n"/>
+      <c r="E34" s="4" t="n"/>
+      <c r="F34" s="4" t="n"/>
+      <c r="G34" s="4" t="n"/>
+      <c r="H34" s="4" t="n"/>
+      <c r="I34" s="6">
+        <f>IFERROR(AVERAGE(I35:I36),0)</f>
+        <v/>
+      </c>
+      <c r="J34" s="5" t="n"/>
+      <c r="K34" s="5" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="32" t="inlineStr">
         <is>
           <t>5.1</t>
         </is>
       </c>
-      <c r="B34" s="30" t="inlineStr">
+      <c r="B35" s="32" t="inlineStr">
         <is>
           <t>배포</t>
         </is>
       </c>
-      <c r="C34" s="8" t="inlineStr">
+      <c r="C35" s="8" t="inlineStr">
         <is>
           <t>프론트 버셀 연결</t>
         </is>
       </c>
-      <c r="D34" s="8" t="inlineStr">
+      <c r="D35" s="8" t="inlineStr">
         <is>
           <t>main은 정식 주소, PR마다 미리보기 주소</t>
         </is>
       </c>
-      <c r="E34" s="30" t="inlineStr">
+      <c r="E35" s="32" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F34" s="30" t="inlineStr">
+      <c r="F35" s="32" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="G34" s="30" t="inlineStr">
+      <c r="G35" s="32" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="H34" s="30" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I34" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="J34" s="8" t="inlineStr">
+      <c r="H35" s="32" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I35" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" s="8" t="inlineStr">
         <is>
           <t>https://ax-platform-5.vercel.app</t>
         </is>
       </c>
-      <c r="K34" s="8" t="inlineStr">
+      <c r="K35" s="8" t="inlineStr">
         <is>
           <t>버셀 Hobby(개인 계정), main 자동 배포</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="30" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="32" t="inlineStr">
         <is>
           <t>5.2</t>
         </is>
       </c>
-      <c r="B35" s="30" t="inlineStr">
+      <c r="B36" s="32" t="inlineStr">
         <is>
           <t>배포</t>
         </is>
       </c>
-      <c r="C35" s="8" t="inlineStr">
+      <c r="C36" s="8" t="inlineStr">
         <is>
           <t>백엔드 서버 배포(렌더)</t>
         </is>
       </c>
-      <c r="D35" s="8" t="inlineStr">
+      <c r="D36" s="8" t="inlineStr">
         <is>
           <t>저장 디스크 방식 정하기, 프론트와 연결</t>
         </is>
       </c>
-      <c r="E35" s="30" t="inlineStr">
+      <c r="E36" s="32" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F35" s="30" t="inlineStr">
+      <c r="F36" s="32" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="G35" s="30" t="inlineStr">
+      <c r="G36" s="32" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="H35" s="30" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I35" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="J35" s="8" t="inlineStr">
+      <c r="H36" s="32" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I36" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" s="8" t="inlineStr">
         <is>
           <t>https://ax-coaching-api.onrender.com</t>
         </is>
       </c>
-      <c r="K35" s="8" t="inlineStr">
+      <c r="K36" s="8" t="inlineStr">
         <is>
           <t>렌더 Free(개인 계정), Mock·데이터 휘발</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>실제 AI 연결·튜닝</t>
         </is>
       </c>
-      <c r="D36" s="5" t="n"/>
-      <c r="E36" s="4" t="n"/>
-      <c r="F36" s="4" t="n"/>
-      <c r="G36" s="4" t="n"/>
-      <c r="H36" s="4" t="n"/>
-      <c r="I36" s="6">
-        <f>IFERROR(AVERAGE(I37:I45),0)</f>
-        <v/>
-      </c>
-      <c r="J36" s="5" t="n"/>
-      <c r="K36" s="5" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="30" t="inlineStr">
+      <c r="D37" s="5" t="n"/>
+      <c r="E37" s="4" t="n"/>
+      <c r="F37" s="4" t="n"/>
+      <c r="G37" s="4" t="n"/>
+      <c r="H37" s="4" t="n"/>
+      <c r="I37" s="6">
+        <f>IFERROR(AVERAGE(I38:I46),0)</f>
+        <v/>
+      </c>
+      <c r="J37" s="5" t="n"/>
+      <c r="K37" s="5" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="32" t="inlineStr">
         <is>
           <t>6.1</t>
         </is>
       </c>
-      <c r="B37" s="30" t="inlineStr">
+      <c r="B38" s="32" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
       </c>
-      <c r="C37" s="8" t="inlineStr">
+      <c r="C38" s="8" t="inlineStr">
         <is>
           <t>Claude 모델 연결</t>
         </is>
       </c>
-      <c r="D37" s="8" t="inlineStr">
+      <c r="D38" s="8" t="inlineStr">
         <is>
           <t>가짜 모델(Mock) 대신 실제 모델</t>
         </is>
       </c>
-      <c r="E37" s="30" t="inlineStr">
+      <c r="E38" s="32" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F37" s="30" t="inlineStr">
+      <c r="F38" s="32" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="G37" s="30" t="inlineStr">
+      <c r="G38" s="32" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="H37" s="30" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I37" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="J37" s="8" t="inlineStr">
+      <c r="H38" s="32" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I38" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" s="8" t="inlineStr">
         <is>
           <t>PR #20</t>
         </is>
       </c>
-      <c r="K37" s="8" t="inlineStr">
+      <c r="K38" s="8" t="inlineStr">
         <is>
           <t>어댑터 준비(기본 Mock). 실제 호출·모델·비용은 인수 기업</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="30" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="32" t="inlineStr">
         <is>
           <t>6.2</t>
         </is>
       </c>
-      <c r="B38" s="30" t="inlineStr">
+      <c r="B39" s="32" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
       </c>
-      <c r="C38" s="8" t="inlineStr">
+      <c r="C39" s="8" t="inlineStr">
         <is>
           <t>과제별 질문·결과 품질 튜닝</t>
         </is>
       </c>
-      <c r="D38" s="8" t="inlineStr">
+      <c r="D39" s="8" t="inlineStr">
         <is>
           <t>준비도 기준·항목 가중치·프롬프트를 시나리오로 측정</t>
         </is>
       </c>
-      <c r="E38" s="30" t="inlineStr">
+      <c r="E39" s="32" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F38" s="30" t="n"/>
-      <c r="G38" s="30" t="n"/>
-      <c r="H38" s="30" t="inlineStr">
+      <c r="F39" s="32" t="n"/>
+      <c r="G39" s="32" t="n"/>
+      <c r="H39" s="32" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="I38" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="8" t="n"/>
-      <c r="K38" s="8" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="30" t="inlineStr">
-        <is>
-          <t>6.3</t>
-        </is>
-      </c>
-      <c r="B39" s="30" t="inlineStr">
-        <is>
-          <t>실제 AI 연결</t>
-        </is>
-      </c>
-      <c r="C39" s="8" t="inlineStr">
-        <is>
-          <t>이미지 생성·웹 검색 근거 연결</t>
-        </is>
-      </c>
-      <c r="D39" s="8" t="inlineStr">
-        <is>
-          <t>지금의 자리표시·샘플 자리에 실제 기능 연결</t>
-        </is>
-      </c>
-      <c r="E39" s="30" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F39" s="30" t="n"/>
-      <c r="G39" s="30" t="n"/>
-      <c r="H39" s="30" t="inlineStr">
-        <is>
-          <t>예정</t>
-        </is>
-      </c>
-      <c r="I39" s="31" t="n">
+      <c r="I39" s="33" t="n">
         <v>0</v>
       </c>
       <c r="J39" s="8" t="n"/>
       <c r="K39" s="8" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="30" t="inlineStr">
+      <c r="A40" s="32" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="B40" s="32" t="inlineStr">
+        <is>
+          <t>실제 AI 연결</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>이미지 생성·웹 검색 근거 연결</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>지금의 자리표시·샘플 자리에 실제 기능 연결</t>
+        </is>
+      </c>
+      <c r="E40" s="32" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F40" s="32" t="n"/>
+      <c r="G40" s="32" t="n"/>
+      <c r="H40" s="32" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="I40" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="8" t="n"/>
+      <c r="K40" s="8" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="32" t="inlineStr">
         <is>
           <t>6.4</t>
         </is>
       </c>
-      <c r="B40" s="30" t="inlineStr">
+      <c r="B41" s="32" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
       </c>
-      <c r="C40" s="8" t="inlineStr">
+      <c r="C41" s="8" t="inlineStr">
         <is>
           <t>외부 전송 보호(개인정보 가림·비공개·동의)</t>
         </is>
       </c>
-      <c r="D40" s="8" t="n"/>
-      <c r="E40" s="30" t="inlineStr">
+      <c r="D41" s="8" t="n"/>
+      <c r="E41" s="32" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F40" s="30" t="inlineStr">
+      <c r="F41" s="32" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="G40" s="30" t="inlineStr">
+      <c r="G41" s="32" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="H40" s="30" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I40" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="J40" s="8" t="inlineStr">
+      <c r="H41" s="32" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I41" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" s="8" t="inlineStr">
         <is>
           <t>PR #24</t>
         </is>
       </c>
-      <c r="K40" s="8" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="30" t="inlineStr">
+      <c r="K41" s="8" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="32" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="B41" s="30" t="inlineStr">
+      <c r="B42" s="32" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
       </c>
-      <c r="C41" s="8" t="inlineStr">
+      <c r="C42" s="8" t="inlineStr">
         <is>
           <t>프롬프트 주입 기본 방어(입력 감싸기·유출 차단)</t>
         </is>
       </c>
-      <c r="D41" s="8" t="n"/>
-      <c r="E41" s="30" t="inlineStr">
+      <c r="D42" s="8" t="n"/>
+      <c r="E42" s="32" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F41" s="30" t="inlineStr">
+      <c r="F42" s="32" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="G41" s="30" t="inlineStr">
+      <c r="G42" s="32" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="H41" s="30" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I41" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="J41" s="8" t="inlineStr">
+      <c r="H42" s="32" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I42" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" s="8" t="inlineStr">
         <is>
           <t>PR #25</t>
         </is>
       </c>
-      <c r="K41" s="8" t="inlineStr">
+      <c r="K42" s="8" t="inlineStr">
         <is>
           <t>PR #25</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="30" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="32" t="inlineStr">
         <is>
           <t>6.6</t>
         </is>
       </c>
-      <c r="B42" s="30" t="inlineStr">
+      <c r="B43" s="32" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
       </c>
-      <c r="C42" s="8" t="inlineStr">
+      <c r="C43" s="8" t="inlineStr">
         <is>
           <t>단계별 모델 라우팅·하네스 로드맵·인수 안내</t>
         </is>
       </c>
-      <c r="D42" s="8" t="n"/>
-      <c r="E42" s="30" t="inlineStr">
+      <c r="D43" s="8" t="n"/>
+      <c r="E43" s="32" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F42" s="30" t="inlineStr">
+      <c r="F43" s="32" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="G42" s="30" t="inlineStr">
+      <c r="G43" s="32" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="H42" s="30" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I42" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="J42" s="8" t="inlineStr">
+      <c r="H43" s="32" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I43" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J43" s="8" t="inlineStr">
         <is>
           <t>PR #26</t>
         </is>
       </c>
-      <c r="K42" s="8" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="30" t="inlineStr">
+      <c r="K43" s="8" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="32" t="inlineStr">
         <is>
           <t>6.7</t>
         </is>
       </c>
-      <c r="B43" s="30" t="inlineStr">
+      <c r="B44" s="32" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
       </c>
-      <c r="C43" s="8" t="inlineStr">
+      <c r="C44" s="8" t="inlineStr">
         <is>
           <t>AI 동시 호출 상한(붐비면 503)</t>
         </is>
       </c>
-      <c r="D43" s="8" t="inlineStr">
+      <c r="D44" s="8" t="inlineStr">
         <is>
           <t>LLM·이미지 호출 자리 수 제한, 대기 뒤 거절, 세션 되돌림</t>
         </is>
       </c>
-      <c r="E43" s="30" t="inlineStr">
+      <c r="E44" s="32" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F43" s="30" t="inlineStr">
+      <c r="F44" s="32" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="G43" s="30" t="inlineStr">
+      <c r="G44" s="32" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="H43" s="30" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I43" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="J43" s="8" t="inlineStr">
+      <c r="H44" s="32" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I44" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" s="8" t="inlineStr">
         <is>
           <t>PR #27</t>
         </is>
       </c>
-      <c r="K43" s="8" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="30" t="inlineStr">
+      <c r="K44" s="8" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="32" t="inlineStr">
         <is>
           <t>6.8</t>
         </is>
       </c>
-      <c r="B44" s="30" t="inlineStr">
+      <c r="B45" s="32" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
       </c>
-      <c r="C44" s="8" t="inlineStr">
+      <c r="C45" s="8" t="inlineStr">
         <is>
           <t>병렬 생성(기본 꺼짐)·설계 고민 기록</t>
         </is>
       </c>
-      <c r="D44" s="8" t="inlineStr">
+      <c r="D45" s="8" t="inlineStr">
         <is>
           <t>결과 항목 조각 동시 생성·코드 합치기·부분 결과 캐시, README 설계 고민, 로드맵 측정표</t>
         </is>
       </c>
-      <c r="E44" s="30" t="inlineStr">
+      <c r="E45" s="32" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F44" s="30" t="inlineStr">
+      <c r="F45" s="32" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="G44" s="30" t="inlineStr">
+      <c r="G45" s="32" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="H44" s="30" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I44" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="J44" s="8" t="inlineStr">
+      <c r="H45" s="32" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I45" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" s="8" t="inlineStr">
         <is>
           <t>PR #28</t>
         </is>
       </c>
-      <c r="K44" s="8" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="30" t="inlineStr">
+      <c r="K45" s="8" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="32" t="inlineStr">
         <is>
           <t>6.9</t>
         </is>
       </c>
-      <c r="B45" s="30" t="inlineStr">
+      <c r="B46" s="32" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
       </c>
-      <c r="C45" s="8" t="inlineStr">
+      <c r="C46" s="8" t="inlineStr">
         <is>
           <t>측정 준비(응답 시간 기록·측정 도구)</t>
         </is>
       </c>
-      <c r="D45" s="8" t="inlineStr">
+      <c r="D46" s="8" t="inlineStr">
         <is>
           <t>trace duration_ms, 실제 모델용 시나리오 실행, quick-skip 시나리오, scripts/measure.py(기본 Mock, 비용 상한)</t>
         </is>
       </c>
-      <c r="E45" s="30" t="inlineStr">
+      <c r="E46" s="32" t="inlineStr">
         <is>
           <t>개발</t>
         </is>
       </c>
-      <c r="F45" s="30" t="inlineStr">
+      <c r="F46" s="32" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="G45" s="30" t="inlineStr">
+      <c r="G46" s="32" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="H45" s="30" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I45" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="J45" s="8" t="inlineStr">
+      <c r="H46" s="32" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I46" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" s="8" t="inlineStr">
         <is>
           <t>PR #29</t>
         </is>
       </c>
-      <c r="K45" s="8" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+      <c r="K46" s="8" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B46" s="4" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>마무리</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
+      <c r="C47" s="5" t="inlineStr">
         <is>
           <t>평가·발표</t>
         </is>
       </c>
-      <c r="D46" s="5" t="n"/>
-      <c r="E46" s="4" t="n"/>
-      <c r="F46" s="4" t="n"/>
-      <c r="G46" s="4" t="n"/>
-      <c r="H46" s="4" t="n"/>
-      <c r="I46" s="6">
-        <f>IFERROR(AVERAGE(I47:I48),0)</f>
-        <v/>
-      </c>
-      <c r="J46" s="5" t="n"/>
-      <c r="K46" s="5" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="30" t="inlineStr">
+      <c r="D47" s="5" t="n"/>
+      <c r="E47" s="4" t="n"/>
+      <c r="F47" s="4" t="n"/>
+      <c r="G47" s="4" t="n"/>
+      <c r="H47" s="4" t="n"/>
+      <c r="I47" s="6">
+        <f>IFERROR(AVERAGE(I48:I49),0)</f>
+        <v/>
+      </c>
+      <c r="J47" s="5" t="n"/>
+      <c r="K47" s="5" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="32" t="inlineStr">
         <is>
           <t>7.1</t>
         </is>
       </c>
-      <c r="B47" s="30" t="inlineStr">
+      <c r="B48" s="32" t="inlineStr">
         <is>
           <t>마무리</t>
         </is>
       </c>
-      <c r="C47" s="8" t="inlineStr">
+      <c r="C48" s="8" t="inlineStr">
         <is>
           <t>사용성 확인·평가 지표 측정</t>
         </is>
       </c>
-      <c r="D47" s="8" t="inlineStr">
+      <c r="D48" s="8" t="inlineStr">
         <is>
           <t>필수정보 충족률, 질문 효율, 가정 표시율 등(기획서 14장)</t>
         </is>
       </c>
-      <c r="E47" s="30" t="inlineStr">
+      <c r="E48" s="32" t="inlineStr">
         <is>
           <t>공동</t>
         </is>
       </c>
-      <c r="F47" s="30" t="inlineStr">
+      <c r="F48" s="32" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="G47" s="30" t="n"/>
-      <c r="H47" s="30" t="inlineStr">
+      <c r="G48" s="32" t="n"/>
+      <c r="H48" s="32" t="inlineStr">
         <is>
           <t>진행 중</t>
         </is>
       </c>
-      <c r="I47" s="31" t="n">
+      <c r="I48" s="33" t="n">
         <v>0.3</v>
       </c>
-      <c r="J47" s="8" t="inlineStr">
+      <c r="J48" s="8" t="inlineStr">
         <is>
           <t>PR #30 평가 계획·통계 도구</t>
         </is>
       </c>
-      <c r="K47" s="8" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="30" t="inlineStr">
+      <c r="K48" s="8" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="32" t="inlineStr">
         <is>
           <t>7.2</t>
         </is>
       </c>
-      <c r="B48" s="30" t="inlineStr">
+      <c r="B49" s="32" t="inlineStr">
         <is>
           <t>마무리</t>
         </is>
       </c>
-      <c r="C48" s="8" t="inlineStr">
+      <c r="C49" s="8" t="inlineStr">
         <is>
           <t>최종 발표 자료</t>
         </is>
       </c>
-      <c r="D48" s="8" t="n"/>
-      <c r="E48" s="30" t="inlineStr">
+      <c r="D49" s="8" t="n"/>
+      <c r="E49" s="32" t="inlineStr">
         <is>
           <t>공동</t>
         </is>
       </c>
-      <c r="F48" s="30" t="inlineStr">
+      <c r="F49" s="32" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="G48" s="30" t="n"/>
-      <c r="H48" s="30" t="inlineStr">
+      <c r="G49" s="32" t="n"/>
+      <c r="H49" s="32" t="inlineStr">
         <is>
           <t>진행 중</t>
         </is>
       </c>
-      <c r="I48" s="31" t="n">
+      <c r="I49" s="33" t="n">
         <v>0.3</v>
       </c>
-      <c r="J48" s="8" t="inlineStr">
+      <c r="J49" s="8" t="inlineStr">
         <is>
           <t>PR #30 시연 순서</t>
         </is>
       </c>
-      <c r="K48" s="8" t="n"/>
+      <c r="K49" s="8" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:K48"/>
-  <conditionalFormatting sqref="H5:H48">
+  <autoFilter ref="A4:K49"/>
+  <conditionalFormatting sqref="H5:H49">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"완료"</formula>
     </cfRule>
@@ -2680,7 +2737,7 @@
       <formula>"보류"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I5:I48">
+  <conditionalFormatting sqref="I5:I49">
     <cfRule type="dataBar" priority="4">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -2690,10 +2747,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="H5:H48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"완료,진행 중,예정,보류"</formula1>
     </dataValidation>
-    <dataValidation sqref="E5:E48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"개발,디자인,공동"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2764,23 +2821,23 @@
         </is>
       </c>
       <c r="B4" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$48,A4,WBS!$H$5:$H$48,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$49,A4,WBS!$H$5:$H$49,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C4" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$48,A4,WBS!$H$5:$H$48,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$49,A4,WBS!$H$5:$H$49,"완료")</f>
         <v/>
       </c>
       <c r="D4" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$48,A4,WBS!$H$5:$H$48,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$49,A4,WBS!$H$5:$H$49,"진행 중")</f>
         <v/>
       </c>
       <c r="E4" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$48,A4,WBS!$H$5:$H$48,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$49,A4,WBS!$H$5:$H$49,"예정")</f>
         <v/>
       </c>
       <c r="F4" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$48,WBS!$B$5:$B$48,A4,WBS!$H$5:$H$48,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$49,WBS!$B$5:$B$49,A4,WBS!$H$5:$H$49,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2791,23 +2848,23 @@
         </is>
       </c>
       <c r="B5" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$48,A5,WBS!$H$5:$H$48,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$49,A5,WBS!$H$5:$H$49,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C5" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$48,A5,WBS!$H$5:$H$48,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$49,A5,WBS!$H$5:$H$49,"완료")</f>
         <v/>
       </c>
       <c r="D5" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$48,A5,WBS!$H$5:$H$48,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$49,A5,WBS!$H$5:$H$49,"진행 중")</f>
         <v/>
       </c>
       <c r="E5" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$48,A5,WBS!$H$5:$H$48,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$49,A5,WBS!$H$5:$H$49,"예정")</f>
         <v/>
       </c>
       <c r="F5" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$48,WBS!$B$5:$B$48,A5,WBS!$H$5:$H$48,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$49,WBS!$B$5:$B$49,A5,WBS!$H$5:$H$49,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2818,23 +2875,23 @@
         </is>
       </c>
       <c r="B6" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$48,A6,WBS!$H$5:$H$48,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$49,A6,WBS!$H$5:$H$49,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C6" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$48,A6,WBS!$H$5:$H$48,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$49,A6,WBS!$H$5:$H$49,"완료")</f>
         <v/>
       </c>
       <c r="D6" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$48,A6,WBS!$H$5:$H$48,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$49,A6,WBS!$H$5:$H$49,"진행 중")</f>
         <v/>
       </c>
       <c r="E6" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$48,A6,WBS!$H$5:$H$48,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$49,A6,WBS!$H$5:$H$49,"예정")</f>
         <v/>
       </c>
       <c r="F6" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$48,WBS!$B$5:$B$48,A6,WBS!$H$5:$H$48,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$49,WBS!$B$5:$B$49,A6,WBS!$H$5:$H$49,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2845,23 +2902,23 @@
         </is>
       </c>
       <c r="B7" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$48,A7,WBS!$H$5:$H$48,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$49,A7,WBS!$H$5:$H$49,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C7" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$48,A7,WBS!$H$5:$H$48,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$49,A7,WBS!$H$5:$H$49,"완료")</f>
         <v/>
       </c>
       <c r="D7" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$48,A7,WBS!$H$5:$H$48,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$49,A7,WBS!$H$5:$H$49,"진행 중")</f>
         <v/>
       </c>
       <c r="E7" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$48,A7,WBS!$H$5:$H$48,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$49,A7,WBS!$H$5:$H$49,"예정")</f>
         <v/>
       </c>
       <c r="F7" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$48,WBS!$B$5:$B$48,A7,WBS!$H$5:$H$48,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$49,WBS!$B$5:$B$49,A7,WBS!$H$5:$H$49,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2872,23 +2929,23 @@
         </is>
       </c>
       <c r="B8" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$48,A8,WBS!$H$5:$H$48,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$49,A8,WBS!$H$5:$H$49,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C8" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$48,A8,WBS!$H$5:$H$48,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$49,A8,WBS!$H$5:$H$49,"완료")</f>
         <v/>
       </c>
       <c r="D8" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$48,A8,WBS!$H$5:$H$48,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$49,A8,WBS!$H$5:$H$49,"진행 중")</f>
         <v/>
       </c>
       <c r="E8" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$48,A8,WBS!$H$5:$H$48,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$49,A8,WBS!$H$5:$H$49,"예정")</f>
         <v/>
       </c>
       <c r="F8" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$48,WBS!$B$5:$B$48,A8,WBS!$H$5:$H$48,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$49,WBS!$B$5:$B$49,A8,WBS!$H$5:$H$49,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2899,23 +2956,23 @@
         </is>
       </c>
       <c r="B9" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$48,A9,WBS!$H$5:$H$48,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$49,A9,WBS!$H$5:$H$49,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C9" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$48,A9,WBS!$H$5:$H$48,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$49,A9,WBS!$H$5:$H$49,"완료")</f>
         <v/>
       </c>
       <c r="D9" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$48,A9,WBS!$H$5:$H$48,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$49,A9,WBS!$H$5:$H$49,"진행 중")</f>
         <v/>
       </c>
       <c r="E9" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$48,A9,WBS!$H$5:$H$48,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$49,A9,WBS!$H$5:$H$49,"예정")</f>
         <v/>
       </c>
       <c r="F9" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$48,WBS!$B$5:$B$48,A9,WBS!$H$5:$H$48,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$49,WBS!$B$5:$B$49,A9,WBS!$H$5:$H$49,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2926,23 +2983,23 @@
         </is>
       </c>
       <c r="B10" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$48,A10,WBS!$H$5:$H$48,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$49,A10,WBS!$H$5:$H$49,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C10" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$48,A10,WBS!$H$5:$H$48,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$49,A10,WBS!$H$5:$H$49,"완료")</f>
         <v/>
       </c>
       <c r="D10" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$48,A10,WBS!$H$5:$H$48,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$49,A10,WBS!$H$5:$H$49,"진행 중")</f>
         <v/>
       </c>
       <c r="E10" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$48,A10,WBS!$H$5:$H$48,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$49,A10,WBS!$H$5:$H$49,"예정")</f>
         <v/>
       </c>
       <c r="F10" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$48,WBS!$B$5:$B$48,A10,WBS!$H$5:$H$48,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$49,WBS!$B$5:$B$49,A10,WBS!$H$5:$H$49,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2969,7 +3026,7 @@
         <v/>
       </c>
       <c r="F11" s="14">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$48,WBS!$H$5:$H$48,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$49,WBS!$H$5:$H$49,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>

--- a/docs/WBS.xlsx
+++ b/docs/WBS.xlsx
@@ -11,7 +11,7 @@
     <sheet name="요약" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS'!$A$4:$K$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS'!$A$4:$K$52</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -98,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -129,6 +129,24 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -571,7 +589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K49"/>
+  <dimension ref="A1:K52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -687,12 +705,12 @@
       <c r="K5" s="5" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="32" t="inlineStr">
+      <c r="A6" s="38" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="B6" s="32" t="inlineStr">
+      <c r="B6" s="38" t="inlineStr">
         <is>
           <t>기획·설계</t>
         </is>
@@ -707,23 +725,23 @@
           <t>과제 4개(사업계획·상품기획·브랜딩·마케팅), 적응형 질문, 사실·가정 분리 원칙</t>
         </is>
       </c>
-      <c r="E6" s="32" t="inlineStr">
+      <c r="E6" s="38" t="inlineStr">
         <is>
           <t>공동</t>
         </is>
       </c>
-      <c r="F6" s="32" t="n"/>
-      <c r="G6" s="32" t="inlineStr">
+      <c r="F6" s="38" t="n"/>
+      <c r="G6" s="38" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="H6" s="32" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I6" s="33" t="n">
+      <c r="H6" s="38" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I6" s="39" t="n">
         <v>1</v>
       </c>
       <c r="J6" s="8" t="inlineStr">
@@ -734,12 +752,12 @@
       <c r="K6" s="8" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="32" t="inlineStr">
+      <c r="A7" s="38" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="B7" s="32" t="inlineStr">
+      <c r="B7" s="38" t="inlineStr">
         <is>
           <t>기획·설계</t>
         </is>
@@ -754,27 +772,27 @@
           <t>FastAPI 하네스 구조, API 계약, 테스트 전략</t>
         </is>
       </c>
-      <c r="E7" s="32" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F7" s="32" t="inlineStr">
+      <c r="E7" s="38" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F7" s="38" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="G7" s="32" t="inlineStr">
+      <c r="G7" s="38" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="H7" s="32" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I7" s="33" t="n">
+      <c r="H7" s="38" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I7" s="39" t="n">
         <v>1</v>
       </c>
       <c r="J7" s="8" t="inlineStr">
@@ -785,12 +803,12 @@
       <c r="K7" s="8" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="32" t="inlineStr">
+      <c r="A8" s="38" t="inlineStr">
         <is>
           <t>1.3</t>
         </is>
       </c>
-      <c r="B8" s="32" t="inlineStr">
+      <c r="B8" s="38" t="inlineStr">
         <is>
           <t>기획·설계</t>
         </is>
@@ -805,27 +823,27 @@
           <t>V2 화면 흐름, 묶음 0~4로 작업 나누기</t>
         </is>
       </c>
-      <c r="E8" s="32" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F8" s="32" t="inlineStr">
+      <c r="E8" s="38" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F8" s="38" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G8" s="32" t="inlineStr">
+      <c r="G8" s="38" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H8" s="32" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I8" s="33" t="n">
+      <c r="H8" s="38" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I8" s="39" t="n">
         <v>1</v>
       </c>
       <c r="J8" s="8" t="inlineStr">
@@ -836,12 +854,12 @@
       <c r="K8" s="8" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="32" t="inlineStr">
+      <c r="A9" s="38" t="inlineStr">
         <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="B9" s="32" t="inlineStr">
+      <c r="B9" s="38" t="inlineStr">
         <is>
           <t>기획·설계</t>
         </is>
@@ -856,27 +874,27 @@
           <t>지금 상태·다음 할 일·작업 방식·환경 팁, PR마다 갱신</t>
         </is>
       </c>
-      <c r="E9" s="32" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F9" s="32" t="inlineStr">
+      <c r="E9" s="38" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F9" s="38" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="G9" s="32" t="inlineStr">
+      <c r="G9" s="38" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="H9" s="32" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I9" s="33" t="n">
+      <c r="H9" s="38" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I9" s="39" t="n">
         <v>1</v>
       </c>
       <c r="J9" s="8" t="inlineStr">
@@ -887,12 +905,12 @@
       <c r="K9" s="8" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="32" t="inlineStr">
+      <c r="A10" s="38" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="B10" s="32" t="inlineStr">
+      <c r="B10" s="38" t="inlineStr">
         <is>
           <t>기획·설계</t>
         </is>
@@ -907,27 +925,27 @@
           <t>바로 보기 주소, 된 것, 남은 일·맡을 사람·상의할 점</t>
         </is>
       </c>
-      <c r="E10" s="32" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F10" s="32" t="inlineStr">
+      <c r="E10" s="38" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F10" s="38" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="G10" s="32" t="inlineStr">
+      <c r="G10" s="38" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="H10" s="32" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I10" s="33" t="n">
+      <c r="H10" s="38" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I10" s="39" t="n">
         <v>1</v>
       </c>
       <c r="J10" s="8" t="inlineStr">
@@ -966,12 +984,12 @@
       <c r="K11" s="5" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="32" t="inlineStr">
+      <c r="A12" s="38" t="inlineStr">
         <is>
           <t>2.1</t>
         </is>
       </c>
-      <c r="B12" s="32" t="inlineStr">
+      <c r="B12" s="38" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -986,27 +1004,27 @@
           <t>사실·가정·미정 구분, 정보 출처 표시</t>
         </is>
       </c>
-      <c r="E12" s="32" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F12" s="32" t="inlineStr">
+      <c r="E12" s="38" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F12" s="38" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="G12" s="32" t="inlineStr">
+      <c r="G12" s="38" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H12" s="32" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I12" s="33" t="n">
+      <c r="H12" s="38" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I12" s="39" t="n">
         <v>1</v>
       </c>
       <c r="J12" s="8" t="inlineStr">
@@ -1017,12 +1035,12 @@
       <c r="K12" s="8" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="32" t="inlineStr">
+      <c r="A13" s="38" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
       </c>
-      <c r="B13" s="32" t="inlineStr">
+      <c r="B13" s="38" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1037,27 +1055,27 @@
           <t>비용 없이 개발·테스트하는 가짜 모델</t>
         </is>
       </c>
-      <c r="E13" s="32" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F13" s="32" t="inlineStr">
+      <c r="E13" s="38" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F13" s="38" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="G13" s="32" t="inlineStr">
+      <c r="G13" s="38" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H13" s="32" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I13" s="33" t="n">
+      <c r="H13" s="38" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I13" s="39" t="n">
         <v>1</v>
       </c>
       <c r="J13" s="8" t="inlineStr">
@@ -1068,12 +1086,12 @@
       <c r="K13" s="8" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="32" t="inlineStr">
+      <c r="A14" s="38" t="inlineStr">
         <is>
           <t>2.3</t>
         </is>
       </c>
-      <c r="B14" s="32" t="inlineStr">
+      <c r="B14" s="38" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1088,27 +1106,27 @@
           <t>과제별 질문 정책(policy.yaml), 단계별 프롬프트</t>
         </is>
       </c>
-      <c r="E14" s="32" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F14" s="32" t="inlineStr">
+      <c r="E14" s="38" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F14" s="38" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G14" s="32" t="inlineStr">
+      <c r="G14" s="38" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H14" s="32" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I14" s="33" t="n">
+      <c r="H14" s="38" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I14" s="39" t="n">
         <v>1</v>
       </c>
       <c r="J14" s="8" t="inlineStr">
@@ -1119,12 +1137,12 @@
       <c r="K14" s="8" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="32" t="inlineStr">
+      <c r="A15" s="38" t="inlineStr">
         <is>
           <t>2.4</t>
         </is>
       </c>
-      <c r="B15" s="32" t="inlineStr">
+      <c r="B15" s="38" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1139,27 +1157,27 @@
           <t>모드별 질문 상한, '다른 예시 보기' 단계</t>
         </is>
       </c>
-      <c r="E15" s="32" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F15" s="32" t="inlineStr">
+      <c r="E15" s="38" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F15" s="38" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G15" s="32" t="inlineStr">
+      <c r="G15" s="38" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H15" s="32" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I15" s="33" t="n">
+      <c r="H15" s="38" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I15" s="39" t="n">
         <v>1</v>
       </c>
       <c r="J15" s="8" t="inlineStr">
@@ -1170,12 +1188,12 @@
       <c r="K15" s="8" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="32" t="inlineStr">
+      <c r="A16" s="38" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
       </c>
-      <c r="B16" s="32" t="inlineStr">
+      <c r="B16" s="38" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1186,27 +1204,27 @@
         </is>
       </c>
       <c r="D16" s="8" t="n"/>
-      <c r="E16" s="32" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F16" s="32" t="inlineStr">
+      <c r="E16" s="38" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F16" s="38" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G16" s="32" t="inlineStr">
+      <c r="G16" s="38" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H16" s="32" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I16" s="33" t="n">
+      <c r="H16" s="38" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I16" s="39" t="n">
         <v>1</v>
       </c>
       <c r="J16" s="8" t="inlineStr">
@@ -1217,12 +1235,12 @@
       <c r="K16" s="8" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="32" t="inlineStr">
+      <c r="A17" s="38" t="inlineStr">
         <is>
           <t>2.6</t>
         </is>
       </c>
-      <c r="B17" s="32" t="inlineStr">
+      <c r="B17" s="38" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1237,27 +1255,27 @@
           <t>과제별 정책·프롬프트·검증 규칙</t>
         </is>
       </c>
-      <c r="E17" s="32" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F17" s="32" t="inlineStr">
+      <c r="E17" s="38" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F17" s="38" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G17" s="32" t="inlineStr">
+      <c r="G17" s="38" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H17" s="32" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I17" s="33" t="n">
+      <c r="H17" s="38" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I17" s="39" t="n">
         <v>1</v>
       </c>
       <c r="J17" s="8" t="inlineStr">
@@ -1268,12 +1286,12 @@
       <c r="K17" s="8" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="32" t="inlineStr">
+      <c r="A18" s="38" t="inlineStr">
         <is>
           <t>2.7</t>
         </is>
       </c>
-      <c r="B18" s="32" t="inlineStr">
+      <c r="B18" s="38" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1288,27 +1306,27 @@
           <t>한국어 오류 문구, API 문서</t>
         </is>
       </c>
-      <c r="E18" s="32" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F18" s="32" t="inlineStr">
+      <c r="E18" s="38" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F18" s="38" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G18" s="32" t="inlineStr">
+      <c r="G18" s="38" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H18" s="32" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I18" s="33" t="n">
+      <c r="H18" s="38" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I18" s="39" t="n">
         <v>1</v>
       </c>
       <c r="J18" s="8" t="inlineStr">
@@ -1319,12 +1337,12 @@
       <c r="K18" s="8" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="32" t="inlineStr">
+      <c r="A19" s="38" t="inlineStr">
         <is>
           <t>2.8</t>
         </is>
       </c>
-      <c r="B19" s="32" t="inlineStr">
+      <c r="B19" s="38" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1339,27 +1357,27 @@
           <t>API에 맞춘 최소 화면, 개발 안내(CLAUDE.md)</t>
         </is>
       </c>
-      <c r="E19" s="32" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F19" s="32" t="inlineStr">
+      <c r="E19" s="38" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F19" s="38" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G19" s="32" t="inlineStr">
+      <c r="G19" s="38" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H19" s="32" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I19" s="33" t="n">
+      <c r="H19" s="38" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I19" s="39" t="n">
         <v>1</v>
       </c>
       <c r="J19" s="8" t="inlineStr">
@@ -1398,12 +1416,12 @@
       <c r="K20" s="5" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="32" t="inlineStr">
+      <c r="A21" s="38" t="inlineStr">
         <is>
           <t>3.1</t>
         </is>
       </c>
-      <c r="B21" s="32" t="inlineStr">
+      <c r="B21" s="38" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
@@ -1418,23 +1436,23 @@
           <t>전체 화면 흐름 HTML 프로토타입</t>
         </is>
       </c>
-      <c r="E21" s="32" t="inlineStr">
+      <c r="E21" s="38" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
       </c>
-      <c r="F21" s="32" t="n"/>
-      <c r="G21" s="32" t="inlineStr">
+      <c r="F21" s="38" t="n"/>
+      <c r="G21" s="38" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H21" s="32" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I21" s="33" t="n">
+      <c r="H21" s="38" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I21" s="39" t="n">
         <v>1</v>
       </c>
       <c r="J21" s="8" t="inlineStr">
@@ -1445,12 +1463,12 @@
       <c r="K21" s="8" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="32" t="inlineStr">
+      <c r="A22" s="38" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
       </c>
-      <c r="B22" s="32" t="inlineStr">
+      <c r="B22" s="38" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
@@ -1465,27 +1483,27 @@
           <t>모든 질문에 '다른 예시 보기', 모드 설명, 이미지 블록, 생성 중·실패·최신 아님 상태</t>
         </is>
       </c>
-      <c r="E22" s="32" t="inlineStr">
+      <c r="E22" s="38" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
       </c>
-      <c r="F22" s="32" t="inlineStr">
+      <c r="F22" s="38" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G22" s="32" t="inlineStr">
+      <c r="G22" s="38" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H22" s="32" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I22" s="33" t="n">
+      <c r="H22" s="38" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I22" s="39" t="n">
         <v>1</v>
       </c>
       <c r="J22" s="8" t="inlineStr">
@@ -1496,12 +1514,12 @@
       <c r="K22" s="8" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="32" t="inlineStr">
+      <c r="A23" s="38" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
       </c>
-      <c r="B23" s="32" t="inlineStr">
+      <c r="B23" s="38" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
@@ -1516,31 +1534,31 @@
           <t>반응형 자동 배치 확인</t>
         </is>
       </c>
-      <c r="E23" s="32" t="inlineStr">
+      <c r="E23" s="38" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
       </c>
-      <c r="F23" s="32" t="n"/>
-      <c r="G23" s="32" t="n"/>
-      <c r="H23" s="32" t="inlineStr">
+      <c r="F23" s="38" t="n"/>
+      <c r="G23" s="38" t="n"/>
+      <c r="H23" s="38" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="I23" s="33" t="n">
+      <c r="I23" s="39" t="n">
         <v>0</v>
       </c>
       <c r="J23" s="8" t="n"/>
       <c r="K23" s="8" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="32" t="inlineStr">
+      <c r="A24" s="38" t="inlineStr">
         <is>
           <t>3.4</t>
         </is>
       </c>
-      <c r="B24" s="32" t="inlineStr">
+      <c r="B24" s="38" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
@@ -1555,19 +1573,19 @@
           <t>/preview 화면을 html.to.design으로 가져와 수정</t>
         </is>
       </c>
-      <c r="E24" s="32" t="inlineStr">
+      <c r="E24" s="38" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
       </c>
-      <c r="F24" s="32" t="n"/>
-      <c r="G24" s="32" t="n"/>
-      <c r="H24" s="32" t="inlineStr">
+      <c r="F24" s="38" t="n"/>
+      <c r="G24" s="38" t="n"/>
+      <c r="H24" s="38" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="I24" s="33" t="n">
+      <c r="I24" s="39" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="8" t="n"/>
@@ -1595,19 +1613,19 @@
       <c r="G25" s="4" t="n"/>
       <c r="H25" s="4" t="n"/>
       <c r="I25" s="6">
-        <f>IFERROR(AVERAGE(I26:I33),0)</f>
+        <f>IFERROR(AVERAGE(I26:I36),0)</f>
         <v/>
       </c>
       <c r="J25" s="5" t="n"/>
       <c r="K25" s="5" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="32" t="inlineStr">
+      <c r="A26" s="38" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
       </c>
-      <c r="B26" s="32" t="inlineStr">
+      <c r="B26" s="38" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1622,27 +1640,27 @@
           <t>버셀 배포 설정 포함</t>
         </is>
       </c>
-      <c r="E26" s="32" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F26" s="32" t="inlineStr">
+      <c r="E26" s="38" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F26" s="38" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G26" s="32" t="inlineStr">
+      <c r="G26" s="38" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H26" s="32" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I26" s="33" t="n">
+      <c r="H26" s="38" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I26" s="39" t="n">
         <v>1</v>
       </c>
       <c r="J26" s="8" t="inlineStr">
@@ -1653,12 +1671,12 @@
       <c r="K26" s="8" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="32" t="inlineStr">
+      <c r="A27" s="38" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
       </c>
-      <c r="B27" s="32" t="inlineStr">
+      <c r="B27" s="38" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1673,27 +1691,27 @@
           <t>답변 종류, 흐름 패널, 익명 사용자</t>
         </is>
       </c>
-      <c r="E27" s="32" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F27" s="32" t="inlineStr">
+      <c r="E27" s="38" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F27" s="38" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G27" s="32" t="inlineStr">
+      <c r="G27" s="38" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H27" s="32" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I27" s="33" t="n">
+      <c r="H27" s="38" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I27" s="39" t="n">
         <v>1</v>
       </c>
       <c r="J27" s="8" t="inlineStr">
@@ -1704,12 +1722,12 @@
       <c r="K27" s="8" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="32" t="inlineStr">
+      <c r="A28" s="38" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
       </c>
-      <c r="B28" s="32" t="inlineStr">
+      <c r="B28" s="38" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1724,27 +1742,27 @@
           <t>서버 저장(SQLite), 문서 내려받기</t>
         </is>
       </c>
-      <c r="E28" s="32" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F28" s="32" t="inlineStr">
+      <c r="E28" s="38" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F28" s="38" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G28" s="32" t="inlineStr">
+      <c r="G28" s="38" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H28" s="32" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I28" s="33" t="n">
+      <c r="H28" s="38" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I28" s="39" t="n">
         <v>1</v>
       </c>
       <c r="J28" s="8" t="inlineStr">
@@ -1755,12 +1773,12 @@
       <c r="K28" s="8" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="32" t="inlineStr">
+      <c r="A29" s="38" t="inlineStr">
         <is>
           <t>4.4</t>
         </is>
       </c>
-      <c r="B29" s="32" t="inlineStr">
+      <c r="B29" s="38" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1775,27 +1793,27 @@
           <t>결과를 섹션·블록으로</t>
         </is>
       </c>
-      <c r="E29" s="32" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F29" s="32" t="inlineStr">
+      <c r="E29" s="38" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F29" s="38" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G29" s="32" t="inlineStr">
+      <c r="G29" s="38" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H29" s="32" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I29" s="33" t="n">
+      <c r="H29" s="38" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I29" s="39" t="n">
         <v>1</v>
       </c>
       <c r="J29" s="8" t="inlineStr">
@@ -1806,12 +1824,12 @@
       <c r="K29" s="8" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="32" t="inlineStr">
+      <c r="A30" s="38" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
       </c>
-      <c r="B30" s="32" t="inlineStr">
+      <c r="B30" s="38" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1826,27 +1844,27 @@
           <t>샘플 근거 자료, 자리표시 이미지</t>
         </is>
       </c>
-      <c r="E30" s="32" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F30" s="32" t="inlineStr">
+      <c r="E30" s="38" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F30" s="38" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G30" s="32" t="inlineStr">
+      <c r="G30" s="38" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H30" s="32" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I30" s="33" t="n">
+      <c r="H30" s="38" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I30" s="39" t="n">
         <v>1</v>
       </c>
       <c r="J30" s="8" t="inlineStr">
@@ -1857,12 +1875,12 @@
       <c r="K30" s="8" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="32" t="inlineStr">
+      <c r="A31" s="38" t="inlineStr">
         <is>
           <t>4.6</t>
         </is>
       </c>
-      <c r="B31" s="32" t="inlineStr">
+      <c r="B31" s="38" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1877,27 +1895,27 @@
           <t>생성 중·생성 실패 화면, 최신 아님 배너, 이미지 상자, 모드 설명</t>
         </is>
       </c>
-      <c r="E31" s="32" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F31" s="32" t="inlineStr">
+      <c r="E31" s="38" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F31" s="38" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G31" s="32" t="inlineStr">
+      <c r="G31" s="38" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H31" s="32" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I31" s="33" t="n">
+      <c r="H31" s="38" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I31" s="39" t="n">
         <v>1</v>
       </c>
       <c r="J31" s="8" t="inlineStr">
@@ -1908,12 +1926,12 @@
       <c r="K31" s="8" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="32" t="inlineStr">
+      <c r="A32" s="38" t="inlineStr">
         <is>
           <t>4.7</t>
         </is>
       </c>
-      <c r="B32" s="32" t="inlineStr">
+      <c r="B32" s="38" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1928,27 +1946,27 @@
           <t>이전 결과를 다음 과제의 기준으로 가져오기</t>
         </is>
       </c>
-      <c r="E32" s="32" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F32" s="32" t="inlineStr">
+      <c r="E32" s="38" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F32" s="38" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G32" s="32" t="inlineStr">
+      <c r="G32" s="38" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H32" s="32" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I32" s="33" t="n">
+      <c r="H32" s="38" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I32" s="39" t="n">
         <v>1</v>
       </c>
       <c r="J32" s="8" t="inlineStr">
@@ -1959,12 +1977,12 @@
       <c r="K32" s="8" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="32" t="inlineStr">
+      <c r="A33" s="38" t="inlineStr">
         <is>
           <t>4.8</t>
         </is>
       </c>
-      <c r="B33" s="32" t="inlineStr">
+      <c r="B33" s="38" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1975,27 +1993,27 @@
         </is>
       </c>
       <c r="D33" s="8" t="n"/>
-      <c r="E33" s="32" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F33" s="32" t="inlineStr">
+      <c r="E33" s="38" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F33" s="38" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="G33" s="32" t="inlineStr">
+      <c r="G33" s="38" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="H33" s="32" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I33" s="33" t="n">
+      <c r="H33" s="38" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I33" s="39" t="n">
         <v>1</v>
       </c>
       <c r="J33" s="8" t="inlineStr">
@@ -2010,157 +2028,132 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>배포</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>배포</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="n"/>
-      <c r="E34" s="4" t="n"/>
-      <c r="F34" s="4" t="n"/>
-      <c r="G34" s="4" t="n"/>
-      <c r="H34" s="4" t="n"/>
-      <c r="I34" s="6">
-        <f>IFERROR(AVERAGE(I35:I36),0)</f>
-        <v/>
-      </c>
-      <c r="J34" s="5" t="n"/>
-      <c r="K34" s="5" t="n"/>
+      <c r="A34" s="38" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="B34" s="38" t="inlineStr">
+        <is>
+          <t>화면 개발(V2)</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>작업·결과물 정리(삭제·이름·빼기)</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="n"/>
+      <c r="E34" s="38" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F34" s="38" t="n"/>
+      <c r="G34" s="38" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="H34" s="38" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I34" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" s="8" t="inlineStr">
+        <is>
+          <t>PR #32</t>
+        </is>
+      </c>
+      <c r="K34" s="8" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="32" t="inlineStr">
-        <is>
-          <t>5.1</t>
-        </is>
-      </c>
-      <c r="B35" s="32" t="inlineStr">
-        <is>
-          <t>배포</t>
+      <c r="A35" s="38" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="B35" s="38" t="inlineStr">
+        <is>
+          <t>화면 개발(V2)</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>프론트 버셀 연결</t>
-        </is>
-      </c>
-      <c r="D35" s="8" t="inlineStr">
-        <is>
-          <t>main은 정식 주소, PR마다 미리보기 주소</t>
-        </is>
-      </c>
-      <c r="E35" s="32" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F35" s="32" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="G35" s="32" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="H35" s="32" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I35" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="J35" s="8" t="inlineStr">
-        <is>
-          <t>https://ax-platform-5.vercel.app</t>
-        </is>
-      </c>
-      <c r="K35" s="8" t="inlineStr">
-        <is>
-          <t>버셀 Hobby(개인 계정), main 자동 배포</t>
-        </is>
-      </c>
+          <t>후순위: 로그인(다른 기기에서 내 작업)</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="n"/>
+      <c r="E35" s="38" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F35" s="38" t="n"/>
+      <c r="G35" s="38" t="n"/>
+      <c r="H35" s="38" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="I35" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="8" t="n"/>
+      <c r="K35" s="8" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="32" t="inlineStr">
-        <is>
-          <t>5.2</t>
-        </is>
-      </c>
-      <c r="B36" s="32" t="inlineStr">
-        <is>
-          <t>배포</t>
+      <c r="A36" s="38" t="inlineStr">
+        <is>
+          <t>4.11</t>
+        </is>
+      </c>
+      <c r="B36" s="38" t="inlineStr">
+        <is>
+          <t>화면 개발(V2)</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>백엔드 서버 배포(렌더)</t>
-        </is>
-      </c>
-      <c r="D36" s="8" t="inlineStr">
-        <is>
-          <t>저장 디스크 방식 정하기, 프론트와 연결</t>
-        </is>
-      </c>
-      <c r="E36" s="32" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F36" s="32" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="G36" s="32" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="H36" s="32" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I36" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="J36" s="8" t="inlineStr">
-        <is>
-          <t>https://ax-coaching-api.onrender.com</t>
-        </is>
-      </c>
-      <c r="K36" s="8" t="inlineStr">
-        <is>
-          <t>렌더 Free(개인 계정), Mock·데이터 휘발</t>
-        </is>
-      </c>
+          <t>후순위: 결과물 공유 링크(읽기 전용)</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="n"/>
+      <c r="E36" s="38" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F36" s="38" t="n"/>
+      <c r="G36" s="38" t="n"/>
+      <c r="H36" s="38" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="I36" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="8" t="n"/>
+      <c r="K36" s="8" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>실제 AI 연결</t>
+          <t>배포</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>실제 AI 연결·튜닝</t>
+          <t>배포</t>
         </is>
       </c>
       <c r="D37" s="5" t="n"/>
@@ -2169,564 +2162,702 @@
       <c r="G37" s="4" t="n"/>
       <c r="H37" s="4" t="n"/>
       <c r="I37" s="6">
-        <f>IFERROR(AVERAGE(I38:I46),0)</f>
+        <f>IFERROR(AVERAGE(I38:I39),0)</f>
         <v/>
       </c>
       <c r="J37" s="5" t="n"/>
       <c r="K37" s="5" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="32" t="inlineStr">
+      <c r="A38" s="38" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="B38" s="38" t="inlineStr">
+        <is>
+          <t>배포</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>프론트 버셀 연결</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>main은 정식 주소, PR마다 미리보기 주소</t>
+        </is>
+      </c>
+      <c r="E38" s="38" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F38" s="38" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="G38" s="38" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="H38" s="38" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I38" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" s="8" t="inlineStr">
+        <is>
+          <t>https://ax-platform-5.vercel.app</t>
+        </is>
+      </c>
+      <c r="K38" s="8" t="inlineStr">
+        <is>
+          <t>버셀 Hobby(개인 계정), main 자동 배포</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="38" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="B39" s="38" t="inlineStr">
+        <is>
+          <t>배포</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>백엔드 서버 배포(렌더)</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>저장 디스크 방식 정하기, 프론트와 연결</t>
+        </is>
+      </c>
+      <c r="E39" s="38" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F39" s="38" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="G39" s="38" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="H39" s="38" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I39" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" s="8" t="inlineStr">
+        <is>
+          <t>https://ax-coaching-api.onrender.com</t>
+        </is>
+      </c>
+      <c r="K39" s="8" t="inlineStr">
+        <is>
+          <t>렌더 Free(개인 계정), Mock·데이터 휘발</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>실제 AI 연결</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>실제 AI 연결·튜닝</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="n"/>
+      <c r="E40" s="4" t="n"/>
+      <c r="F40" s="4" t="n"/>
+      <c r="G40" s="4" t="n"/>
+      <c r="H40" s="4" t="n"/>
+      <c r="I40" s="6">
+        <f>IFERROR(AVERAGE(I41:I49),0)</f>
+        <v/>
+      </c>
+      <c r="J40" s="5" t="n"/>
+      <c r="K40" s="5" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="38" t="inlineStr">
         <is>
           <t>6.1</t>
         </is>
       </c>
-      <c r="B38" s="32" t="inlineStr">
+      <c r="B41" s="38" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
       </c>
-      <c r="C38" s="8" t="inlineStr">
+      <c r="C41" s="8" t="inlineStr">
         <is>
           <t>Claude 모델 연결</t>
         </is>
       </c>
-      <c r="D38" s="8" t="inlineStr">
+      <c r="D41" s="8" t="inlineStr">
         <is>
           <t>가짜 모델(Mock) 대신 실제 모델</t>
         </is>
       </c>
-      <c r="E38" s="32" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F38" s="32" t="inlineStr">
+      <c r="E41" s="38" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F41" s="38" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="G38" s="32" t="inlineStr">
+      <c r="G41" s="38" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="H38" s="32" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I38" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="J38" s="8" t="inlineStr">
+      <c r="H41" s="38" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I41" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" s="8" t="inlineStr">
         <is>
           <t>PR #20</t>
         </is>
       </c>
-      <c r="K38" s="8" t="inlineStr">
+      <c r="K41" s="8" t="inlineStr">
         <is>
           <t>어댑터 준비(기본 Mock). 실제 호출·모델·비용은 인수 기업</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="32" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="38" t="inlineStr">
         <is>
           <t>6.2</t>
         </is>
       </c>
-      <c r="B39" s="32" t="inlineStr">
+      <c r="B42" s="38" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
       </c>
-      <c r="C39" s="8" t="inlineStr">
+      <c r="C42" s="8" t="inlineStr">
         <is>
           <t>과제별 질문·결과 품질 튜닝</t>
         </is>
       </c>
-      <c r="D39" s="8" t="inlineStr">
+      <c r="D42" s="8" t="inlineStr">
         <is>
           <t>준비도 기준·항목 가중치·프롬프트를 시나리오로 측정</t>
         </is>
       </c>
-      <c r="E39" s="32" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F39" s="32" t="n"/>
-      <c r="G39" s="32" t="n"/>
-      <c r="H39" s="32" t="inlineStr">
+      <c r="E42" s="38" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F42" s="38" t="n"/>
+      <c r="G42" s="38" t="n"/>
+      <c r="H42" s="38" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="I39" s="33" t="n">
+      <c r="I42" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="J39" s="8" t="n"/>
-      <c r="K39" s="8" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="32" t="inlineStr">
+      <c r="J42" s="8" t="n"/>
+      <c r="K42" s="8" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="38" t="inlineStr">
         <is>
           <t>6.3</t>
         </is>
       </c>
-      <c r="B40" s="32" t="inlineStr">
+      <c r="B43" s="38" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
       </c>
-      <c r="C40" s="8" t="inlineStr">
+      <c r="C43" s="8" t="inlineStr">
         <is>
           <t>이미지 생성·웹 검색 근거 연결</t>
         </is>
       </c>
-      <c r="D40" s="8" t="inlineStr">
+      <c r="D43" s="8" t="inlineStr">
         <is>
           <t>지금의 자리표시·샘플 자리에 실제 기능 연결</t>
         </is>
       </c>
-      <c r="E40" s="32" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F40" s="32" t="n"/>
-      <c r="G40" s="32" t="n"/>
-      <c r="H40" s="32" t="inlineStr">
+      <c r="E43" s="38" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F43" s="38" t="n"/>
+      <c r="G43" s="38" t="n"/>
+      <c r="H43" s="38" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="I40" s="33" t="n">
+      <c r="I43" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="J40" s="8" t="n"/>
-      <c r="K40" s="8" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="32" t="inlineStr">
+      <c r="J43" s="8" t="n"/>
+      <c r="K43" s="8" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="38" t="inlineStr">
         <is>
           <t>6.4</t>
         </is>
       </c>
-      <c r="B41" s="32" t="inlineStr">
+      <c r="B44" s="38" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
       </c>
-      <c r="C41" s="8" t="inlineStr">
+      <c r="C44" s="8" t="inlineStr">
         <is>
           <t>외부 전송 보호(개인정보 가림·비공개·동의)</t>
         </is>
       </c>
-      <c r="D41" s="8" t="n"/>
-      <c r="E41" s="32" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F41" s="32" t="inlineStr">
+      <c r="D44" s="8" t="n"/>
+      <c r="E44" s="38" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F44" s="38" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="G41" s="32" t="inlineStr">
+      <c r="G44" s="38" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="H41" s="32" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I41" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="J41" s="8" t="inlineStr">
+      <c r="H44" s="38" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I44" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" s="8" t="inlineStr">
         <is>
           <t>PR #24</t>
         </is>
       </c>
-      <c r="K41" s="8" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="32" t="inlineStr">
+      <c r="K44" s="8" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="38" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="B42" s="32" t="inlineStr">
+      <c r="B45" s="38" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
       </c>
-      <c r="C42" s="8" t="inlineStr">
+      <c r="C45" s="8" t="inlineStr">
         <is>
           <t>프롬프트 주입 기본 방어(입력 감싸기·유출 차단)</t>
         </is>
       </c>
-      <c r="D42" s="8" t="n"/>
-      <c r="E42" s="32" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F42" s="32" t="inlineStr">
+      <c r="D45" s="8" t="n"/>
+      <c r="E45" s="38" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F45" s="38" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="G42" s="32" t="inlineStr">
+      <c r="G45" s="38" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="H42" s="32" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I42" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="J42" s="8" t="inlineStr">
+      <c r="H45" s="38" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I45" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" s="8" t="inlineStr">
         <is>
           <t>PR #25</t>
         </is>
       </c>
-      <c r="K42" s="8" t="inlineStr">
+      <c r="K45" s="8" t="inlineStr">
         <is>
           <t>PR #25</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="32" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="38" t="inlineStr">
         <is>
           <t>6.6</t>
         </is>
       </c>
-      <c r="B43" s="32" t="inlineStr">
+      <c r="B46" s="38" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
       </c>
-      <c r="C43" s="8" t="inlineStr">
+      <c r="C46" s="8" t="inlineStr">
         <is>
           <t>단계별 모델 라우팅·하네스 로드맵·인수 안내</t>
         </is>
       </c>
-      <c r="D43" s="8" t="n"/>
-      <c r="E43" s="32" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F43" s="32" t="inlineStr">
+      <c r="D46" s="8" t="n"/>
+      <c r="E46" s="38" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F46" s="38" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="G43" s="32" t="inlineStr">
+      <c r="G46" s="38" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="H43" s="32" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I43" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="J43" s="8" t="inlineStr">
+      <c r="H46" s="38" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I46" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" s="8" t="inlineStr">
         <is>
           <t>PR #26</t>
         </is>
       </c>
-      <c r="K43" s="8" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="32" t="inlineStr">
+      <c r="K46" s="8" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="38" t="inlineStr">
         <is>
           <t>6.7</t>
         </is>
       </c>
-      <c r="B44" s="32" t="inlineStr">
+      <c r="B47" s="38" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
       </c>
-      <c r="C44" s="8" t="inlineStr">
+      <c r="C47" s="8" t="inlineStr">
         <is>
           <t>AI 동시 호출 상한(붐비면 503)</t>
         </is>
       </c>
-      <c r="D44" s="8" t="inlineStr">
+      <c r="D47" s="8" t="inlineStr">
         <is>
           <t>LLM·이미지 호출 자리 수 제한, 대기 뒤 거절, 세션 되돌림</t>
         </is>
       </c>
-      <c r="E44" s="32" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F44" s="32" t="inlineStr">
+      <c r="E47" s="38" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F47" s="38" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="G44" s="32" t="inlineStr">
+      <c r="G47" s="38" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="H44" s="32" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I44" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="J44" s="8" t="inlineStr">
+      <c r="H47" s="38" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I47" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" s="8" t="inlineStr">
         <is>
           <t>PR #27</t>
         </is>
       </c>
-      <c r="K44" s="8" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="32" t="inlineStr">
+      <c r="K47" s="8" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="38" t="inlineStr">
         <is>
           <t>6.8</t>
         </is>
       </c>
-      <c r="B45" s="32" t="inlineStr">
+      <c r="B48" s="38" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
       </c>
-      <c r="C45" s="8" t="inlineStr">
+      <c r="C48" s="8" t="inlineStr">
         <is>
           <t>병렬 생성(기본 꺼짐)·설계 고민 기록</t>
         </is>
       </c>
-      <c r="D45" s="8" t="inlineStr">
+      <c r="D48" s="8" t="inlineStr">
         <is>
           <t>결과 항목 조각 동시 생성·코드 합치기·부분 결과 캐시, README 설계 고민, 로드맵 측정표</t>
         </is>
       </c>
-      <c r="E45" s="32" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F45" s="32" t="inlineStr">
+      <c r="E48" s="38" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F48" s="38" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="G45" s="32" t="inlineStr">
+      <c r="G48" s="38" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="H45" s="32" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I45" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="J45" s="8" t="inlineStr">
+      <c r="H48" s="38" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I48" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" s="8" t="inlineStr">
         <is>
           <t>PR #28</t>
         </is>
       </c>
-      <c r="K45" s="8" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="32" t="inlineStr">
+      <c r="K48" s="8" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="38" t="inlineStr">
         <is>
           <t>6.9</t>
         </is>
       </c>
-      <c r="B46" s="32" t="inlineStr">
+      <c r="B49" s="38" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
       </c>
-      <c r="C46" s="8" t="inlineStr">
+      <c r="C49" s="8" t="inlineStr">
         <is>
           <t>측정 준비(응답 시간 기록·측정 도구)</t>
         </is>
       </c>
-      <c r="D46" s="8" t="inlineStr">
+      <c r="D49" s="8" t="inlineStr">
         <is>
           <t>trace duration_ms, 실제 모델용 시나리오 실행, quick-skip 시나리오, scripts/measure.py(기본 Mock, 비용 상한)</t>
         </is>
       </c>
-      <c r="E46" s="32" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F46" s="32" t="inlineStr">
+      <c r="E49" s="38" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F49" s="38" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="G46" s="32" t="inlineStr">
+      <c r="G49" s="38" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="H46" s="32" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I46" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="J46" s="8" t="inlineStr">
+      <c r="H49" s="38" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I49" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" s="8" t="inlineStr">
         <is>
           <t>PR #29</t>
         </is>
       </c>
-      <c r="K46" s="8" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="4" t="inlineStr">
+      <c r="K49" s="8" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B47" s="4" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>마무리</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C50" s="5" t="inlineStr">
         <is>
           <t>평가·발표</t>
         </is>
       </c>
-      <c r="D47" s="5" t="n"/>
-      <c r="E47" s="4" t="n"/>
-      <c r="F47" s="4" t="n"/>
-      <c r="G47" s="4" t="n"/>
-      <c r="H47" s="4" t="n"/>
-      <c r="I47" s="6">
-        <f>IFERROR(AVERAGE(I48:I49),0)</f>
-        <v/>
-      </c>
-      <c r="J47" s="5" t="n"/>
-      <c r="K47" s="5" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="32" t="inlineStr">
+      <c r="D50" s="5" t="n"/>
+      <c r="E50" s="4" t="n"/>
+      <c r="F50" s="4" t="n"/>
+      <c r="G50" s="4" t="n"/>
+      <c r="H50" s="4" t="n"/>
+      <c r="I50" s="6">
+        <f>IFERROR(AVERAGE(I51:I52),0)</f>
+        <v/>
+      </c>
+      <c r="J50" s="5" t="n"/>
+      <c r="K50" s="5" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="38" t="inlineStr">
         <is>
           <t>7.1</t>
         </is>
       </c>
-      <c r="B48" s="32" t="inlineStr">
+      <c r="B51" s="38" t="inlineStr">
         <is>
           <t>마무리</t>
         </is>
       </c>
-      <c r="C48" s="8" t="inlineStr">
+      <c r="C51" s="8" t="inlineStr">
         <is>
           <t>사용성 확인·평가 지표 측정</t>
         </is>
       </c>
-      <c r="D48" s="8" t="inlineStr">
+      <c r="D51" s="8" t="inlineStr">
         <is>
           <t>필수정보 충족률, 질문 효율, 가정 표시율 등(기획서 14장)</t>
         </is>
       </c>
-      <c r="E48" s="32" t="inlineStr">
+      <c r="E51" s="38" t="inlineStr">
         <is>
           <t>공동</t>
         </is>
       </c>
-      <c r="F48" s="32" t="inlineStr">
+      <c r="F51" s="38" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="G48" s="32" t="n"/>
-      <c r="H48" s="32" t="inlineStr">
+      <c r="G51" s="38" t="n"/>
+      <c r="H51" s="38" t="inlineStr">
         <is>
           <t>진행 중</t>
         </is>
       </c>
-      <c r="I48" s="33" t="n">
+      <c r="I51" s="39" t="n">
         <v>0.3</v>
       </c>
-      <c r="J48" s="8" t="inlineStr">
+      <c r="J51" s="8" t="inlineStr">
         <is>
           <t>PR #30 평가 계획·통계 도구</t>
         </is>
       </c>
-      <c r="K48" s="8" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="32" t="inlineStr">
+      <c r="K51" s="8" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="38" t="inlineStr">
         <is>
           <t>7.2</t>
         </is>
       </c>
-      <c r="B49" s="32" t="inlineStr">
+      <c r="B52" s="38" t="inlineStr">
         <is>
           <t>마무리</t>
         </is>
       </c>
-      <c r="C49" s="8" t="inlineStr">
+      <c r="C52" s="8" t="inlineStr">
         <is>
           <t>최종 발표 자료</t>
         </is>
       </c>
-      <c r="D49" s="8" t="n"/>
-      <c r="E49" s="32" t="inlineStr">
+      <c r="D52" s="8" t="n"/>
+      <c r="E52" s="38" t="inlineStr">
         <is>
           <t>공동</t>
         </is>
       </c>
-      <c r="F49" s="32" t="inlineStr">
+      <c r="F52" s="38" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="G49" s="32" t="n"/>
-      <c r="H49" s="32" t="inlineStr">
+      <c r="G52" s="38" t="n"/>
+      <c r="H52" s="38" t="inlineStr">
         <is>
           <t>진행 중</t>
         </is>
       </c>
-      <c r="I49" s="33" t="n">
+      <c r="I52" s="39" t="n">
         <v>0.3</v>
       </c>
-      <c r="J49" s="8" t="inlineStr">
+      <c r="J52" s="8" t="inlineStr">
         <is>
           <t>PR #30 시연 순서</t>
         </is>
       </c>
-      <c r="K49" s="8" t="n"/>
+      <c r="K52" s="8" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:K49"/>
-  <conditionalFormatting sqref="H5:H49">
+  <autoFilter ref="A4:K52"/>
+  <conditionalFormatting sqref="H5:H52">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"완료"</formula>
     </cfRule>
@@ -2737,7 +2868,7 @@
       <formula>"보류"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I5:I49">
+  <conditionalFormatting sqref="I5:I52">
     <cfRule type="dataBar" priority="4">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -2747,10 +2878,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="H5:H49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"완료,진행 중,예정,보류"</formula1>
     </dataValidation>
-    <dataValidation sqref="E5:E49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"개발,디자인,공동"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2821,23 +2952,23 @@
         </is>
       </c>
       <c r="B4" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$49,A4,WBS!$H$5:$H$49,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$52,A4,WBS!$H$5:$H$52,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C4" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$49,A4,WBS!$H$5:$H$49,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$52,A4,WBS!$H$5:$H$52,"완료")</f>
         <v/>
       </c>
       <c r="D4" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$49,A4,WBS!$H$5:$H$49,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$52,A4,WBS!$H$5:$H$52,"진행 중")</f>
         <v/>
       </c>
       <c r="E4" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$49,A4,WBS!$H$5:$H$49,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$52,A4,WBS!$H$5:$H$52,"예정")</f>
         <v/>
       </c>
       <c r="F4" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$49,WBS!$B$5:$B$49,A4,WBS!$H$5:$H$49,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$52,WBS!$B$5:$B$52,A4,WBS!$H$5:$H$52,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2848,23 +2979,23 @@
         </is>
       </c>
       <c r="B5" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$49,A5,WBS!$H$5:$H$49,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$52,A5,WBS!$H$5:$H$52,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C5" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$49,A5,WBS!$H$5:$H$49,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$52,A5,WBS!$H$5:$H$52,"완료")</f>
         <v/>
       </c>
       <c r="D5" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$49,A5,WBS!$H$5:$H$49,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$52,A5,WBS!$H$5:$H$52,"진행 중")</f>
         <v/>
       </c>
       <c r="E5" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$49,A5,WBS!$H$5:$H$49,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$52,A5,WBS!$H$5:$H$52,"예정")</f>
         <v/>
       </c>
       <c r="F5" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$49,WBS!$B$5:$B$49,A5,WBS!$H$5:$H$49,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$52,WBS!$B$5:$B$52,A5,WBS!$H$5:$H$52,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2875,23 +3006,23 @@
         </is>
       </c>
       <c r="B6" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$49,A6,WBS!$H$5:$H$49,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$52,A6,WBS!$H$5:$H$52,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C6" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$49,A6,WBS!$H$5:$H$49,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$52,A6,WBS!$H$5:$H$52,"완료")</f>
         <v/>
       </c>
       <c r="D6" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$49,A6,WBS!$H$5:$H$49,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$52,A6,WBS!$H$5:$H$52,"진행 중")</f>
         <v/>
       </c>
       <c r="E6" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$49,A6,WBS!$H$5:$H$49,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$52,A6,WBS!$H$5:$H$52,"예정")</f>
         <v/>
       </c>
       <c r="F6" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$49,WBS!$B$5:$B$49,A6,WBS!$H$5:$H$49,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$52,WBS!$B$5:$B$52,A6,WBS!$H$5:$H$52,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2902,23 +3033,23 @@
         </is>
       </c>
       <c r="B7" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$49,A7,WBS!$H$5:$H$49,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$52,A7,WBS!$H$5:$H$52,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C7" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$49,A7,WBS!$H$5:$H$49,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$52,A7,WBS!$H$5:$H$52,"완료")</f>
         <v/>
       </c>
       <c r="D7" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$49,A7,WBS!$H$5:$H$49,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$52,A7,WBS!$H$5:$H$52,"진행 중")</f>
         <v/>
       </c>
       <c r="E7" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$49,A7,WBS!$H$5:$H$49,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$52,A7,WBS!$H$5:$H$52,"예정")</f>
         <v/>
       </c>
       <c r="F7" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$49,WBS!$B$5:$B$49,A7,WBS!$H$5:$H$49,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$52,WBS!$B$5:$B$52,A7,WBS!$H$5:$H$52,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2929,23 +3060,23 @@
         </is>
       </c>
       <c r="B8" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$49,A8,WBS!$H$5:$H$49,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$52,A8,WBS!$H$5:$H$52,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C8" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$49,A8,WBS!$H$5:$H$49,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$52,A8,WBS!$H$5:$H$52,"완료")</f>
         <v/>
       </c>
       <c r="D8" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$49,A8,WBS!$H$5:$H$49,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$52,A8,WBS!$H$5:$H$52,"진행 중")</f>
         <v/>
       </c>
       <c r="E8" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$49,A8,WBS!$H$5:$H$49,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$52,A8,WBS!$H$5:$H$52,"예정")</f>
         <v/>
       </c>
       <c r="F8" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$49,WBS!$B$5:$B$49,A8,WBS!$H$5:$H$49,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$52,WBS!$B$5:$B$52,A8,WBS!$H$5:$H$52,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2956,23 +3087,23 @@
         </is>
       </c>
       <c r="B9" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$49,A9,WBS!$H$5:$H$49,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$52,A9,WBS!$H$5:$H$52,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C9" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$49,A9,WBS!$H$5:$H$49,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$52,A9,WBS!$H$5:$H$52,"완료")</f>
         <v/>
       </c>
       <c r="D9" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$49,A9,WBS!$H$5:$H$49,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$52,A9,WBS!$H$5:$H$52,"진행 중")</f>
         <v/>
       </c>
       <c r="E9" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$49,A9,WBS!$H$5:$H$49,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$52,A9,WBS!$H$5:$H$52,"예정")</f>
         <v/>
       </c>
       <c r="F9" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$49,WBS!$B$5:$B$49,A9,WBS!$H$5:$H$49,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$52,WBS!$B$5:$B$52,A9,WBS!$H$5:$H$52,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2983,23 +3114,23 @@
         </is>
       </c>
       <c r="B10" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$49,A10,WBS!$H$5:$H$49,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$52,A10,WBS!$H$5:$H$52,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C10" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$49,A10,WBS!$H$5:$H$49,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$52,A10,WBS!$H$5:$H$52,"완료")</f>
         <v/>
       </c>
       <c r="D10" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$49,A10,WBS!$H$5:$H$49,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$52,A10,WBS!$H$5:$H$52,"진행 중")</f>
         <v/>
       </c>
       <c r="E10" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$49,A10,WBS!$H$5:$H$49,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$52,A10,WBS!$H$5:$H$52,"예정")</f>
         <v/>
       </c>
       <c r="F10" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$49,WBS!$B$5:$B$49,A10,WBS!$H$5:$H$49,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$52,WBS!$B$5:$B$52,A10,WBS!$H$5:$H$52,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -3026,7 +3157,7 @@
         <v/>
       </c>
       <c r="F11" s="14">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$49,WBS!$H$5:$H$49,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$52,WBS!$H$5:$H$52,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>

--- a/docs/WBS.xlsx
+++ b/docs/WBS.xlsx
@@ -11,7 +11,7 @@
     <sheet name="요약" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS'!$A$4:$K$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS'!$A$4:$K$53</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -98,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -129,6 +129,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -589,7 +595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K52"/>
+  <dimension ref="A1:K53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -705,12 +711,12 @@
       <c r="K5" s="5" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="38" t="inlineStr">
+      <c r="A6" s="40" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="B6" s="38" t="inlineStr">
+      <c r="B6" s="40" t="inlineStr">
         <is>
           <t>기획·설계</t>
         </is>
@@ -725,23 +731,23 @@
           <t>과제 4개(사업계획·상품기획·브랜딩·마케팅), 적응형 질문, 사실·가정 분리 원칙</t>
         </is>
       </c>
-      <c r="E6" s="38" t="inlineStr">
+      <c r="E6" s="40" t="inlineStr">
         <is>
           <t>공동</t>
         </is>
       </c>
-      <c r="F6" s="38" t="n"/>
-      <c r="G6" s="38" t="inlineStr">
+      <c r="F6" s="40" t="n"/>
+      <c r="G6" s="40" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="H6" s="38" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I6" s="39" t="n">
+      <c r="H6" s="40" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I6" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J6" s="8" t="inlineStr">
@@ -752,12 +758,12 @@
       <c r="K6" s="8" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="38" t="inlineStr">
+      <c r="A7" s="40" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="B7" s="38" t="inlineStr">
+      <c r="B7" s="40" t="inlineStr">
         <is>
           <t>기획·설계</t>
         </is>
@@ -772,27 +778,27 @@
           <t>FastAPI 하네스 구조, API 계약, 테스트 전략</t>
         </is>
       </c>
-      <c r="E7" s="38" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F7" s="38" t="inlineStr">
+      <c r="E7" s="40" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F7" s="40" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="G7" s="38" t="inlineStr">
+      <c r="G7" s="40" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="H7" s="38" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I7" s="39" t="n">
+      <c r="H7" s="40" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I7" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J7" s="8" t="inlineStr">
@@ -803,12 +809,12 @@
       <c r="K7" s="8" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="38" t="inlineStr">
+      <c r="A8" s="40" t="inlineStr">
         <is>
           <t>1.3</t>
         </is>
       </c>
-      <c r="B8" s="38" t="inlineStr">
+      <c r="B8" s="40" t="inlineStr">
         <is>
           <t>기획·설계</t>
         </is>
@@ -823,27 +829,27 @@
           <t>V2 화면 흐름, 묶음 0~4로 작업 나누기</t>
         </is>
       </c>
-      <c r="E8" s="38" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F8" s="38" t="inlineStr">
+      <c r="E8" s="40" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F8" s="40" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G8" s="38" t="inlineStr">
+      <c r="G8" s="40" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H8" s="38" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I8" s="39" t="n">
+      <c r="H8" s="40" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I8" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J8" s="8" t="inlineStr">
@@ -854,12 +860,12 @@
       <c r="K8" s="8" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="38" t="inlineStr">
+      <c r="A9" s="40" t="inlineStr">
         <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="B9" s="38" t="inlineStr">
+      <c r="B9" s="40" t="inlineStr">
         <is>
           <t>기획·설계</t>
         </is>
@@ -874,27 +880,27 @@
           <t>지금 상태·다음 할 일·작업 방식·환경 팁, PR마다 갱신</t>
         </is>
       </c>
-      <c r="E9" s="38" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F9" s="38" t="inlineStr">
+      <c r="E9" s="40" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F9" s="40" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="G9" s="38" t="inlineStr">
+      <c r="G9" s="40" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="H9" s="38" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I9" s="39" t="n">
+      <c r="H9" s="40" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I9" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J9" s="8" t="inlineStr">
@@ -905,12 +911,12 @@
       <c r="K9" s="8" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="38" t="inlineStr">
+      <c r="A10" s="40" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="B10" s="38" t="inlineStr">
+      <c r="B10" s="40" t="inlineStr">
         <is>
           <t>기획·설계</t>
         </is>
@@ -925,27 +931,27 @@
           <t>바로 보기 주소, 된 것, 남은 일·맡을 사람·상의할 점</t>
         </is>
       </c>
-      <c r="E10" s="38" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F10" s="38" t="inlineStr">
+      <c r="E10" s="40" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F10" s="40" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="G10" s="38" t="inlineStr">
+      <c r="G10" s="40" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="H10" s="38" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I10" s="39" t="n">
+      <c r="H10" s="40" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I10" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J10" s="8" t="inlineStr">
@@ -984,12 +990,12 @@
       <c r="K11" s="5" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="38" t="inlineStr">
+      <c r="A12" s="40" t="inlineStr">
         <is>
           <t>2.1</t>
         </is>
       </c>
-      <c r="B12" s="38" t="inlineStr">
+      <c r="B12" s="40" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1004,27 +1010,27 @@
           <t>사실·가정·미정 구분, 정보 출처 표시</t>
         </is>
       </c>
-      <c r="E12" s="38" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F12" s="38" t="inlineStr">
+      <c r="E12" s="40" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F12" s="40" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="G12" s="38" t="inlineStr">
+      <c r="G12" s="40" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H12" s="38" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I12" s="39" t="n">
+      <c r="H12" s="40" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I12" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J12" s="8" t="inlineStr">
@@ -1035,12 +1041,12 @@
       <c r="K12" s="8" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="38" t="inlineStr">
+      <c r="A13" s="40" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
       </c>
-      <c r="B13" s="38" t="inlineStr">
+      <c r="B13" s="40" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1055,27 +1061,27 @@
           <t>비용 없이 개발·테스트하는 가짜 모델</t>
         </is>
       </c>
-      <c r="E13" s="38" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F13" s="38" t="inlineStr">
+      <c r="E13" s="40" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F13" s="40" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="G13" s="38" t="inlineStr">
+      <c r="G13" s="40" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H13" s="38" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I13" s="39" t="n">
+      <c r="H13" s="40" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I13" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J13" s="8" t="inlineStr">
@@ -1086,12 +1092,12 @@
       <c r="K13" s="8" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="38" t="inlineStr">
+      <c r="A14" s="40" t="inlineStr">
         <is>
           <t>2.3</t>
         </is>
       </c>
-      <c r="B14" s="38" t="inlineStr">
+      <c r="B14" s="40" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1106,27 +1112,27 @@
           <t>과제별 질문 정책(policy.yaml), 단계별 프롬프트</t>
         </is>
       </c>
-      <c r="E14" s="38" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F14" s="38" t="inlineStr">
+      <c r="E14" s="40" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F14" s="40" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G14" s="38" t="inlineStr">
+      <c r="G14" s="40" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H14" s="38" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I14" s="39" t="n">
+      <c r="H14" s="40" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I14" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J14" s="8" t="inlineStr">
@@ -1137,12 +1143,12 @@
       <c r="K14" s="8" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="38" t="inlineStr">
+      <c r="A15" s="40" t="inlineStr">
         <is>
           <t>2.4</t>
         </is>
       </c>
-      <c r="B15" s="38" t="inlineStr">
+      <c r="B15" s="40" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1157,27 +1163,27 @@
           <t>모드별 질문 상한, '다른 예시 보기' 단계</t>
         </is>
       </c>
-      <c r="E15" s="38" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F15" s="38" t="inlineStr">
+      <c r="E15" s="40" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F15" s="40" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G15" s="38" t="inlineStr">
+      <c r="G15" s="40" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H15" s="38" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I15" s="39" t="n">
+      <c r="H15" s="40" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I15" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J15" s="8" t="inlineStr">
@@ -1188,12 +1194,12 @@
       <c r="K15" s="8" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="38" t="inlineStr">
+      <c r="A16" s="40" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
       </c>
-      <c r="B16" s="38" t="inlineStr">
+      <c r="B16" s="40" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1204,27 +1210,27 @@
         </is>
       </c>
       <c r="D16" s="8" t="n"/>
-      <c r="E16" s="38" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F16" s="38" t="inlineStr">
+      <c r="E16" s="40" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F16" s="40" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G16" s="38" t="inlineStr">
+      <c r="G16" s="40" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H16" s="38" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I16" s="39" t="n">
+      <c r="H16" s="40" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I16" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J16" s="8" t="inlineStr">
@@ -1235,12 +1241,12 @@
       <c r="K16" s="8" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="38" t="inlineStr">
+      <c r="A17" s="40" t="inlineStr">
         <is>
           <t>2.6</t>
         </is>
       </c>
-      <c r="B17" s="38" t="inlineStr">
+      <c r="B17" s="40" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1255,27 +1261,27 @@
           <t>과제별 정책·프롬프트·검증 규칙</t>
         </is>
       </c>
-      <c r="E17" s="38" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F17" s="38" t="inlineStr">
+      <c r="E17" s="40" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F17" s="40" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G17" s="38" t="inlineStr">
+      <c r="G17" s="40" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H17" s="38" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I17" s="39" t="n">
+      <c r="H17" s="40" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I17" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J17" s="8" t="inlineStr">
@@ -1286,12 +1292,12 @@
       <c r="K17" s="8" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="38" t="inlineStr">
+      <c r="A18" s="40" t="inlineStr">
         <is>
           <t>2.7</t>
         </is>
       </c>
-      <c r="B18" s="38" t="inlineStr">
+      <c r="B18" s="40" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1306,27 +1312,27 @@
           <t>한국어 오류 문구, API 문서</t>
         </is>
       </c>
-      <c r="E18" s="38" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F18" s="38" t="inlineStr">
+      <c r="E18" s="40" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F18" s="40" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G18" s="38" t="inlineStr">
+      <c r="G18" s="40" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H18" s="38" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I18" s="39" t="n">
+      <c r="H18" s="40" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I18" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J18" s="8" t="inlineStr">
@@ -1337,12 +1343,12 @@
       <c r="K18" s="8" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="38" t="inlineStr">
+      <c r="A19" s="40" t="inlineStr">
         <is>
           <t>2.8</t>
         </is>
       </c>
-      <c r="B19" s="38" t="inlineStr">
+      <c r="B19" s="40" t="inlineStr">
         <is>
           <t>백엔드 기반</t>
         </is>
@@ -1357,27 +1363,27 @@
           <t>API에 맞춘 최소 화면, 개발 안내(CLAUDE.md)</t>
         </is>
       </c>
-      <c r="E19" s="38" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F19" s="38" t="inlineStr">
+      <c r="E19" s="40" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F19" s="40" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G19" s="38" t="inlineStr">
+      <c r="G19" s="40" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H19" s="38" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I19" s="39" t="n">
+      <c r="H19" s="40" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I19" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J19" s="8" t="inlineStr">
@@ -1416,12 +1422,12 @@
       <c r="K20" s="5" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="38" t="inlineStr">
+      <c r="A21" s="40" t="inlineStr">
         <is>
           <t>3.1</t>
         </is>
       </c>
-      <c r="B21" s="38" t="inlineStr">
+      <c r="B21" s="40" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
@@ -1436,23 +1442,23 @@
           <t>전체 화면 흐름 HTML 프로토타입</t>
         </is>
       </c>
-      <c r="E21" s="38" t="inlineStr">
+      <c r="E21" s="40" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
       </c>
-      <c r="F21" s="38" t="n"/>
-      <c r="G21" s="38" t="inlineStr">
+      <c r="F21" s="40" t="n"/>
+      <c r="G21" s="40" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H21" s="38" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I21" s="39" t="n">
+      <c r="H21" s="40" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I21" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J21" s="8" t="inlineStr">
@@ -1463,12 +1469,12 @@
       <c r="K21" s="8" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="38" t="inlineStr">
+      <c r="A22" s="40" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
       </c>
-      <c r="B22" s="38" t="inlineStr">
+      <c r="B22" s="40" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
@@ -1483,27 +1489,27 @@
           <t>모든 질문에 '다른 예시 보기', 모드 설명, 이미지 블록, 생성 중·실패·최신 아님 상태</t>
         </is>
       </c>
-      <c r="E22" s="38" t="inlineStr">
+      <c r="E22" s="40" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
       </c>
-      <c r="F22" s="38" t="inlineStr">
+      <c r="F22" s="40" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G22" s="38" t="inlineStr">
+      <c r="G22" s="40" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H22" s="38" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I22" s="39" t="n">
+      <c r="H22" s="40" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I22" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J22" s="8" t="inlineStr">
@@ -1514,12 +1520,12 @@
       <c r="K22" s="8" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="38" t="inlineStr">
+      <c r="A23" s="40" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
       </c>
-      <c r="B23" s="38" t="inlineStr">
+      <c r="B23" s="40" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
@@ -1534,31 +1540,31 @@
           <t>반응형 자동 배치 확인</t>
         </is>
       </c>
-      <c r="E23" s="38" t="inlineStr">
+      <c r="E23" s="40" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
       </c>
-      <c r="F23" s="38" t="n"/>
-      <c r="G23" s="38" t="n"/>
-      <c r="H23" s="38" t="inlineStr">
+      <c r="F23" s="40" t="n"/>
+      <c r="G23" s="40" t="n"/>
+      <c r="H23" s="40" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="I23" s="39" t="n">
+      <c r="I23" s="41" t="n">
         <v>0</v>
       </c>
       <c r="J23" s="8" t="n"/>
       <c r="K23" s="8" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="38" t="inlineStr">
+      <c r="A24" s="40" t="inlineStr">
         <is>
           <t>3.4</t>
         </is>
       </c>
-      <c r="B24" s="38" t="inlineStr">
+      <c r="B24" s="40" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
@@ -1573,19 +1579,19 @@
           <t>/preview 화면을 html.to.design으로 가져와 수정</t>
         </is>
       </c>
-      <c r="E24" s="38" t="inlineStr">
+      <c r="E24" s="40" t="inlineStr">
         <is>
           <t>디자인</t>
         </is>
       </c>
-      <c r="F24" s="38" t="n"/>
-      <c r="G24" s="38" t="n"/>
-      <c r="H24" s="38" t="inlineStr">
+      <c r="F24" s="40" t="n"/>
+      <c r="G24" s="40" t="n"/>
+      <c r="H24" s="40" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="I24" s="39" t="n">
+      <c r="I24" s="41" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="8" t="n"/>
@@ -1620,12 +1626,12 @@
       <c r="K25" s="5" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="38" t="inlineStr">
+      <c r="A26" s="40" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
       </c>
-      <c r="B26" s="38" t="inlineStr">
+      <c r="B26" s="40" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1640,27 +1646,27 @@
           <t>버셀 배포 설정 포함</t>
         </is>
       </c>
-      <c r="E26" s="38" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F26" s="38" t="inlineStr">
+      <c r="E26" s="40" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F26" s="40" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="G26" s="38" t="inlineStr">
+      <c r="G26" s="40" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="H26" s="38" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I26" s="39" t="n">
+      <c r="H26" s="40" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I26" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J26" s="8" t="inlineStr">
@@ -1671,12 +1677,12 @@
       <c r="K26" s="8" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="38" t="inlineStr">
+      <c r="A27" s="40" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
       </c>
-      <c r="B27" s="38" t="inlineStr">
+      <c r="B27" s="40" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1691,27 +1697,27 @@
           <t>답변 종류, 흐름 패널, 익명 사용자</t>
         </is>
       </c>
-      <c r="E27" s="38" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F27" s="38" t="inlineStr">
+      <c r="E27" s="40" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F27" s="40" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G27" s="38" t="inlineStr">
+      <c r="G27" s="40" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H27" s="38" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I27" s="39" t="n">
+      <c r="H27" s="40" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I27" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J27" s="8" t="inlineStr">
@@ -1722,12 +1728,12 @@
       <c r="K27" s="8" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="38" t="inlineStr">
+      <c r="A28" s="40" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
       </c>
-      <c r="B28" s="38" t="inlineStr">
+      <c r="B28" s="40" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1742,27 +1748,27 @@
           <t>서버 저장(SQLite), 문서 내려받기</t>
         </is>
       </c>
-      <c r="E28" s="38" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F28" s="38" t="inlineStr">
+      <c r="E28" s="40" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F28" s="40" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G28" s="38" t="inlineStr">
+      <c r="G28" s="40" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H28" s="38" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I28" s="39" t="n">
+      <c r="H28" s="40" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I28" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J28" s="8" t="inlineStr">
@@ -1773,12 +1779,12 @@
       <c r="K28" s="8" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="38" t="inlineStr">
+      <c r="A29" s="40" t="inlineStr">
         <is>
           <t>4.4</t>
         </is>
       </c>
-      <c r="B29" s="38" t="inlineStr">
+      <c r="B29" s="40" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1793,27 +1799,27 @@
           <t>결과를 섹션·블록으로</t>
         </is>
       </c>
-      <c r="E29" s="38" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F29" s="38" t="inlineStr">
+      <c r="E29" s="40" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F29" s="40" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G29" s="38" t="inlineStr">
+      <c r="G29" s="40" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H29" s="38" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I29" s="39" t="n">
+      <c r="H29" s="40" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I29" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J29" s="8" t="inlineStr">
@@ -1824,12 +1830,12 @@
       <c r="K29" s="8" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="38" t="inlineStr">
+      <c r="A30" s="40" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
       </c>
-      <c r="B30" s="38" t="inlineStr">
+      <c r="B30" s="40" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1844,27 +1850,27 @@
           <t>샘플 근거 자료, 자리표시 이미지</t>
         </is>
       </c>
-      <c r="E30" s="38" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F30" s="38" t="inlineStr">
+      <c r="E30" s="40" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F30" s="40" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G30" s="38" t="inlineStr">
+      <c r="G30" s="40" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H30" s="38" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I30" s="39" t="n">
+      <c r="H30" s="40" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I30" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J30" s="8" t="inlineStr">
@@ -1875,12 +1881,12 @@
       <c r="K30" s="8" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="38" t="inlineStr">
+      <c r="A31" s="40" t="inlineStr">
         <is>
           <t>4.6</t>
         </is>
       </c>
-      <c r="B31" s="38" t="inlineStr">
+      <c r="B31" s="40" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1895,27 +1901,27 @@
           <t>생성 중·생성 실패 화면, 최신 아님 배너, 이미지 상자, 모드 설명</t>
         </is>
       </c>
-      <c r="E31" s="38" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F31" s="38" t="inlineStr">
+      <c r="E31" s="40" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F31" s="40" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G31" s="38" t="inlineStr">
+      <c r="G31" s="40" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H31" s="38" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I31" s="39" t="n">
+      <c r="H31" s="40" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I31" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J31" s="8" t="inlineStr">
@@ -1926,12 +1932,12 @@
       <c r="K31" s="8" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="38" t="inlineStr">
+      <c r="A32" s="40" t="inlineStr">
         <is>
           <t>4.7</t>
         </is>
       </c>
-      <c r="B32" s="38" t="inlineStr">
+      <c r="B32" s="40" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1946,27 +1952,27 @@
           <t>이전 결과를 다음 과제의 기준으로 가져오기</t>
         </is>
       </c>
-      <c r="E32" s="38" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F32" s="38" t="inlineStr">
+      <c r="E32" s="40" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F32" s="40" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="G32" s="38" t="inlineStr">
+      <c r="G32" s="40" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="H32" s="38" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I32" s="39" t="n">
+      <c r="H32" s="40" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I32" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J32" s="8" t="inlineStr">
@@ -1977,12 +1983,12 @@
       <c r="K32" s="8" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="38" t="inlineStr">
+      <c r="A33" s="40" t="inlineStr">
         <is>
           <t>4.8</t>
         </is>
       </c>
-      <c r="B33" s="38" t="inlineStr">
+      <c r="B33" s="40" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -1993,27 +1999,27 @@
         </is>
       </c>
       <c r="D33" s="8" t="n"/>
-      <c r="E33" s="38" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F33" s="38" t="inlineStr">
+      <c r="E33" s="40" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F33" s="40" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="G33" s="38" t="inlineStr">
+      <c r="G33" s="40" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="H33" s="38" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I33" s="39" t="n">
+      <c r="H33" s="40" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I33" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J33" s="8" t="inlineStr">
@@ -2028,12 +2034,12 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="38" t="inlineStr">
+      <c r="A34" s="40" t="inlineStr">
         <is>
           <t>4.9</t>
         </is>
       </c>
-      <c r="B34" s="38" t="inlineStr">
+      <c r="B34" s="40" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -2044,23 +2050,23 @@
         </is>
       </c>
       <c r="D34" s="8" t="n"/>
-      <c r="E34" s="38" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F34" s="38" t="n"/>
-      <c r="G34" s="38" t="inlineStr">
+      <c r="E34" s="40" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F34" s="40" t="n"/>
+      <c r="G34" s="40" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="H34" s="38" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I34" s="39" t="n">
+      <c r="H34" s="40" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I34" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J34" s="8" t="inlineStr">
@@ -2071,12 +2077,12 @@
       <c r="K34" s="8" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="38" t="inlineStr">
+      <c r="A35" s="40" t="inlineStr">
         <is>
           <t>4.10</t>
         </is>
       </c>
-      <c r="B35" s="38" t="inlineStr">
+      <c r="B35" s="40" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -2087,31 +2093,31 @@
         </is>
       </c>
       <c r="D35" s="8" t="n"/>
-      <c r="E35" s="38" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F35" s="38" t="n"/>
-      <c r="G35" s="38" t="n"/>
-      <c r="H35" s="38" t="inlineStr">
+      <c r="E35" s="40" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F35" s="40" t="n"/>
+      <c r="G35" s="40" t="n"/>
+      <c r="H35" s="40" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="I35" s="39" t="n">
+      <c r="I35" s="41" t="n">
         <v>0</v>
       </c>
       <c r="J35" s="8" t="n"/>
       <c r="K35" s="8" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="38" t="inlineStr">
+      <c r="A36" s="40" t="inlineStr">
         <is>
           <t>4.11</t>
         </is>
       </c>
-      <c r="B36" s="38" t="inlineStr">
+      <c r="B36" s="40" t="inlineStr">
         <is>
           <t>화면 개발(V2)</t>
         </is>
@@ -2122,19 +2128,19 @@
         </is>
       </c>
       <c r="D36" s="8" t="n"/>
-      <c r="E36" s="38" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F36" s="38" t="n"/>
-      <c r="G36" s="38" t="n"/>
-      <c r="H36" s="38" t="inlineStr">
+      <c r="E36" s="40" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F36" s="40" t="n"/>
+      <c r="G36" s="40" t="n"/>
+      <c r="H36" s="40" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="I36" s="39" t="n">
+      <c r="I36" s="41" t="n">
         <v>0</v>
       </c>
       <c r="J36" s="8" t="n"/>
@@ -2162,19 +2168,19 @@
       <c r="G37" s="4" t="n"/>
       <c r="H37" s="4" t="n"/>
       <c r="I37" s="6">
-        <f>IFERROR(AVERAGE(I38:I39),0)</f>
+        <f>IFERROR(AVERAGE(I38:I40),0)</f>
         <v/>
       </c>
       <c r="J37" s="5" t="n"/>
       <c r="K37" s="5" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="38" t="inlineStr">
+      <c r="A38" s="40" t="inlineStr">
         <is>
           <t>5.1</t>
         </is>
       </c>
-      <c r="B38" s="38" t="inlineStr">
+      <c r="B38" s="40" t="inlineStr">
         <is>
           <t>배포</t>
         </is>
@@ -2189,27 +2195,27 @@
           <t>main은 정식 주소, PR마다 미리보기 주소</t>
         </is>
       </c>
-      <c r="E38" s="38" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F38" s="38" t="inlineStr">
+      <c r="E38" s="40" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F38" s="40" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="G38" s="38" t="inlineStr">
+      <c r="G38" s="40" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="H38" s="38" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I38" s="39" t="n">
+      <c r="H38" s="40" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I38" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J38" s="8" t="inlineStr">
@@ -2224,12 +2230,12 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="38" t="inlineStr">
+      <c r="A39" s="40" t="inlineStr">
         <is>
           <t>5.2</t>
         </is>
       </c>
-      <c r="B39" s="38" t="inlineStr">
+      <c r="B39" s="40" t="inlineStr">
         <is>
           <t>배포</t>
         </is>
@@ -2244,27 +2250,27 @@
           <t>저장 디스크 방식 정하기, 프론트와 연결</t>
         </is>
       </c>
-      <c r="E39" s="38" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F39" s="38" t="inlineStr">
+      <c r="E39" s="40" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F39" s="40" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="G39" s="38" t="inlineStr">
+      <c r="G39" s="40" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="H39" s="38" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I39" s="39" t="n">
+      <c r="H39" s="40" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I39" s="41" t="n">
         <v>1</v>
       </c>
       <c r="J39" s="8" t="inlineStr">
@@ -2279,585 +2285,632 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="A40" s="40" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="B40" s="40" t="inlineStr">
+        <is>
+          <t>배포</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>데이터 보존(Neon Postgres)</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="n"/>
+      <c r="E40" s="40" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F40" s="40" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G40" s="40" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="H40" s="40" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I40" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" s="8" t="inlineStr">
+        <is>
+          <t>PR #33</t>
+        </is>
+      </c>
+      <c r="K40" s="8" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>실제 AI 연결·튜닝</t>
         </is>
       </c>
-      <c r="D40" s="5" t="n"/>
-      <c r="E40" s="4" t="n"/>
-      <c r="F40" s="4" t="n"/>
-      <c r="G40" s="4" t="n"/>
-      <c r="H40" s="4" t="n"/>
-      <c r="I40" s="6">
-        <f>IFERROR(AVERAGE(I41:I49),0)</f>
-        <v/>
-      </c>
-      <c r="J40" s="5" t="n"/>
-      <c r="K40" s="5" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="38" t="inlineStr">
+      <c r="D41" s="5" t="n"/>
+      <c r="E41" s="4" t="n"/>
+      <c r="F41" s="4" t="n"/>
+      <c r="G41" s="4" t="n"/>
+      <c r="H41" s="4" t="n"/>
+      <c r="I41" s="6">
+        <f>IFERROR(AVERAGE(I42:I50),0)</f>
+        <v/>
+      </c>
+      <c r="J41" s="5" t="n"/>
+      <c r="K41" s="5" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="40" t="inlineStr">
         <is>
           <t>6.1</t>
         </is>
       </c>
-      <c r="B41" s="38" t="inlineStr">
+      <c r="B42" s="40" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
       </c>
-      <c r="C41" s="8" t="inlineStr">
+      <c r="C42" s="8" t="inlineStr">
         <is>
           <t>Claude 모델 연결</t>
         </is>
       </c>
-      <c r="D41" s="8" t="inlineStr">
+      <c r="D42" s="8" t="inlineStr">
         <is>
           <t>가짜 모델(Mock) 대신 실제 모델</t>
         </is>
       </c>
-      <c r="E41" s="38" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F41" s="38" t="inlineStr">
+      <c r="E42" s="40" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F42" s="40" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="G41" s="38" t="inlineStr">
+      <c r="G42" s="40" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="H41" s="38" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I41" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="J41" s="8" t="inlineStr">
+      <c r="H42" s="40" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I42" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" s="8" t="inlineStr">
         <is>
           <t>PR #20</t>
         </is>
       </c>
-      <c r="K41" s="8" t="inlineStr">
+      <c r="K42" s="8" t="inlineStr">
         <is>
           <t>어댑터 준비(기본 Mock). 실제 호출·모델·비용은 인수 기업</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="38" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="40" t="inlineStr">
         <is>
           <t>6.2</t>
         </is>
       </c>
-      <c r="B42" s="38" t="inlineStr">
+      <c r="B43" s="40" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
       </c>
-      <c r="C42" s="8" t="inlineStr">
+      <c r="C43" s="8" t="inlineStr">
         <is>
           <t>과제별 질문·결과 품질 튜닝</t>
         </is>
       </c>
-      <c r="D42" s="8" t="inlineStr">
+      <c r="D43" s="8" t="inlineStr">
         <is>
           <t>준비도 기준·항목 가중치·프롬프트를 시나리오로 측정</t>
         </is>
       </c>
-      <c r="E42" s="38" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F42" s="38" t="n"/>
-      <c r="G42" s="38" t="n"/>
-      <c r="H42" s="38" t="inlineStr">
+      <c r="E43" s="40" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F43" s="40" t="n"/>
+      <c r="G43" s="40" t="n"/>
+      <c r="H43" s="40" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="I42" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="8" t="n"/>
-      <c r="K42" s="8" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="38" t="inlineStr">
-        <is>
-          <t>6.3</t>
-        </is>
-      </c>
-      <c r="B43" s="38" t="inlineStr">
-        <is>
-          <t>실제 AI 연결</t>
-        </is>
-      </c>
-      <c r="C43" s="8" t="inlineStr">
-        <is>
-          <t>이미지 생성·웹 검색 근거 연결</t>
-        </is>
-      </c>
-      <c r="D43" s="8" t="inlineStr">
-        <is>
-          <t>지금의 자리표시·샘플 자리에 실제 기능 연결</t>
-        </is>
-      </c>
-      <c r="E43" s="38" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F43" s="38" t="n"/>
-      <c r="G43" s="38" t="n"/>
-      <c r="H43" s="38" t="inlineStr">
-        <is>
-          <t>예정</t>
-        </is>
-      </c>
-      <c r="I43" s="39" t="n">
+      <c r="I43" s="41" t="n">
         <v>0</v>
       </c>
       <c r="J43" s="8" t="n"/>
       <c r="K43" s="8" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="38" t="inlineStr">
+      <c r="A44" s="40" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="B44" s="40" t="inlineStr">
+        <is>
+          <t>실제 AI 연결</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>이미지 생성·웹 검색 근거 연결</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>지금의 자리표시·샘플 자리에 실제 기능 연결</t>
+        </is>
+      </c>
+      <c r="E44" s="40" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F44" s="40" t="n"/>
+      <c r="G44" s="40" t="n"/>
+      <c r="H44" s="40" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="I44" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="8" t="n"/>
+      <c r="K44" s="8" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="40" t="inlineStr">
         <is>
           <t>6.4</t>
         </is>
       </c>
-      <c r="B44" s="38" t="inlineStr">
+      <c r="B45" s="40" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
       </c>
-      <c r="C44" s="8" t="inlineStr">
+      <c r="C45" s="8" t="inlineStr">
         <is>
           <t>외부 전송 보호(개인정보 가림·비공개·동의)</t>
         </is>
       </c>
-      <c r="D44" s="8" t="n"/>
-      <c r="E44" s="38" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F44" s="38" t="inlineStr">
+      <c r="D45" s="8" t="n"/>
+      <c r="E45" s="40" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F45" s="40" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="G44" s="38" t="inlineStr">
+      <c r="G45" s="40" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="H44" s="38" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I44" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="J44" s="8" t="inlineStr">
+      <c r="H45" s="40" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I45" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" s="8" t="inlineStr">
         <is>
           <t>PR #24</t>
         </is>
       </c>
-      <c r="K44" s="8" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="38" t="inlineStr">
+      <c r="K45" s="8" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="40" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="B45" s="38" t="inlineStr">
+      <c r="B46" s="40" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
       </c>
-      <c r="C45" s="8" t="inlineStr">
+      <c r="C46" s="8" t="inlineStr">
         <is>
           <t>프롬프트 주입 기본 방어(입력 감싸기·유출 차단)</t>
         </is>
       </c>
-      <c r="D45" s="8" t="n"/>
-      <c r="E45" s="38" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F45" s="38" t="inlineStr">
+      <c r="D46" s="8" t="n"/>
+      <c r="E46" s="40" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F46" s="40" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="G45" s="38" t="inlineStr">
+      <c r="G46" s="40" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="H45" s="38" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I45" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="J45" s="8" t="inlineStr">
+      <c r="H46" s="40" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I46" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" s="8" t="inlineStr">
         <is>
           <t>PR #25</t>
         </is>
       </c>
-      <c r="K45" s="8" t="inlineStr">
+      <c r="K46" s="8" t="inlineStr">
         <is>
           <t>PR #25</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="38" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="40" t="inlineStr">
         <is>
           <t>6.6</t>
         </is>
       </c>
-      <c r="B46" s="38" t="inlineStr">
+      <c r="B47" s="40" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
       </c>
-      <c r="C46" s="8" t="inlineStr">
+      <c r="C47" s="8" t="inlineStr">
         <is>
           <t>단계별 모델 라우팅·하네스 로드맵·인수 안내</t>
         </is>
       </c>
-      <c r="D46" s="8" t="n"/>
-      <c r="E46" s="38" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F46" s="38" t="inlineStr">
+      <c r="D47" s="8" t="n"/>
+      <c r="E47" s="40" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F47" s="40" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="G46" s="38" t="inlineStr">
+      <c r="G47" s="40" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="H46" s="38" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I46" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="J46" s="8" t="inlineStr">
+      <c r="H47" s="40" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I47" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" s="8" t="inlineStr">
         <is>
           <t>PR #26</t>
         </is>
       </c>
-      <c r="K46" s="8" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="38" t="inlineStr">
+      <c r="K47" s="8" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="40" t="inlineStr">
         <is>
           <t>6.7</t>
         </is>
       </c>
-      <c r="B47" s="38" t="inlineStr">
+      <c r="B48" s="40" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
       </c>
-      <c r="C47" s="8" t="inlineStr">
+      <c r="C48" s="8" t="inlineStr">
         <is>
           <t>AI 동시 호출 상한(붐비면 503)</t>
         </is>
       </c>
-      <c r="D47" s="8" t="inlineStr">
+      <c r="D48" s="8" t="inlineStr">
         <is>
           <t>LLM·이미지 호출 자리 수 제한, 대기 뒤 거절, 세션 되돌림</t>
         </is>
       </c>
-      <c r="E47" s="38" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F47" s="38" t="inlineStr">
+      <c r="E48" s="40" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F48" s="40" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="G47" s="38" t="inlineStr">
+      <c r="G48" s="40" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="H47" s="38" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I47" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="J47" s="8" t="inlineStr">
+      <c r="H48" s="40" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I48" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" s="8" t="inlineStr">
         <is>
           <t>PR #27</t>
         </is>
       </c>
-      <c r="K47" s="8" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="38" t="inlineStr">
+      <c r="K48" s="8" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="40" t="inlineStr">
         <is>
           <t>6.8</t>
         </is>
       </c>
-      <c r="B48" s="38" t="inlineStr">
+      <c r="B49" s="40" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
       </c>
-      <c r="C48" s="8" t="inlineStr">
+      <c r="C49" s="8" t="inlineStr">
         <is>
           <t>병렬 생성(기본 꺼짐)·설계 고민 기록</t>
         </is>
       </c>
-      <c r="D48" s="8" t="inlineStr">
+      <c r="D49" s="8" t="inlineStr">
         <is>
           <t>결과 항목 조각 동시 생성·코드 합치기·부분 결과 캐시, README 설계 고민, 로드맵 측정표</t>
         </is>
       </c>
-      <c r="E48" s="38" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F48" s="38" t="inlineStr">
+      <c r="E49" s="40" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F49" s="40" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="G48" s="38" t="inlineStr">
+      <c r="G49" s="40" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="H48" s="38" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I48" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="J48" s="8" t="inlineStr">
+      <c r="H49" s="40" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I49" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" s="8" t="inlineStr">
         <is>
           <t>PR #28</t>
         </is>
       </c>
-      <c r="K48" s="8" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="38" t="inlineStr">
+      <c r="K49" s="8" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="40" t="inlineStr">
         <is>
           <t>6.9</t>
         </is>
       </c>
-      <c r="B49" s="38" t="inlineStr">
+      <c r="B50" s="40" t="inlineStr">
         <is>
           <t>실제 AI 연결</t>
         </is>
       </c>
-      <c r="C49" s="8" t="inlineStr">
+      <c r="C50" s="8" t="inlineStr">
         <is>
           <t>측정 준비(응답 시간 기록·측정 도구)</t>
         </is>
       </c>
-      <c r="D49" s="8" t="inlineStr">
+      <c r="D50" s="8" t="inlineStr">
         <is>
           <t>trace duration_ms, 실제 모델용 시나리오 실행, quick-skip 시나리오, scripts/measure.py(기본 Mock, 비용 상한)</t>
         </is>
       </c>
-      <c r="E49" s="38" t="inlineStr">
-        <is>
-          <t>개발</t>
-        </is>
-      </c>
-      <c r="F49" s="38" t="inlineStr">
+      <c r="E50" s="40" t="inlineStr">
+        <is>
+          <t>개발</t>
+        </is>
+      </c>
+      <c r="F50" s="40" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="G49" s="38" t="inlineStr">
+      <c r="G50" s="40" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="H49" s="38" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I49" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="J49" s="8" t="inlineStr">
+      <c r="H50" s="40" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I50" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J50" s="8" t="inlineStr">
         <is>
           <t>PR #29</t>
         </is>
       </c>
-      <c r="K49" s="8" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
+      <c r="K50" s="8" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>마무리</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C51" s="5" t="inlineStr">
         <is>
           <t>평가·발표</t>
         </is>
       </c>
-      <c r="D50" s="5" t="n"/>
-      <c r="E50" s="4" t="n"/>
-      <c r="F50" s="4" t="n"/>
-      <c r="G50" s="4" t="n"/>
-      <c r="H50" s="4" t="n"/>
-      <c r="I50" s="6">
-        <f>IFERROR(AVERAGE(I51:I52),0)</f>
-        <v/>
-      </c>
-      <c r="J50" s="5" t="n"/>
-      <c r="K50" s="5" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="38" t="inlineStr">
+      <c r="D51" s="5" t="n"/>
+      <c r="E51" s="4" t="n"/>
+      <c r="F51" s="4" t="n"/>
+      <c r="G51" s="4" t="n"/>
+      <c r="H51" s="4" t="n"/>
+      <c r="I51" s="6">
+        <f>IFERROR(AVERAGE(I52:I53),0)</f>
+        <v/>
+      </c>
+      <c r="J51" s="5" t="n"/>
+      <c r="K51" s="5" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="40" t="inlineStr">
         <is>
           <t>7.1</t>
         </is>
       </c>
-      <c r="B51" s="38" t="inlineStr">
+      <c r="B52" s="40" t="inlineStr">
         <is>
           <t>마무리</t>
         </is>
       </c>
-      <c r="C51" s="8" t="inlineStr">
+      <c r="C52" s="8" t="inlineStr">
         <is>
           <t>사용성 확인·평가 지표 측정</t>
         </is>
       </c>
-      <c r="D51" s="8" t="inlineStr">
+      <c r="D52" s="8" t="inlineStr">
         <is>
           <t>필수정보 충족률, 질문 효율, 가정 표시율 등(기획서 14장)</t>
         </is>
       </c>
-      <c r="E51" s="38" t="inlineStr">
+      <c r="E52" s="40" t="inlineStr">
         <is>
           <t>공동</t>
         </is>
       </c>
-      <c r="F51" s="38" t="inlineStr">
+      <c r="F52" s="40" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="G51" s="38" t="n"/>
-      <c r="H51" s="38" t="inlineStr">
+      <c r="G52" s="40" t="n"/>
+      <c r="H52" s="40" t="inlineStr">
         <is>
           <t>진행 중</t>
         </is>
       </c>
-      <c r="I51" s="39" t="n">
+      <c r="I52" s="41" t="n">
         <v>0.3</v>
       </c>
-      <c r="J51" s="8" t="inlineStr">
+      <c r="J52" s="8" t="inlineStr">
         <is>
           <t>PR #30 평가 계획·통계 도구</t>
         </is>
       </c>
-      <c r="K51" s="8" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="38" t="inlineStr">
+      <c r="K52" s="8" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="40" t="inlineStr">
         <is>
           <t>7.2</t>
         </is>
       </c>
-      <c r="B52" s="38" t="inlineStr">
+      <c r="B53" s="40" t="inlineStr">
         <is>
           <t>마무리</t>
         </is>
       </c>
-      <c r="C52" s="8" t="inlineStr">
+      <c r="C53" s="8" t="inlineStr">
         <is>
           <t>최종 발표 자료</t>
         </is>
       </c>
-      <c r="D52" s="8" t="n"/>
-      <c r="E52" s="38" t="inlineStr">
+      <c r="D53" s="8" t="n"/>
+      <c r="E53" s="40" t="inlineStr">
         <is>
           <t>공동</t>
         </is>
       </c>
-      <c r="F52" s="38" t="inlineStr">
+      <c r="F53" s="40" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="G52" s="38" t="n"/>
-      <c r="H52" s="38" t="inlineStr">
+      <c r="G53" s="40" t="n"/>
+      <c r="H53" s="40" t="inlineStr">
         <is>
           <t>진행 중</t>
         </is>
       </c>
-      <c r="I52" s="39" t="n">
+      <c r="I53" s="41" t="n">
         <v>0.3</v>
       </c>
-      <c r="J52" s="8" t="inlineStr">
+      <c r="J53" s="8" t="inlineStr">
         <is>
           <t>PR #30 시연 순서</t>
         </is>
       </c>
-      <c r="K52" s="8" t="n"/>
+      <c r="K53" s="8" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:K52"/>
-  <conditionalFormatting sqref="H5:H52">
+  <autoFilter ref="A4:K53"/>
+  <conditionalFormatting sqref="H5:H53">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"완료"</formula>
     </cfRule>
@@ -2868,7 +2921,7 @@
       <formula>"보류"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I5:I52">
+  <conditionalFormatting sqref="I5:I53">
     <cfRule type="dataBar" priority="4">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -2878,10 +2931,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="H5:H52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"완료,진행 중,예정,보류"</formula1>
     </dataValidation>
-    <dataValidation sqref="E5:E52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"개발,디자인,공동"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2952,23 +3005,23 @@
         </is>
       </c>
       <c r="B4" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$52,A4,WBS!$H$5:$H$52,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$53,A4,WBS!$H$5:$H$53,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C4" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$52,A4,WBS!$H$5:$H$52,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$53,A4,WBS!$H$5:$H$53,"완료")</f>
         <v/>
       </c>
       <c r="D4" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$52,A4,WBS!$H$5:$H$52,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$53,A4,WBS!$H$5:$H$53,"진행 중")</f>
         <v/>
       </c>
       <c r="E4" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$52,A4,WBS!$H$5:$H$52,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$53,A4,WBS!$H$5:$H$53,"예정")</f>
         <v/>
       </c>
       <c r="F4" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$52,WBS!$B$5:$B$52,A4,WBS!$H$5:$H$52,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$53,WBS!$B$5:$B$53,A4,WBS!$H$5:$H$53,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -2979,23 +3032,23 @@
         </is>
       </c>
       <c r="B5" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$52,A5,WBS!$H$5:$H$52,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$53,A5,WBS!$H$5:$H$53,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C5" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$52,A5,WBS!$H$5:$H$52,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$53,A5,WBS!$H$5:$H$53,"완료")</f>
         <v/>
       </c>
       <c r="D5" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$52,A5,WBS!$H$5:$H$52,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$53,A5,WBS!$H$5:$H$53,"진행 중")</f>
         <v/>
       </c>
       <c r="E5" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$52,A5,WBS!$H$5:$H$52,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$53,A5,WBS!$H$5:$H$53,"예정")</f>
         <v/>
       </c>
       <c r="F5" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$52,WBS!$B$5:$B$52,A5,WBS!$H$5:$H$52,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$53,WBS!$B$5:$B$53,A5,WBS!$H$5:$H$53,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -3006,23 +3059,23 @@
         </is>
       </c>
       <c r="B6" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$52,A6,WBS!$H$5:$H$52,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$53,A6,WBS!$H$5:$H$53,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C6" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$52,A6,WBS!$H$5:$H$52,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$53,A6,WBS!$H$5:$H$53,"완료")</f>
         <v/>
       </c>
       <c r="D6" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$52,A6,WBS!$H$5:$H$52,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$53,A6,WBS!$H$5:$H$53,"진행 중")</f>
         <v/>
       </c>
       <c r="E6" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$52,A6,WBS!$H$5:$H$52,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$53,A6,WBS!$H$5:$H$53,"예정")</f>
         <v/>
       </c>
       <c r="F6" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$52,WBS!$B$5:$B$52,A6,WBS!$H$5:$H$52,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$53,WBS!$B$5:$B$53,A6,WBS!$H$5:$H$53,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -3033,23 +3086,23 @@
         </is>
       </c>
       <c r="B7" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$52,A7,WBS!$H$5:$H$52,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$53,A7,WBS!$H$5:$H$53,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C7" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$52,A7,WBS!$H$5:$H$52,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$53,A7,WBS!$H$5:$H$53,"완료")</f>
         <v/>
       </c>
       <c r="D7" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$52,A7,WBS!$H$5:$H$52,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$53,A7,WBS!$H$5:$H$53,"진행 중")</f>
         <v/>
       </c>
       <c r="E7" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$52,A7,WBS!$H$5:$H$52,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$53,A7,WBS!$H$5:$H$53,"예정")</f>
         <v/>
       </c>
       <c r="F7" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$52,WBS!$B$5:$B$52,A7,WBS!$H$5:$H$52,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$53,WBS!$B$5:$B$53,A7,WBS!$H$5:$H$53,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -3060,23 +3113,23 @@
         </is>
       </c>
       <c r="B8" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$52,A8,WBS!$H$5:$H$52,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$53,A8,WBS!$H$5:$H$53,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C8" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$52,A8,WBS!$H$5:$H$52,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$53,A8,WBS!$H$5:$H$53,"완료")</f>
         <v/>
       </c>
       <c r="D8" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$52,A8,WBS!$H$5:$H$52,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$53,A8,WBS!$H$5:$H$53,"진행 중")</f>
         <v/>
       </c>
       <c r="E8" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$52,A8,WBS!$H$5:$H$52,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$53,A8,WBS!$H$5:$H$53,"예정")</f>
         <v/>
       </c>
       <c r="F8" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$52,WBS!$B$5:$B$52,A8,WBS!$H$5:$H$52,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$53,WBS!$B$5:$B$53,A8,WBS!$H$5:$H$53,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -3087,23 +3140,23 @@
         </is>
       </c>
       <c r="B9" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$52,A9,WBS!$H$5:$H$52,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$53,A9,WBS!$H$5:$H$53,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C9" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$52,A9,WBS!$H$5:$H$52,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$53,A9,WBS!$H$5:$H$53,"완료")</f>
         <v/>
       </c>
       <c r="D9" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$52,A9,WBS!$H$5:$H$52,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$53,A9,WBS!$H$5:$H$53,"진행 중")</f>
         <v/>
       </c>
       <c r="E9" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$52,A9,WBS!$H$5:$H$52,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$53,A9,WBS!$H$5:$H$53,"예정")</f>
         <v/>
       </c>
       <c r="F9" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$52,WBS!$B$5:$B$52,A9,WBS!$H$5:$H$52,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$53,WBS!$B$5:$B$53,A9,WBS!$H$5:$H$53,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -3114,23 +3167,23 @@
         </is>
       </c>
       <c r="B10" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$52,A10,WBS!$H$5:$H$52,"&lt;&gt;")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$53,A10,WBS!$H$5:$H$53,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C10" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$52,A10,WBS!$H$5:$H$52,"완료")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$53,A10,WBS!$H$5:$H$53,"완료")</f>
         <v/>
       </c>
       <c r="D10" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$52,A10,WBS!$H$5:$H$52,"진행 중")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$53,A10,WBS!$H$5:$H$53,"진행 중")</f>
         <v/>
       </c>
       <c r="E10" s="11">
-        <f>COUNTIFS(WBS!$B$5:$B$52,A10,WBS!$H$5:$H$52,"예정")</f>
+        <f>COUNTIFS(WBS!$B$5:$B$53,A10,WBS!$H$5:$H$53,"예정")</f>
         <v/>
       </c>
       <c r="F10" s="12">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$52,WBS!$B$5:$B$52,A10,WBS!$H$5:$H$52,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$53,WBS!$B$5:$B$53,A10,WBS!$H$5:$H$53,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
@@ -3157,7 +3210,7 @@
         <v/>
       </c>
       <c r="F11" s="14">
-        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$52,WBS!$H$5:$H$52,"&lt;&gt;"),0)</f>
+        <f>IFERROR(AVERAGEIFS(WBS!$I$5:$I$53,WBS!$H$5:$H$53,"&lt;&gt;"),0)</f>
         <v/>
       </c>
     </row>
